--- a/Översikt PITEÅ.xlsx
+++ b/Översikt PITEÅ.xlsx
@@ -569,7 +569,7 @@
         <v>44617</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -665,7 +665,7 @@
         <v>44839</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
         <v>44839</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>44459</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
         <v>44617</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>43896</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>45191</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>45203</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>44740</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>44280</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>44539</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>44550</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>45119</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>44014</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>44522</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>44526</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         <v>44553</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>44810</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>44917</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>45103</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>45106</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         <v>43802</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>43902</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2727,7 +2727,7 @@
         <v>43908</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         <v>44053</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2908,7 +2908,7 @@
         <v>44193</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>44298</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>44840</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
         <v>44852</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3262,7 +3262,7 @@
         <v>44859</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>44944</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3434,7 +3434,7 @@
         <v>45120</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
         <v>45187</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         <v>45209</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3701,7 +3701,7 @@
         <v>45219</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>45243</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         <v>45293</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
         <v>45296</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>43714</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         <v>44014</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4225,7 +4225,7 @@
         <v>44106</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4310,7 +4310,7 @@
         <v>44309</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>44342</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4485,7 +4485,7 @@
         <v>44495</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
         <v>44525</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4665,7 +4665,7 @@
         <v>44525</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4755,7 +4755,7 @@
         <v>44538</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4840,7 +4840,7 @@
         <v>44727</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4929,7 +4929,7 @@
         <v>44804</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5014,7 +5014,7 @@
         <v>44917</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5104,7 +5104,7 @@
         <v>45049</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5193,7 +5193,7 @@
         <v>45098</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>45103</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5373,7 +5373,7 @@
         <v>45148</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
         <v>45175</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         <v>45181</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5642,7 +5642,7 @@
         <v>45188</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5732,7 +5732,7 @@
         <v>45224</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5817,7 +5817,7 @@
         <v>45243</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5907,7 +5907,7 @@
         <v>45265</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5992,7 +5992,7 @@
         <v>45323</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
         <v>43325</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6139,7 +6139,7 @@
         <v>43332</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6196,7 +6196,7 @@
         <v>43336</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6253,7 +6253,7 @@
         <v>43339</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         <v>43339</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
         <v>43341</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6424,7 +6424,7 @@
         <v>43355</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>43355</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         <v>43374</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6600,7 +6600,7 @@
         <v>43374</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6662,7 +6662,7 @@
         <v>43375</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6719,7 +6719,7 @@
         <v>43376</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
         <v>43376</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6833,7 +6833,7 @@
         <v>43381</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6890,7 +6890,7 @@
         <v>43383</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6947,7 +6947,7 @@
         <v>43391</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>43391</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7061,7 +7061,7 @@
         <v>43392</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7118,7 +7118,7 @@
         <v>43392</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7175,7 +7175,7 @@
         <v>43398</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7232,7 +7232,7 @@
         <v>43402</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7289,7 +7289,7 @@
         <v>43404</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7346,7 +7346,7 @@
         <v>43406</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7403,7 +7403,7 @@
         <v>43406</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
         <v>43406</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>43406</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>43406</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>43416</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>43418</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7745,7 +7745,7 @@
         <v>43418</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7802,7 +7802,7 @@
         <v>43418</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         <v>43419</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7916,7 +7916,7 @@
         <v>43420</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         <v>43424</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8035,7 +8035,7 @@
         <v>43427</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8097,7 +8097,7 @@
         <v>43427</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8154,7 +8154,7 @@
         <v>43427</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8216,7 +8216,7 @@
         <v>43427</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8278,7 +8278,7 @@
         <v>43436</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
         <v>43438</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8392,7 +8392,7 @@
         <v>43438</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8449,7 +8449,7 @@
         <v>43438</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8506,7 +8506,7 @@
         <v>43438</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8563,7 +8563,7 @@
         <v>43451</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8625,7 +8625,7 @@
         <v>43472</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8682,7 +8682,7 @@
         <v>43475</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8739,7 +8739,7 @@
         <v>43479</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8796,7 +8796,7 @@
         <v>43479</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8853,7 +8853,7 @@
         <v>43486</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
         <v>43489</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8967,7 +8967,7 @@
         <v>43489</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9024,7 +9024,7 @@
         <v>43489</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9081,7 +9081,7 @@
         <v>43489</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9138,7 +9138,7 @@
         <v>43489</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9195,7 +9195,7 @@
         <v>43490</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9252,7 +9252,7 @@
         <v>43490</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9309,7 +9309,7 @@
         <v>43493</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9371,7 +9371,7 @@
         <v>43509</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9428,7 +9428,7 @@
         <v>43510</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9485,7 +9485,7 @@
         <v>43510</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9542,7 +9542,7 @@
         <v>43514</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9599,7 +9599,7 @@
         <v>43514</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9656,7 +9656,7 @@
         <v>43514</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9713,7 +9713,7 @@
         <v>43516</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9775,7 +9775,7 @@
         <v>43518</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9832,7 +9832,7 @@
         <v>43521</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9894,7 +9894,7 @@
         <v>43521</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9956,7 +9956,7 @@
         <v>43521</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10018,7 +10018,7 @@
         <v>43521</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10080,7 +10080,7 @@
         <v>43521</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10142,7 +10142,7 @@
         <v>43522</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10199,7 +10199,7 @@
         <v>43523</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10256,7 +10256,7 @@
         <v>43523</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10313,7 +10313,7 @@
         <v>43523</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10370,7 +10370,7 @@
         <v>43532</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10427,7 +10427,7 @@
         <v>43532</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10484,7 +10484,7 @@
         <v>43542</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10541,7 +10541,7 @@
         <v>43544</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10603,7 +10603,7 @@
         <v>43544</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10665,7 +10665,7 @@
         <v>43554</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10722,7 +10722,7 @@
         <v>43556</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10779,7 +10779,7 @@
         <v>43557</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10841,7 +10841,7 @@
         <v>43557</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10898,7 +10898,7 @@
         <v>43557</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10955,7 +10955,7 @@
         <v>43557</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11012,7 +11012,7 @@
         <v>43557</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11074,7 +11074,7 @@
         <v>43564</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11131,7 +11131,7 @@
         <v>43564</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11188,7 +11188,7 @@
         <v>43567</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11245,7 +11245,7 @@
         <v>43570</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11302,7 +11302,7 @@
         <v>43570</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11359,7 +11359,7 @@
         <v>43570</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11416,7 +11416,7 @@
         <v>43584</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11473,7 +11473,7 @@
         <v>43605</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11530,7 +11530,7 @@
         <v>43608</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11587,7 +11587,7 @@
         <v>43614</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11649,7 +11649,7 @@
         <v>43616</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11711,7 +11711,7 @@
         <v>43616</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11773,7 +11773,7 @@
         <v>43629</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11830,7 +11830,7 @@
         <v>43629</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11892,7 +11892,7 @@
         <v>43633</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11949,7 +11949,7 @@
         <v>43633</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12006,7 +12006,7 @@
         <v>43640</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12063,7 +12063,7 @@
         <v>43640</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12120,7 +12120,7 @@
         <v>43647</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12177,7 +12177,7 @@
         <v>43647</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12234,7 +12234,7 @@
         <v>43650</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12291,7 +12291,7 @@
         <v>43652</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12353,7 +12353,7 @@
         <v>43677</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12410,7 +12410,7 @@
         <v>43678</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12467,7 +12467,7 @@
         <v>43682</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12524,7 +12524,7 @@
         <v>43691</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12586,7 +12586,7 @@
         <v>43691</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12648,7 +12648,7 @@
         <v>43696</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12710,7 +12710,7 @@
         <v>43697</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12767,7 +12767,7 @@
         <v>43698</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12829,7 +12829,7 @@
         <v>43698</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12891,7 +12891,7 @@
         <v>43706</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12948,7 +12948,7 @@
         <v>43707</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13010,7 +13010,7 @@
         <v>43711</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13067,7 +13067,7 @@
         <v>43713</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13124,7 +13124,7 @@
         <v>43718</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13181,7 +13181,7 @@
         <v>43718</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13238,7 +13238,7 @@
         <v>43718</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13300,7 +13300,7 @@
         <v>43720</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13357,7 +13357,7 @@
         <v>43721</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13414,7 +13414,7 @@
         <v>43732</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13471,7 +13471,7 @@
         <v>43741</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13533,7 +13533,7 @@
         <v>43741</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13590,7 +13590,7 @@
         <v>43752</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13652,7 +13652,7 @@
         <v>43755</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13709,7 +13709,7 @@
         <v>43755</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13766,7 +13766,7 @@
         <v>43755</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13823,7 +13823,7 @@
         <v>43755</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13880,7 +13880,7 @@
         <v>43760</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13942,7 +13942,7 @@
         <v>43760</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14004,7 +14004,7 @@
         <v>43760</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14061,7 +14061,7 @@
         <v>43762</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14123,7 +14123,7 @@
         <v>43766</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14180,7 +14180,7 @@
         <v>43766</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14237,7 +14237,7 @@
         <v>43768</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14294,7 +14294,7 @@
         <v>43770</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14356,7 +14356,7 @@
         <v>43775</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14418,7 +14418,7 @@
         <v>43775</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14480,7 +14480,7 @@
         <v>43777</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14537,7 +14537,7 @@
         <v>43780</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14594,7 +14594,7 @@
         <v>43780</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14651,7 +14651,7 @@
         <v>43780</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14708,7 +14708,7 @@
         <v>43782</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14770,7 +14770,7 @@
         <v>43789</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14832,7 +14832,7 @@
         <v>43798</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14889,7 +14889,7 @@
         <v>43801</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14951,7 +14951,7 @@
         <v>43802</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15008,7 +15008,7 @@
         <v>43802</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15065,7 +15065,7 @@
         <v>43802</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15122,7 +15122,7 @@
         <v>43802</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15179,7 +15179,7 @@
         <v>43802</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15236,7 +15236,7 @@
         <v>43802</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15293,7 +15293,7 @@
         <v>43807</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15350,7 +15350,7 @@
         <v>43809</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15407,7 +15407,7 @@
         <v>43817</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15464,7 +15464,7 @@
         <v>43817</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15526,7 +15526,7 @@
         <v>43822</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15583,7 +15583,7 @@
         <v>43822</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15640,7 +15640,7 @@
         <v>43833</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15697,7 +15697,7 @@
         <v>43846</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15754,7 +15754,7 @@
         <v>43852</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15811,7 +15811,7 @@
         <v>43853</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15868,7 +15868,7 @@
         <v>43854</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15925,7 +15925,7 @@
         <v>43859</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15987,7 +15987,7 @@
         <v>43859</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16044,7 +16044,7 @@
         <v>43859</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16101,7 +16101,7 @@
         <v>43859</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16158,7 +16158,7 @@
         <v>43859</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16215,7 +16215,7 @@
         <v>43860</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16272,7 +16272,7 @@
         <v>43868</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16329,7 +16329,7 @@
         <v>43868</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16386,7 +16386,7 @@
         <v>43874</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16448,7 +16448,7 @@
         <v>43878</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16505,7 +16505,7 @@
         <v>43880</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16562,7 +16562,7 @@
         <v>43880</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16619,7 +16619,7 @@
         <v>43889</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16676,7 +16676,7 @@
         <v>43895</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16738,7 +16738,7 @@
         <v>43896</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16795,7 +16795,7 @@
         <v>43902</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16852,7 +16852,7 @@
         <v>43902</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16914,7 +16914,7 @@
         <v>43907</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16971,7 +16971,7 @@
         <v>43913</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17028,7 +17028,7 @@
         <v>43914</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17090,7 +17090,7 @@
         <v>43927</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17152,7 +17152,7 @@
         <v>43929</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         <v>43929</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>43931</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17328,7 +17328,7 @@
         <v>43950</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17385,7 +17385,7 @@
         <v>43957</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17447,7 +17447,7 @@
         <v>43958</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17504,7 +17504,7 @@
         <v>43958</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17561,7 +17561,7 @@
         <v>43959</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17618,7 +17618,7 @@
         <v>43962</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17675,7 +17675,7 @@
         <v>43962</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17732,7 +17732,7 @@
         <v>43962</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17789,7 +17789,7 @@
         <v>43962</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17846,7 +17846,7 @@
         <v>43970</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17908,7 +17908,7 @@
         <v>43971</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17970,7 +17970,7 @@
         <v>43976</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18027,7 +18027,7 @@
         <v>43979</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18084,7 +18084,7 @@
         <v>43979</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18141,7 +18141,7 @@
         <v>43979</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18198,7 +18198,7 @@
         <v>43984</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18260,7 +18260,7 @@
         <v>43984</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18317,7 +18317,7 @@
         <v>43987</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18374,7 +18374,7 @@
         <v>43990</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18431,7 +18431,7 @@
         <v>43994</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18493,7 +18493,7 @@
         <v>43997</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18550,7 +18550,7 @@
         <v>43999</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18607,7 +18607,7 @@
         <v>44000</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18669,7 +18669,7 @@
         <v>44006</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18726,7 +18726,7 @@
         <v>44006</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18783,7 +18783,7 @@
         <v>44007</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18840,7 +18840,7 @@
         <v>44007</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18897,7 +18897,7 @@
         <v>44011</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18954,7 +18954,7 @@
         <v>44012</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19016,7 +19016,7 @@
         <v>44020</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19078,7 +19078,7 @@
         <v>44020</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19135,7 +19135,7 @@
         <v>44020</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19197,7 +19197,7 @@
         <v>44026</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19259,7 +19259,7 @@
         <v>44035</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19316,7 +19316,7 @@
         <v>44049</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19373,7 +19373,7 @@
         <v>44063</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19435,7 +19435,7 @@
         <v>44067</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19497,7 +19497,7 @@
         <v>44067</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19559,7 +19559,7 @@
         <v>44068</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19621,7 +19621,7 @@
         <v>44069</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19678,7 +19678,7 @@
         <v>44070</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19735,7 +19735,7 @@
         <v>44074</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19792,7 +19792,7 @@
         <v>44075</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19849,7 +19849,7 @@
         <v>44078</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19906,7 +19906,7 @@
         <v>44083</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19963,7 +19963,7 @@
         <v>44083</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20020,7 +20020,7 @@
         <v>44087</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20077,7 +20077,7 @@
         <v>44088</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20139,7 +20139,7 @@
         <v>44088</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20196,7 +20196,7 @@
         <v>44088</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20258,7 +20258,7 @@
         <v>44092</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20315,7 +20315,7 @@
         <v>44092</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20372,7 +20372,7 @@
         <v>44092</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20429,7 +20429,7 @@
         <v>44095</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20486,7 +20486,7 @@
         <v>44099</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20543,7 +20543,7 @@
         <v>44099</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20600,7 +20600,7 @@
         <v>44099</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20657,7 +20657,7 @@
         <v>44099</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20714,7 +20714,7 @@
         <v>44103</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20771,7 +20771,7 @@
         <v>44103</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20828,7 +20828,7 @@
         <v>44106</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20885,7 +20885,7 @@
         <v>44111</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20947,7 +20947,7 @@
         <v>44111</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21009,7 +21009,7 @@
         <v>44123</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21066,7 +21066,7 @@
         <v>44127</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21123,7 +21123,7 @@
         <v>44132</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21180,7 +21180,7 @@
         <v>44139</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21237,7 +21237,7 @@
         <v>44141</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21294,7 +21294,7 @@
         <v>44141</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21351,7 +21351,7 @@
         <v>44155</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21408,7 +21408,7 @@
         <v>44162</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21470,7 +21470,7 @@
         <v>44166</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21532,7 +21532,7 @@
         <v>44172</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21589,7 +21589,7 @@
         <v>44180</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21646,7 +21646,7 @@
         <v>44186</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21703,7 +21703,7 @@
         <v>44209</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21760,7 +21760,7 @@
         <v>44211</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21817,7 +21817,7 @@
         <v>44211</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21874,7 +21874,7 @@
         <v>44211</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21931,7 +21931,7 @@
         <v>44215</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21993,7 +21993,7 @@
         <v>44221</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22055,7 +22055,7 @@
         <v>44237</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22117,7 +22117,7 @@
         <v>44238</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22174,7 +22174,7 @@
         <v>44256</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22231,7 +22231,7 @@
         <v>44257</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22288,7 +22288,7 @@
         <v>44258</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22345,7 +22345,7 @@
         <v>44280</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22407,7 +22407,7 @@
         <v>44281</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22464,7 +22464,7 @@
         <v>44281</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22521,7 +22521,7 @@
         <v>44281</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22578,7 +22578,7 @@
         <v>44285</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22640,7 +22640,7 @@
         <v>44286</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22697,7 +22697,7 @@
         <v>44292</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22754,7 +22754,7 @@
         <v>44294</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22816,7 +22816,7 @@
         <v>44309</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22873,7 +22873,7 @@
         <v>44320</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22930,7 +22930,7 @@
         <v>44321</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22987,7 +22987,7 @@
         <v>44321</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23044,7 +23044,7 @@
         <v>44326</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23101,7 +23101,7 @@
         <v>44326</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23163,7 +23163,7 @@
         <v>44334</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23220,7 +23220,7 @@
         <v>44339</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23277,7 +23277,7 @@
         <v>44339</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23334,7 +23334,7 @@
         <v>44339</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23391,7 +23391,7 @@
         <v>44343</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23453,7 +23453,7 @@
         <v>44342</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23515,7 +23515,7 @@
         <v>44344</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23572,7 +23572,7 @@
         <v>44350</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23629,7 +23629,7 @@
         <v>44350</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23686,7 +23686,7 @@
         <v>44351</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23748,7 +23748,7 @@
         <v>44354</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23810,7 +23810,7 @@
         <v>44355</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23872,7 +23872,7 @@
         <v>44355</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23934,7 +23934,7 @@
         <v>44357</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23991,7 +23991,7 @@
         <v>44358</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24053,7 +24053,7 @@
         <v>44361</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24110,7 +24110,7 @@
         <v>44361</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24167,7 +24167,7 @@
         <v>44361</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24224,7 +24224,7 @@
         <v>44362</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24286,7 +24286,7 @@
         <v>44361</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24348,7 +24348,7 @@
         <v>44362</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24405,7 +24405,7 @@
         <v>44368</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24467,7 +24467,7 @@
         <v>44368</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24529,7 +24529,7 @@
         <v>44368</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24591,7 +24591,7 @@
         <v>44369</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24653,7 +24653,7 @@
         <v>44370</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24715,7 +24715,7 @@
         <v>44370</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24777,7 +24777,7 @@
         <v>44370</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24839,7 +24839,7 @@
         <v>44370</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24901,7 +24901,7 @@
         <v>44371</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24963,7 +24963,7 @@
         <v>44372</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25025,7 +25025,7 @@
         <v>44372</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25087,7 +25087,7 @@
         <v>44375</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25149,7 +25149,7 @@
         <v>44376</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25211,7 +25211,7 @@
         <v>44376</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25273,7 +25273,7 @@
         <v>44376</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25330,7 +25330,7 @@
         <v>44377</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25392,7 +25392,7 @@
         <v>44378</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25449,7 +25449,7 @@
         <v>44378</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25511,7 +25511,7 @@
         <v>44378</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25568,7 +25568,7 @@
         <v>44383</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25625,7 +25625,7 @@
         <v>44383</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25682,7 +25682,7 @@
         <v>44383</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25739,7 +25739,7 @@
         <v>44383</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25796,7 +25796,7 @@
         <v>44383</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25853,7 +25853,7 @@
         <v>44384</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25915,7 +25915,7 @@
         <v>44383</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25972,7 +25972,7 @@
         <v>44386</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26029,7 +26029,7 @@
         <v>44398</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26086,7 +26086,7 @@
         <v>44404</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26143,7 +26143,7 @@
         <v>44405</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26205,7 +26205,7 @@
         <v>44418</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26267,7 +26267,7 @@
         <v>44421</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26329,7 +26329,7 @@
         <v>44428</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26386,7 +26386,7 @@
         <v>44432</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26443,7 +26443,7 @@
         <v>44432</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26500,7 +26500,7 @@
         <v>44433</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26562,7 +26562,7 @@
         <v>44433</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26624,7 +26624,7 @@
         <v>44438</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26686,7 +26686,7 @@
         <v>44439</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26748,7 +26748,7 @@
         <v>44440</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26805,7 +26805,7 @@
         <v>44441</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26867,7 +26867,7 @@
         <v>44440</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26929,7 +26929,7 @@
         <v>44446</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26986,7 +26986,7 @@
         <v>44447</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27048,7 +27048,7 @@
         <v>44453</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27105,7 +27105,7 @@
         <v>44454</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27162,7 +27162,7 @@
         <v>44454</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27219,7 +27219,7 @@
         <v>44459</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27276,7 +27276,7 @@
         <v>44463</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27338,7 +27338,7 @@
         <v>44463</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27400,7 +27400,7 @@
         <v>44463</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27457,7 +27457,7 @@
         <v>44468</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27514,7 +27514,7 @@
         <v>44468</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27571,7 +27571,7 @@
         <v>44476</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27628,7 +27628,7 @@
         <v>44480</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27685,7 +27685,7 @@
         <v>44481</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27742,7 +27742,7 @@
         <v>44484</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27799,7 +27799,7 @@
         <v>44487</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27861,7 +27861,7 @@
         <v>44490</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27918,7 +27918,7 @@
         <v>44489</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27980,7 +27980,7 @@
         <v>44496</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28037,7 +28037,7 @@
         <v>44497</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28099,7 +28099,7 @@
         <v>44497</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28156,7 +28156,7 @@
         <v>44497</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28213,7 +28213,7 @@
         <v>44498</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28270,7 +28270,7 @@
         <v>44498</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28327,7 +28327,7 @@
         <v>44499</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28384,7 +28384,7 @@
         <v>44502</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28441,7 +28441,7 @@
         <v>44516</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28498,7 +28498,7 @@
         <v>44522</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28555,7 +28555,7 @@
         <v>44523</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28612,7 +28612,7 @@
         <v>44525</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28674,7 +28674,7 @@
         <v>44525</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28731,7 +28731,7 @@
         <v>44529</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28788,7 +28788,7 @@
         <v>44530</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28850,7 +28850,7 @@
         <v>44530</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28912,7 +28912,7 @@
         <v>44531</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28969,7 +28969,7 @@
         <v>44531</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29026,7 +29026,7 @@
         <v>44536</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29083,7 +29083,7 @@
         <v>44536</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29140,7 +29140,7 @@
         <v>44538</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29197,7 +29197,7 @@
         <v>44538</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29254,7 +29254,7 @@
         <v>44538</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29311,7 +29311,7 @@
         <v>44538</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29368,7 +29368,7 @@
         <v>44538</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29425,7 +29425,7 @@
         <v>44538</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29482,7 +29482,7 @@
         <v>44538</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29539,7 +29539,7 @@
         <v>44538</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29596,7 +29596,7 @@
         <v>44539</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29658,7 +29658,7 @@
         <v>44543</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29720,7 +29720,7 @@
         <v>44543</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29782,7 +29782,7 @@
         <v>44543</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29844,7 +29844,7 @@
         <v>44543</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29906,7 +29906,7 @@
         <v>44547</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29968,7 +29968,7 @@
         <v>44550</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30025,7 +30025,7 @@
         <v>44550</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30082,7 +30082,7 @@
         <v>44571</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30139,7 +30139,7 @@
         <v>44582</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30196,7 +30196,7 @@
         <v>44582</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30253,7 +30253,7 @@
         <v>44582</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30310,7 +30310,7 @@
         <v>44582</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30367,7 +30367,7 @@
         <v>44588</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30424,7 +30424,7 @@
         <v>44589</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30481,7 +30481,7 @@
         <v>44590</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30538,7 +30538,7 @@
         <v>44590</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30595,7 +30595,7 @@
         <v>44592</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30652,7 +30652,7 @@
         <v>44592</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30709,7 +30709,7 @@
         <v>44596</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30766,7 +30766,7 @@
         <v>44599</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30823,7 +30823,7 @@
         <v>44608</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30880,7 +30880,7 @@
         <v>44615</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30937,7 +30937,7 @@
         <v>44616</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30999,7 +30999,7 @@
         <v>44617</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31061,7 +31061,7 @@
         <v>44621</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31118,7 +31118,7 @@
         <v>44621</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31180,7 +31180,7 @@
         <v>44622</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31237,7 +31237,7 @@
         <v>44623</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31294,7 +31294,7 @@
         <v>44642</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31351,7 +31351,7 @@
         <v>44643</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31408,7 +31408,7 @@
         <v>44643</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31470,7 +31470,7 @@
         <v>44644</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31527,7 +31527,7 @@
         <v>44656</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31584,7 +31584,7 @@
         <v>44658</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31641,7 +31641,7 @@
         <v>44683</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31698,7 +31698,7 @@
         <v>44683</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31755,7 +31755,7 @@
         <v>44685</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31812,7 +31812,7 @@
         <v>44685</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31869,7 +31869,7 @@
         <v>44685</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31926,7 +31926,7 @@
         <v>44687</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31983,7 +31983,7 @@
         <v>44700</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32040,7 +32040,7 @@
         <v>44708</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32097,7 +32097,7 @@
         <v>44708</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32154,7 +32154,7 @@
         <v>44708</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32211,7 +32211,7 @@
         <v>44722</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32268,7 +32268,7 @@
         <v>44727</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32330,7 +32330,7 @@
         <v>44729</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32392,7 +32392,7 @@
         <v>44735</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32449,7 +32449,7 @@
         <v>44735</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32506,7 +32506,7 @@
         <v>44741</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32563,7 +32563,7 @@
         <v>44741</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32620,7 +32620,7 @@
         <v>44741</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32677,7 +32677,7 @@
         <v>44743</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32739,7 +32739,7 @@
         <v>44743</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32796,7 +32796,7 @@
         <v>44748</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32858,7 +32858,7 @@
         <v>44747</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32920,7 +32920,7 @@
         <v>44748</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32982,7 +32982,7 @@
         <v>44748</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33039,7 +33039,7 @@
         <v>44750</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33096,7 +33096,7 @@
         <v>44756</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33153,7 +33153,7 @@
         <v>44761</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33210,7 +33210,7 @@
         <v>44776</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33267,7 +33267,7 @@
         <v>44777</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33329,7 +33329,7 @@
         <v>44781</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33386,7 +33386,7 @@
         <v>44783</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33443,7 +33443,7 @@
         <v>44785</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33505,7 +33505,7 @@
         <v>44784</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33567,7 +33567,7 @@
         <v>44785</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33624,7 +33624,7 @@
         <v>44792</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33681,7 +33681,7 @@
         <v>44792</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33743,7 +33743,7 @@
         <v>44795</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33800,7 +33800,7 @@
         <v>44795</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33862,7 +33862,7 @@
         <v>44803</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33924,7 +33924,7 @@
         <v>44805</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33986,7 +33986,7 @@
         <v>44806</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34043,7 +34043,7 @@
         <v>44809</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34105,7 +34105,7 @@
         <v>44809</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34167,7 +34167,7 @@
         <v>44811</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34224,7 +34224,7 @@
         <v>44813</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34281,7 +34281,7 @@
         <v>44813</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34338,7 +34338,7 @@
         <v>44813</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34395,7 +34395,7 @@
         <v>44813</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34452,7 +34452,7 @@
         <v>44813</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34509,7 +34509,7 @@
         <v>44816</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34566,7 +34566,7 @@
         <v>44816</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34623,7 +34623,7 @@
         <v>44817</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34685,7 +34685,7 @@
         <v>44817</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34742,7 +34742,7 @@
         <v>44818</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34804,7 +34804,7 @@
         <v>44818</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34866,7 +34866,7 @@
         <v>44818</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34928,7 +34928,7 @@
         <v>44817</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34985,7 +34985,7 @@
         <v>44818</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35047,7 +35047,7 @@
         <v>44818</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35109,7 +35109,7 @@
         <v>44818</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35171,7 +35171,7 @@
         <v>44818</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35228,7 +35228,7 @@
         <v>44819</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35285,7 +35285,7 @@
         <v>44820</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35342,7 +35342,7 @@
         <v>44823</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35404,7 +35404,7 @@
         <v>44824</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35461,7 +35461,7 @@
         <v>44827</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35523,7 +35523,7 @@
         <v>44838</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35585,7 +35585,7 @@
         <v>44838</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35642,7 +35642,7 @@
         <v>44839</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35699,7 +35699,7 @@
         <v>44840</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35756,7 +35756,7 @@
         <v>44840</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35813,7 +35813,7 @@
         <v>44841</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35875,7 +35875,7 @@
         <v>44845</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35937,7 +35937,7 @@
         <v>44845</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35999,7 +35999,7 @@
         <v>44848</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36061,7 +36061,7 @@
         <v>44848</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36123,7 +36123,7 @@
         <v>44849</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36185,7 +36185,7 @@
         <v>44848</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36242,7 +36242,7 @@
         <v>44853</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36304,7 +36304,7 @@
         <v>44853</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36366,7 +36366,7 @@
         <v>44853</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36428,7 +36428,7 @@
         <v>44856</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36490,7 +36490,7 @@
         <v>44855</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36552,7 +36552,7 @@
         <v>44857</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36609,7 +36609,7 @@
         <v>44859</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36666,7 +36666,7 @@
         <v>44859</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36723,7 +36723,7 @@
         <v>44861</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36785,7 +36785,7 @@
         <v>44861</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36842,7 +36842,7 @@
         <v>44861</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36904,7 +36904,7 @@
         <v>44861</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36961,7 +36961,7 @@
         <v>44861</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37023,7 +37023,7 @@
         <v>44861</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37085,7 +37085,7 @@
         <v>44861</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37142,7 +37142,7 @@
         <v>44862</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37204,7 +37204,7 @@
         <v>44866</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37266,7 +37266,7 @@
         <v>44867</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37328,7 +37328,7 @@
         <v>44867</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37390,7 +37390,7 @@
         <v>44867</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37447,7 +37447,7 @@
         <v>44868</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37504,7 +37504,7 @@
         <v>44873</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37566,7 +37566,7 @@
         <v>44874</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37623,7 +37623,7 @@
         <v>44874</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37685,7 +37685,7 @@
         <v>44875</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37742,7 +37742,7 @@
         <v>44879</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37799,7 +37799,7 @@
         <v>44879</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37856,7 +37856,7 @@
         <v>44879</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37913,7 +37913,7 @@
         <v>44879</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37970,7 +37970,7 @@
         <v>44883</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38032,7 +38032,7 @@
         <v>44886</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38089,7 +38089,7 @@
         <v>44888</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38146,7 +38146,7 @@
         <v>44888</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38203,7 +38203,7 @@
         <v>44889</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38265,7 +38265,7 @@
         <v>44889</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38327,7 +38327,7 @@
         <v>44890</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38384,7 +38384,7 @@
         <v>44890</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38441,7 +38441,7 @@
         <v>44890</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38503,7 +38503,7 @@
         <v>44893</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38565,7 +38565,7 @@
         <v>44895</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38627,7 +38627,7 @@
         <v>44897</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38684,7 +38684,7 @@
         <v>44901</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38741,7 +38741,7 @@
         <v>44904</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38798,7 +38798,7 @@
         <v>44907</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38855,7 +38855,7 @@
         <v>44907</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38912,7 +38912,7 @@
         <v>44909</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38974,7 +38974,7 @@
         <v>44910</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39031,7 +39031,7 @@
         <v>44910</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39088,7 +39088,7 @@
         <v>44911</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39150,7 +39150,7 @@
         <v>44911</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39212,7 +39212,7 @@
         <v>44911</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39269,7 +39269,7 @@
         <v>44916</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39326,7 +39326,7 @@
         <v>44917</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39388,7 +39388,7 @@
         <v>44929</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39445,7 +39445,7 @@
         <v>44929</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39502,7 +39502,7 @@
         <v>44941</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39559,7 +39559,7 @@
         <v>44942</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39616,7 +39616,7 @@
         <v>44942</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39673,7 +39673,7 @@
         <v>44942</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39730,7 +39730,7 @@
         <v>44942</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39787,7 +39787,7 @@
         <v>44944</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39844,7 +39844,7 @@
         <v>44950</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39901,7 +39901,7 @@
         <v>44951</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39958,7 +39958,7 @@
         <v>44960</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40015,7 +40015,7 @@
         <v>44963</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40072,7 +40072,7 @@
         <v>44965</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40129,7 +40129,7 @@
         <v>44965</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40186,7 +40186,7 @@
         <v>44966</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40243,7 +40243,7 @@
         <v>44966</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40300,7 +40300,7 @@
         <v>44971</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40362,7 +40362,7 @@
         <v>44971</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40419,7 +40419,7 @@
         <v>44972</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40476,7 +40476,7 @@
         <v>44973</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40533,7 +40533,7 @@
         <v>44973</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40590,7 +40590,7 @@
         <v>44973</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40647,7 +40647,7 @@
         <v>44977</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40704,7 +40704,7 @@
         <v>44981</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40761,7 +40761,7 @@
         <v>44984</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40818,7 +40818,7 @@
         <v>44985</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40875,7 +40875,7 @@
         <v>44985</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40932,7 +40932,7 @@
         <v>44985</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40989,7 +40989,7 @@
         <v>44991</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41046,7 +41046,7 @@
         <v>44991</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41103,7 +41103,7 @@
         <v>45006</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41160,7 +41160,7 @@
         <v>45006</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41217,7 +41217,7 @@
         <v>45013</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41274,7 +41274,7 @@
         <v>45015</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41336,7 +41336,7 @@
         <v>45015</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41398,7 +41398,7 @@
         <v>45015</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41455,7 +41455,7 @@
         <v>45021</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41512,7 +41512,7 @@
         <v>45021</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41569,7 +41569,7 @@
         <v>45028</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41626,7 +41626,7 @@
         <v>45029</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41683,7 +41683,7 @@
         <v>45030</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41740,7 +41740,7 @@
         <v>45036</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41797,7 +41797,7 @@
         <v>45036</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41854,7 +41854,7 @@
         <v>45036</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41911,7 +41911,7 @@
         <v>45035</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41973,7 +41973,7 @@
         <v>45036</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42030,7 +42030,7 @@
         <v>45035</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42087,7 +42087,7 @@
         <v>45043</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42144,7 +42144,7 @@
         <v>45043</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42201,7 +42201,7 @@
         <v>45043</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42258,7 +42258,7 @@
         <v>45044</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42320,7 +42320,7 @@
         <v>45048</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42377,7 +42377,7 @@
         <v>45050</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42434,7 +42434,7 @@
         <v>45055</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42491,7 +42491,7 @@
         <v>45057</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42548,7 +42548,7 @@
         <v>45056</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42605,7 +42605,7 @@
         <v>45062</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42667,7 +42667,7 @@
         <v>45062</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42729,7 +42729,7 @@
         <v>45064</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42791,7 +42791,7 @@
         <v>45066</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42853,7 +42853,7 @@
         <v>45068</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42915,7 +42915,7 @@
         <v>45070</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42977,7 +42977,7 @@
         <v>45072</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -43039,7 +43039,7 @@
         <v>45072</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43101,7 +43101,7 @@
         <v>45076</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43158,7 +43158,7 @@
         <v>45076</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43215,7 +43215,7 @@
         <v>45077</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43272,7 +43272,7 @@
         <v>45079</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43334,7 +43334,7 @@
         <v>45079</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43396,7 +43396,7 @@
         <v>45086</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43458,7 +43458,7 @@
         <v>45085</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43520,7 +43520,7 @@
         <v>45086</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43577,7 +43577,7 @@
         <v>45086</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43634,7 +43634,7 @@
         <v>45086</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43691,7 +43691,7 @@
         <v>45086</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43748,7 +43748,7 @@
         <v>45086</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43805,7 +43805,7 @@
         <v>45086</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43862,7 +43862,7 @@
         <v>45090</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43924,7 +43924,7 @@
         <v>45089</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43981,7 +43981,7 @@
         <v>45090</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -44038,7 +44038,7 @@
         <v>45090</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44095,7 +44095,7 @@
         <v>45090</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44152,7 +44152,7 @@
         <v>45090</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44209,7 +44209,7 @@
         <v>45090</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44266,7 +44266,7 @@
         <v>45091</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44323,7 +44323,7 @@
         <v>45091</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44380,7 +44380,7 @@
         <v>45091</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44437,7 +44437,7 @@
         <v>45091</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44494,7 +44494,7 @@
         <v>45093</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44556,7 +44556,7 @@
         <v>45094</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44618,7 +44618,7 @@
         <v>45096</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44675,7 +44675,7 @@
         <v>45096</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44732,7 +44732,7 @@
         <v>45096</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44794,7 +44794,7 @@
         <v>45098</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44851,7 +44851,7 @@
         <v>45098</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44913,7 +44913,7 @@
         <v>45098</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44975,7 +44975,7 @@
         <v>45098</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -45037,7 +45037,7 @@
         <v>45098</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -45094,7 +45094,7 @@
         <v>45098</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45151,7 +45151,7 @@
         <v>45098</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45213,7 +45213,7 @@
         <v>45098</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45275,7 +45275,7 @@
         <v>45098</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45332,7 +45332,7 @@
         <v>45098</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45394,7 +45394,7 @@
         <v>45098</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45451,7 +45451,7 @@
         <v>45098</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45508,7 +45508,7 @@
         <v>45098</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45565,7 +45565,7 @@
         <v>45098</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45622,7 +45622,7 @@
         <v>45099</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45684,7 +45684,7 @@
         <v>45100</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45746,7 +45746,7 @@
         <v>45100</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45808,7 +45808,7 @@
         <v>45100</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45870,7 +45870,7 @@
         <v>45100</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45927,7 +45927,7 @@
         <v>45103</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45989,7 +45989,7 @@
         <v>45104</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -46046,7 +46046,7 @@
         <v>45104</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -46103,7 +46103,7 @@
         <v>45104</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46160,7 +46160,7 @@
         <v>45104</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46217,7 +46217,7 @@
         <v>45104</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46274,7 +46274,7 @@
         <v>45106</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46331,7 +46331,7 @@
         <v>45106</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46388,7 +46388,7 @@
         <v>45106</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46445,7 +46445,7 @@
         <v>45106</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46502,7 +46502,7 @@
         <v>45106</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46559,7 +46559,7 @@
         <v>45106</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46616,7 +46616,7 @@
         <v>45107</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46673,7 +46673,7 @@
         <v>45107</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46730,7 +46730,7 @@
         <v>45107</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46787,7 +46787,7 @@
         <v>45107</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46844,7 +46844,7 @@
         <v>45110</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46901,7 +46901,7 @@
         <v>45110</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46958,7 +46958,7 @@
         <v>45110</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -47015,7 +47015,7 @@
         <v>45110</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -47072,7 +47072,7 @@
         <v>45111</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47129,7 +47129,7 @@
         <v>45114</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47186,7 +47186,7 @@
         <v>45114</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47243,7 +47243,7 @@
         <v>45118</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47305,7 +47305,7 @@
         <v>45118</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47367,7 +47367,7 @@
         <v>45118</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47429,7 +47429,7 @@
         <v>45118</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47491,7 +47491,7 @@
         <v>45118</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47553,7 +47553,7 @@
         <v>45118</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47615,7 +47615,7 @@
         <v>45119</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47677,7 +47677,7 @@
         <v>45119</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47734,7 +47734,7 @@
         <v>45120</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47791,7 +47791,7 @@
         <v>45120</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47848,7 +47848,7 @@
         <v>45120</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47905,7 +47905,7 @@
         <v>45120</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47962,7 +47962,7 @@
         <v>45125</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -48019,7 +48019,7 @@
         <v>45125</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -48076,7 +48076,7 @@
         <v>45125</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -48133,7 +48133,7 @@
         <v>45129</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48190,7 +48190,7 @@
         <v>45129</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48247,7 +48247,7 @@
         <v>45135</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48304,7 +48304,7 @@
         <v>45135</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48361,7 +48361,7 @@
         <v>45138</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48418,7 +48418,7 @@
         <v>45138</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48475,7 +48475,7 @@
         <v>45139</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48532,7 +48532,7 @@
         <v>45139</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48589,7 +48589,7 @@
         <v>45139</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48646,7 +48646,7 @@
         <v>45140</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48708,7 +48708,7 @@
         <v>45140</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48765,7 +48765,7 @@
         <v>45140</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48827,7 +48827,7 @@
         <v>45141</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48884,7 +48884,7 @@
         <v>45145</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48941,7 +48941,7 @@
         <v>45152</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -49003,7 +49003,7 @@
         <v>45152</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -49065,7 +49065,7 @@
         <v>45156</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -49122,7 +49122,7 @@
         <v>45159</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49179,7 +49179,7 @@
         <v>45159</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49236,7 +49236,7 @@
         <v>45160</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49298,7 +49298,7 @@
         <v>45160</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49360,7 +49360,7 @@
         <v>45160</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49417,7 +49417,7 @@
         <v>45162</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49474,7 +49474,7 @@
         <v>45162</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49531,7 +49531,7 @@
         <v>45163</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49588,7 +49588,7 @@
         <v>45167</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49650,7 +49650,7 @@
         <v>45167</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49712,7 +49712,7 @@
         <v>45167</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49769,7 +49769,7 @@
         <v>45167</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49831,7 +49831,7 @@
         <v>45168</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49893,7 +49893,7 @@
         <v>45167</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49950,7 +49950,7 @@
         <v>45168</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -50012,7 +50012,7 @@
         <v>45168</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -50074,7 +50074,7 @@
         <v>45170</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -50131,7 +50131,7 @@
         <v>45170</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -50188,7 +50188,7 @@
         <v>45175</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -50245,7 +50245,7 @@
         <v>45176</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50307,7 +50307,7 @@
         <v>45176</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50369,7 +50369,7 @@
         <v>45176</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50426,7 +50426,7 @@
         <v>45177</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50483,7 +50483,7 @@
         <v>45177</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50540,7 +50540,7 @@
         <v>45177</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50597,7 +50597,7 @@
         <v>45180</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50654,7 +50654,7 @@
         <v>45181</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50716,7 +50716,7 @@
         <v>45181</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50778,7 +50778,7 @@
         <v>45181</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50835,7 +50835,7 @@
         <v>45181</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50892,7 +50892,7 @@
         <v>45182</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50949,7 +50949,7 @@
         <v>45183</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -51006,7 +51006,7 @@
         <v>45184</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -51068,7 +51068,7 @@
         <v>45187</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -51125,7 +51125,7 @@
         <v>45187</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -51182,7 +51182,7 @@
         <v>45187</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -51239,7 +51239,7 @@
         <v>45187</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -51296,7 +51296,7 @@
         <v>45187</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -51353,7 +51353,7 @@
         <v>45187</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -51410,7 +51410,7 @@
         <v>45187</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -51467,7 +51467,7 @@
         <v>45188</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51529,7 +51529,7 @@
         <v>45188</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51591,7 +51591,7 @@
         <v>45188</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51653,7 +51653,7 @@
         <v>45188</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51715,7 +51715,7 @@
         <v>45188</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51777,7 +51777,7 @@
         <v>45188</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51839,7 +51839,7 @@
         <v>45188</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51901,7 +51901,7 @@
         <v>45188</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51958,7 +51958,7 @@
         <v>45189</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -52020,7 +52020,7 @@
         <v>45190</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -52077,7 +52077,7 @@
         <v>45190</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -52134,7 +52134,7 @@
         <v>45190</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -52191,7 +52191,7 @@
         <v>45190</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -52248,7 +52248,7 @@
         <v>45196</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -52305,7 +52305,7 @@
         <v>45197</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -52362,7 +52362,7 @@
         <v>45197</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -52419,7 +52419,7 @@
         <v>45198</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -52481,7 +52481,7 @@
         <v>45201</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -52543,7 +52543,7 @@
         <v>45201</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52605,7 +52605,7 @@
         <v>45202</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52667,7 +52667,7 @@
         <v>45202</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52724,7 +52724,7 @@
         <v>45203</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52781,7 +52781,7 @@
         <v>45204</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52843,7 +52843,7 @@
         <v>45208</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52900,7 +52900,7 @@
         <v>45209</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52957,7 +52957,7 @@
         <v>45208</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -53019,7 +53019,7 @@
         <v>45211</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -53076,7 +53076,7 @@
         <v>45211</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -53133,7 +53133,7 @@
         <v>45211</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -53190,7 +53190,7 @@
         <v>45211</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -53252,7 +53252,7 @@
         <v>45211</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -53314,7 +53314,7 @@
         <v>45211</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -53371,7 +53371,7 @@
         <v>45212</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -53428,7 +53428,7 @@
         <v>45213</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -53485,7 +53485,7 @@
         <v>45215</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -53542,7 +53542,7 @@
         <v>45215</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53599,7 +53599,7 @@
         <v>45216</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53656,7 +53656,7 @@
         <v>45216</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53718,7 +53718,7 @@
         <v>45218</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -53775,7 +53775,7 @@
         <v>45218</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -53837,7 +53837,7 @@
         <v>45218</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -53894,7 +53894,7 @@
         <v>45218</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -53951,7 +53951,7 @@
         <v>45219</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -54008,7 +54008,7 @@
         <v>45219</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -54065,7 +54065,7 @@
         <v>45219</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -54127,7 +54127,7 @@
         <v>45219</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -54189,7 +54189,7 @@
         <v>45219</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -54246,7 +54246,7 @@
         <v>45219</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -54303,7 +54303,7 @@
         <v>45222</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -54360,7 +54360,7 @@
         <v>45222</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -54422,7 +54422,7 @@
         <v>45222</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -54479,7 +54479,7 @@
         <v>45225</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -54536,7 +54536,7 @@
         <v>45225</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -54593,7 +54593,7 @@
         <v>45230</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -54655,7 +54655,7 @@
         <v>45230</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -54712,7 +54712,7 @@
         <v>45230</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -54769,7 +54769,7 @@
         <v>45230</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -54826,7 +54826,7 @@
         <v>45232</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -54888,7 +54888,7 @@
         <v>45232</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -54950,7 +54950,7 @@
         <v>45232</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -55012,7 +55012,7 @@
         <v>45236</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -55074,7 +55074,7 @@
         <v>45236</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -55131,7 +55131,7 @@
         <v>45237</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -55188,7 +55188,7 @@
         <v>45237</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -55245,7 +55245,7 @@
         <v>45237</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -55302,7 +55302,7 @@
         <v>45237</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -55359,7 +55359,7 @@
         <v>45237</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -55421,7 +55421,7 @@
         <v>45237</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -55478,7 +55478,7 @@
         <v>45237</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -55535,7 +55535,7 @@
         <v>45238</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -55592,7 +55592,7 @@
         <v>45239</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -55649,7 +55649,7 @@
         <v>45239</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -55711,7 +55711,7 @@
         <v>45239</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -55768,7 +55768,7 @@
         <v>45239</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -55825,7 +55825,7 @@
         <v>45240</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -55882,7 +55882,7 @@
         <v>45240</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -55939,7 +55939,7 @@
         <v>45243</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -56001,7 +56001,7 @@
         <v>45243</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -56063,7 +56063,7 @@
         <v>45244</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -56120,7 +56120,7 @@
         <v>45244</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -56177,7 +56177,7 @@
         <v>45244</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -56234,7 +56234,7 @@
         <v>45244</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -56291,7 +56291,7 @@
         <v>45244</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -56348,7 +56348,7 @@
         <v>45244</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -56405,7 +56405,7 @@
         <v>45244</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -56462,7 +56462,7 @@
         <v>45244</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -56519,7 +56519,7 @@
         <v>45244</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -56576,7 +56576,7 @@
         <v>45245</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -56633,7 +56633,7 @@
         <v>45245</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -56690,7 +56690,7 @@
         <v>45245</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -56747,7 +56747,7 @@
         <v>45246</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -56804,7 +56804,7 @@
         <v>45246</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -56861,7 +56861,7 @@
         <v>45247</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -56918,7 +56918,7 @@
         <v>45251</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -56975,7 +56975,7 @@
         <v>45252</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -57032,7 +57032,7 @@
         <v>45252</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -57089,7 +57089,7 @@
         <v>45253</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -57146,7 +57146,7 @@
         <v>45254</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -57203,7 +57203,7 @@
         <v>45254</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -57260,7 +57260,7 @@
         <v>45257</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -57317,7 +57317,7 @@
         <v>45257</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -57374,7 +57374,7 @@
         <v>45258</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -57431,7 +57431,7 @@
         <v>45259</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -57488,7 +57488,7 @@
         <v>45259</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -57545,7 +57545,7 @@
         <v>45260</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -57602,7 +57602,7 @@
         <v>45260</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -57659,7 +57659,7 @@
         <v>45260</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -57716,7 +57716,7 @@
         <v>45260</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -57773,7 +57773,7 @@
         <v>45261</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -57830,7 +57830,7 @@
         <v>45261</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -57887,7 +57887,7 @@
         <v>45262</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -57944,7 +57944,7 @@
         <v>45264</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -58001,7 +58001,7 @@
         <v>45264</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -58058,7 +58058,7 @@
         <v>45264</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -58115,7 +58115,7 @@
         <v>45264</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -58177,7 +58177,7 @@
         <v>45264</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -58234,7 +58234,7 @@
         <v>45265</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -58291,7 +58291,7 @@
         <v>45265</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -58348,7 +58348,7 @@
         <v>45266</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -58405,7 +58405,7 @@
         <v>45266</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -58462,7 +58462,7 @@
         <v>45266</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -58519,7 +58519,7 @@
         <v>45267</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -58576,7 +58576,7 @@
         <v>45271</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -58633,7 +58633,7 @@
         <v>45271</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -58690,7 +58690,7 @@
         <v>45273</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -58747,7 +58747,7 @@
         <v>45273</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -58804,7 +58804,7 @@
         <v>45273</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -58861,7 +58861,7 @@
         <v>45273</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -58918,7 +58918,7 @@
         <v>45273</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -58975,7 +58975,7 @@
         <v>45273</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -59032,7 +59032,7 @@
         <v>45273</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -59089,7 +59089,7 @@
         <v>45278</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -59146,7 +59146,7 @@
         <v>45279</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -59203,7 +59203,7 @@
         <v>45279</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -59260,7 +59260,7 @@
         <v>45279</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -59317,7 +59317,7 @@
         <v>45281</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -59374,7 +59374,7 @@
         <v>45282</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -59436,7 +59436,7 @@
         <v>45285</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -59493,7 +59493,7 @@
         <v>45285</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -59550,7 +59550,7 @@
         <v>45285</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -59607,7 +59607,7 @@
         <v>45285</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -59664,7 +59664,7 @@
         <v>45287</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -59721,7 +59721,7 @@
         <v>45287</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -59778,7 +59778,7 @@
         <v>45289</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -59835,7 +59835,7 @@
         <v>45299</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -59885,14 +59885,14 @@
     <row r="983" ht="15" customHeight="1">
       <c r="A983" t="inlineStr">
         <is>
-          <t>A 1911-2024</t>
+          <t>A 1908-2024</t>
         </is>
       </c>
       <c r="B983" s="1" t="n">
         <v>45308</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -59905,7 +59905,7 @@
         </is>
       </c>
       <c r="G983" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="H983" t="n">
         <v>0</v>
@@ -59942,14 +59942,14 @@
     <row r="984" ht="15" customHeight="1">
       <c r="A984" t="inlineStr">
         <is>
-          <t>A 1908-2024</t>
+          <t>A 1911-2024</t>
         </is>
       </c>
       <c r="B984" s="1" t="n">
         <v>45308</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -59962,7 +59962,7 @@
         </is>
       </c>
       <c r="G984" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="H984" t="n">
         <v>0</v>
@@ -60006,7 +60006,7 @@
         <v>45309</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -60063,7 +60063,7 @@
         <v>45310</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -60120,7 +60120,7 @@
         <v>45310</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -60177,7 +60177,7 @@
         <v>45311</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -60234,7 +60234,7 @@
         <v>45311</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -60291,7 +60291,7 @@
         <v>45312</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -60348,7 +60348,7 @@
         <v>45312</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -60405,7 +60405,7 @@
         <v>45313</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -60462,7 +60462,7 @@
         <v>45315</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -60519,7 +60519,7 @@
         <v>45315</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -60576,7 +60576,7 @@
         <v>45315</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -60626,14 +60626,14 @@
     <row r="996" ht="15" customHeight="1">
       <c r="A996" t="inlineStr">
         <is>
-          <t>A 3220-2024</t>
+          <t>A 3218-2024</t>
         </is>
       </c>
       <c r="B996" s="1" t="n">
         <v>45316</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -60646,7 +60646,7 @@
         </is>
       </c>
       <c r="G996" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
       <c r="H996" t="n">
         <v>0</v>
@@ -60683,14 +60683,14 @@
     <row r="997" ht="15" customHeight="1">
       <c r="A997" t="inlineStr">
         <is>
-          <t>A 3218-2024</t>
+          <t>A 3215-2024</t>
         </is>
       </c>
       <c r="B997" s="1" t="n">
         <v>45316</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -60703,7 +60703,7 @@
         </is>
       </c>
       <c r="G997" t="n">
-        <v>2.1</v>
+        <v>4.1</v>
       </c>
       <c r="H997" t="n">
         <v>0</v>
@@ -60740,14 +60740,14 @@
     <row r="998" ht="15" customHeight="1">
       <c r="A998" t="inlineStr">
         <is>
-          <t>A 3215-2024</t>
+          <t>A 3220-2024</t>
         </is>
       </c>
       <c r="B998" s="1" t="n">
         <v>45316</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -60760,7 +60760,7 @@
         </is>
       </c>
       <c r="G998" t="n">
-        <v>4.1</v>
+        <v>0.4</v>
       </c>
       <c r="H998" t="n">
         <v>0</v>
@@ -60804,7 +60804,7 @@
         <v>45320</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -60861,7 +60861,7 @@
         <v>45320</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -60918,7 +60918,7 @@
         <v>45323</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -60975,7 +60975,7 @@
         <v>45323</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -61037,7 +61037,7 @@
         <v>45323</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -61099,7 +61099,7 @@
         <v>45323</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -61156,7 +61156,7 @@
         <v>45323</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -61218,7 +61218,7 @@
         <v>45324</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -61280,7 +61280,7 @@
         <v>45324</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -61337,7 +61337,7 @@
         <v>45324</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -61399,7 +61399,7 @@
         <v>45329</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -61456,7 +61456,7 @@
         <v>45330</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -61513,7 +61513,7 @@
         <v>45334</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -61570,7 +61570,7 @@
         <v>45335</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>

--- a/Översikt PITEÅ.xlsx
+++ b/Översikt PITEÅ.xlsx
@@ -569,7 +569,7 @@
         <v>44617</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -665,7 +665,7 @@
         <v>44839</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
         <v>44839</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>44459</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
         <v>44617</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>43896</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>45191</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>45203</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>44740</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>44280</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>44539</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>44550</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>45119</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>44014</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>44522</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>44526</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         <v>44553</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>44810</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>44917</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>45103</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>45106</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         <v>43802</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>43902</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2727,7 +2727,7 @@
         <v>43908</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         <v>44053</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2908,7 +2908,7 @@
         <v>44193</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>44298</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>44840</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
         <v>44852</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3262,7 +3262,7 @@
         <v>44859</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>44944</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3434,7 +3434,7 @@
         <v>45120</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
         <v>45187</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         <v>45209</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3701,7 +3701,7 @@
         <v>45219</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>45243</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         <v>45293</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
         <v>45296</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>43714</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         <v>44014</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4225,7 +4225,7 @@
         <v>44106</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4310,7 +4310,7 @@
         <v>44309</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>44342</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4485,7 +4485,7 @@
         <v>44495</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
         <v>44525</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4665,7 +4665,7 @@
         <v>44525</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4755,7 +4755,7 @@
         <v>44538</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4840,7 +4840,7 @@
         <v>44727</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4929,7 +4929,7 @@
         <v>44804</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5014,7 +5014,7 @@
         <v>44917</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5104,7 +5104,7 @@
         <v>45049</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5193,7 +5193,7 @@
         <v>45098</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>45103</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5373,7 +5373,7 @@
         <v>45148</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
         <v>45175</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         <v>45181</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5642,7 +5642,7 @@
         <v>45188</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5732,7 +5732,7 @@
         <v>45224</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5817,7 +5817,7 @@
         <v>45243</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5907,7 +5907,7 @@
         <v>45265</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5992,7 +5992,7 @@
         <v>45323</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
         <v>43325</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6139,7 +6139,7 @@
         <v>43332</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6196,7 +6196,7 @@
         <v>43336</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6253,7 +6253,7 @@
         <v>43339</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         <v>43339</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
         <v>43341</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6424,7 +6424,7 @@
         <v>43355</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>43355</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         <v>43374</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6600,7 +6600,7 @@
         <v>43374</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6662,7 +6662,7 @@
         <v>43375</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6719,7 +6719,7 @@
         <v>43376</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
         <v>43376</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6833,7 +6833,7 @@
         <v>43381</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6890,7 +6890,7 @@
         <v>43383</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6947,7 +6947,7 @@
         <v>43391</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>43391</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7061,7 +7061,7 @@
         <v>43392</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7118,7 +7118,7 @@
         <v>43392</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7175,7 +7175,7 @@
         <v>43398</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7232,7 +7232,7 @@
         <v>43402</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7289,7 +7289,7 @@
         <v>43404</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7346,7 +7346,7 @@
         <v>43406</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7403,7 +7403,7 @@
         <v>43406</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
         <v>43406</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>43406</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>43406</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>43416</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>43418</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7745,7 +7745,7 @@
         <v>43418</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7802,7 +7802,7 @@
         <v>43418</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         <v>43419</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7916,7 +7916,7 @@
         <v>43420</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         <v>43424</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8035,7 +8035,7 @@
         <v>43427</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8097,7 +8097,7 @@
         <v>43427</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8154,7 +8154,7 @@
         <v>43427</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8216,7 +8216,7 @@
         <v>43427</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8278,7 +8278,7 @@
         <v>43436</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
         <v>43438</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8392,7 +8392,7 @@
         <v>43438</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8449,7 +8449,7 @@
         <v>43438</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8506,7 +8506,7 @@
         <v>43438</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8563,7 +8563,7 @@
         <v>43451</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8625,7 +8625,7 @@
         <v>43472</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8682,7 +8682,7 @@
         <v>43475</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8739,7 +8739,7 @@
         <v>43479</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8796,7 +8796,7 @@
         <v>43479</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8853,7 +8853,7 @@
         <v>43486</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
         <v>43489</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8967,7 +8967,7 @@
         <v>43489</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9024,7 +9024,7 @@
         <v>43489</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9081,7 +9081,7 @@
         <v>43489</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9138,7 +9138,7 @@
         <v>43489</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9195,7 +9195,7 @@
         <v>43490</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9252,7 +9252,7 @@
         <v>43490</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9309,7 +9309,7 @@
         <v>43493</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9371,7 +9371,7 @@
         <v>43509</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9428,7 +9428,7 @@
         <v>43510</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9485,7 +9485,7 @@
         <v>43510</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9542,7 +9542,7 @@
         <v>43514</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9599,7 +9599,7 @@
         <v>43514</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9656,7 +9656,7 @@
         <v>43514</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9713,7 +9713,7 @@
         <v>43516</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9775,7 +9775,7 @@
         <v>43518</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9832,7 +9832,7 @@
         <v>43521</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9894,7 +9894,7 @@
         <v>43521</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9956,7 +9956,7 @@
         <v>43521</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10018,7 +10018,7 @@
         <v>43521</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10080,7 +10080,7 @@
         <v>43521</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10142,7 +10142,7 @@
         <v>43522</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10199,7 +10199,7 @@
         <v>43523</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10256,7 +10256,7 @@
         <v>43523</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10313,7 +10313,7 @@
         <v>43523</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10370,7 +10370,7 @@
         <v>43532</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10427,7 +10427,7 @@
         <v>43532</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10484,7 +10484,7 @@
         <v>43542</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10541,7 +10541,7 @@
         <v>43544</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10603,7 +10603,7 @@
         <v>43544</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10665,7 +10665,7 @@
         <v>43554</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10722,7 +10722,7 @@
         <v>43556</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10779,7 +10779,7 @@
         <v>43557</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10841,7 +10841,7 @@
         <v>43557</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10898,7 +10898,7 @@
         <v>43557</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10955,7 +10955,7 @@
         <v>43557</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11012,7 +11012,7 @@
         <v>43557</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11074,7 +11074,7 @@
         <v>43564</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11131,7 +11131,7 @@
         <v>43564</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11188,7 +11188,7 @@
         <v>43567</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11245,7 +11245,7 @@
         <v>43570</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11302,7 +11302,7 @@
         <v>43570</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11359,7 +11359,7 @@
         <v>43570</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11416,7 +11416,7 @@
         <v>43584</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11473,7 +11473,7 @@
         <v>43605</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11530,7 +11530,7 @@
         <v>43608</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11587,7 +11587,7 @@
         <v>43614</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11649,7 +11649,7 @@
         <v>43616</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11711,7 +11711,7 @@
         <v>43616</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11773,7 +11773,7 @@
         <v>43629</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11830,7 +11830,7 @@
         <v>43629</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11892,7 +11892,7 @@
         <v>43633</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11949,7 +11949,7 @@
         <v>43633</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12006,7 +12006,7 @@
         <v>43640</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12063,7 +12063,7 @@
         <v>43640</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12120,7 +12120,7 @@
         <v>43647</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12177,7 +12177,7 @@
         <v>43647</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12234,7 +12234,7 @@
         <v>43650</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12291,7 +12291,7 @@
         <v>43652</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12353,7 +12353,7 @@
         <v>43677</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12410,7 +12410,7 @@
         <v>43678</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12467,7 +12467,7 @@
         <v>43682</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12524,7 +12524,7 @@
         <v>43691</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12586,7 +12586,7 @@
         <v>43691</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12648,7 +12648,7 @@
         <v>43696</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12710,7 +12710,7 @@
         <v>43697</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12767,7 +12767,7 @@
         <v>43698</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12829,7 +12829,7 @@
         <v>43698</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12891,7 +12891,7 @@
         <v>43706</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12948,7 +12948,7 @@
         <v>43707</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13010,7 +13010,7 @@
         <v>43711</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13067,7 +13067,7 @@
         <v>43713</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13124,7 +13124,7 @@
         <v>43718</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13181,7 +13181,7 @@
         <v>43718</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13238,7 +13238,7 @@
         <v>43718</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13300,7 +13300,7 @@
         <v>43720</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13357,7 +13357,7 @@
         <v>43721</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13414,7 +13414,7 @@
         <v>43732</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13471,7 +13471,7 @@
         <v>43741</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13533,7 +13533,7 @@
         <v>43741</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13590,7 +13590,7 @@
         <v>43752</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13652,7 +13652,7 @@
         <v>43755</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13709,7 +13709,7 @@
         <v>43755</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13766,7 +13766,7 @@
         <v>43755</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13823,7 +13823,7 @@
         <v>43755</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13880,7 +13880,7 @@
         <v>43760</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13942,7 +13942,7 @@
         <v>43760</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14004,7 +14004,7 @@
         <v>43760</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14061,7 +14061,7 @@
         <v>43762</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14123,7 +14123,7 @@
         <v>43766</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14180,7 +14180,7 @@
         <v>43766</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14237,7 +14237,7 @@
         <v>43768</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14294,7 +14294,7 @@
         <v>43770</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14356,7 +14356,7 @@
         <v>43775</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14418,7 +14418,7 @@
         <v>43775</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14480,7 +14480,7 @@
         <v>43777</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14537,7 +14537,7 @@
         <v>43780</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14594,7 +14594,7 @@
         <v>43780</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14651,7 +14651,7 @@
         <v>43780</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14708,7 +14708,7 @@
         <v>43782</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14770,7 +14770,7 @@
         <v>43789</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14832,7 +14832,7 @@
         <v>43798</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14889,7 +14889,7 @@
         <v>43801</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14951,7 +14951,7 @@
         <v>43802</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15008,7 +15008,7 @@
         <v>43802</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15065,7 +15065,7 @@
         <v>43802</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15122,7 +15122,7 @@
         <v>43802</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15179,7 +15179,7 @@
         <v>43802</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15236,7 +15236,7 @@
         <v>43802</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15293,7 +15293,7 @@
         <v>43807</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15350,7 +15350,7 @@
         <v>43809</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15407,7 +15407,7 @@
         <v>43817</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15464,7 +15464,7 @@
         <v>43817</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15526,7 +15526,7 @@
         <v>43822</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15583,7 +15583,7 @@
         <v>43822</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15640,7 +15640,7 @@
         <v>43833</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15697,7 +15697,7 @@
         <v>43846</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15754,7 +15754,7 @@
         <v>43852</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15811,7 +15811,7 @@
         <v>43853</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15868,7 +15868,7 @@
         <v>43854</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15925,7 +15925,7 @@
         <v>43859</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15987,7 +15987,7 @@
         <v>43859</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16044,7 +16044,7 @@
         <v>43859</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16101,7 +16101,7 @@
         <v>43859</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16158,7 +16158,7 @@
         <v>43859</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16215,7 +16215,7 @@
         <v>43860</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16272,7 +16272,7 @@
         <v>43868</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16329,7 +16329,7 @@
         <v>43868</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16386,7 +16386,7 @@
         <v>43874</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16448,7 +16448,7 @@
         <v>43878</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16505,7 +16505,7 @@
         <v>43880</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16562,7 +16562,7 @@
         <v>43880</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16619,7 +16619,7 @@
         <v>43889</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16676,7 +16676,7 @@
         <v>43895</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16738,7 +16738,7 @@
         <v>43896</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16795,7 +16795,7 @@
         <v>43902</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16852,7 +16852,7 @@
         <v>43902</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16914,7 +16914,7 @@
         <v>43907</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16971,7 +16971,7 @@
         <v>43913</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17028,7 +17028,7 @@
         <v>43914</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17090,7 +17090,7 @@
         <v>43927</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17152,7 +17152,7 @@
         <v>43929</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         <v>43929</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>43931</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17328,7 +17328,7 @@
         <v>43950</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17385,7 +17385,7 @@
         <v>43957</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17447,7 +17447,7 @@
         <v>43958</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17504,7 +17504,7 @@
         <v>43958</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17561,7 +17561,7 @@
         <v>43959</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17618,7 +17618,7 @@
         <v>43962</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17675,7 +17675,7 @@
         <v>43962</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17732,7 +17732,7 @@
         <v>43962</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17789,7 +17789,7 @@
         <v>43962</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17846,7 +17846,7 @@
         <v>43970</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17908,7 +17908,7 @@
         <v>43971</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17970,7 +17970,7 @@
         <v>43976</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18027,7 +18027,7 @@
         <v>43979</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18084,7 +18084,7 @@
         <v>43979</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18141,7 +18141,7 @@
         <v>43979</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18198,7 +18198,7 @@
         <v>43984</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18260,7 +18260,7 @@
         <v>43984</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18317,7 +18317,7 @@
         <v>43987</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18374,7 +18374,7 @@
         <v>43990</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18431,7 +18431,7 @@
         <v>43994</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18493,7 +18493,7 @@
         <v>43997</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18550,7 +18550,7 @@
         <v>43999</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18607,7 +18607,7 @@
         <v>44000</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18669,7 +18669,7 @@
         <v>44006</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18726,7 +18726,7 @@
         <v>44006</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18783,7 +18783,7 @@
         <v>44007</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18840,7 +18840,7 @@
         <v>44007</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18897,7 +18897,7 @@
         <v>44011</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18954,7 +18954,7 @@
         <v>44012</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19016,7 +19016,7 @@
         <v>44020</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19078,7 +19078,7 @@
         <v>44020</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19135,7 +19135,7 @@
         <v>44020</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19197,7 +19197,7 @@
         <v>44026</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19259,7 +19259,7 @@
         <v>44035</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19316,7 +19316,7 @@
         <v>44049</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19373,7 +19373,7 @@
         <v>44063</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19435,7 +19435,7 @@
         <v>44067</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19497,7 +19497,7 @@
         <v>44067</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19559,7 +19559,7 @@
         <v>44068</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19621,7 +19621,7 @@
         <v>44069</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19678,7 +19678,7 @@
         <v>44070</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19735,7 +19735,7 @@
         <v>44074</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19792,7 +19792,7 @@
         <v>44075</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19849,7 +19849,7 @@
         <v>44078</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19906,7 +19906,7 @@
         <v>44083</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19963,7 +19963,7 @@
         <v>44083</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20020,7 +20020,7 @@
         <v>44087</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20077,7 +20077,7 @@
         <v>44088</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20139,7 +20139,7 @@
         <v>44088</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20196,7 +20196,7 @@
         <v>44088</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20258,7 +20258,7 @@
         <v>44092</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20315,7 +20315,7 @@
         <v>44092</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20372,7 +20372,7 @@
         <v>44092</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20429,7 +20429,7 @@
         <v>44095</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20486,7 +20486,7 @@
         <v>44099</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20543,7 +20543,7 @@
         <v>44099</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20600,7 +20600,7 @@
         <v>44099</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20657,7 +20657,7 @@
         <v>44099</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20714,7 +20714,7 @@
         <v>44103</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20771,7 +20771,7 @@
         <v>44103</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20828,7 +20828,7 @@
         <v>44106</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20885,7 +20885,7 @@
         <v>44111</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20947,7 +20947,7 @@
         <v>44111</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21009,7 +21009,7 @@
         <v>44123</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21066,7 +21066,7 @@
         <v>44127</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21123,7 +21123,7 @@
         <v>44132</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21180,7 +21180,7 @@
         <v>44139</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21237,7 +21237,7 @@
         <v>44141</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21294,7 +21294,7 @@
         <v>44141</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21351,7 +21351,7 @@
         <v>44155</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21408,7 +21408,7 @@
         <v>44162</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21470,7 +21470,7 @@
         <v>44166</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21532,7 +21532,7 @@
         <v>44172</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21589,7 +21589,7 @@
         <v>44180</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21646,7 +21646,7 @@
         <v>44186</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21703,7 +21703,7 @@
         <v>44209</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21760,7 +21760,7 @@
         <v>44211</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21817,7 +21817,7 @@
         <v>44211</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21874,7 +21874,7 @@
         <v>44211</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21931,7 +21931,7 @@
         <v>44215</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21993,7 +21993,7 @@
         <v>44221</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22055,7 +22055,7 @@
         <v>44237</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22117,7 +22117,7 @@
         <v>44238</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22174,7 +22174,7 @@
         <v>44256</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22231,7 +22231,7 @@
         <v>44257</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22288,7 +22288,7 @@
         <v>44258</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22345,7 +22345,7 @@
         <v>44280</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22407,7 +22407,7 @@
         <v>44281</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22464,7 +22464,7 @@
         <v>44281</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22521,7 +22521,7 @@
         <v>44281</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22578,7 +22578,7 @@
         <v>44285</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22640,7 +22640,7 @@
         <v>44286</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22697,7 +22697,7 @@
         <v>44292</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22754,7 +22754,7 @@
         <v>44294</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22816,7 +22816,7 @@
         <v>44309</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22873,7 +22873,7 @@
         <v>44320</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22930,7 +22930,7 @@
         <v>44321</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22987,7 +22987,7 @@
         <v>44321</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23044,7 +23044,7 @@
         <v>44326</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23101,7 +23101,7 @@
         <v>44326</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23163,7 +23163,7 @@
         <v>44334</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23220,7 +23220,7 @@
         <v>44339</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23277,7 +23277,7 @@
         <v>44339</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23334,7 +23334,7 @@
         <v>44339</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23391,7 +23391,7 @@
         <v>44343</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23453,7 +23453,7 @@
         <v>44342</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23515,7 +23515,7 @@
         <v>44344</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23572,7 +23572,7 @@
         <v>44350</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23629,7 +23629,7 @@
         <v>44350</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23686,7 +23686,7 @@
         <v>44351</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23748,7 +23748,7 @@
         <v>44354</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23810,7 +23810,7 @@
         <v>44355</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23872,7 +23872,7 @@
         <v>44355</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23934,7 +23934,7 @@
         <v>44357</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23991,7 +23991,7 @@
         <v>44358</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24053,7 +24053,7 @@
         <v>44361</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24110,7 +24110,7 @@
         <v>44361</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24167,7 +24167,7 @@
         <v>44361</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24224,7 +24224,7 @@
         <v>44362</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24286,7 +24286,7 @@
         <v>44361</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24348,7 +24348,7 @@
         <v>44362</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24405,7 +24405,7 @@
         <v>44368</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24467,7 +24467,7 @@
         <v>44368</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24529,7 +24529,7 @@
         <v>44368</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24591,7 +24591,7 @@
         <v>44369</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24653,7 +24653,7 @@
         <v>44370</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24715,7 +24715,7 @@
         <v>44370</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24777,7 +24777,7 @@
         <v>44370</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24839,7 +24839,7 @@
         <v>44370</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24901,7 +24901,7 @@
         <v>44371</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24963,7 +24963,7 @@
         <v>44372</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25025,7 +25025,7 @@
         <v>44372</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25087,7 +25087,7 @@
         <v>44375</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25149,7 +25149,7 @@
         <v>44376</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25211,7 +25211,7 @@
         <v>44376</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25273,7 +25273,7 @@
         <v>44376</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25330,7 +25330,7 @@
         <v>44377</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25392,7 +25392,7 @@
         <v>44378</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25449,7 +25449,7 @@
         <v>44378</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25511,7 +25511,7 @@
         <v>44378</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25568,7 +25568,7 @@
         <v>44383</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25625,7 +25625,7 @@
         <v>44383</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25682,7 +25682,7 @@
         <v>44383</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25739,7 +25739,7 @@
         <v>44383</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25796,7 +25796,7 @@
         <v>44383</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25853,7 +25853,7 @@
         <v>44384</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25915,7 +25915,7 @@
         <v>44383</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25972,7 +25972,7 @@
         <v>44386</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26029,7 +26029,7 @@
         <v>44398</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26086,7 +26086,7 @@
         <v>44404</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26143,7 +26143,7 @@
         <v>44405</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26205,7 +26205,7 @@
         <v>44418</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26267,7 +26267,7 @@
         <v>44421</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26329,7 +26329,7 @@
         <v>44428</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26386,7 +26386,7 @@
         <v>44432</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26443,7 +26443,7 @@
         <v>44432</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26500,7 +26500,7 @@
         <v>44433</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26562,7 +26562,7 @@
         <v>44433</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26624,7 +26624,7 @@
         <v>44438</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26686,7 +26686,7 @@
         <v>44439</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26748,7 +26748,7 @@
         <v>44440</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26805,7 +26805,7 @@
         <v>44441</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26867,7 +26867,7 @@
         <v>44440</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26929,7 +26929,7 @@
         <v>44446</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26986,7 +26986,7 @@
         <v>44447</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27048,7 +27048,7 @@
         <v>44453</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27105,7 +27105,7 @@
         <v>44454</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27162,7 +27162,7 @@
         <v>44454</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27219,7 +27219,7 @@
         <v>44459</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27276,7 +27276,7 @@
         <v>44463</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27338,7 +27338,7 @@
         <v>44463</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27400,7 +27400,7 @@
         <v>44463</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27457,7 +27457,7 @@
         <v>44468</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27514,7 +27514,7 @@
         <v>44468</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27571,7 +27571,7 @@
         <v>44476</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27628,7 +27628,7 @@
         <v>44480</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27685,7 +27685,7 @@
         <v>44481</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27742,7 +27742,7 @@
         <v>44484</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27799,7 +27799,7 @@
         <v>44487</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27861,7 +27861,7 @@
         <v>44490</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27918,7 +27918,7 @@
         <v>44489</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27980,7 +27980,7 @@
         <v>44496</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28037,7 +28037,7 @@
         <v>44497</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28099,7 +28099,7 @@
         <v>44497</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28156,7 +28156,7 @@
         <v>44497</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28213,7 +28213,7 @@
         <v>44498</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28270,7 +28270,7 @@
         <v>44498</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28327,7 +28327,7 @@
         <v>44499</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28384,7 +28384,7 @@
         <v>44502</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28441,7 +28441,7 @@
         <v>44516</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28498,7 +28498,7 @@
         <v>44522</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28555,7 +28555,7 @@
         <v>44523</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28612,7 +28612,7 @@
         <v>44525</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28674,7 +28674,7 @@
         <v>44525</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28731,7 +28731,7 @@
         <v>44529</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28788,7 +28788,7 @@
         <v>44530</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28850,7 +28850,7 @@
         <v>44530</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28912,7 +28912,7 @@
         <v>44531</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28969,7 +28969,7 @@
         <v>44531</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29026,7 +29026,7 @@
         <v>44536</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29083,7 +29083,7 @@
         <v>44536</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29140,7 +29140,7 @@
         <v>44538</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29197,7 +29197,7 @@
         <v>44538</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29254,7 +29254,7 @@
         <v>44538</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29311,7 +29311,7 @@
         <v>44538</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29368,7 +29368,7 @@
         <v>44538</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29425,7 +29425,7 @@
         <v>44538</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29482,7 +29482,7 @@
         <v>44538</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29539,7 +29539,7 @@
         <v>44538</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29596,7 +29596,7 @@
         <v>44539</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29658,7 +29658,7 @@
         <v>44543</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29720,7 +29720,7 @@
         <v>44543</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29782,7 +29782,7 @@
         <v>44543</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29844,7 +29844,7 @@
         <v>44543</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29906,7 +29906,7 @@
         <v>44547</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29968,7 +29968,7 @@
         <v>44550</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30025,7 +30025,7 @@
         <v>44550</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30082,7 +30082,7 @@
         <v>44571</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30139,7 +30139,7 @@
         <v>44582</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30196,7 +30196,7 @@
         <v>44582</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30253,7 +30253,7 @@
         <v>44582</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30310,7 +30310,7 @@
         <v>44582</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30367,7 +30367,7 @@
         <v>44588</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30424,7 +30424,7 @@
         <v>44589</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30481,7 +30481,7 @@
         <v>44590</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30538,7 +30538,7 @@
         <v>44590</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30595,7 +30595,7 @@
         <v>44592</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30652,7 +30652,7 @@
         <v>44592</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30709,7 +30709,7 @@
         <v>44596</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30766,7 +30766,7 @@
         <v>44599</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30823,7 +30823,7 @@
         <v>44608</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30880,7 +30880,7 @@
         <v>44615</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30937,7 +30937,7 @@
         <v>44616</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30999,7 +30999,7 @@
         <v>44617</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31061,7 +31061,7 @@
         <v>44621</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31118,7 +31118,7 @@
         <v>44621</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31180,7 +31180,7 @@
         <v>44622</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31237,7 +31237,7 @@
         <v>44623</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31294,7 +31294,7 @@
         <v>44642</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31351,7 +31351,7 @@
         <v>44643</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31408,7 +31408,7 @@
         <v>44643</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31470,7 +31470,7 @@
         <v>44644</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31527,7 +31527,7 @@
         <v>44656</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31584,7 +31584,7 @@
         <v>44658</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31641,7 +31641,7 @@
         <v>44683</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31698,7 +31698,7 @@
         <v>44683</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31755,7 +31755,7 @@
         <v>44685</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31812,7 +31812,7 @@
         <v>44685</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31869,7 +31869,7 @@
         <v>44685</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31926,7 +31926,7 @@
         <v>44687</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31983,7 +31983,7 @@
         <v>44700</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32040,7 +32040,7 @@
         <v>44708</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32097,7 +32097,7 @@
         <v>44708</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32154,7 +32154,7 @@
         <v>44708</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32211,7 +32211,7 @@
         <v>44722</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32268,7 +32268,7 @@
         <v>44727</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32330,7 +32330,7 @@
         <v>44729</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32392,7 +32392,7 @@
         <v>44735</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32449,7 +32449,7 @@
         <v>44735</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32506,7 +32506,7 @@
         <v>44741</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32563,7 +32563,7 @@
         <v>44741</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32620,7 +32620,7 @@
         <v>44741</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32677,7 +32677,7 @@
         <v>44743</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32739,7 +32739,7 @@
         <v>44743</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32796,7 +32796,7 @@
         <v>44748</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32858,7 +32858,7 @@
         <v>44747</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32920,7 +32920,7 @@
         <v>44748</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32982,7 +32982,7 @@
         <v>44748</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33039,7 +33039,7 @@
         <v>44750</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33096,7 +33096,7 @@
         <v>44756</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33153,7 +33153,7 @@
         <v>44761</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33210,7 +33210,7 @@
         <v>44776</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33267,7 +33267,7 @@
         <v>44777</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33329,7 +33329,7 @@
         <v>44781</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33386,7 +33386,7 @@
         <v>44783</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33443,7 +33443,7 @@
         <v>44785</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33505,7 +33505,7 @@
         <v>44784</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33567,7 +33567,7 @@
         <v>44785</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33624,7 +33624,7 @@
         <v>44792</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33681,7 +33681,7 @@
         <v>44792</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33743,7 +33743,7 @@
         <v>44795</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33800,7 +33800,7 @@
         <v>44795</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33862,7 +33862,7 @@
         <v>44803</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33924,7 +33924,7 @@
         <v>44805</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33986,7 +33986,7 @@
         <v>44806</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34043,7 +34043,7 @@
         <v>44809</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34105,7 +34105,7 @@
         <v>44809</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34167,7 +34167,7 @@
         <v>44811</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34224,7 +34224,7 @@
         <v>44813</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34281,7 +34281,7 @@
         <v>44813</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34338,7 +34338,7 @@
         <v>44813</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34395,7 +34395,7 @@
         <v>44813</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34452,7 +34452,7 @@
         <v>44813</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34509,7 +34509,7 @@
         <v>44816</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34566,7 +34566,7 @@
         <v>44816</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34623,7 +34623,7 @@
         <v>44817</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34685,7 +34685,7 @@
         <v>44817</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34742,7 +34742,7 @@
         <v>44818</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34804,7 +34804,7 @@
         <v>44818</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34866,7 +34866,7 @@
         <v>44818</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34928,7 +34928,7 @@
         <v>44817</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34985,7 +34985,7 @@
         <v>44818</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35047,7 +35047,7 @@
         <v>44818</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35109,7 +35109,7 @@
         <v>44818</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35171,7 +35171,7 @@
         <v>44818</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35228,7 +35228,7 @@
         <v>44819</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35285,7 +35285,7 @@
         <v>44820</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35342,7 +35342,7 @@
         <v>44823</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35404,7 +35404,7 @@
         <v>44824</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35461,7 +35461,7 @@
         <v>44827</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35523,7 +35523,7 @@
         <v>44838</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35585,7 +35585,7 @@
         <v>44838</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35642,7 +35642,7 @@
         <v>44839</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35699,7 +35699,7 @@
         <v>44840</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35756,7 +35756,7 @@
         <v>44840</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35813,7 +35813,7 @@
         <v>44841</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35875,7 +35875,7 @@
         <v>44845</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35937,7 +35937,7 @@
         <v>44845</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35999,7 +35999,7 @@
         <v>44848</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36061,7 +36061,7 @@
         <v>44848</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36123,7 +36123,7 @@
         <v>44849</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36185,7 +36185,7 @@
         <v>44848</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36242,7 +36242,7 @@
         <v>44853</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36304,7 +36304,7 @@
         <v>44853</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36366,7 +36366,7 @@
         <v>44853</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36428,7 +36428,7 @@
         <v>44856</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36490,7 +36490,7 @@
         <v>44855</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36552,7 +36552,7 @@
         <v>44857</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36609,7 +36609,7 @@
         <v>44859</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36666,7 +36666,7 @@
         <v>44859</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36723,7 +36723,7 @@
         <v>44861</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36785,7 +36785,7 @@
         <v>44861</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36842,7 +36842,7 @@
         <v>44861</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36904,7 +36904,7 @@
         <v>44861</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36961,7 +36961,7 @@
         <v>44861</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37023,7 +37023,7 @@
         <v>44861</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37085,7 +37085,7 @@
         <v>44861</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37142,7 +37142,7 @@
         <v>44862</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37204,7 +37204,7 @@
         <v>44866</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37266,7 +37266,7 @@
         <v>44867</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37328,7 +37328,7 @@
         <v>44867</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37390,7 +37390,7 @@
         <v>44867</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37447,7 +37447,7 @@
         <v>44868</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37504,7 +37504,7 @@
         <v>44873</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37566,7 +37566,7 @@
         <v>44874</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37623,7 +37623,7 @@
         <v>44874</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37685,7 +37685,7 @@
         <v>44875</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37742,7 +37742,7 @@
         <v>44879</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37799,7 +37799,7 @@
         <v>44879</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37856,7 +37856,7 @@
         <v>44879</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37913,7 +37913,7 @@
         <v>44879</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37970,7 +37970,7 @@
         <v>44883</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38032,7 +38032,7 @@
         <v>44886</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38089,7 +38089,7 @@
         <v>44888</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38146,7 +38146,7 @@
         <v>44888</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38203,7 +38203,7 @@
         <v>44889</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38265,7 +38265,7 @@
         <v>44889</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38327,7 +38327,7 @@
         <v>44890</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38384,7 +38384,7 @@
         <v>44890</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38441,7 +38441,7 @@
         <v>44890</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38503,7 +38503,7 @@
         <v>44893</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38565,7 +38565,7 @@
         <v>44895</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38627,7 +38627,7 @@
         <v>44897</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38684,7 +38684,7 @@
         <v>44901</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38741,7 +38741,7 @@
         <v>44904</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38798,7 +38798,7 @@
         <v>44907</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38855,7 +38855,7 @@
         <v>44907</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38912,7 +38912,7 @@
         <v>44909</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38974,7 +38974,7 @@
         <v>44910</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39031,7 +39031,7 @@
         <v>44910</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39088,7 +39088,7 @@
         <v>44911</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39150,7 +39150,7 @@
         <v>44911</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39212,7 +39212,7 @@
         <v>44911</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39269,7 +39269,7 @@
         <v>44916</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39326,7 +39326,7 @@
         <v>44917</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39388,7 +39388,7 @@
         <v>44929</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39445,7 +39445,7 @@
         <v>44929</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39502,7 +39502,7 @@
         <v>44941</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39559,7 +39559,7 @@
         <v>44942</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39616,7 +39616,7 @@
         <v>44942</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39673,7 +39673,7 @@
         <v>44942</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39730,7 +39730,7 @@
         <v>44942</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39787,7 +39787,7 @@
         <v>44944</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39844,7 +39844,7 @@
         <v>44950</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39901,7 +39901,7 @@
         <v>44951</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39958,7 +39958,7 @@
         <v>44960</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40015,7 +40015,7 @@
         <v>44963</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40072,7 +40072,7 @@
         <v>44965</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40129,7 +40129,7 @@
         <v>44965</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40186,7 +40186,7 @@
         <v>44966</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40243,7 +40243,7 @@
         <v>44966</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40300,7 +40300,7 @@
         <v>44971</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40362,7 +40362,7 @@
         <v>44971</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40419,7 +40419,7 @@
         <v>44972</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40476,7 +40476,7 @@
         <v>44973</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40533,7 +40533,7 @@
         <v>44973</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40590,7 +40590,7 @@
         <v>44973</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40647,7 +40647,7 @@
         <v>44977</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40704,7 +40704,7 @@
         <v>44981</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40761,7 +40761,7 @@
         <v>44984</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40818,7 +40818,7 @@
         <v>44985</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40875,7 +40875,7 @@
         <v>44985</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40932,7 +40932,7 @@
         <v>44985</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40989,7 +40989,7 @@
         <v>44991</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41046,7 +41046,7 @@
         <v>44991</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41103,7 +41103,7 @@
         <v>45006</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41160,7 +41160,7 @@
         <v>45006</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41217,7 +41217,7 @@
         <v>45013</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41274,7 +41274,7 @@
         <v>45015</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41336,7 +41336,7 @@
         <v>45015</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41398,7 +41398,7 @@
         <v>45015</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41455,7 +41455,7 @@
         <v>45021</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41512,7 +41512,7 @@
         <v>45021</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41569,7 +41569,7 @@
         <v>45028</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41626,7 +41626,7 @@
         <v>45029</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41683,7 +41683,7 @@
         <v>45030</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41740,7 +41740,7 @@
         <v>45036</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41797,7 +41797,7 @@
         <v>45036</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41854,7 +41854,7 @@
         <v>45036</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41911,7 +41911,7 @@
         <v>45035</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41973,7 +41973,7 @@
         <v>45036</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42030,7 +42030,7 @@
         <v>45035</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42087,7 +42087,7 @@
         <v>45043</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42144,7 +42144,7 @@
         <v>45043</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42201,7 +42201,7 @@
         <v>45043</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42258,7 +42258,7 @@
         <v>45044</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42320,7 +42320,7 @@
         <v>45048</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42377,7 +42377,7 @@
         <v>45050</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42434,7 +42434,7 @@
         <v>45055</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42491,7 +42491,7 @@
         <v>45057</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42548,7 +42548,7 @@
         <v>45056</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42605,7 +42605,7 @@
         <v>45062</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42667,7 +42667,7 @@
         <v>45062</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42729,7 +42729,7 @@
         <v>45064</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42791,7 +42791,7 @@
         <v>45066</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42853,7 +42853,7 @@
         <v>45068</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42915,7 +42915,7 @@
         <v>45070</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42977,7 +42977,7 @@
         <v>45072</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -43039,7 +43039,7 @@
         <v>45072</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43101,7 +43101,7 @@
         <v>45076</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43158,7 +43158,7 @@
         <v>45076</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43215,7 +43215,7 @@
         <v>45077</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43272,7 +43272,7 @@
         <v>45079</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43334,7 +43334,7 @@
         <v>45079</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43396,7 +43396,7 @@
         <v>45086</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43458,7 +43458,7 @@
         <v>45085</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43520,7 +43520,7 @@
         <v>45086</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43577,7 +43577,7 @@
         <v>45086</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43634,7 +43634,7 @@
         <v>45086</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43691,7 +43691,7 @@
         <v>45086</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43748,7 +43748,7 @@
         <v>45086</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43805,7 +43805,7 @@
         <v>45086</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43862,7 +43862,7 @@
         <v>45090</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43924,7 +43924,7 @@
         <v>45089</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43981,7 +43981,7 @@
         <v>45090</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -44038,7 +44038,7 @@
         <v>45090</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44095,7 +44095,7 @@
         <v>45090</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44152,7 +44152,7 @@
         <v>45090</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44209,7 +44209,7 @@
         <v>45090</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44266,7 +44266,7 @@
         <v>45091</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44323,7 +44323,7 @@
         <v>45091</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44380,7 +44380,7 @@
         <v>45091</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44437,7 +44437,7 @@
         <v>45091</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44494,7 +44494,7 @@
         <v>45093</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44556,7 +44556,7 @@
         <v>45094</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44618,7 +44618,7 @@
         <v>45096</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44675,7 +44675,7 @@
         <v>45096</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44732,7 +44732,7 @@
         <v>45096</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44794,7 +44794,7 @@
         <v>45098</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44851,7 +44851,7 @@
         <v>45098</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44913,7 +44913,7 @@
         <v>45098</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44975,7 +44975,7 @@
         <v>45098</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -45037,7 +45037,7 @@
         <v>45098</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -45094,7 +45094,7 @@
         <v>45098</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45151,7 +45151,7 @@
         <v>45098</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45213,7 +45213,7 @@
         <v>45098</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45275,7 +45275,7 @@
         <v>45098</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45332,7 +45332,7 @@
         <v>45098</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45394,7 +45394,7 @@
         <v>45098</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45451,7 +45451,7 @@
         <v>45098</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45508,7 +45508,7 @@
         <v>45098</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45565,7 +45565,7 @@
         <v>45098</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45622,7 +45622,7 @@
         <v>45099</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45684,7 +45684,7 @@
         <v>45100</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45746,7 +45746,7 @@
         <v>45100</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45808,7 +45808,7 @@
         <v>45100</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45870,7 +45870,7 @@
         <v>45100</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45927,7 +45927,7 @@
         <v>45103</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45989,7 +45989,7 @@
         <v>45104</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -46046,7 +46046,7 @@
         <v>45104</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -46103,7 +46103,7 @@
         <v>45104</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46160,7 +46160,7 @@
         <v>45104</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46217,7 +46217,7 @@
         <v>45104</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46274,7 +46274,7 @@
         <v>45106</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46331,7 +46331,7 @@
         <v>45106</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46388,7 +46388,7 @@
         <v>45106</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46445,7 +46445,7 @@
         <v>45106</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46502,7 +46502,7 @@
         <v>45106</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46559,7 +46559,7 @@
         <v>45106</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46616,7 +46616,7 @@
         <v>45107</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46673,7 +46673,7 @@
         <v>45107</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46730,7 +46730,7 @@
         <v>45107</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46787,7 +46787,7 @@
         <v>45107</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46844,7 +46844,7 @@
         <v>45110</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46901,7 +46901,7 @@
         <v>45110</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46958,7 +46958,7 @@
         <v>45110</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -47015,7 +47015,7 @@
         <v>45110</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -47072,7 +47072,7 @@
         <v>45111</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47129,7 +47129,7 @@
         <v>45114</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47186,7 +47186,7 @@
         <v>45114</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47243,7 +47243,7 @@
         <v>45118</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47305,7 +47305,7 @@
         <v>45118</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47367,7 +47367,7 @@
         <v>45118</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47429,7 +47429,7 @@
         <v>45118</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47491,7 +47491,7 @@
         <v>45118</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47553,7 +47553,7 @@
         <v>45118</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47615,7 +47615,7 @@
         <v>45119</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47677,7 +47677,7 @@
         <v>45119</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47734,7 +47734,7 @@
         <v>45120</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47791,7 +47791,7 @@
         <v>45120</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47848,7 +47848,7 @@
         <v>45120</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47905,7 +47905,7 @@
         <v>45120</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47962,7 +47962,7 @@
         <v>45125</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -48019,7 +48019,7 @@
         <v>45125</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -48076,7 +48076,7 @@
         <v>45125</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -48133,7 +48133,7 @@
         <v>45129</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48190,7 +48190,7 @@
         <v>45129</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48247,7 +48247,7 @@
         <v>45135</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48304,7 +48304,7 @@
         <v>45135</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48361,7 +48361,7 @@
         <v>45138</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48418,7 +48418,7 @@
         <v>45138</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48475,7 +48475,7 @@
         <v>45139</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48532,7 +48532,7 @@
         <v>45139</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48589,7 +48589,7 @@
         <v>45139</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48646,7 +48646,7 @@
         <v>45140</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48708,7 +48708,7 @@
         <v>45140</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48765,7 +48765,7 @@
         <v>45140</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48827,7 +48827,7 @@
         <v>45141</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48884,7 +48884,7 @@
         <v>45145</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48941,7 +48941,7 @@
         <v>45152</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -49003,7 +49003,7 @@
         <v>45152</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -49065,7 +49065,7 @@
         <v>45156</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -49122,7 +49122,7 @@
         <v>45159</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49179,7 +49179,7 @@
         <v>45159</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49236,7 +49236,7 @@
         <v>45160</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49298,7 +49298,7 @@
         <v>45160</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49360,7 +49360,7 @@
         <v>45160</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49417,7 +49417,7 @@
         <v>45162</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49474,7 +49474,7 @@
         <v>45162</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49531,7 +49531,7 @@
         <v>45163</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49588,7 +49588,7 @@
         <v>45167</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49650,7 +49650,7 @@
         <v>45167</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49712,7 +49712,7 @@
         <v>45167</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49769,7 +49769,7 @@
         <v>45167</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49831,7 +49831,7 @@
         <v>45168</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49893,7 +49893,7 @@
         <v>45167</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49950,7 +49950,7 @@
         <v>45168</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -50012,7 +50012,7 @@
         <v>45168</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -50074,7 +50074,7 @@
         <v>45170</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -50131,7 +50131,7 @@
         <v>45170</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -50188,7 +50188,7 @@
         <v>45175</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -50245,7 +50245,7 @@
         <v>45176</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50307,7 +50307,7 @@
         <v>45176</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50369,7 +50369,7 @@
         <v>45176</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50426,7 +50426,7 @@
         <v>45177</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50483,7 +50483,7 @@
         <v>45177</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50540,7 +50540,7 @@
         <v>45177</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50597,7 +50597,7 @@
         <v>45180</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50654,7 +50654,7 @@
         <v>45181</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50716,7 +50716,7 @@
         <v>45181</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50778,7 +50778,7 @@
         <v>45181</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50835,7 +50835,7 @@
         <v>45181</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50892,7 +50892,7 @@
         <v>45182</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50949,7 +50949,7 @@
         <v>45183</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -51006,7 +51006,7 @@
         <v>45184</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -51068,7 +51068,7 @@
         <v>45187</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -51125,7 +51125,7 @@
         <v>45187</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -51182,7 +51182,7 @@
         <v>45187</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -51239,7 +51239,7 @@
         <v>45187</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -51296,7 +51296,7 @@
         <v>45187</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -51353,7 +51353,7 @@
         <v>45187</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -51410,7 +51410,7 @@
         <v>45187</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -51467,7 +51467,7 @@
         <v>45188</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51529,7 +51529,7 @@
         <v>45188</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51591,7 +51591,7 @@
         <v>45188</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51653,7 +51653,7 @@
         <v>45188</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51715,7 +51715,7 @@
         <v>45188</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51777,7 +51777,7 @@
         <v>45188</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51839,7 +51839,7 @@
         <v>45188</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51901,7 +51901,7 @@
         <v>45188</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51958,7 +51958,7 @@
         <v>45189</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -52020,7 +52020,7 @@
         <v>45190</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -52077,7 +52077,7 @@
         <v>45190</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -52134,7 +52134,7 @@
         <v>45190</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -52191,7 +52191,7 @@
         <v>45190</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -52248,7 +52248,7 @@
         <v>45196</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -52305,7 +52305,7 @@
         <v>45197</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -52362,7 +52362,7 @@
         <v>45197</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -52419,7 +52419,7 @@
         <v>45198</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -52481,7 +52481,7 @@
         <v>45201</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -52543,7 +52543,7 @@
         <v>45201</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52605,7 +52605,7 @@
         <v>45202</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52667,7 +52667,7 @@
         <v>45202</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52724,7 +52724,7 @@
         <v>45203</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52781,7 +52781,7 @@
         <v>45204</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52843,7 +52843,7 @@
         <v>45208</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52900,7 +52900,7 @@
         <v>45209</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52957,7 +52957,7 @@
         <v>45208</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -53019,7 +53019,7 @@
         <v>45211</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -53076,7 +53076,7 @@
         <v>45211</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -53133,7 +53133,7 @@
         <v>45211</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -53190,7 +53190,7 @@
         <v>45211</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -53252,7 +53252,7 @@
         <v>45211</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -53314,7 +53314,7 @@
         <v>45211</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -53371,7 +53371,7 @@
         <v>45212</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -53428,7 +53428,7 @@
         <v>45213</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -53485,7 +53485,7 @@
         <v>45215</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -53542,7 +53542,7 @@
         <v>45215</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53599,7 +53599,7 @@
         <v>45216</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53656,7 +53656,7 @@
         <v>45216</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53718,7 +53718,7 @@
         <v>45218</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -53775,7 +53775,7 @@
         <v>45218</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -53837,7 +53837,7 @@
         <v>45218</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -53894,7 +53894,7 @@
         <v>45218</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -53951,7 +53951,7 @@
         <v>45219</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -54008,7 +54008,7 @@
         <v>45219</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -54065,7 +54065,7 @@
         <v>45219</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -54127,7 +54127,7 @@
         <v>45219</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -54189,7 +54189,7 @@
         <v>45219</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -54246,7 +54246,7 @@
         <v>45219</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -54303,7 +54303,7 @@
         <v>45222</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -54360,7 +54360,7 @@
         <v>45222</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -54422,7 +54422,7 @@
         <v>45222</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -54479,7 +54479,7 @@
         <v>45225</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -54536,7 +54536,7 @@
         <v>45225</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -54593,7 +54593,7 @@
         <v>45230</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -54655,7 +54655,7 @@
         <v>45230</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -54712,7 +54712,7 @@
         <v>45230</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -54769,7 +54769,7 @@
         <v>45230</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -54826,7 +54826,7 @@
         <v>45232</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -54888,7 +54888,7 @@
         <v>45232</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -54950,7 +54950,7 @@
         <v>45232</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -55012,7 +55012,7 @@
         <v>45236</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -55074,7 +55074,7 @@
         <v>45236</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -55131,7 +55131,7 @@
         <v>45237</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -55188,7 +55188,7 @@
         <v>45237</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -55245,7 +55245,7 @@
         <v>45237</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -55302,7 +55302,7 @@
         <v>45237</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -55359,7 +55359,7 @@
         <v>45237</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -55421,7 +55421,7 @@
         <v>45237</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -55478,7 +55478,7 @@
         <v>45237</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -55535,7 +55535,7 @@
         <v>45238</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -55592,7 +55592,7 @@
         <v>45239</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -55649,7 +55649,7 @@
         <v>45239</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -55711,7 +55711,7 @@
         <v>45239</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -55768,7 +55768,7 @@
         <v>45239</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -55825,7 +55825,7 @@
         <v>45240</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -55882,7 +55882,7 @@
         <v>45240</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -55939,7 +55939,7 @@
         <v>45243</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -56001,7 +56001,7 @@
         <v>45243</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -56063,7 +56063,7 @@
         <v>45244</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -56120,7 +56120,7 @@
         <v>45244</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -56177,7 +56177,7 @@
         <v>45244</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -56234,7 +56234,7 @@
         <v>45244</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -56291,7 +56291,7 @@
         <v>45244</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -56348,7 +56348,7 @@
         <v>45244</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -56405,7 +56405,7 @@
         <v>45244</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -56462,7 +56462,7 @@
         <v>45244</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -56519,7 +56519,7 @@
         <v>45244</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -56576,7 +56576,7 @@
         <v>45245</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -56633,7 +56633,7 @@
         <v>45245</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -56690,7 +56690,7 @@
         <v>45245</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -56747,7 +56747,7 @@
         <v>45246</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -56804,7 +56804,7 @@
         <v>45246</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -56861,7 +56861,7 @@
         <v>45247</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -56918,7 +56918,7 @@
         <v>45251</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -56975,7 +56975,7 @@
         <v>45252</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -57032,7 +57032,7 @@
         <v>45252</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -57089,7 +57089,7 @@
         <v>45253</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -57146,7 +57146,7 @@
         <v>45254</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -57203,7 +57203,7 @@
         <v>45254</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -57260,7 +57260,7 @@
         <v>45257</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -57317,7 +57317,7 @@
         <v>45257</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -57374,7 +57374,7 @@
         <v>45258</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -57431,7 +57431,7 @@
         <v>45259</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -57488,7 +57488,7 @@
         <v>45259</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -57545,7 +57545,7 @@
         <v>45260</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -57602,7 +57602,7 @@
         <v>45260</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -57659,7 +57659,7 @@
         <v>45260</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -57716,7 +57716,7 @@
         <v>45260</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -57773,7 +57773,7 @@
         <v>45261</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -57830,7 +57830,7 @@
         <v>45261</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -57887,7 +57887,7 @@
         <v>45262</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -57944,7 +57944,7 @@
         <v>45264</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -58001,7 +58001,7 @@
         <v>45264</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -58058,7 +58058,7 @@
         <v>45264</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -58115,7 +58115,7 @@
         <v>45264</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -58177,7 +58177,7 @@
         <v>45264</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -58234,7 +58234,7 @@
         <v>45265</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -58291,7 +58291,7 @@
         <v>45265</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -58348,7 +58348,7 @@
         <v>45266</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -58405,7 +58405,7 @@
         <v>45266</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -58462,7 +58462,7 @@
         <v>45266</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -58519,7 +58519,7 @@
         <v>45267</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -58576,7 +58576,7 @@
         <v>45271</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -58633,7 +58633,7 @@
         <v>45271</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -58690,7 +58690,7 @@
         <v>45273</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -58747,7 +58747,7 @@
         <v>45273</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -58804,7 +58804,7 @@
         <v>45273</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -58861,7 +58861,7 @@
         <v>45273</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -58918,7 +58918,7 @@
         <v>45273</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -58975,7 +58975,7 @@
         <v>45273</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -59032,7 +59032,7 @@
         <v>45273</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -59089,7 +59089,7 @@
         <v>45278</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -59146,7 +59146,7 @@
         <v>45279</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -59203,7 +59203,7 @@
         <v>45279</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -59260,7 +59260,7 @@
         <v>45279</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -59317,7 +59317,7 @@
         <v>45281</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -59374,7 +59374,7 @@
         <v>45282</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -59436,7 +59436,7 @@
         <v>45285</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -59493,7 +59493,7 @@
         <v>45285</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -59550,7 +59550,7 @@
         <v>45285</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -59607,7 +59607,7 @@
         <v>45285</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -59664,7 +59664,7 @@
         <v>45287</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -59721,7 +59721,7 @@
         <v>45287</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -59778,7 +59778,7 @@
         <v>45289</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -59835,7 +59835,7 @@
         <v>45299</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -59892,7 +59892,7 @@
         <v>45308</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -59949,7 +59949,7 @@
         <v>45308</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -60006,7 +60006,7 @@
         <v>45309</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -60063,7 +60063,7 @@
         <v>45310</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -60120,7 +60120,7 @@
         <v>45310</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -60177,7 +60177,7 @@
         <v>45311</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -60234,7 +60234,7 @@
         <v>45311</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -60291,7 +60291,7 @@
         <v>45312</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -60348,7 +60348,7 @@
         <v>45312</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -60405,7 +60405,7 @@
         <v>45313</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -60462,7 +60462,7 @@
         <v>45315</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -60519,7 +60519,7 @@
         <v>45315</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -60576,7 +60576,7 @@
         <v>45315</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -60633,7 +60633,7 @@
         <v>45316</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -60690,7 +60690,7 @@
         <v>45316</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -60747,7 +60747,7 @@
         <v>45316</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -60797,14 +60797,14 @@
     <row r="999" ht="15" customHeight="1">
       <c r="A999" t="inlineStr">
         <is>
-          <t>A 3521-2024</t>
+          <t>A 3504-2024</t>
         </is>
       </c>
       <c r="B999" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -60817,7 +60817,7 @@
         </is>
       </c>
       <c r="G999" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="H999" t="n">
         <v>0</v>
@@ -60854,14 +60854,14 @@
     <row r="1000" ht="15" customHeight="1">
       <c r="A1000" t="inlineStr">
         <is>
-          <t>A 3504-2024</t>
+          <t>A 3521-2024</t>
         </is>
       </c>
       <c r="B1000" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -60874,7 +60874,7 @@
         </is>
       </c>
       <c r="G1000" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="H1000" t="n">
         <v>0</v>
@@ -60918,7 +60918,7 @@
         <v>45323</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -60975,7 +60975,7 @@
         <v>45323</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -61030,14 +61030,14 @@
     <row r="1003" ht="15" customHeight="1">
       <c r="A1003" t="inlineStr">
         <is>
-          <t>A 4127-2024</t>
+          <t>A 4046-2024</t>
         </is>
       </c>
       <c r="B1003" s="1" t="n">
         <v>45323</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -61049,13 +61049,8 @@
           <t>PITEÅ</t>
         </is>
       </c>
-      <c r="F1003" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="G1003" t="n">
-        <v>4.5</v>
+        <v>11</v>
       </c>
       <c r="H1003" t="n">
         <v>0</v>
@@ -61092,14 +61087,14 @@
     <row r="1004" ht="15" customHeight="1">
       <c r="A1004" t="inlineStr">
         <is>
-          <t>A 4046-2024</t>
+          <t>A 4127-2024</t>
         </is>
       </c>
       <c r="B1004" s="1" t="n">
         <v>45323</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -61111,8 +61106,13 @@
           <t>PITEÅ</t>
         </is>
       </c>
+      <c r="F1004" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="G1004" t="n">
-        <v>11</v>
+        <v>4.5</v>
       </c>
       <c r="H1004" t="n">
         <v>0</v>
@@ -61156,7 +61156,7 @@
         <v>45323</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -61218,7 +61218,7 @@
         <v>45324</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -61280,7 +61280,7 @@
         <v>45324</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -61337,7 +61337,7 @@
         <v>45324</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -61399,7 +61399,7 @@
         <v>45329</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -61456,7 +61456,7 @@
         <v>45330</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -61513,7 +61513,7 @@
         <v>45334</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -61570,7 +61570,7 @@
         <v>45335</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>

--- a/Översikt PITEÅ.xlsx
+++ b/Översikt PITEÅ.xlsx
@@ -569,7 +569,7 @@
         <v>44617</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -665,7 +665,7 @@
         <v>44839</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
         <v>44839</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>44459</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
         <v>44617</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>43896</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>45191</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>45203</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>44740</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>44280</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>44539</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>44550</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>45119</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>44014</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>44522</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>44526</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         <v>44553</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>44810</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>44917</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>45103</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>45106</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         <v>43802</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>43902</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2727,7 +2727,7 @@
         <v>43908</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         <v>44053</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2908,7 +2908,7 @@
         <v>44193</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>44298</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>44840</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
         <v>44852</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3262,7 +3262,7 @@
         <v>44859</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>44944</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3434,7 +3434,7 @@
         <v>45120</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
         <v>45187</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         <v>45209</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3701,7 +3701,7 @@
         <v>45219</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>45243</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         <v>45293</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
         <v>45296</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>43714</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         <v>44014</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4225,7 +4225,7 @@
         <v>44106</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4310,7 +4310,7 @@
         <v>44309</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>44342</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4485,7 +4485,7 @@
         <v>44495</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
         <v>44525</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4665,7 +4665,7 @@
         <v>44525</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4755,7 +4755,7 @@
         <v>44538</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4840,7 +4840,7 @@
         <v>44727</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4929,7 +4929,7 @@
         <v>44804</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5014,7 +5014,7 @@
         <v>44917</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5104,7 +5104,7 @@
         <v>45049</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5193,7 +5193,7 @@
         <v>45098</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>45103</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5373,7 +5373,7 @@
         <v>45148</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
         <v>45175</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         <v>45181</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5642,7 +5642,7 @@
         <v>45188</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5732,7 +5732,7 @@
         <v>45224</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5817,7 +5817,7 @@
         <v>45243</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5907,7 +5907,7 @@
         <v>45265</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5992,7 +5992,7 @@
         <v>45323</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
         <v>43325</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6139,7 +6139,7 @@
         <v>43332</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6196,7 +6196,7 @@
         <v>43336</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6253,7 +6253,7 @@
         <v>43339</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         <v>43339</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
         <v>43341</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6424,7 +6424,7 @@
         <v>43355</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>43355</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         <v>43374</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6600,7 +6600,7 @@
         <v>43374</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6662,7 +6662,7 @@
         <v>43375</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6719,7 +6719,7 @@
         <v>43376</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
         <v>43376</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6833,7 +6833,7 @@
         <v>43381</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6890,7 +6890,7 @@
         <v>43383</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6947,7 +6947,7 @@
         <v>43391</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>43391</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7061,7 +7061,7 @@
         <v>43392</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7118,7 +7118,7 @@
         <v>43392</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7175,7 +7175,7 @@
         <v>43398</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7232,7 +7232,7 @@
         <v>43402</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7289,7 +7289,7 @@
         <v>43404</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7346,7 +7346,7 @@
         <v>43406</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7403,7 +7403,7 @@
         <v>43406</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
         <v>43406</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>43406</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>43406</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>43416</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>43418</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7745,7 +7745,7 @@
         <v>43418</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7802,7 +7802,7 @@
         <v>43418</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         <v>43419</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7916,7 +7916,7 @@
         <v>43420</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         <v>43424</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8035,7 +8035,7 @@
         <v>43427</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8097,7 +8097,7 @@
         <v>43427</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8154,7 +8154,7 @@
         <v>43427</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8216,7 +8216,7 @@
         <v>43427</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8278,7 +8278,7 @@
         <v>43436</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
         <v>43438</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8392,7 +8392,7 @@
         <v>43438</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8449,7 +8449,7 @@
         <v>43438</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8506,7 +8506,7 @@
         <v>43438</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8563,7 +8563,7 @@
         <v>43451</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8625,7 +8625,7 @@
         <v>43472</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8682,7 +8682,7 @@
         <v>43475</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8739,7 +8739,7 @@
         <v>43479</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8796,7 +8796,7 @@
         <v>43479</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8853,7 +8853,7 @@
         <v>43486</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
         <v>43489</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8967,7 +8967,7 @@
         <v>43489</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9024,7 +9024,7 @@
         <v>43489</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9081,7 +9081,7 @@
         <v>43489</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9138,7 +9138,7 @@
         <v>43489</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9195,7 +9195,7 @@
         <v>43490</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9252,7 +9252,7 @@
         <v>43490</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9309,7 +9309,7 @@
         <v>43493</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9371,7 +9371,7 @@
         <v>43509</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9428,7 +9428,7 @@
         <v>43510</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9485,7 +9485,7 @@
         <v>43510</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9542,7 +9542,7 @@
         <v>43514</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9599,7 +9599,7 @@
         <v>43514</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9656,7 +9656,7 @@
         <v>43514</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9713,7 +9713,7 @@
         <v>43516</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9775,7 +9775,7 @@
         <v>43518</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9832,7 +9832,7 @@
         <v>43521</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9894,7 +9894,7 @@
         <v>43521</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9956,7 +9956,7 @@
         <v>43521</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10018,7 +10018,7 @@
         <v>43521</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10080,7 +10080,7 @@
         <v>43521</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10142,7 +10142,7 @@
         <v>43522</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10199,7 +10199,7 @@
         <v>43523</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10256,7 +10256,7 @@
         <v>43523</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10313,7 +10313,7 @@
         <v>43523</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10370,7 +10370,7 @@
         <v>43532</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10427,7 +10427,7 @@
         <v>43532</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10484,7 +10484,7 @@
         <v>43542</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10541,7 +10541,7 @@
         <v>43544</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10603,7 +10603,7 @@
         <v>43544</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10665,7 +10665,7 @@
         <v>43554</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10722,7 +10722,7 @@
         <v>43556</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10779,7 +10779,7 @@
         <v>43557</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10841,7 +10841,7 @@
         <v>43557</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10898,7 +10898,7 @@
         <v>43557</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10955,7 +10955,7 @@
         <v>43557</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11012,7 +11012,7 @@
         <v>43557</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11074,7 +11074,7 @@
         <v>43564</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11131,7 +11131,7 @@
         <v>43564</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11188,7 +11188,7 @@
         <v>43567</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11245,7 +11245,7 @@
         <v>43570</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11302,7 +11302,7 @@
         <v>43570</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11359,7 +11359,7 @@
         <v>43570</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11416,7 +11416,7 @@
         <v>43584</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11473,7 +11473,7 @@
         <v>43605</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11530,7 +11530,7 @@
         <v>43608</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11587,7 +11587,7 @@
         <v>43614</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11649,7 +11649,7 @@
         <v>43616</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11711,7 +11711,7 @@
         <v>43616</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11773,7 +11773,7 @@
         <v>43629</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11830,7 +11830,7 @@
         <v>43629</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11892,7 +11892,7 @@
         <v>43633</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11949,7 +11949,7 @@
         <v>43633</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12006,7 +12006,7 @@
         <v>43640</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12063,7 +12063,7 @@
         <v>43640</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12120,7 +12120,7 @@
         <v>43647</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12177,7 +12177,7 @@
         <v>43647</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12234,7 +12234,7 @@
         <v>43650</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12291,7 +12291,7 @@
         <v>43652</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12353,7 +12353,7 @@
         <v>43677</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12410,7 +12410,7 @@
         <v>43678</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12467,7 +12467,7 @@
         <v>43682</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12524,7 +12524,7 @@
         <v>43691</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12586,7 +12586,7 @@
         <v>43691</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12648,7 +12648,7 @@
         <v>43696</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12710,7 +12710,7 @@
         <v>43697</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12767,7 +12767,7 @@
         <v>43698</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12829,7 +12829,7 @@
         <v>43698</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12891,7 +12891,7 @@
         <v>43706</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12948,7 +12948,7 @@
         <v>43707</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13010,7 +13010,7 @@
         <v>43711</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13067,7 +13067,7 @@
         <v>43713</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13124,7 +13124,7 @@
         <v>43718</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13181,7 +13181,7 @@
         <v>43718</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13238,7 +13238,7 @@
         <v>43718</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13300,7 +13300,7 @@
         <v>43720</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13357,7 +13357,7 @@
         <v>43721</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13414,7 +13414,7 @@
         <v>43732</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13471,7 +13471,7 @@
         <v>43741</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13533,7 +13533,7 @@
         <v>43741</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13590,7 +13590,7 @@
         <v>43752</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13652,7 +13652,7 @@
         <v>43755</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13709,7 +13709,7 @@
         <v>43755</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13766,7 +13766,7 @@
         <v>43755</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13823,7 +13823,7 @@
         <v>43755</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13880,7 +13880,7 @@
         <v>43760</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13942,7 +13942,7 @@
         <v>43760</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14004,7 +14004,7 @@
         <v>43760</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14061,7 +14061,7 @@
         <v>43762</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14123,7 +14123,7 @@
         <v>43766</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14180,7 +14180,7 @@
         <v>43766</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14237,7 +14237,7 @@
         <v>43768</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14294,7 +14294,7 @@
         <v>43770</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14356,7 +14356,7 @@
         <v>43775</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14418,7 +14418,7 @@
         <v>43775</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14480,7 +14480,7 @@
         <v>43777</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14537,7 +14537,7 @@
         <v>43780</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14594,7 +14594,7 @@
         <v>43780</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14651,7 +14651,7 @@
         <v>43780</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14708,7 +14708,7 @@
         <v>43782</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14770,7 +14770,7 @@
         <v>43789</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14832,7 +14832,7 @@
         <v>43798</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14889,7 +14889,7 @@
         <v>43801</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14951,7 +14951,7 @@
         <v>43802</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15008,7 +15008,7 @@
         <v>43802</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15065,7 +15065,7 @@
         <v>43802</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15122,7 +15122,7 @@
         <v>43802</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15179,7 +15179,7 @@
         <v>43802</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15236,7 +15236,7 @@
         <v>43802</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15293,7 +15293,7 @@
         <v>43807</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15350,7 +15350,7 @@
         <v>43809</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15407,7 +15407,7 @@
         <v>43817</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15464,7 +15464,7 @@
         <v>43817</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15526,7 +15526,7 @@
         <v>43822</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15583,7 +15583,7 @@
         <v>43822</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15640,7 +15640,7 @@
         <v>43833</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15697,7 +15697,7 @@
         <v>43846</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15754,7 +15754,7 @@
         <v>43852</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15811,7 +15811,7 @@
         <v>43853</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15868,7 +15868,7 @@
         <v>43854</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15925,7 +15925,7 @@
         <v>43859</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15987,7 +15987,7 @@
         <v>43859</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16044,7 +16044,7 @@
         <v>43859</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16101,7 +16101,7 @@
         <v>43859</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16158,7 +16158,7 @@
         <v>43859</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16215,7 +16215,7 @@
         <v>43860</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16272,7 +16272,7 @@
         <v>43868</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16329,7 +16329,7 @@
         <v>43868</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16386,7 +16386,7 @@
         <v>43874</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16448,7 +16448,7 @@
         <v>43878</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16505,7 +16505,7 @@
         <v>43880</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16562,7 +16562,7 @@
         <v>43880</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16619,7 +16619,7 @@
         <v>43889</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16676,7 +16676,7 @@
         <v>43895</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16738,7 +16738,7 @@
         <v>43896</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16795,7 +16795,7 @@
         <v>43902</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16852,7 +16852,7 @@
         <v>43902</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16914,7 +16914,7 @@
         <v>43907</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16971,7 +16971,7 @@
         <v>43913</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17028,7 +17028,7 @@
         <v>43914</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17090,7 +17090,7 @@
         <v>43927</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17152,7 +17152,7 @@
         <v>43929</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         <v>43929</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>43931</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17328,7 +17328,7 @@
         <v>43950</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17385,7 +17385,7 @@
         <v>43957</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17447,7 +17447,7 @@
         <v>43958</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17504,7 +17504,7 @@
         <v>43958</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17561,7 +17561,7 @@
         <v>43959</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17618,7 +17618,7 @@
         <v>43962</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17675,7 +17675,7 @@
         <v>43962</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17732,7 +17732,7 @@
         <v>43962</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17789,7 +17789,7 @@
         <v>43962</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17846,7 +17846,7 @@
         <v>43970</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17908,7 +17908,7 @@
         <v>43971</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17970,7 +17970,7 @@
         <v>43976</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18027,7 +18027,7 @@
         <v>43979</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18084,7 +18084,7 @@
         <v>43979</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18141,7 +18141,7 @@
         <v>43979</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18198,7 +18198,7 @@
         <v>43984</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18260,7 +18260,7 @@
         <v>43984</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18317,7 +18317,7 @@
         <v>43987</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18374,7 +18374,7 @@
         <v>43990</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18431,7 +18431,7 @@
         <v>43994</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18493,7 +18493,7 @@
         <v>43997</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18550,7 +18550,7 @@
         <v>43999</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18607,7 +18607,7 @@
         <v>44000</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18669,7 +18669,7 @@
         <v>44006</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18726,7 +18726,7 @@
         <v>44006</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18783,7 +18783,7 @@
         <v>44007</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18840,7 +18840,7 @@
         <v>44007</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18897,7 +18897,7 @@
         <v>44011</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18954,7 +18954,7 @@
         <v>44012</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19016,7 +19016,7 @@
         <v>44020</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19078,7 +19078,7 @@
         <v>44020</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19135,7 +19135,7 @@
         <v>44020</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19197,7 +19197,7 @@
         <v>44026</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19259,7 +19259,7 @@
         <v>44035</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19316,7 +19316,7 @@
         <v>44049</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19373,7 +19373,7 @@
         <v>44063</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19435,7 +19435,7 @@
         <v>44067</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19497,7 +19497,7 @@
         <v>44067</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19559,7 +19559,7 @@
         <v>44068</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19621,7 +19621,7 @@
         <v>44069</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19678,7 +19678,7 @@
         <v>44070</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19735,7 +19735,7 @@
         <v>44074</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19792,7 +19792,7 @@
         <v>44075</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19849,7 +19849,7 @@
         <v>44078</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19906,7 +19906,7 @@
         <v>44083</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19963,7 +19963,7 @@
         <v>44083</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20020,7 +20020,7 @@
         <v>44087</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20077,7 +20077,7 @@
         <v>44088</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20139,7 +20139,7 @@
         <v>44088</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20196,7 +20196,7 @@
         <v>44088</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20258,7 +20258,7 @@
         <v>44092</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20315,7 +20315,7 @@
         <v>44092</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20372,7 +20372,7 @@
         <v>44092</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20429,7 +20429,7 @@
         <v>44095</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20486,7 +20486,7 @@
         <v>44099</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20543,7 +20543,7 @@
         <v>44099</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20600,7 +20600,7 @@
         <v>44099</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20657,7 +20657,7 @@
         <v>44099</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20714,7 +20714,7 @@
         <v>44103</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20771,7 +20771,7 @@
         <v>44103</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20828,7 +20828,7 @@
         <v>44106</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20885,7 +20885,7 @@
         <v>44111</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20947,7 +20947,7 @@
         <v>44111</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21009,7 +21009,7 @@
         <v>44123</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21066,7 +21066,7 @@
         <v>44127</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21123,7 +21123,7 @@
         <v>44132</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21180,7 +21180,7 @@
         <v>44139</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21237,7 +21237,7 @@
         <v>44141</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21294,7 +21294,7 @@
         <v>44141</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21351,7 +21351,7 @@
         <v>44155</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21408,7 +21408,7 @@
         <v>44162</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21470,7 +21470,7 @@
         <v>44166</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21532,7 +21532,7 @@
         <v>44172</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21589,7 +21589,7 @@
         <v>44180</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21646,7 +21646,7 @@
         <v>44186</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21703,7 +21703,7 @@
         <v>44209</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21760,7 +21760,7 @@
         <v>44211</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21817,7 +21817,7 @@
         <v>44211</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21874,7 +21874,7 @@
         <v>44211</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21931,7 +21931,7 @@
         <v>44215</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21993,7 +21993,7 @@
         <v>44221</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22055,7 +22055,7 @@
         <v>44237</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22117,7 +22117,7 @@
         <v>44238</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22174,7 +22174,7 @@
         <v>44256</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22231,7 +22231,7 @@
         <v>44257</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22288,7 +22288,7 @@
         <v>44258</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22345,7 +22345,7 @@
         <v>44280</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22407,7 +22407,7 @@
         <v>44281</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22464,7 +22464,7 @@
         <v>44281</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22521,7 +22521,7 @@
         <v>44281</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22578,7 +22578,7 @@
         <v>44285</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22640,7 +22640,7 @@
         <v>44286</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22697,7 +22697,7 @@
         <v>44292</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22754,7 +22754,7 @@
         <v>44294</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22816,7 +22816,7 @@
         <v>44309</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22873,7 +22873,7 @@
         <v>44320</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22930,7 +22930,7 @@
         <v>44321</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22987,7 +22987,7 @@
         <v>44321</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23044,7 +23044,7 @@
         <v>44326</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23101,7 +23101,7 @@
         <v>44326</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23163,7 +23163,7 @@
         <v>44334</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23220,7 +23220,7 @@
         <v>44339</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23277,7 +23277,7 @@
         <v>44339</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23334,7 +23334,7 @@
         <v>44339</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23391,7 +23391,7 @@
         <v>44343</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23453,7 +23453,7 @@
         <v>44342</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23515,7 +23515,7 @@
         <v>44344</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23572,7 +23572,7 @@
         <v>44350</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23629,7 +23629,7 @@
         <v>44350</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23686,7 +23686,7 @@
         <v>44351</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23748,7 +23748,7 @@
         <v>44354</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23810,7 +23810,7 @@
         <v>44355</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23872,7 +23872,7 @@
         <v>44355</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23934,7 +23934,7 @@
         <v>44357</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23991,7 +23991,7 @@
         <v>44358</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24053,7 +24053,7 @@
         <v>44361</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24110,7 +24110,7 @@
         <v>44361</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24167,7 +24167,7 @@
         <v>44361</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24224,7 +24224,7 @@
         <v>44362</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24286,7 +24286,7 @@
         <v>44361</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24348,7 +24348,7 @@
         <v>44362</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24405,7 +24405,7 @@
         <v>44368</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24467,7 +24467,7 @@
         <v>44368</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24529,7 +24529,7 @@
         <v>44368</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24591,7 +24591,7 @@
         <v>44369</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24653,7 +24653,7 @@
         <v>44370</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24715,7 +24715,7 @@
         <v>44370</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24777,7 +24777,7 @@
         <v>44370</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24839,7 +24839,7 @@
         <v>44370</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24901,7 +24901,7 @@
         <v>44371</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24963,7 +24963,7 @@
         <v>44372</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25025,7 +25025,7 @@
         <v>44372</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25087,7 +25087,7 @@
         <v>44375</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25149,7 +25149,7 @@
         <v>44376</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25211,7 +25211,7 @@
         <v>44376</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25273,7 +25273,7 @@
         <v>44376</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25330,7 +25330,7 @@
         <v>44377</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25392,7 +25392,7 @@
         <v>44378</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25449,7 +25449,7 @@
         <v>44378</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25511,7 +25511,7 @@
         <v>44378</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25568,7 +25568,7 @@
         <v>44383</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25625,7 +25625,7 @@
         <v>44383</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25682,7 +25682,7 @@
         <v>44383</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25739,7 +25739,7 @@
         <v>44383</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25796,7 +25796,7 @@
         <v>44383</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25853,7 +25853,7 @@
         <v>44384</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25915,7 +25915,7 @@
         <v>44383</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25972,7 +25972,7 @@
         <v>44386</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26029,7 +26029,7 @@
         <v>44398</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26086,7 +26086,7 @@
         <v>44404</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26143,7 +26143,7 @@
         <v>44405</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26205,7 +26205,7 @@
         <v>44418</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26267,7 +26267,7 @@
         <v>44421</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26329,7 +26329,7 @@
         <v>44428</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26386,7 +26386,7 @@
         <v>44432</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26443,7 +26443,7 @@
         <v>44432</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26500,7 +26500,7 @@
         <v>44433</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26562,7 +26562,7 @@
         <v>44433</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26624,7 +26624,7 @@
         <v>44438</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26686,7 +26686,7 @@
         <v>44439</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26748,7 +26748,7 @@
         <v>44440</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26805,7 +26805,7 @@
         <v>44441</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26867,7 +26867,7 @@
         <v>44440</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26929,7 +26929,7 @@
         <v>44446</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26986,7 +26986,7 @@
         <v>44447</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27048,7 +27048,7 @@
         <v>44453</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27105,7 +27105,7 @@
         <v>44454</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27162,7 +27162,7 @@
         <v>44454</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27219,7 +27219,7 @@
         <v>44459</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27276,7 +27276,7 @@
         <v>44463</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27338,7 +27338,7 @@
         <v>44463</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27400,7 +27400,7 @@
         <v>44463</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27457,7 +27457,7 @@
         <v>44468</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27514,7 +27514,7 @@
         <v>44468</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27571,7 +27571,7 @@
         <v>44476</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27628,7 +27628,7 @@
         <v>44480</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27685,7 +27685,7 @@
         <v>44481</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27742,7 +27742,7 @@
         <v>44484</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27799,7 +27799,7 @@
         <v>44487</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27861,7 +27861,7 @@
         <v>44490</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27918,7 +27918,7 @@
         <v>44489</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27980,7 +27980,7 @@
         <v>44496</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28037,7 +28037,7 @@
         <v>44497</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28099,7 +28099,7 @@
         <v>44497</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28156,7 +28156,7 @@
         <v>44497</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28213,7 +28213,7 @@
         <v>44498</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28270,7 +28270,7 @@
         <v>44498</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28327,7 +28327,7 @@
         <v>44499</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28384,7 +28384,7 @@
         <v>44502</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28441,7 +28441,7 @@
         <v>44516</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28498,7 +28498,7 @@
         <v>44522</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28555,7 +28555,7 @@
         <v>44523</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28612,7 +28612,7 @@
         <v>44525</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28674,7 +28674,7 @@
         <v>44525</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28731,7 +28731,7 @@
         <v>44529</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28788,7 +28788,7 @@
         <v>44530</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28850,7 +28850,7 @@
         <v>44530</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28912,7 +28912,7 @@
         <v>44531</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28969,7 +28969,7 @@
         <v>44531</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29026,7 +29026,7 @@
         <v>44536</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29083,7 +29083,7 @@
         <v>44536</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29140,7 +29140,7 @@
         <v>44538</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29197,7 +29197,7 @@
         <v>44538</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29254,7 +29254,7 @@
         <v>44538</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29311,7 +29311,7 @@
         <v>44538</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29368,7 +29368,7 @@
         <v>44538</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29425,7 +29425,7 @@
         <v>44538</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29482,7 +29482,7 @@
         <v>44538</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29539,7 +29539,7 @@
         <v>44538</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29596,7 +29596,7 @@
         <v>44539</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29658,7 +29658,7 @@
         <v>44543</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29720,7 +29720,7 @@
         <v>44543</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29782,7 +29782,7 @@
         <v>44543</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29844,7 +29844,7 @@
         <v>44543</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29906,7 +29906,7 @@
         <v>44547</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29968,7 +29968,7 @@
         <v>44550</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30025,7 +30025,7 @@
         <v>44550</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30082,7 +30082,7 @@
         <v>44571</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30139,7 +30139,7 @@
         <v>44582</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30196,7 +30196,7 @@
         <v>44582</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30253,7 +30253,7 @@
         <v>44582</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30310,7 +30310,7 @@
         <v>44582</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30367,7 +30367,7 @@
         <v>44588</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30424,7 +30424,7 @@
         <v>44589</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30481,7 +30481,7 @@
         <v>44590</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30538,7 +30538,7 @@
         <v>44590</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30595,7 +30595,7 @@
         <v>44592</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30652,7 +30652,7 @@
         <v>44592</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30709,7 +30709,7 @@
         <v>44596</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30766,7 +30766,7 @@
         <v>44599</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30823,7 +30823,7 @@
         <v>44608</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30880,7 +30880,7 @@
         <v>44615</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30937,7 +30937,7 @@
         <v>44616</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30999,7 +30999,7 @@
         <v>44617</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31061,7 +31061,7 @@
         <v>44621</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31118,7 +31118,7 @@
         <v>44621</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31180,7 +31180,7 @@
         <v>44622</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31237,7 +31237,7 @@
         <v>44623</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31294,7 +31294,7 @@
         <v>44642</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31351,7 +31351,7 @@
         <v>44643</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31408,7 +31408,7 @@
         <v>44643</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31470,7 +31470,7 @@
         <v>44644</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31527,7 +31527,7 @@
         <v>44656</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31584,7 +31584,7 @@
         <v>44658</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31641,7 +31641,7 @@
         <v>44683</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31698,7 +31698,7 @@
         <v>44683</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31755,7 +31755,7 @@
         <v>44685</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31812,7 +31812,7 @@
         <v>44685</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31869,7 +31869,7 @@
         <v>44685</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31926,7 +31926,7 @@
         <v>44687</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31983,7 +31983,7 @@
         <v>44700</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32040,7 +32040,7 @@
         <v>44708</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32097,7 +32097,7 @@
         <v>44708</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32154,7 +32154,7 @@
         <v>44708</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32211,7 +32211,7 @@
         <v>44722</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32268,7 +32268,7 @@
         <v>44727</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32330,7 +32330,7 @@
         <v>44729</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32392,7 +32392,7 @@
         <v>44735</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32449,7 +32449,7 @@
         <v>44735</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32506,7 +32506,7 @@
         <v>44741</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32563,7 +32563,7 @@
         <v>44741</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32620,7 +32620,7 @@
         <v>44741</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32677,7 +32677,7 @@
         <v>44743</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32739,7 +32739,7 @@
         <v>44743</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32796,7 +32796,7 @@
         <v>44748</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32858,7 +32858,7 @@
         <v>44747</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32920,7 +32920,7 @@
         <v>44748</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32982,7 +32982,7 @@
         <v>44748</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33039,7 +33039,7 @@
         <v>44750</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33096,7 +33096,7 @@
         <v>44756</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33153,7 +33153,7 @@
         <v>44761</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33210,7 +33210,7 @@
         <v>44776</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33267,7 +33267,7 @@
         <v>44777</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33329,7 +33329,7 @@
         <v>44781</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33386,7 +33386,7 @@
         <v>44783</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33443,7 +33443,7 @@
         <v>44785</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33505,7 +33505,7 @@
         <v>44784</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33567,7 +33567,7 @@
         <v>44785</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33624,7 +33624,7 @@
         <v>44792</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33681,7 +33681,7 @@
         <v>44792</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33743,7 +33743,7 @@
         <v>44795</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33800,7 +33800,7 @@
         <v>44795</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33862,7 +33862,7 @@
         <v>44803</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33924,7 +33924,7 @@
         <v>44805</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33986,7 +33986,7 @@
         <v>44806</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34043,7 +34043,7 @@
         <v>44809</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34105,7 +34105,7 @@
         <v>44809</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34167,7 +34167,7 @@
         <v>44811</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34224,7 +34224,7 @@
         <v>44813</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34281,7 +34281,7 @@
         <v>44813</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34338,7 +34338,7 @@
         <v>44813</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34395,7 +34395,7 @@
         <v>44813</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34452,7 +34452,7 @@
         <v>44813</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34509,7 +34509,7 @@
         <v>44816</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34566,7 +34566,7 @@
         <v>44816</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34623,7 +34623,7 @@
         <v>44817</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34685,7 +34685,7 @@
         <v>44817</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34742,7 +34742,7 @@
         <v>44818</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34804,7 +34804,7 @@
         <v>44818</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34866,7 +34866,7 @@
         <v>44818</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34928,7 +34928,7 @@
         <v>44817</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34985,7 +34985,7 @@
         <v>44818</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35047,7 +35047,7 @@
         <v>44818</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35109,7 +35109,7 @@
         <v>44818</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35171,7 +35171,7 @@
         <v>44818</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35228,7 +35228,7 @@
         <v>44819</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35285,7 +35285,7 @@
         <v>44820</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35342,7 +35342,7 @@
         <v>44823</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35404,7 +35404,7 @@
         <v>44824</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35461,7 +35461,7 @@
         <v>44827</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35523,7 +35523,7 @@
         <v>44838</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35585,7 +35585,7 @@
         <v>44838</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35642,7 +35642,7 @@
         <v>44839</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35699,7 +35699,7 @@
         <v>44840</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35756,7 +35756,7 @@
         <v>44840</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35813,7 +35813,7 @@
         <v>44841</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35875,7 +35875,7 @@
         <v>44845</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35937,7 +35937,7 @@
         <v>44845</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35999,7 +35999,7 @@
         <v>44848</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36061,7 +36061,7 @@
         <v>44848</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36123,7 +36123,7 @@
         <v>44849</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36185,7 +36185,7 @@
         <v>44848</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36242,7 +36242,7 @@
         <v>44853</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36304,7 +36304,7 @@
         <v>44853</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36366,7 +36366,7 @@
         <v>44853</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36428,7 +36428,7 @@
         <v>44856</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36490,7 +36490,7 @@
         <v>44855</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36552,7 +36552,7 @@
         <v>44857</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36609,7 +36609,7 @@
         <v>44859</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36666,7 +36666,7 @@
         <v>44859</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36723,7 +36723,7 @@
         <v>44861</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36785,7 +36785,7 @@
         <v>44861</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36842,7 +36842,7 @@
         <v>44861</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36904,7 +36904,7 @@
         <v>44861</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36961,7 +36961,7 @@
         <v>44861</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37023,7 +37023,7 @@
         <v>44861</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37085,7 +37085,7 @@
         <v>44861</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37142,7 +37142,7 @@
         <v>44862</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37204,7 +37204,7 @@
         <v>44866</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37266,7 +37266,7 @@
         <v>44867</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37328,7 +37328,7 @@
         <v>44867</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37390,7 +37390,7 @@
         <v>44867</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37447,7 +37447,7 @@
         <v>44868</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37504,7 +37504,7 @@
         <v>44873</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37566,7 +37566,7 @@
         <v>44874</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37623,7 +37623,7 @@
         <v>44874</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37685,7 +37685,7 @@
         <v>44875</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37742,7 +37742,7 @@
         <v>44879</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37799,7 +37799,7 @@
         <v>44879</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37856,7 +37856,7 @@
         <v>44879</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37913,7 +37913,7 @@
         <v>44879</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37970,7 +37970,7 @@
         <v>44883</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38032,7 +38032,7 @@
         <v>44886</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38089,7 +38089,7 @@
         <v>44888</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38146,7 +38146,7 @@
         <v>44888</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38203,7 +38203,7 @@
         <v>44889</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38265,7 +38265,7 @@
         <v>44889</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38327,7 +38327,7 @@
         <v>44890</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38384,7 +38384,7 @@
         <v>44890</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38441,7 +38441,7 @@
         <v>44890</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38503,7 +38503,7 @@
         <v>44893</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38565,7 +38565,7 @@
         <v>44895</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38627,7 +38627,7 @@
         <v>44897</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38684,7 +38684,7 @@
         <v>44901</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38741,7 +38741,7 @@
         <v>44904</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38798,7 +38798,7 @@
         <v>44907</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38855,7 +38855,7 @@
         <v>44907</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38912,7 +38912,7 @@
         <v>44909</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38974,7 +38974,7 @@
         <v>44910</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39031,7 +39031,7 @@
         <v>44910</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39088,7 +39088,7 @@
         <v>44911</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39150,7 +39150,7 @@
         <v>44911</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39212,7 +39212,7 @@
         <v>44911</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39269,7 +39269,7 @@
         <v>44916</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39326,7 +39326,7 @@
         <v>44917</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39388,7 +39388,7 @@
         <v>44929</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39445,7 +39445,7 @@
         <v>44929</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39502,7 +39502,7 @@
         <v>44941</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39559,7 +39559,7 @@
         <v>44942</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39616,7 +39616,7 @@
         <v>44942</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39673,7 +39673,7 @@
         <v>44942</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39730,7 +39730,7 @@
         <v>44942</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39787,7 +39787,7 @@
         <v>44944</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39844,7 +39844,7 @@
         <v>44950</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39901,7 +39901,7 @@
         <v>44951</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39958,7 +39958,7 @@
         <v>44960</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40015,7 +40015,7 @@
         <v>44963</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40072,7 +40072,7 @@
         <v>44965</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40129,7 +40129,7 @@
         <v>44965</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40186,7 +40186,7 @@
         <v>44966</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40243,7 +40243,7 @@
         <v>44966</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40300,7 +40300,7 @@
         <v>44971</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40362,7 +40362,7 @@
         <v>44971</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40419,7 +40419,7 @@
         <v>44972</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40476,7 +40476,7 @@
         <v>44973</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40533,7 +40533,7 @@
         <v>44973</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40590,7 +40590,7 @@
         <v>44973</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40647,7 +40647,7 @@
         <v>44977</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40704,7 +40704,7 @@
         <v>44981</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40761,7 +40761,7 @@
         <v>44984</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40818,7 +40818,7 @@
         <v>44985</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40875,7 +40875,7 @@
         <v>44985</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40932,7 +40932,7 @@
         <v>44985</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40989,7 +40989,7 @@
         <v>44991</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41046,7 +41046,7 @@
         <v>44991</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41103,7 +41103,7 @@
         <v>45006</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41160,7 +41160,7 @@
         <v>45006</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41217,7 +41217,7 @@
         <v>45013</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41274,7 +41274,7 @@
         <v>45015</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41336,7 +41336,7 @@
         <v>45015</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41398,7 +41398,7 @@
         <v>45015</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41455,7 +41455,7 @@
         <v>45021</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41512,7 +41512,7 @@
         <v>45021</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41569,7 +41569,7 @@
         <v>45028</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41626,7 +41626,7 @@
         <v>45029</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41683,7 +41683,7 @@
         <v>45030</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41740,7 +41740,7 @@
         <v>45036</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41797,7 +41797,7 @@
         <v>45036</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41854,7 +41854,7 @@
         <v>45036</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41911,7 +41911,7 @@
         <v>45035</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41973,7 +41973,7 @@
         <v>45036</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42030,7 +42030,7 @@
         <v>45035</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42087,7 +42087,7 @@
         <v>45043</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42144,7 +42144,7 @@
         <v>45043</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42201,7 +42201,7 @@
         <v>45043</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42258,7 +42258,7 @@
         <v>45044</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42320,7 +42320,7 @@
         <v>45048</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42377,7 +42377,7 @@
         <v>45050</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42434,7 +42434,7 @@
         <v>45055</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42491,7 +42491,7 @@
         <v>45057</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42548,7 +42548,7 @@
         <v>45056</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42605,7 +42605,7 @@
         <v>45062</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42667,7 +42667,7 @@
         <v>45062</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42729,7 +42729,7 @@
         <v>45064</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42791,7 +42791,7 @@
         <v>45066</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42853,7 +42853,7 @@
         <v>45068</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42915,7 +42915,7 @@
         <v>45070</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42977,7 +42977,7 @@
         <v>45072</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -43039,7 +43039,7 @@
         <v>45072</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43101,7 +43101,7 @@
         <v>45076</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43158,7 +43158,7 @@
         <v>45076</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43215,7 +43215,7 @@
         <v>45077</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43272,7 +43272,7 @@
         <v>45079</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43334,7 +43334,7 @@
         <v>45079</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43396,7 +43396,7 @@
         <v>45086</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43458,7 +43458,7 @@
         <v>45085</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43520,7 +43520,7 @@
         <v>45086</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43577,7 +43577,7 @@
         <v>45086</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43634,7 +43634,7 @@
         <v>45086</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43691,7 +43691,7 @@
         <v>45086</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43748,7 +43748,7 @@
         <v>45086</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43805,7 +43805,7 @@
         <v>45086</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43862,7 +43862,7 @@
         <v>45090</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43924,7 +43924,7 @@
         <v>45089</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43981,7 +43981,7 @@
         <v>45090</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -44038,7 +44038,7 @@
         <v>45090</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44095,7 +44095,7 @@
         <v>45090</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44152,7 +44152,7 @@
         <v>45090</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44209,7 +44209,7 @@
         <v>45090</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44266,7 +44266,7 @@
         <v>45091</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44323,7 +44323,7 @@
         <v>45091</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44380,7 +44380,7 @@
         <v>45091</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44437,7 +44437,7 @@
         <v>45091</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44494,7 +44494,7 @@
         <v>45093</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44556,7 +44556,7 @@
         <v>45094</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44618,7 +44618,7 @@
         <v>45096</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44675,7 +44675,7 @@
         <v>45096</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44732,7 +44732,7 @@
         <v>45096</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44794,7 +44794,7 @@
         <v>45098</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44851,7 +44851,7 @@
         <v>45098</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44913,7 +44913,7 @@
         <v>45098</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44975,7 +44975,7 @@
         <v>45098</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -45037,7 +45037,7 @@
         <v>45098</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -45094,7 +45094,7 @@
         <v>45098</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45151,7 +45151,7 @@
         <v>45098</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45213,7 +45213,7 @@
         <v>45098</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45275,7 +45275,7 @@
         <v>45098</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45332,7 +45332,7 @@
         <v>45098</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45394,7 +45394,7 @@
         <v>45098</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45451,7 +45451,7 @@
         <v>45098</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45508,7 +45508,7 @@
         <v>45098</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45565,7 +45565,7 @@
         <v>45098</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45622,7 +45622,7 @@
         <v>45099</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45684,7 +45684,7 @@
         <v>45100</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45746,7 +45746,7 @@
         <v>45100</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45808,7 +45808,7 @@
         <v>45100</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45870,7 +45870,7 @@
         <v>45100</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45927,7 +45927,7 @@
         <v>45103</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45989,7 +45989,7 @@
         <v>45104</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -46046,7 +46046,7 @@
         <v>45104</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -46103,7 +46103,7 @@
         <v>45104</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46160,7 +46160,7 @@
         <v>45104</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46217,7 +46217,7 @@
         <v>45104</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46274,7 +46274,7 @@
         <v>45106</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46331,7 +46331,7 @@
         <v>45106</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46388,7 +46388,7 @@
         <v>45106</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46445,7 +46445,7 @@
         <v>45106</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46502,7 +46502,7 @@
         <v>45106</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46559,7 +46559,7 @@
         <v>45106</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46616,7 +46616,7 @@
         <v>45107</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46673,7 +46673,7 @@
         <v>45107</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46730,7 +46730,7 @@
         <v>45107</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46787,7 +46787,7 @@
         <v>45107</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46844,7 +46844,7 @@
         <v>45110</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46901,7 +46901,7 @@
         <v>45110</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46958,7 +46958,7 @@
         <v>45110</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -47015,7 +47015,7 @@
         <v>45110</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -47072,7 +47072,7 @@
         <v>45111</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47129,7 +47129,7 @@
         <v>45114</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47186,7 +47186,7 @@
         <v>45114</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47243,7 +47243,7 @@
         <v>45118</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47305,7 +47305,7 @@
         <v>45118</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47367,7 +47367,7 @@
         <v>45118</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47429,7 +47429,7 @@
         <v>45118</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47491,7 +47491,7 @@
         <v>45118</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47553,7 +47553,7 @@
         <v>45118</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47615,7 +47615,7 @@
         <v>45119</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47677,7 +47677,7 @@
         <v>45119</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47734,7 +47734,7 @@
         <v>45120</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47791,7 +47791,7 @@
         <v>45120</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47848,7 +47848,7 @@
         <v>45120</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47905,7 +47905,7 @@
         <v>45120</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47962,7 +47962,7 @@
         <v>45125</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -48019,7 +48019,7 @@
         <v>45125</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -48076,7 +48076,7 @@
         <v>45125</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -48133,7 +48133,7 @@
         <v>45129</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48190,7 +48190,7 @@
         <v>45129</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48247,7 +48247,7 @@
         <v>45135</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48304,7 +48304,7 @@
         <v>45135</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48361,7 +48361,7 @@
         <v>45138</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48418,7 +48418,7 @@
         <v>45138</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48475,7 +48475,7 @@
         <v>45139</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48532,7 +48532,7 @@
         <v>45139</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48589,7 +48589,7 @@
         <v>45139</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48646,7 +48646,7 @@
         <v>45140</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48708,7 +48708,7 @@
         <v>45140</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48765,7 +48765,7 @@
         <v>45140</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48827,7 +48827,7 @@
         <v>45141</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48884,7 +48884,7 @@
         <v>45145</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48941,7 +48941,7 @@
         <v>45152</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -49003,7 +49003,7 @@
         <v>45152</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -49065,7 +49065,7 @@
         <v>45156</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -49122,7 +49122,7 @@
         <v>45159</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49179,7 +49179,7 @@
         <v>45159</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49236,7 +49236,7 @@
         <v>45160</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49298,7 +49298,7 @@
         <v>45160</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49360,7 +49360,7 @@
         <v>45160</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49417,7 +49417,7 @@
         <v>45162</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49474,7 +49474,7 @@
         <v>45162</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49531,7 +49531,7 @@
         <v>45163</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49588,7 +49588,7 @@
         <v>45167</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49650,7 +49650,7 @@
         <v>45167</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49712,7 +49712,7 @@
         <v>45167</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49769,7 +49769,7 @@
         <v>45167</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49831,7 +49831,7 @@
         <v>45168</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49893,7 +49893,7 @@
         <v>45167</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49950,7 +49950,7 @@
         <v>45168</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -50012,7 +50012,7 @@
         <v>45168</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -50074,7 +50074,7 @@
         <v>45170</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -50131,7 +50131,7 @@
         <v>45170</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -50188,7 +50188,7 @@
         <v>45175</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -50245,7 +50245,7 @@
         <v>45176</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50307,7 +50307,7 @@
         <v>45176</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50369,7 +50369,7 @@
         <v>45176</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50426,7 +50426,7 @@
         <v>45177</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50483,7 +50483,7 @@
         <v>45177</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50540,7 +50540,7 @@
         <v>45177</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50597,7 +50597,7 @@
         <v>45180</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50654,7 +50654,7 @@
         <v>45181</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50716,7 +50716,7 @@
         <v>45181</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50778,7 +50778,7 @@
         <v>45181</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50835,7 +50835,7 @@
         <v>45181</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50892,7 +50892,7 @@
         <v>45182</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50949,7 +50949,7 @@
         <v>45183</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -51006,7 +51006,7 @@
         <v>45184</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -51068,7 +51068,7 @@
         <v>45187</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -51125,7 +51125,7 @@
         <v>45187</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -51182,7 +51182,7 @@
         <v>45187</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -51239,7 +51239,7 @@
         <v>45187</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -51296,7 +51296,7 @@
         <v>45187</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -51353,7 +51353,7 @@
         <v>45187</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -51410,7 +51410,7 @@
         <v>45187</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -51467,7 +51467,7 @@
         <v>45188</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51529,7 +51529,7 @@
         <v>45188</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51591,7 +51591,7 @@
         <v>45188</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51653,7 +51653,7 @@
         <v>45188</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51715,7 +51715,7 @@
         <v>45188</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51777,7 +51777,7 @@
         <v>45188</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51839,7 +51839,7 @@
         <v>45188</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51901,7 +51901,7 @@
         <v>45188</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51958,7 +51958,7 @@
         <v>45189</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -52020,7 +52020,7 @@
         <v>45190</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -52077,7 +52077,7 @@
         <v>45190</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -52134,7 +52134,7 @@
         <v>45190</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -52191,7 +52191,7 @@
         <v>45190</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -52248,7 +52248,7 @@
         <v>45196</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -52305,7 +52305,7 @@
         <v>45197</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -52362,7 +52362,7 @@
         <v>45197</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -52419,7 +52419,7 @@
         <v>45198</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -52481,7 +52481,7 @@
         <v>45201</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -52543,7 +52543,7 @@
         <v>45201</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52605,7 +52605,7 @@
         <v>45202</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52667,7 +52667,7 @@
         <v>45202</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52724,7 +52724,7 @@
         <v>45203</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52781,7 +52781,7 @@
         <v>45204</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52843,7 +52843,7 @@
         <v>45208</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52900,7 +52900,7 @@
         <v>45209</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52957,7 +52957,7 @@
         <v>45208</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -53019,7 +53019,7 @@
         <v>45211</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -53076,7 +53076,7 @@
         <v>45211</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -53133,7 +53133,7 @@
         <v>45211</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -53190,7 +53190,7 @@
         <v>45211</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -53252,7 +53252,7 @@
         <v>45211</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -53314,7 +53314,7 @@
         <v>45211</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -53371,7 +53371,7 @@
         <v>45212</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -53428,7 +53428,7 @@
         <v>45213</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -53485,7 +53485,7 @@
         <v>45215</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -53542,7 +53542,7 @@
         <v>45215</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53599,7 +53599,7 @@
         <v>45216</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53656,7 +53656,7 @@
         <v>45216</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53718,7 +53718,7 @@
         <v>45218</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -53775,7 +53775,7 @@
         <v>45218</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -53837,7 +53837,7 @@
         <v>45218</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -53894,7 +53894,7 @@
         <v>45218</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -53951,7 +53951,7 @@
         <v>45219</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -54008,7 +54008,7 @@
         <v>45219</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -54065,7 +54065,7 @@
         <v>45219</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -54127,7 +54127,7 @@
         <v>45219</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -54189,7 +54189,7 @@
         <v>45219</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -54246,7 +54246,7 @@
         <v>45219</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -54303,7 +54303,7 @@
         <v>45222</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -54360,7 +54360,7 @@
         <v>45222</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -54422,7 +54422,7 @@
         <v>45222</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -54479,7 +54479,7 @@
         <v>45225</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -54536,7 +54536,7 @@
         <v>45225</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -54593,7 +54593,7 @@
         <v>45230</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -54655,7 +54655,7 @@
         <v>45230</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -54712,7 +54712,7 @@
         <v>45230</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -54769,7 +54769,7 @@
         <v>45230</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -54826,7 +54826,7 @@
         <v>45232</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -54888,7 +54888,7 @@
         <v>45232</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -54950,7 +54950,7 @@
         <v>45232</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -55012,7 +55012,7 @@
         <v>45236</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -55074,7 +55074,7 @@
         <v>45236</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -55131,7 +55131,7 @@
         <v>45237</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -55188,7 +55188,7 @@
         <v>45237</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -55245,7 +55245,7 @@
         <v>45237</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -55302,7 +55302,7 @@
         <v>45237</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -55359,7 +55359,7 @@
         <v>45237</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -55421,7 +55421,7 @@
         <v>45237</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -55478,7 +55478,7 @@
         <v>45237</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -55535,7 +55535,7 @@
         <v>45238</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -55592,7 +55592,7 @@
         <v>45239</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -55649,7 +55649,7 @@
         <v>45239</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -55711,7 +55711,7 @@
         <v>45239</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -55768,7 +55768,7 @@
         <v>45239</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -55825,7 +55825,7 @@
         <v>45240</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -55882,7 +55882,7 @@
         <v>45240</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -55939,7 +55939,7 @@
         <v>45243</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -56001,7 +56001,7 @@
         <v>45243</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -56063,7 +56063,7 @@
         <v>45244</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -56120,7 +56120,7 @@
         <v>45244</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -56177,7 +56177,7 @@
         <v>45244</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -56234,7 +56234,7 @@
         <v>45244</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -56291,7 +56291,7 @@
         <v>45244</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -56348,7 +56348,7 @@
         <v>45244</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -56405,7 +56405,7 @@
         <v>45244</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -56462,7 +56462,7 @@
         <v>45244</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -56519,7 +56519,7 @@
         <v>45244</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -56576,7 +56576,7 @@
         <v>45245</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -56633,7 +56633,7 @@
         <v>45245</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -56690,7 +56690,7 @@
         <v>45245</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -56747,7 +56747,7 @@
         <v>45246</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -56804,7 +56804,7 @@
         <v>45246</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -56861,7 +56861,7 @@
         <v>45247</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -56918,7 +56918,7 @@
         <v>45251</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -56975,7 +56975,7 @@
         <v>45252</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -57032,7 +57032,7 @@
         <v>45252</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -57089,7 +57089,7 @@
         <v>45253</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -57146,7 +57146,7 @@
         <v>45254</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -57203,7 +57203,7 @@
         <v>45254</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -57260,7 +57260,7 @@
         <v>45257</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -57317,7 +57317,7 @@
         <v>45257</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -57374,7 +57374,7 @@
         <v>45258</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -57431,7 +57431,7 @@
         <v>45259</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -57488,7 +57488,7 @@
         <v>45259</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -57545,7 +57545,7 @@
         <v>45260</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -57602,7 +57602,7 @@
         <v>45260</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -57659,7 +57659,7 @@
         <v>45260</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -57716,7 +57716,7 @@
         <v>45260</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -57773,7 +57773,7 @@
         <v>45261</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -57830,7 +57830,7 @@
         <v>45261</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -57887,7 +57887,7 @@
         <v>45262</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -57944,7 +57944,7 @@
         <v>45264</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -58001,7 +58001,7 @@
         <v>45264</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -58058,7 +58058,7 @@
         <v>45264</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -58115,7 +58115,7 @@
         <v>45264</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -58177,7 +58177,7 @@
         <v>45264</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -58234,7 +58234,7 @@
         <v>45265</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -58291,7 +58291,7 @@
         <v>45265</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -58348,7 +58348,7 @@
         <v>45266</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -58405,7 +58405,7 @@
         <v>45266</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -58462,7 +58462,7 @@
         <v>45266</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -58519,7 +58519,7 @@
         <v>45267</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -58576,7 +58576,7 @@
         <v>45271</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -58633,7 +58633,7 @@
         <v>45271</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -58690,7 +58690,7 @@
         <v>45273</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -58747,7 +58747,7 @@
         <v>45273</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -58804,7 +58804,7 @@
         <v>45273</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -58861,7 +58861,7 @@
         <v>45273</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -58918,7 +58918,7 @@
         <v>45273</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -58975,7 +58975,7 @@
         <v>45273</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -59032,7 +59032,7 @@
         <v>45273</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -59089,7 +59089,7 @@
         <v>45278</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -59146,7 +59146,7 @@
         <v>45279</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -59203,7 +59203,7 @@
         <v>45279</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -59260,7 +59260,7 @@
         <v>45279</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -59317,7 +59317,7 @@
         <v>45281</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -59374,7 +59374,7 @@
         <v>45282</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -59436,7 +59436,7 @@
         <v>45285</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -59493,7 +59493,7 @@
         <v>45285</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -59550,7 +59550,7 @@
         <v>45285</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -59607,7 +59607,7 @@
         <v>45285</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -59664,7 +59664,7 @@
         <v>45287</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -59721,7 +59721,7 @@
         <v>45287</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -59778,7 +59778,7 @@
         <v>45289</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -59835,7 +59835,7 @@
         <v>45299</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -59892,7 +59892,7 @@
         <v>45308</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -59949,7 +59949,7 @@
         <v>45308</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -60006,7 +60006,7 @@
         <v>45309</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -60063,7 +60063,7 @@
         <v>45310</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -60120,7 +60120,7 @@
         <v>45310</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -60177,7 +60177,7 @@
         <v>45311</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -60234,7 +60234,7 @@
         <v>45311</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -60284,14 +60284,14 @@
     <row r="990" ht="15" customHeight="1">
       <c r="A990" t="inlineStr">
         <is>
-          <t>A 2453-2024</t>
+          <t>A 2452-2024</t>
         </is>
       </c>
       <c r="B990" s="1" t="n">
         <v>45312</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -60304,7 +60304,7 @@
         </is>
       </c>
       <c r="G990" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="H990" t="n">
         <v>0</v>
@@ -60341,14 +60341,14 @@
     <row r="991" ht="15" customHeight="1">
       <c r="A991" t="inlineStr">
         <is>
-          <t>A 2452-2024</t>
+          <t>A 2453-2024</t>
         </is>
       </c>
       <c r="B991" s="1" t="n">
         <v>45312</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -60361,7 +60361,7 @@
         </is>
       </c>
       <c r="G991" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="H991" t="n">
         <v>0</v>
@@ -60405,7 +60405,7 @@
         <v>45313</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -60455,14 +60455,14 @@
     <row r="993" ht="15" customHeight="1">
       <c r="A993" t="inlineStr">
         <is>
-          <t>A 2847-2024</t>
+          <t>A 2842-2024</t>
         </is>
       </c>
       <c r="B993" s="1" t="n">
         <v>45315</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -60475,7 +60475,7 @@
         </is>
       </c>
       <c r="G993" t="n">
-        <v>3.5</v>
+        <v>1.2</v>
       </c>
       <c r="H993" t="n">
         <v>0</v>
@@ -60512,14 +60512,14 @@
     <row r="994" ht="15" customHeight="1">
       <c r="A994" t="inlineStr">
         <is>
-          <t>A 2842-2024</t>
+          <t>A 2847-2024</t>
         </is>
       </c>
       <c r="B994" s="1" t="n">
         <v>45315</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -60532,7 +60532,7 @@
         </is>
       </c>
       <c r="G994" t="n">
-        <v>1.2</v>
+        <v>3.5</v>
       </c>
       <c r="H994" t="n">
         <v>0</v>
@@ -60576,7 +60576,7 @@
         <v>45315</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -60626,14 +60626,14 @@
     <row r="996" ht="15" customHeight="1">
       <c r="A996" t="inlineStr">
         <is>
-          <t>A 3218-2024</t>
+          <t>A 3220-2024</t>
         </is>
       </c>
       <c r="B996" s="1" t="n">
         <v>45316</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -60646,7 +60646,7 @@
         </is>
       </c>
       <c r="G996" t="n">
-        <v>2.1</v>
+        <v>0.4</v>
       </c>
       <c r="H996" t="n">
         <v>0</v>
@@ -60690,7 +60690,7 @@
         <v>45316</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -60740,14 +60740,14 @@
     <row r="998" ht="15" customHeight="1">
       <c r="A998" t="inlineStr">
         <is>
-          <t>A 3220-2024</t>
+          <t>A 3218-2024</t>
         </is>
       </c>
       <c r="B998" s="1" t="n">
         <v>45316</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -60760,7 +60760,7 @@
         </is>
       </c>
       <c r="G998" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
       <c r="H998" t="n">
         <v>0</v>
@@ -60804,7 +60804,7 @@
         <v>45320</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -60861,7 +60861,7 @@
         <v>45320</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -60911,14 +60911,14 @@
     <row r="1001" ht="15" customHeight="1">
       <c r="A1001" t="inlineStr">
         <is>
-          <t>A 4049-2024</t>
+          <t>A 4046-2024</t>
         </is>
       </c>
       <c r="B1001" s="1" t="n">
         <v>45323</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -60931,7 +60931,7 @@
         </is>
       </c>
       <c r="G1001" t="n">
-        <v>2.8</v>
+        <v>11</v>
       </c>
       <c r="H1001" t="n">
         <v>0</v>
@@ -60975,7 +60975,7 @@
         <v>45323</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -61030,14 +61030,14 @@
     <row r="1003" ht="15" customHeight="1">
       <c r="A1003" t="inlineStr">
         <is>
-          <t>A 4046-2024</t>
+          <t>A 4049-2024</t>
         </is>
       </c>
       <c r="B1003" s="1" t="n">
         <v>45323</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -61050,7 +61050,7 @@
         </is>
       </c>
       <c r="G1003" t="n">
-        <v>11</v>
+        <v>2.8</v>
       </c>
       <c r="H1003" t="n">
         <v>0</v>
@@ -61094,7 +61094,7 @@
         <v>45323</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -61156,7 +61156,7 @@
         <v>45323</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -61218,7 +61218,7 @@
         <v>45324</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -61273,14 +61273,14 @@
     <row r="1007" ht="15" customHeight="1">
       <c r="A1007" t="inlineStr">
         <is>
-          <t>A 4245-2024</t>
+          <t>A 4232-2024</t>
         </is>
       </c>
       <c r="B1007" s="1" t="n">
         <v>45324</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -61292,8 +61292,13 @@
           <t>PITEÅ</t>
         </is>
       </c>
+      <c r="F1007" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="G1007" t="n">
-        <v>7.2</v>
+        <v>11.1</v>
       </c>
       <c r="H1007" t="n">
         <v>0</v>
@@ -61330,14 +61335,14 @@
     <row r="1008" ht="15" customHeight="1">
       <c r="A1008" t="inlineStr">
         <is>
-          <t>A 4232-2024</t>
+          <t>A 4245-2024</t>
         </is>
       </c>
       <c r="B1008" s="1" t="n">
         <v>45324</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -61349,13 +61354,8 @@
           <t>PITEÅ</t>
         </is>
       </c>
-      <c r="F1008" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="G1008" t="n">
-        <v>11.1</v>
+        <v>7.2</v>
       </c>
       <c r="H1008" t="n">
         <v>0</v>
@@ -61399,7 +61399,7 @@
         <v>45329</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -61456,7 +61456,7 @@
         <v>45330</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -61513,7 +61513,7 @@
         <v>45334</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -61570,7 +61570,7 @@
         <v>45335</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>

--- a/Översikt PITEÅ.xlsx
+++ b/Översikt PITEÅ.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z1012"/>
+  <dimension ref="A1:Z1015"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>44617</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -665,7 +665,7 @@
         <v>44839</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
         <v>44839</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>44459</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
         <v>44617</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>43896</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>45191</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>45203</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>44740</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>44280</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>44539</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>44550</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>45119</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>44014</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>44522</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>44526</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         <v>44553</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>44810</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>44917</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>45103</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>45106</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         <v>43802</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>43902</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2727,7 +2727,7 @@
         <v>43908</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         <v>44053</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2908,7 +2908,7 @@
         <v>44193</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>44298</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>44840</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
         <v>44852</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3262,7 +3262,7 @@
         <v>44859</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>44944</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3434,7 +3434,7 @@
         <v>45120</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
         <v>45187</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         <v>45209</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3701,7 +3701,7 @@
         <v>45219</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>45243</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         <v>45293</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
         <v>45296</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>43714</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         <v>44014</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4225,7 +4225,7 @@
         <v>44106</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4310,7 +4310,7 @@
         <v>44309</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>44342</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4485,7 +4485,7 @@
         <v>44495</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
         <v>44525</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4665,7 +4665,7 @@
         <v>44525</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4755,7 +4755,7 @@
         <v>44538</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4840,7 +4840,7 @@
         <v>44727</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4929,7 +4929,7 @@
         <v>44804</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5014,7 +5014,7 @@
         <v>44917</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5104,7 +5104,7 @@
         <v>45049</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5193,7 +5193,7 @@
         <v>45098</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>45103</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5373,7 +5373,7 @@
         <v>45148</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
         <v>45175</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         <v>45181</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5642,7 +5642,7 @@
         <v>45188</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5732,7 +5732,7 @@
         <v>45224</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5817,7 +5817,7 @@
         <v>45243</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5907,7 +5907,7 @@
         <v>45265</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5992,7 +5992,7 @@
         <v>45323</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
         <v>43325</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6139,7 +6139,7 @@
         <v>43332</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6196,7 +6196,7 @@
         <v>43336</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6253,7 +6253,7 @@
         <v>43339</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         <v>43339</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
         <v>43341</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6424,7 +6424,7 @@
         <v>43355</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>43355</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         <v>43374</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6600,7 +6600,7 @@
         <v>43374</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6662,7 +6662,7 @@
         <v>43375</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6719,7 +6719,7 @@
         <v>43376</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
         <v>43376</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6833,7 +6833,7 @@
         <v>43381</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6890,7 +6890,7 @@
         <v>43383</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6947,7 +6947,7 @@
         <v>43391</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>43391</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7061,7 +7061,7 @@
         <v>43392</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7118,7 +7118,7 @@
         <v>43392</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7175,7 +7175,7 @@
         <v>43398</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7232,7 +7232,7 @@
         <v>43402</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7289,7 +7289,7 @@
         <v>43404</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7346,7 +7346,7 @@
         <v>43406</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7403,7 +7403,7 @@
         <v>43406</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
         <v>43406</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>43406</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>43406</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>43416</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>43418</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7745,7 +7745,7 @@
         <v>43418</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7802,7 +7802,7 @@
         <v>43418</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         <v>43419</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7916,7 +7916,7 @@
         <v>43420</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         <v>43424</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8035,7 +8035,7 @@
         <v>43427</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8097,7 +8097,7 @@
         <v>43427</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8154,7 +8154,7 @@
         <v>43427</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8216,7 +8216,7 @@
         <v>43427</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8278,7 +8278,7 @@
         <v>43436</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
         <v>43438</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8392,7 +8392,7 @@
         <v>43438</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8449,7 +8449,7 @@
         <v>43438</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8506,7 +8506,7 @@
         <v>43438</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8563,7 +8563,7 @@
         <v>43451</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8625,7 +8625,7 @@
         <v>43472</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8682,7 +8682,7 @@
         <v>43475</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8739,7 +8739,7 @@
         <v>43479</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8796,7 +8796,7 @@
         <v>43479</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8853,7 +8853,7 @@
         <v>43486</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
         <v>43489</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8967,7 +8967,7 @@
         <v>43489</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9024,7 +9024,7 @@
         <v>43489</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9081,7 +9081,7 @@
         <v>43489</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9138,7 +9138,7 @@
         <v>43489</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9195,7 +9195,7 @@
         <v>43490</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9252,7 +9252,7 @@
         <v>43490</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9309,7 +9309,7 @@
         <v>43493</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9371,7 +9371,7 @@
         <v>43509</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9428,7 +9428,7 @@
         <v>43510</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9485,7 +9485,7 @@
         <v>43510</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9542,7 +9542,7 @@
         <v>43514</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9599,7 +9599,7 @@
         <v>43514</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9656,7 +9656,7 @@
         <v>43514</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9713,7 +9713,7 @@
         <v>43516</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9775,7 +9775,7 @@
         <v>43518</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9832,7 +9832,7 @@
         <v>43521</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9894,7 +9894,7 @@
         <v>43521</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9956,7 +9956,7 @@
         <v>43521</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10018,7 +10018,7 @@
         <v>43521</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10080,7 +10080,7 @@
         <v>43521</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10142,7 +10142,7 @@
         <v>43522</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10199,7 +10199,7 @@
         <v>43523</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10256,7 +10256,7 @@
         <v>43523</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10313,7 +10313,7 @@
         <v>43523</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10370,7 +10370,7 @@
         <v>43532</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10427,7 +10427,7 @@
         <v>43532</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10484,7 +10484,7 @@
         <v>43542</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10541,7 +10541,7 @@
         <v>43544</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10603,7 +10603,7 @@
         <v>43544</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10665,7 +10665,7 @@
         <v>43554</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10722,7 +10722,7 @@
         <v>43556</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10779,7 +10779,7 @@
         <v>43557</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10841,7 +10841,7 @@
         <v>43557</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10898,7 +10898,7 @@
         <v>43557</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10955,7 +10955,7 @@
         <v>43557</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11012,7 +11012,7 @@
         <v>43557</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11074,7 +11074,7 @@
         <v>43564</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11131,7 +11131,7 @@
         <v>43564</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11188,7 +11188,7 @@
         <v>43567</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11245,7 +11245,7 @@
         <v>43570</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11302,7 +11302,7 @@
         <v>43570</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11359,7 +11359,7 @@
         <v>43570</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11416,7 +11416,7 @@
         <v>43584</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11473,7 +11473,7 @@
         <v>43605</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11530,7 +11530,7 @@
         <v>43608</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11587,7 +11587,7 @@
         <v>43614</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11649,7 +11649,7 @@
         <v>43616</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11711,7 +11711,7 @@
         <v>43616</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11773,7 +11773,7 @@
         <v>43629</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11830,7 +11830,7 @@
         <v>43629</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11892,7 +11892,7 @@
         <v>43633</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11949,7 +11949,7 @@
         <v>43633</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12006,7 +12006,7 @@
         <v>43640</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12063,7 +12063,7 @@
         <v>43640</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12120,7 +12120,7 @@
         <v>43647</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12177,7 +12177,7 @@
         <v>43647</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12234,7 +12234,7 @@
         <v>43650</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12291,7 +12291,7 @@
         <v>43652</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12353,7 +12353,7 @@
         <v>43677</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12410,7 +12410,7 @@
         <v>43678</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12467,7 +12467,7 @@
         <v>43682</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12524,7 +12524,7 @@
         <v>43691</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12586,7 +12586,7 @@
         <v>43691</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12648,7 +12648,7 @@
         <v>43696</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12710,7 +12710,7 @@
         <v>43697</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12767,7 +12767,7 @@
         <v>43698</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12829,7 +12829,7 @@
         <v>43698</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12891,7 +12891,7 @@
         <v>43706</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12948,7 +12948,7 @@
         <v>43707</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13010,7 +13010,7 @@
         <v>43711</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13067,7 +13067,7 @@
         <v>43713</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13124,7 +13124,7 @@
         <v>43718</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13181,7 +13181,7 @@
         <v>43718</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13238,7 +13238,7 @@
         <v>43718</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13300,7 +13300,7 @@
         <v>43720</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13357,7 +13357,7 @@
         <v>43721</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13414,7 +13414,7 @@
         <v>43732</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13471,7 +13471,7 @@
         <v>43741</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13533,7 +13533,7 @@
         <v>43741</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13590,7 +13590,7 @@
         <v>43752</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13652,7 +13652,7 @@
         <v>43755</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13709,7 +13709,7 @@
         <v>43755</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13766,7 +13766,7 @@
         <v>43755</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13823,7 +13823,7 @@
         <v>43755</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13880,7 +13880,7 @@
         <v>43760</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13942,7 +13942,7 @@
         <v>43760</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14004,7 +14004,7 @@
         <v>43760</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14061,7 +14061,7 @@
         <v>43762</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14123,7 +14123,7 @@
         <v>43766</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14180,7 +14180,7 @@
         <v>43766</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14237,7 +14237,7 @@
         <v>43768</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14294,7 +14294,7 @@
         <v>43770</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14356,7 +14356,7 @@
         <v>43775</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14418,7 +14418,7 @@
         <v>43775</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14480,7 +14480,7 @@
         <v>43777</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14537,7 +14537,7 @@
         <v>43780</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14594,7 +14594,7 @@
         <v>43780</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14651,7 +14651,7 @@
         <v>43780</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14708,7 +14708,7 @@
         <v>43782</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14770,7 +14770,7 @@
         <v>43789</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14832,7 +14832,7 @@
         <v>43798</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14889,7 +14889,7 @@
         <v>43801</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14951,7 +14951,7 @@
         <v>43802</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15008,7 +15008,7 @@
         <v>43802</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15065,7 +15065,7 @@
         <v>43802</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15122,7 +15122,7 @@
         <v>43802</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15179,7 +15179,7 @@
         <v>43802</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15236,7 +15236,7 @@
         <v>43802</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15293,7 +15293,7 @@
         <v>43807</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15350,7 +15350,7 @@
         <v>43809</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15407,7 +15407,7 @@
         <v>43817</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15464,7 +15464,7 @@
         <v>43817</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15526,7 +15526,7 @@
         <v>43822</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15583,7 +15583,7 @@
         <v>43822</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15640,7 +15640,7 @@
         <v>43833</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15697,7 +15697,7 @@
         <v>43846</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15754,7 +15754,7 @@
         <v>43852</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15811,7 +15811,7 @@
         <v>43853</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15868,7 +15868,7 @@
         <v>43854</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15925,7 +15925,7 @@
         <v>43859</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15987,7 +15987,7 @@
         <v>43859</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16044,7 +16044,7 @@
         <v>43859</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16101,7 +16101,7 @@
         <v>43859</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16158,7 +16158,7 @@
         <v>43859</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16215,7 +16215,7 @@
         <v>43860</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16272,7 +16272,7 @@
         <v>43868</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16329,7 +16329,7 @@
         <v>43868</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16386,7 +16386,7 @@
         <v>43874</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16448,7 +16448,7 @@
         <v>43878</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16505,7 +16505,7 @@
         <v>43880</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16562,7 +16562,7 @@
         <v>43880</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16619,7 +16619,7 @@
         <v>43889</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16676,7 +16676,7 @@
         <v>43895</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16738,7 +16738,7 @@
         <v>43896</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16795,7 +16795,7 @@
         <v>43902</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16852,7 +16852,7 @@
         <v>43902</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16914,7 +16914,7 @@
         <v>43907</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16971,7 +16971,7 @@
         <v>43913</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17028,7 +17028,7 @@
         <v>43914</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17090,7 +17090,7 @@
         <v>43927</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17152,7 +17152,7 @@
         <v>43929</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         <v>43929</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>43931</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17328,7 +17328,7 @@
         <v>43950</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17385,7 +17385,7 @@
         <v>43957</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17447,7 +17447,7 @@
         <v>43958</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17504,7 +17504,7 @@
         <v>43958</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17561,7 +17561,7 @@
         <v>43959</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17618,7 +17618,7 @@
         <v>43962</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17675,7 +17675,7 @@
         <v>43962</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17732,7 +17732,7 @@
         <v>43962</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17789,7 +17789,7 @@
         <v>43962</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17846,7 +17846,7 @@
         <v>43970</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17908,7 +17908,7 @@
         <v>43971</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17970,7 +17970,7 @@
         <v>43976</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18027,7 +18027,7 @@
         <v>43979</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18084,7 +18084,7 @@
         <v>43979</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18141,7 +18141,7 @@
         <v>43979</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18198,7 +18198,7 @@
         <v>43984</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18260,7 +18260,7 @@
         <v>43984</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18317,7 +18317,7 @@
         <v>43987</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18374,7 +18374,7 @@
         <v>43990</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18431,7 +18431,7 @@
         <v>43994</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18493,7 +18493,7 @@
         <v>43997</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18550,7 +18550,7 @@
         <v>43999</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18607,7 +18607,7 @@
         <v>44000</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18669,7 +18669,7 @@
         <v>44006</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18726,7 +18726,7 @@
         <v>44006</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18783,7 +18783,7 @@
         <v>44007</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18840,7 +18840,7 @@
         <v>44007</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18897,7 +18897,7 @@
         <v>44011</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18954,7 +18954,7 @@
         <v>44012</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19016,7 +19016,7 @@
         <v>44020</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19078,7 +19078,7 @@
         <v>44020</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19135,7 +19135,7 @@
         <v>44020</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19197,7 +19197,7 @@
         <v>44026</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19259,7 +19259,7 @@
         <v>44035</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19316,7 +19316,7 @@
         <v>44049</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19373,7 +19373,7 @@
         <v>44063</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19435,7 +19435,7 @@
         <v>44067</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19497,7 +19497,7 @@
         <v>44067</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19559,7 +19559,7 @@
         <v>44068</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19621,7 +19621,7 @@
         <v>44069</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19678,7 +19678,7 @@
         <v>44070</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19735,7 +19735,7 @@
         <v>44074</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19792,7 +19792,7 @@
         <v>44075</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19849,7 +19849,7 @@
         <v>44078</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19906,7 +19906,7 @@
         <v>44083</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19963,7 +19963,7 @@
         <v>44083</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20020,7 +20020,7 @@
         <v>44087</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20077,7 +20077,7 @@
         <v>44088</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20139,7 +20139,7 @@
         <v>44088</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20196,7 +20196,7 @@
         <v>44088</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20258,7 +20258,7 @@
         <v>44092</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20315,7 +20315,7 @@
         <v>44092</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20372,7 +20372,7 @@
         <v>44092</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20429,7 +20429,7 @@
         <v>44095</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20486,7 +20486,7 @@
         <v>44099</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20543,7 +20543,7 @@
         <v>44099</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20600,7 +20600,7 @@
         <v>44099</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20657,7 +20657,7 @@
         <v>44099</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20714,7 +20714,7 @@
         <v>44103</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20771,7 +20771,7 @@
         <v>44103</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20828,7 +20828,7 @@
         <v>44106</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20885,7 +20885,7 @@
         <v>44111</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20947,7 +20947,7 @@
         <v>44111</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21009,7 +21009,7 @@
         <v>44123</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21066,7 +21066,7 @@
         <v>44127</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21123,7 +21123,7 @@
         <v>44132</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21180,7 +21180,7 @@
         <v>44139</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21237,7 +21237,7 @@
         <v>44141</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21294,7 +21294,7 @@
         <v>44141</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21351,7 +21351,7 @@
         <v>44155</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21408,7 +21408,7 @@
         <v>44162</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21470,7 +21470,7 @@
         <v>44166</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21532,7 +21532,7 @@
         <v>44172</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21589,7 +21589,7 @@
         <v>44180</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21646,7 +21646,7 @@
         <v>44186</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21703,7 +21703,7 @@
         <v>44209</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21760,7 +21760,7 @@
         <v>44211</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21817,7 +21817,7 @@
         <v>44211</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21874,7 +21874,7 @@
         <v>44211</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21931,7 +21931,7 @@
         <v>44215</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21993,7 +21993,7 @@
         <v>44221</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22055,7 +22055,7 @@
         <v>44237</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22117,7 +22117,7 @@
         <v>44238</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22174,7 +22174,7 @@
         <v>44256</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22231,7 +22231,7 @@
         <v>44257</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22288,7 +22288,7 @@
         <v>44258</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22345,7 +22345,7 @@
         <v>44280</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22407,7 +22407,7 @@
         <v>44281</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22464,7 +22464,7 @@
         <v>44281</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22521,7 +22521,7 @@
         <v>44281</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22578,7 +22578,7 @@
         <v>44285</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22640,7 +22640,7 @@
         <v>44286</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22697,7 +22697,7 @@
         <v>44292</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22754,7 +22754,7 @@
         <v>44294</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22816,7 +22816,7 @@
         <v>44309</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22873,7 +22873,7 @@
         <v>44320</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22930,7 +22930,7 @@
         <v>44321</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22987,7 +22987,7 @@
         <v>44321</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23044,7 +23044,7 @@
         <v>44326</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23101,7 +23101,7 @@
         <v>44326</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23163,7 +23163,7 @@
         <v>44334</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23220,7 +23220,7 @@
         <v>44339</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23277,7 +23277,7 @@
         <v>44339</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23334,7 +23334,7 @@
         <v>44339</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23391,7 +23391,7 @@
         <v>44343</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23453,7 +23453,7 @@
         <v>44342</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23515,7 +23515,7 @@
         <v>44344</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23572,7 +23572,7 @@
         <v>44350</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23629,7 +23629,7 @@
         <v>44350</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23686,7 +23686,7 @@
         <v>44351</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23748,7 +23748,7 @@
         <v>44354</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23810,7 +23810,7 @@
         <v>44355</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23872,7 +23872,7 @@
         <v>44355</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23934,7 +23934,7 @@
         <v>44357</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23991,7 +23991,7 @@
         <v>44358</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24053,7 +24053,7 @@
         <v>44361</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24110,7 +24110,7 @@
         <v>44361</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24167,7 +24167,7 @@
         <v>44361</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24224,7 +24224,7 @@
         <v>44362</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24286,7 +24286,7 @@
         <v>44361</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24348,7 +24348,7 @@
         <v>44362</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24405,7 +24405,7 @@
         <v>44368</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24467,7 +24467,7 @@
         <v>44368</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24529,7 +24529,7 @@
         <v>44368</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24591,7 +24591,7 @@
         <v>44369</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24653,7 +24653,7 @@
         <v>44370</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24715,7 +24715,7 @@
         <v>44370</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24777,7 +24777,7 @@
         <v>44370</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24839,7 +24839,7 @@
         <v>44370</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24901,7 +24901,7 @@
         <v>44371</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24963,7 +24963,7 @@
         <v>44372</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25025,7 +25025,7 @@
         <v>44372</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25087,7 +25087,7 @@
         <v>44375</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25149,7 +25149,7 @@
         <v>44376</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25211,7 +25211,7 @@
         <v>44376</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25273,7 +25273,7 @@
         <v>44376</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25330,7 +25330,7 @@
         <v>44377</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25392,7 +25392,7 @@
         <v>44378</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25449,7 +25449,7 @@
         <v>44378</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25511,7 +25511,7 @@
         <v>44378</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25568,7 +25568,7 @@
         <v>44383</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25625,7 +25625,7 @@
         <v>44383</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25682,7 +25682,7 @@
         <v>44383</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25739,7 +25739,7 @@
         <v>44383</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25796,7 +25796,7 @@
         <v>44383</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25853,7 +25853,7 @@
         <v>44384</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25915,7 +25915,7 @@
         <v>44383</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25972,7 +25972,7 @@
         <v>44386</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26029,7 +26029,7 @@
         <v>44398</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26086,7 +26086,7 @@
         <v>44404</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26143,7 +26143,7 @@
         <v>44405</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26205,7 +26205,7 @@
         <v>44418</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26267,7 +26267,7 @@
         <v>44421</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26329,7 +26329,7 @@
         <v>44428</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26386,7 +26386,7 @@
         <v>44432</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26443,7 +26443,7 @@
         <v>44432</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26500,7 +26500,7 @@
         <v>44433</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26562,7 +26562,7 @@
         <v>44433</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26624,7 +26624,7 @@
         <v>44438</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26686,7 +26686,7 @@
         <v>44439</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26748,7 +26748,7 @@
         <v>44440</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26805,7 +26805,7 @@
         <v>44441</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26867,7 +26867,7 @@
         <v>44440</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26929,7 +26929,7 @@
         <v>44446</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26986,7 +26986,7 @@
         <v>44447</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27048,7 +27048,7 @@
         <v>44453</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27105,7 +27105,7 @@
         <v>44454</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27162,7 +27162,7 @@
         <v>44454</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27219,7 +27219,7 @@
         <v>44459</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27276,7 +27276,7 @@
         <v>44463</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27338,7 +27338,7 @@
         <v>44463</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27400,7 +27400,7 @@
         <v>44463</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27457,7 +27457,7 @@
         <v>44468</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27514,7 +27514,7 @@
         <v>44468</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27571,7 +27571,7 @@
         <v>44476</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27628,7 +27628,7 @@
         <v>44480</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27685,7 +27685,7 @@
         <v>44481</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27742,7 +27742,7 @@
         <v>44484</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27799,7 +27799,7 @@
         <v>44487</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27861,7 +27861,7 @@
         <v>44490</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27918,7 +27918,7 @@
         <v>44489</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27980,7 +27980,7 @@
         <v>44496</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28037,7 +28037,7 @@
         <v>44497</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28099,7 +28099,7 @@
         <v>44497</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28156,7 +28156,7 @@
         <v>44497</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28213,7 +28213,7 @@
         <v>44498</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28270,7 +28270,7 @@
         <v>44498</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28327,7 +28327,7 @@
         <v>44499</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28384,7 +28384,7 @@
         <v>44502</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28441,7 +28441,7 @@
         <v>44516</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28498,7 +28498,7 @@
         <v>44522</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28555,7 +28555,7 @@
         <v>44523</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28612,7 +28612,7 @@
         <v>44525</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28674,7 +28674,7 @@
         <v>44525</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28731,7 +28731,7 @@
         <v>44529</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28788,7 +28788,7 @@
         <v>44530</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28850,7 +28850,7 @@
         <v>44530</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28912,7 +28912,7 @@
         <v>44531</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28969,7 +28969,7 @@
         <v>44531</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29026,7 +29026,7 @@
         <v>44536</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29083,7 +29083,7 @@
         <v>44536</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29140,7 +29140,7 @@
         <v>44538</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29197,7 +29197,7 @@
         <v>44538</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29254,7 +29254,7 @@
         <v>44538</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29311,7 +29311,7 @@
         <v>44538</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29368,7 +29368,7 @@
         <v>44538</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29425,7 +29425,7 @@
         <v>44538</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29482,7 +29482,7 @@
         <v>44538</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29539,7 +29539,7 @@
         <v>44538</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29596,7 +29596,7 @@
         <v>44539</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29658,7 +29658,7 @@
         <v>44543</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29720,7 +29720,7 @@
         <v>44543</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29782,7 +29782,7 @@
         <v>44543</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29844,7 +29844,7 @@
         <v>44543</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29906,7 +29906,7 @@
         <v>44547</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29968,7 +29968,7 @@
         <v>44550</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30025,7 +30025,7 @@
         <v>44550</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30082,7 +30082,7 @@
         <v>44571</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30139,7 +30139,7 @@
         <v>44582</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30196,7 +30196,7 @@
         <v>44582</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30253,7 +30253,7 @@
         <v>44582</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30310,7 +30310,7 @@
         <v>44582</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30367,7 +30367,7 @@
         <v>44588</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30424,7 +30424,7 @@
         <v>44589</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30481,7 +30481,7 @@
         <v>44590</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30538,7 +30538,7 @@
         <v>44590</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30595,7 +30595,7 @@
         <v>44592</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30652,7 +30652,7 @@
         <v>44592</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30709,7 +30709,7 @@
         <v>44596</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30766,7 +30766,7 @@
         <v>44599</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30823,7 +30823,7 @@
         <v>44608</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30880,7 +30880,7 @@
         <v>44615</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30937,7 +30937,7 @@
         <v>44616</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30999,7 +30999,7 @@
         <v>44617</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31061,7 +31061,7 @@
         <v>44621</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31118,7 +31118,7 @@
         <v>44621</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31180,7 +31180,7 @@
         <v>44622</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31237,7 +31237,7 @@
         <v>44623</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31294,7 +31294,7 @@
         <v>44642</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31351,7 +31351,7 @@
         <v>44643</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31408,7 +31408,7 @@
         <v>44643</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31470,7 +31470,7 @@
         <v>44644</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31527,7 +31527,7 @@
         <v>44656</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31584,7 +31584,7 @@
         <v>44658</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31641,7 +31641,7 @@
         <v>44683</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31698,7 +31698,7 @@
         <v>44683</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31755,7 +31755,7 @@
         <v>44685</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31812,7 +31812,7 @@
         <v>44685</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31869,7 +31869,7 @@
         <v>44685</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31926,7 +31926,7 @@
         <v>44687</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31983,7 +31983,7 @@
         <v>44700</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32040,7 +32040,7 @@
         <v>44708</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32097,7 +32097,7 @@
         <v>44708</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32154,7 +32154,7 @@
         <v>44708</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32211,7 +32211,7 @@
         <v>44722</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32268,7 +32268,7 @@
         <v>44727</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32330,7 +32330,7 @@
         <v>44729</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32392,7 +32392,7 @@
         <v>44735</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32449,7 +32449,7 @@
         <v>44735</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32506,7 +32506,7 @@
         <v>44741</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32563,7 +32563,7 @@
         <v>44741</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32620,7 +32620,7 @@
         <v>44741</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32677,7 +32677,7 @@
         <v>44743</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32739,7 +32739,7 @@
         <v>44743</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32796,7 +32796,7 @@
         <v>44748</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32858,7 +32858,7 @@
         <v>44747</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32920,7 +32920,7 @@
         <v>44748</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32982,7 +32982,7 @@
         <v>44748</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33039,7 +33039,7 @@
         <v>44750</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33096,7 +33096,7 @@
         <v>44756</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33153,7 +33153,7 @@
         <v>44761</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33210,7 +33210,7 @@
         <v>44776</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33267,7 +33267,7 @@
         <v>44777</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33329,7 +33329,7 @@
         <v>44781</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33386,7 +33386,7 @@
         <v>44783</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33443,7 +33443,7 @@
         <v>44785</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33505,7 +33505,7 @@
         <v>44784</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33567,7 +33567,7 @@
         <v>44785</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33624,7 +33624,7 @@
         <v>44792</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33681,7 +33681,7 @@
         <v>44792</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33743,7 +33743,7 @@
         <v>44795</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33800,7 +33800,7 @@
         <v>44795</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33862,7 +33862,7 @@
         <v>44803</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33924,7 +33924,7 @@
         <v>44805</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33986,7 +33986,7 @@
         <v>44806</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34043,7 +34043,7 @@
         <v>44809</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34105,7 +34105,7 @@
         <v>44809</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34167,7 +34167,7 @@
         <v>44811</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34224,7 +34224,7 @@
         <v>44813</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34281,7 +34281,7 @@
         <v>44813</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34338,7 +34338,7 @@
         <v>44813</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34395,7 +34395,7 @@
         <v>44813</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34452,7 +34452,7 @@
         <v>44813</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34509,7 +34509,7 @@
         <v>44816</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34566,7 +34566,7 @@
         <v>44816</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34623,7 +34623,7 @@
         <v>44817</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34685,7 +34685,7 @@
         <v>44817</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34742,7 +34742,7 @@
         <v>44818</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34804,7 +34804,7 @@
         <v>44818</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34866,7 +34866,7 @@
         <v>44818</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34928,7 +34928,7 @@
         <v>44817</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34985,7 +34985,7 @@
         <v>44818</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35047,7 +35047,7 @@
         <v>44818</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35109,7 +35109,7 @@
         <v>44818</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35171,7 +35171,7 @@
         <v>44818</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35228,7 +35228,7 @@
         <v>44819</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35285,7 +35285,7 @@
         <v>44820</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35342,7 +35342,7 @@
         <v>44823</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35404,7 +35404,7 @@
         <v>44824</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35461,7 +35461,7 @@
         <v>44827</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35523,7 +35523,7 @@
         <v>44838</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35585,7 +35585,7 @@
         <v>44838</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35642,7 +35642,7 @@
         <v>44839</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35699,7 +35699,7 @@
         <v>44840</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35756,7 +35756,7 @@
         <v>44840</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35813,7 +35813,7 @@
         <v>44841</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35875,7 +35875,7 @@
         <v>44845</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35937,7 +35937,7 @@
         <v>44845</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35999,7 +35999,7 @@
         <v>44848</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36061,7 +36061,7 @@
         <v>44848</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36123,7 +36123,7 @@
         <v>44849</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36185,7 +36185,7 @@
         <v>44848</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36242,7 +36242,7 @@
         <v>44853</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36304,7 +36304,7 @@
         <v>44853</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36366,7 +36366,7 @@
         <v>44853</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36428,7 +36428,7 @@
         <v>44856</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36490,7 +36490,7 @@
         <v>44855</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36552,7 +36552,7 @@
         <v>44857</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36609,7 +36609,7 @@
         <v>44859</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36666,7 +36666,7 @@
         <v>44859</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36723,7 +36723,7 @@
         <v>44861</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36785,7 +36785,7 @@
         <v>44861</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36842,7 +36842,7 @@
         <v>44861</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36904,7 +36904,7 @@
         <v>44861</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36961,7 +36961,7 @@
         <v>44861</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37023,7 +37023,7 @@
         <v>44861</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37085,7 +37085,7 @@
         <v>44861</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37142,7 +37142,7 @@
         <v>44862</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37204,7 +37204,7 @@
         <v>44866</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37266,7 +37266,7 @@
         <v>44867</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37328,7 +37328,7 @@
         <v>44867</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37390,7 +37390,7 @@
         <v>44867</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37447,7 +37447,7 @@
         <v>44868</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37504,7 +37504,7 @@
         <v>44873</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37566,7 +37566,7 @@
         <v>44874</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37623,7 +37623,7 @@
         <v>44874</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37685,7 +37685,7 @@
         <v>44875</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37742,7 +37742,7 @@
         <v>44879</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37799,7 +37799,7 @@
         <v>44879</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37856,7 +37856,7 @@
         <v>44879</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37913,7 +37913,7 @@
         <v>44879</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37970,7 +37970,7 @@
         <v>44883</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38032,7 +38032,7 @@
         <v>44886</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38089,7 +38089,7 @@
         <v>44888</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38146,7 +38146,7 @@
         <v>44888</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38203,7 +38203,7 @@
         <v>44889</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38265,7 +38265,7 @@
         <v>44889</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38327,7 +38327,7 @@
         <v>44890</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38384,7 +38384,7 @@
         <v>44890</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38441,7 +38441,7 @@
         <v>44890</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38503,7 +38503,7 @@
         <v>44893</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38565,7 +38565,7 @@
         <v>44895</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38627,7 +38627,7 @@
         <v>44897</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38684,7 +38684,7 @@
         <v>44901</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38741,7 +38741,7 @@
         <v>44904</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38798,7 +38798,7 @@
         <v>44907</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38855,7 +38855,7 @@
         <v>44907</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38912,7 +38912,7 @@
         <v>44909</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38974,7 +38974,7 @@
         <v>44910</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39031,7 +39031,7 @@
         <v>44910</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39088,7 +39088,7 @@
         <v>44911</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39150,7 +39150,7 @@
         <v>44911</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39212,7 +39212,7 @@
         <v>44911</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39269,7 +39269,7 @@
         <v>44916</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39326,7 +39326,7 @@
         <v>44917</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39388,7 +39388,7 @@
         <v>44929</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39445,7 +39445,7 @@
         <v>44929</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39502,7 +39502,7 @@
         <v>44941</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39559,7 +39559,7 @@
         <v>44942</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39616,7 +39616,7 @@
         <v>44942</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39673,7 +39673,7 @@
         <v>44942</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39730,7 +39730,7 @@
         <v>44942</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39787,7 +39787,7 @@
         <v>44944</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39844,7 +39844,7 @@
         <v>44950</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39901,7 +39901,7 @@
         <v>44951</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39958,7 +39958,7 @@
         <v>44960</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40015,7 +40015,7 @@
         <v>44963</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40072,7 +40072,7 @@
         <v>44965</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40129,7 +40129,7 @@
         <v>44965</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40186,7 +40186,7 @@
         <v>44966</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40243,7 +40243,7 @@
         <v>44966</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40300,7 +40300,7 @@
         <v>44971</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40362,7 +40362,7 @@
         <v>44971</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40419,7 +40419,7 @@
         <v>44972</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40476,7 +40476,7 @@
         <v>44973</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40533,7 +40533,7 @@
         <v>44973</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40590,7 +40590,7 @@
         <v>44973</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40647,7 +40647,7 @@
         <v>44977</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40704,7 +40704,7 @@
         <v>44981</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40761,7 +40761,7 @@
         <v>44984</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40818,7 +40818,7 @@
         <v>44985</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40875,7 +40875,7 @@
         <v>44985</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40932,7 +40932,7 @@
         <v>44985</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40989,7 +40989,7 @@
         <v>44991</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41046,7 +41046,7 @@
         <v>44991</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41103,7 +41103,7 @@
         <v>45006</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41160,7 +41160,7 @@
         <v>45006</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41217,7 +41217,7 @@
         <v>45013</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41274,7 +41274,7 @@
         <v>45015</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41336,7 +41336,7 @@
         <v>45015</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41398,7 +41398,7 @@
         <v>45015</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41455,7 +41455,7 @@
         <v>45021</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41512,7 +41512,7 @@
         <v>45021</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41569,7 +41569,7 @@
         <v>45028</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41626,7 +41626,7 @@
         <v>45029</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41683,7 +41683,7 @@
         <v>45030</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41740,7 +41740,7 @@
         <v>45036</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41797,7 +41797,7 @@
         <v>45036</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41854,7 +41854,7 @@
         <v>45036</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41911,7 +41911,7 @@
         <v>45035</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41973,7 +41973,7 @@
         <v>45036</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42030,7 +42030,7 @@
         <v>45035</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42087,7 +42087,7 @@
         <v>45043</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42144,7 +42144,7 @@
         <v>45043</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42201,7 +42201,7 @@
         <v>45043</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42258,7 +42258,7 @@
         <v>45044</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42320,7 +42320,7 @@
         <v>45048</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42377,7 +42377,7 @@
         <v>45050</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42434,7 +42434,7 @@
         <v>45055</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42491,7 +42491,7 @@
         <v>45057</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42548,7 +42548,7 @@
         <v>45056</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42605,7 +42605,7 @@
         <v>45062</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42667,7 +42667,7 @@
         <v>45062</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42729,7 +42729,7 @@
         <v>45064</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42791,7 +42791,7 @@
         <v>45066</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42853,7 +42853,7 @@
         <v>45068</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42915,7 +42915,7 @@
         <v>45070</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42977,7 +42977,7 @@
         <v>45072</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -43039,7 +43039,7 @@
         <v>45072</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43101,7 +43101,7 @@
         <v>45076</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43158,7 +43158,7 @@
         <v>45076</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43215,7 +43215,7 @@
         <v>45077</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43272,7 +43272,7 @@
         <v>45079</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43334,7 +43334,7 @@
         <v>45079</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43396,7 +43396,7 @@
         <v>45086</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43458,7 +43458,7 @@
         <v>45085</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43520,7 +43520,7 @@
         <v>45086</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43577,7 +43577,7 @@
         <v>45086</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43634,7 +43634,7 @@
         <v>45086</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43691,7 +43691,7 @@
         <v>45086</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43748,7 +43748,7 @@
         <v>45086</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43805,7 +43805,7 @@
         <v>45086</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43862,7 +43862,7 @@
         <v>45090</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43924,7 +43924,7 @@
         <v>45089</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43981,7 +43981,7 @@
         <v>45090</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -44038,7 +44038,7 @@
         <v>45090</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44095,7 +44095,7 @@
         <v>45090</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44152,7 +44152,7 @@
         <v>45090</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44209,7 +44209,7 @@
         <v>45090</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44266,7 +44266,7 @@
         <v>45091</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44323,7 +44323,7 @@
         <v>45091</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44380,7 +44380,7 @@
         <v>45091</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44437,7 +44437,7 @@
         <v>45091</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44494,7 +44494,7 @@
         <v>45093</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44556,7 +44556,7 @@
         <v>45094</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44618,7 +44618,7 @@
         <v>45096</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44675,7 +44675,7 @@
         <v>45096</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44732,7 +44732,7 @@
         <v>45096</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44794,7 +44794,7 @@
         <v>45098</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44851,7 +44851,7 @@
         <v>45098</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44913,7 +44913,7 @@
         <v>45098</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44975,7 +44975,7 @@
         <v>45098</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -45037,7 +45037,7 @@
         <v>45098</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -45094,7 +45094,7 @@
         <v>45098</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45151,7 +45151,7 @@
         <v>45098</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45213,7 +45213,7 @@
         <v>45098</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45275,7 +45275,7 @@
         <v>45098</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45332,7 +45332,7 @@
         <v>45098</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45394,7 +45394,7 @@
         <v>45098</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45451,7 +45451,7 @@
         <v>45098</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45508,7 +45508,7 @@
         <v>45098</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45565,7 +45565,7 @@
         <v>45098</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45622,7 +45622,7 @@
         <v>45099</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45684,7 +45684,7 @@
         <v>45100</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45746,7 +45746,7 @@
         <v>45100</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45808,7 +45808,7 @@
         <v>45100</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45870,7 +45870,7 @@
         <v>45100</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45927,7 +45927,7 @@
         <v>45103</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45989,7 +45989,7 @@
         <v>45104</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -46046,7 +46046,7 @@
         <v>45104</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -46103,7 +46103,7 @@
         <v>45104</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46160,7 +46160,7 @@
         <v>45104</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46217,7 +46217,7 @@
         <v>45104</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46274,7 +46274,7 @@
         <v>45106</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46331,7 +46331,7 @@
         <v>45106</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46388,7 +46388,7 @@
         <v>45106</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46445,7 +46445,7 @@
         <v>45106</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46502,7 +46502,7 @@
         <v>45106</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46559,7 +46559,7 @@
         <v>45106</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46616,7 +46616,7 @@
         <v>45107</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46673,7 +46673,7 @@
         <v>45107</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46730,7 +46730,7 @@
         <v>45107</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46787,7 +46787,7 @@
         <v>45107</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46844,7 +46844,7 @@
         <v>45110</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46901,7 +46901,7 @@
         <v>45110</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46958,7 +46958,7 @@
         <v>45110</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -47015,7 +47015,7 @@
         <v>45110</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -47072,7 +47072,7 @@
         <v>45111</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47129,7 +47129,7 @@
         <v>45114</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47186,7 +47186,7 @@
         <v>45114</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47243,7 +47243,7 @@
         <v>45118</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47305,7 +47305,7 @@
         <v>45118</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47367,7 +47367,7 @@
         <v>45118</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47429,7 +47429,7 @@
         <v>45118</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47491,7 +47491,7 @@
         <v>45118</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47553,7 +47553,7 @@
         <v>45118</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47615,7 +47615,7 @@
         <v>45119</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47677,7 +47677,7 @@
         <v>45119</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47734,7 +47734,7 @@
         <v>45120</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47791,7 +47791,7 @@
         <v>45120</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47848,7 +47848,7 @@
         <v>45120</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47905,7 +47905,7 @@
         <v>45120</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47962,7 +47962,7 @@
         <v>45125</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -48019,7 +48019,7 @@
         <v>45125</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -48076,7 +48076,7 @@
         <v>45125</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -48133,7 +48133,7 @@
         <v>45129</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48190,7 +48190,7 @@
         <v>45129</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48247,7 +48247,7 @@
         <v>45135</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48304,7 +48304,7 @@
         <v>45135</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48361,7 +48361,7 @@
         <v>45138</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48418,7 +48418,7 @@
         <v>45138</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48475,7 +48475,7 @@
         <v>45139</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48532,7 +48532,7 @@
         <v>45139</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48589,7 +48589,7 @@
         <v>45139</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48646,7 +48646,7 @@
         <v>45140</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48708,7 +48708,7 @@
         <v>45140</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48765,7 +48765,7 @@
         <v>45140</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48827,7 +48827,7 @@
         <v>45141</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48884,7 +48884,7 @@
         <v>45145</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48941,7 +48941,7 @@
         <v>45152</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -49003,7 +49003,7 @@
         <v>45152</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -49065,7 +49065,7 @@
         <v>45156</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -49122,7 +49122,7 @@
         <v>45159</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49179,7 +49179,7 @@
         <v>45159</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49236,7 +49236,7 @@
         <v>45160</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49298,7 +49298,7 @@
         <v>45160</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49360,7 +49360,7 @@
         <v>45160</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49417,7 +49417,7 @@
         <v>45162</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49474,7 +49474,7 @@
         <v>45162</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49531,7 +49531,7 @@
         <v>45163</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49588,7 +49588,7 @@
         <v>45167</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49650,7 +49650,7 @@
         <v>45167</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49712,7 +49712,7 @@
         <v>45167</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49769,7 +49769,7 @@
         <v>45167</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49831,7 +49831,7 @@
         <v>45168</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49893,7 +49893,7 @@
         <v>45167</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49950,7 +49950,7 @@
         <v>45168</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -50012,7 +50012,7 @@
         <v>45168</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -50074,7 +50074,7 @@
         <v>45170</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -50131,7 +50131,7 @@
         <v>45170</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -50188,7 +50188,7 @@
         <v>45175</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -50245,7 +50245,7 @@
         <v>45176</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50307,7 +50307,7 @@
         <v>45176</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50369,7 +50369,7 @@
         <v>45176</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50426,7 +50426,7 @@
         <v>45177</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50483,7 +50483,7 @@
         <v>45177</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50540,7 +50540,7 @@
         <v>45177</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50597,7 +50597,7 @@
         <v>45180</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50654,7 +50654,7 @@
         <v>45181</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50716,7 +50716,7 @@
         <v>45181</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50778,7 +50778,7 @@
         <v>45181</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50835,7 +50835,7 @@
         <v>45181</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50892,7 +50892,7 @@
         <v>45182</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50949,7 +50949,7 @@
         <v>45183</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -51006,7 +51006,7 @@
         <v>45184</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -51068,7 +51068,7 @@
         <v>45187</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -51125,7 +51125,7 @@
         <v>45187</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -51182,7 +51182,7 @@
         <v>45187</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -51239,7 +51239,7 @@
         <v>45187</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -51296,7 +51296,7 @@
         <v>45187</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -51353,7 +51353,7 @@
         <v>45187</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -51410,7 +51410,7 @@
         <v>45187</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -51467,7 +51467,7 @@
         <v>45188</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51529,7 +51529,7 @@
         <v>45188</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51591,7 +51591,7 @@
         <v>45188</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51653,7 +51653,7 @@
         <v>45188</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51715,7 +51715,7 @@
         <v>45188</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51777,7 +51777,7 @@
         <v>45188</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51839,7 +51839,7 @@
         <v>45188</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51901,7 +51901,7 @@
         <v>45188</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51958,7 +51958,7 @@
         <v>45189</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -52020,7 +52020,7 @@
         <v>45190</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -52077,7 +52077,7 @@
         <v>45190</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -52134,7 +52134,7 @@
         <v>45190</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -52191,7 +52191,7 @@
         <v>45190</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -52248,7 +52248,7 @@
         <v>45196</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -52305,7 +52305,7 @@
         <v>45197</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -52362,7 +52362,7 @@
         <v>45197</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -52419,7 +52419,7 @@
         <v>45198</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -52481,7 +52481,7 @@
         <v>45201</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -52543,7 +52543,7 @@
         <v>45201</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52605,7 +52605,7 @@
         <v>45202</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52667,7 +52667,7 @@
         <v>45202</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52724,7 +52724,7 @@
         <v>45203</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52781,7 +52781,7 @@
         <v>45204</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52843,7 +52843,7 @@
         <v>45208</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52900,7 +52900,7 @@
         <v>45209</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52957,7 +52957,7 @@
         <v>45208</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -53019,7 +53019,7 @@
         <v>45211</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -53076,7 +53076,7 @@
         <v>45211</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -53133,7 +53133,7 @@
         <v>45211</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -53190,7 +53190,7 @@
         <v>45211</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -53252,7 +53252,7 @@
         <v>45211</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -53314,7 +53314,7 @@
         <v>45211</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -53371,7 +53371,7 @@
         <v>45212</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -53428,7 +53428,7 @@
         <v>45213</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -53485,7 +53485,7 @@
         <v>45215</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -53542,7 +53542,7 @@
         <v>45215</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53599,7 +53599,7 @@
         <v>45216</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53656,7 +53656,7 @@
         <v>45216</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53718,7 +53718,7 @@
         <v>45218</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -53775,7 +53775,7 @@
         <v>45218</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -53837,7 +53837,7 @@
         <v>45218</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -53894,7 +53894,7 @@
         <v>45218</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -53951,7 +53951,7 @@
         <v>45219</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -54008,7 +54008,7 @@
         <v>45219</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -54065,7 +54065,7 @@
         <v>45219</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -54127,7 +54127,7 @@
         <v>45219</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -54189,7 +54189,7 @@
         <v>45219</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -54246,7 +54246,7 @@
         <v>45219</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -54303,7 +54303,7 @@
         <v>45222</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -54360,7 +54360,7 @@
         <v>45222</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -54422,7 +54422,7 @@
         <v>45222</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -54479,7 +54479,7 @@
         <v>45225</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -54536,7 +54536,7 @@
         <v>45225</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -54593,7 +54593,7 @@
         <v>45230</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -54655,7 +54655,7 @@
         <v>45230</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -54712,7 +54712,7 @@
         <v>45230</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -54769,7 +54769,7 @@
         <v>45230</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -54826,7 +54826,7 @@
         <v>45232</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -54888,7 +54888,7 @@
         <v>45232</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -54950,7 +54950,7 @@
         <v>45232</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -55012,7 +55012,7 @@
         <v>45236</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -55074,7 +55074,7 @@
         <v>45236</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -55131,7 +55131,7 @@
         <v>45237</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -55188,7 +55188,7 @@
         <v>45237</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -55245,7 +55245,7 @@
         <v>45237</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -55302,7 +55302,7 @@
         <v>45237</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -55359,7 +55359,7 @@
         <v>45237</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -55421,7 +55421,7 @@
         <v>45237</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -55478,7 +55478,7 @@
         <v>45237</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -55535,7 +55535,7 @@
         <v>45238</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -55592,7 +55592,7 @@
         <v>45239</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -55649,7 +55649,7 @@
         <v>45239</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -55711,7 +55711,7 @@
         <v>45239</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -55768,7 +55768,7 @@
         <v>45239</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -55825,7 +55825,7 @@
         <v>45240</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -55882,7 +55882,7 @@
         <v>45240</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -55939,7 +55939,7 @@
         <v>45243</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -56001,7 +56001,7 @@
         <v>45243</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -56063,7 +56063,7 @@
         <v>45244</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -56120,7 +56120,7 @@
         <v>45244</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -56177,7 +56177,7 @@
         <v>45244</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -56234,7 +56234,7 @@
         <v>45244</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -56291,7 +56291,7 @@
         <v>45244</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -56348,7 +56348,7 @@
         <v>45244</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -56405,7 +56405,7 @@
         <v>45244</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -56462,7 +56462,7 @@
         <v>45244</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -56519,7 +56519,7 @@
         <v>45244</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -56576,7 +56576,7 @@
         <v>45245</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -56633,7 +56633,7 @@
         <v>45245</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -56690,7 +56690,7 @@
         <v>45245</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -56747,7 +56747,7 @@
         <v>45246</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -56804,7 +56804,7 @@
         <v>45246</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -56861,7 +56861,7 @@
         <v>45247</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -56918,7 +56918,7 @@
         <v>45251</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -56975,7 +56975,7 @@
         <v>45252</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -57032,7 +57032,7 @@
         <v>45252</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -57089,7 +57089,7 @@
         <v>45253</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -57146,7 +57146,7 @@
         <v>45254</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -57203,7 +57203,7 @@
         <v>45254</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -57260,7 +57260,7 @@
         <v>45257</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -57317,7 +57317,7 @@
         <v>45257</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -57374,7 +57374,7 @@
         <v>45258</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -57431,7 +57431,7 @@
         <v>45259</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -57488,7 +57488,7 @@
         <v>45259</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -57545,7 +57545,7 @@
         <v>45260</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -57602,7 +57602,7 @@
         <v>45260</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -57659,7 +57659,7 @@
         <v>45260</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -57716,7 +57716,7 @@
         <v>45260</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -57773,7 +57773,7 @@
         <v>45261</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -57830,7 +57830,7 @@
         <v>45261</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -57887,7 +57887,7 @@
         <v>45262</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -57944,7 +57944,7 @@
         <v>45264</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -58001,7 +58001,7 @@
         <v>45264</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -58058,7 +58058,7 @@
         <v>45264</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -58115,7 +58115,7 @@
         <v>45264</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -58177,7 +58177,7 @@
         <v>45264</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -58234,7 +58234,7 @@
         <v>45265</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -58291,7 +58291,7 @@
         <v>45265</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -58348,7 +58348,7 @@
         <v>45266</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -58405,7 +58405,7 @@
         <v>45266</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -58462,7 +58462,7 @@
         <v>45266</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -58519,7 +58519,7 @@
         <v>45267</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -58576,7 +58576,7 @@
         <v>45271</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -58633,7 +58633,7 @@
         <v>45271</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -58690,7 +58690,7 @@
         <v>45273</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -58747,7 +58747,7 @@
         <v>45273</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -58804,7 +58804,7 @@
         <v>45273</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -58861,7 +58861,7 @@
         <v>45273</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -58918,7 +58918,7 @@
         <v>45273</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -58975,7 +58975,7 @@
         <v>45273</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -59032,7 +59032,7 @@
         <v>45273</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -59089,7 +59089,7 @@
         <v>45278</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -59146,7 +59146,7 @@
         <v>45279</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -59203,7 +59203,7 @@
         <v>45279</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -59260,7 +59260,7 @@
         <v>45279</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -59317,7 +59317,7 @@
         <v>45281</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -59374,7 +59374,7 @@
         <v>45282</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -59436,7 +59436,7 @@
         <v>45285</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -59493,7 +59493,7 @@
         <v>45285</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -59550,7 +59550,7 @@
         <v>45285</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -59607,7 +59607,7 @@
         <v>45285</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -59664,7 +59664,7 @@
         <v>45287</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -59721,7 +59721,7 @@
         <v>45287</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -59778,7 +59778,7 @@
         <v>45289</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -59835,7 +59835,7 @@
         <v>45299</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -59892,7 +59892,7 @@
         <v>45308</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -59949,7 +59949,7 @@
         <v>45308</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -60006,7 +60006,7 @@
         <v>45309</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -60063,7 +60063,7 @@
         <v>45310</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -60120,7 +60120,7 @@
         <v>45310</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -60177,7 +60177,7 @@
         <v>45311</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -60234,7 +60234,7 @@
         <v>45311</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -60291,7 +60291,7 @@
         <v>45312</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -60348,7 +60348,7 @@
         <v>45312</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -60405,7 +60405,7 @@
         <v>45313</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -60462,7 +60462,7 @@
         <v>45315</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -60512,14 +60512,14 @@
     <row r="994" ht="15" customHeight="1">
       <c r="A994" t="inlineStr">
         <is>
-          <t>A 2847-2024</t>
+          <t>A 2889-2024</t>
         </is>
       </c>
       <c r="B994" s="1" t="n">
         <v>45315</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -60532,7 +60532,7 @@
         </is>
       </c>
       <c r="G994" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="H994" t="n">
         <v>0</v>
@@ -60569,14 +60569,14 @@
     <row r="995" ht="15" customHeight="1">
       <c r="A995" t="inlineStr">
         <is>
-          <t>A 2889-2024</t>
+          <t>A 2847-2024</t>
         </is>
       </c>
       <c r="B995" s="1" t="n">
         <v>45315</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -60589,7 +60589,7 @@
         </is>
       </c>
       <c r="G995" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="H995" t="n">
         <v>0</v>
@@ -60626,14 +60626,14 @@
     <row r="996" ht="15" customHeight="1">
       <c r="A996" t="inlineStr">
         <is>
-          <t>A 3220-2024</t>
+          <t>A 3215-2024</t>
         </is>
       </c>
       <c r="B996" s="1" t="n">
         <v>45316</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -60646,7 +60646,7 @@
         </is>
       </c>
       <c r="G996" t="n">
-        <v>0.4</v>
+        <v>4.1</v>
       </c>
       <c r="H996" t="n">
         <v>0</v>
@@ -60683,14 +60683,14 @@
     <row r="997" ht="15" customHeight="1">
       <c r="A997" t="inlineStr">
         <is>
-          <t>A 3215-2024</t>
+          <t>A 3220-2024</t>
         </is>
       </c>
       <c r="B997" s="1" t="n">
         <v>45316</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -60703,7 +60703,7 @@
         </is>
       </c>
       <c r="G997" t="n">
-        <v>4.1</v>
+        <v>0.4</v>
       </c>
       <c r="H997" t="n">
         <v>0</v>
@@ -60747,7 +60747,7 @@
         <v>45316</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -60804,7 +60804,7 @@
         <v>45320</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -60861,7 +60861,7 @@
         <v>45320</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -60918,7 +60918,7 @@
         <v>45323</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -60968,14 +60968,14 @@
     <row r="1002" ht="15" customHeight="1">
       <c r="A1002" t="inlineStr">
         <is>
-          <t>A 4122-2024</t>
+          <t>A 4049-2024</t>
         </is>
       </c>
       <c r="B1002" s="1" t="n">
         <v>45323</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -60985,11 +60985,6 @@
       <c r="E1002" t="inlineStr">
         <is>
           <t>PITEÅ</t>
-        </is>
-      </c>
-      <c r="F1002" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
         </is>
       </c>
       <c r="G1002" t="n">
@@ -61030,14 +61025,14 @@
     <row r="1003" ht="15" customHeight="1">
       <c r="A1003" t="inlineStr">
         <is>
-          <t>A 4049-2024</t>
+          <t>A 4127-2024</t>
         </is>
       </c>
       <c r="B1003" s="1" t="n">
         <v>45323</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -61049,8 +61044,13 @@
           <t>PITEÅ</t>
         </is>
       </c>
+      <c r="F1003" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="G1003" t="n">
-        <v>2.8</v>
+        <v>4.5</v>
       </c>
       <c r="H1003" t="n">
         <v>0</v>
@@ -61087,14 +61087,14 @@
     <row r="1004" ht="15" customHeight="1">
       <c r="A1004" t="inlineStr">
         <is>
-          <t>A 4127-2024</t>
+          <t>A 4122-2024</t>
         </is>
       </c>
       <c r="B1004" s="1" t="n">
         <v>45323</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -61112,7 +61112,7 @@
         </is>
       </c>
       <c r="G1004" t="n">
-        <v>4.5</v>
+        <v>2.8</v>
       </c>
       <c r="H1004" t="n">
         <v>0</v>
@@ -61156,7 +61156,7 @@
         <v>45323</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -61211,14 +61211,14 @@
     <row r="1006" ht="15" customHeight="1">
       <c r="A1006" t="inlineStr">
         <is>
-          <t>A 4242-2024</t>
+          <t>A 4245-2024</t>
         </is>
       </c>
       <c r="B1006" s="1" t="n">
         <v>45324</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -61230,13 +61230,8 @@
           <t>PITEÅ</t>
         </is>
       </c>
-      <c r="F1006" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="G1006" t="n">
-        <v>3.9</v>
+        <v>7.2</v>
       </c>
       <c r="H1006" t="n">
         <v>0</v>
@@ -61280,7 +61275,7 @@
         <v>45324</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -61335,14 +61330,14 @@
     <row r="1008" ht="15" customHeight="1">
       <c r="A1008" t="inlineStr">
         <is>
-          <t>A 4245-2024</t>
+          <t>A 4242-2024</t>
         </is>
       </c>
       <c r="B1008" s="1" t="n">
         <v>45324</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -61354,8 +61349,13 @@
           <t>PITEÅ</t>
         </is>
       </c>
+      <c r="F1008" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="G1008" t="n">
-        <v>7.2</v>
+        <v>3.9</v>
       </c>
       <c r="H1008" t="n">
         <v>0</v>
@@ -61399,7 +61399,7 @@
         <v>45329</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -61456,7 +61456,7 @@
         <v>45330</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -61513,7 +61513,7 @@
         <v>45334</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -61560,7 +61560,7 @@
       </c>
       <c r="R1011" s="2" t="inlineStr"/>
     </row>
-    <row r="1012">
+    <row r="1012" ht="15" customHeight="1">
       <c r="A1012" t="inlineStr">
         <is>
           <t>A 5769-2024</t>
@@ -61570,7 +61570,7 @@
         <v>45335</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -61616,6 +61616,177 @@
         <v>0</v>
       </c>
       <c r="R1012" s="2" t="inlineStr"/>
+    </row>
+    <row r="1013" ht="15" customHeight="1">
+      <c r="A1013" t="inlineStr">
+        <is>
+          <t>A 6890-2024</t>
+        </is>
+      </c>
+      <c r="B1013" s="1" t="n">
+        <v>45342</v>
+      </c>
+      <c r="C1013" s="1" t="n">
+        <v>45344</v>
+      </c>
+      <c r="D1013" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="E1013" t="inlineStr">
+        <is>
+          <t>PITEÅ</t>
+        </is>
+      </c>
+      <c r="G1013" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="H1013" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1013" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1013" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1013" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1013" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1013" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1013" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1013" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1013" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1013" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1013" s="2" t="inlineStr"/>
+    </row>
+    <row r="1014" ht="15" customHeight="1">
+      <c r="A1014" t="inlineStr">
+        <is>
+          <t>A 6920-2024</t>
+        </is>
+      </c>
+      <c r="B1014" s="1" t="n">
+        <v>45343</v>
+      </c>
+      <c r="C1014" s="1" t="n">
+        <v>45344</v>
+      </c>
+      <c r="D1014" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="E1014" t="inlineStr">
+        <is>
+          <t>PITEÅ</t>
+        </is>
+      </c>
+      <c r="G1014" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="H1014" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1014" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1014" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1014" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1014" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1014" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1014" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1014" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1014" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1014" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1014" s="2" t="inlineStr"/>
+    </row>
+    <row r="1015">
+      <c r="A1015" t="inlineStr">
+        <is>
+          <t>A 6988-2024</t>
+        </is>
+      </c>
+      <c r="B1015" s="1" t="n">
+        <v>45343</v>
+      </c>
+      <c r="C1015" s="1" t="n">
+        <v>45344</v>
+      </c>
+      <c r="D1015" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="E1015" t="inlineStr">
+        <is>
+          <t>PITEÅ</t>
+        </is>
+      </c>
+      <c r="G1015" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H1015" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1015" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1015" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1015" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1015" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1015" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1015" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1015" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1015" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1015" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1015" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt PITEÅ.xlsx
+++ b/Översikt PITEÅ.xlsx
@@ -569,7 +569,7 @@
         <v>44617</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -665,7 +665,7 @@
         <v>44839</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
         <v>44839</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>44459</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
         <v>44617</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>43896</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>45191</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>45203</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>44740</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>44280</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>44539</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>44550</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>45119</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>44014</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>44522</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>44526</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         <v>44553</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>44810</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>44917</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>45103</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>45106</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         <v>43802</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>43902</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2727,7 +2727,7 @@
         <v>43908</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         <v>44053</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2908,7 +2908,7 @@
         <v>44193</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>44298</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>44840</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
         <v>44852</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3262,7 +3262,7 @@
         <v>44859</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>44944</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3434,7 +3434,7 @@
         <v>45120</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
         <v>45187</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         <v>45209</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3701,7 +3701,7 @@
         <v>45219</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>45243</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         <v>45293</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
         <v>45296</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>43714</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         <v>44014</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4225,7 +4225,7 @@
         <v>44106</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4310,7 +4310,7 @@
         <v>44309</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>44342</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4485,7 +4485,7 @@
         <v>44495</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
         <v>44525</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4665,7 +4665,7 @@
         <v>44525</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4755,7 +4755,7 @@
         <v>44538</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4840,7 +4840,7 @@
         <v>44727</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4929,7 +4929,7 @@
         <v>44804</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5014,7 +5014,7 @@
         <v>44917</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5104,7 +5104,7 @@
         <v>45049</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5193,7 +5193,7 @@
         <v>45098</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>45103</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5373,7 +5373,7 @@
         <v>45148</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
         <v>45175</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         <v>45181</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5642,7 +5642,7 @@
         <v>45188</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5732,7 +5732,7 @@
         <v>45224</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5817,7 +5817,7 @@
         <v>45243</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5907,7 +5907,7 @@
         <v>45265</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5992,7 +5992,7 @@
         <v>45323</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
         <v>43325</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6139,7 +6139,7 @@
         <v>43332</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6196,7 +6196,7 @@
         <v>43336</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6253,7 +6253,7 @@
         <v>43339</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         <v>43339</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
         <v>43341</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6424,7 +6424,7 @@
         <v>43355</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>43355</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         <v>43374</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6600,7 +6600,7 @@
         <v>43374</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6662,7 +6662,7 @@
         <v>43375</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6719,7 +6719,7 @@
         <v>43376</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
         <v>43376</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6833,7 +6833,7 @@
         <v>43381</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6890,7 +6890,7 @@
         <v>43383</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6947,7 +6947,7 @@
         <v>43391</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>43391</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7061,7 +7061,7 @@
         <v>43392</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7118,7 +7118,7 @@
         <v>43392</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7175,7 +7175,7 @@
         <v>43398</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7232,7 +7232,7 @@
         <v>43402</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7289,7 +7289,7 @@
         <v>43404</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7346,7 +7346,7 @@
         <v>43406</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7403,7 +7403,7 @@
         <v>43406</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
         <v>43406</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>43406</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>43406</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>43416</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>43418</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7745,7 +7745,7 @@
         <v>43418</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7802,7 +7802,7 @@
         <v>43418</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         <v>43419</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7916,7 +7916,7 @@
         <v>43420</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         <v>43424</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8035,7 +8035,7 @@
         <v>43427</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8097,7 +8097,7 @@
         <v>43427</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8154,7 +8154,7 @@
         <v>43427</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8216,7 +8216,7 @@
         <v>43427</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8278,7 +8278,7 @@
         <v>43436</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
         <v>43438</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8392,7 +8392,7 @@
         <v>43438</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8449,7 +8449,7 @@
         <v>43438</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8506,7 +8506,7 @@
         <v>43438</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8563,7 +8563,7 @@
         <v>43451</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8625,7 +8625,7 @@
         <v>43472</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8682,7 +8682,7 @@
         <v>43475</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8739,7 +8739,7 @@
         <v>43479</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8796,7 +8796,7 @@
         <v>43479</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8853,7 +8853,7 @@
         <v>43486</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
         <v>43489</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8967,7 +8967,7 @@
         <v>43489</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9024,7 +9024,7 @@
         <v>43489</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9081,7 +9081,7 @@
         <v>43489</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9138,7 +9138,7 @@
         <v>43489</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9195,7 +9195,7 @@
         <v>43490</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9252,7 +9252,7 @@
         <v>43490</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9309,7 +9309,7 @@
         <v>43493</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9371,7 +9371,7 @@
         <v>43509</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9428,7 +9428,7 @@
         <v>43510</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9485,7 +9485,7 @@
         <v>43510</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9542,7 +9542,7 @@
         <v>43514</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9599,7 +9599,7 @@
         <v>43514</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9656,7 +9656,7 @@
         <v>43514</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9713,7 +9713,7 @@
         <v>43516</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9775,7 +9775,7 @@
         <v>43518</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9832,7 +9832,7 @@
         <v>43521</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9894,7 +9894,7 @@
         <v>43521</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9956,7 +9956,7 @@
         <v>43521</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10018,7 +10018,7 @@
         <v>43521</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10080,7 +10080,7 @@
         <v>43521</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10142,7 +10142,7 @@
         <v>43522</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10199,7 +10199,7 @@
         <v>43523</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10256,7 +10256,7 @@
         <v>43523</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10313,7 +10313,7 @@
         <v>43523</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10370,7 +10370,7 @@
         <v>43532</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10427,7 +10427,7 @@
         <v>43532</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10484,7 +10484,7 @@
         <v>43542</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10541,7 +10541,7 @@
         <v>43544</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10603,7 +10603,7 @@
         <v>43544</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10665,7 +10665,7 @@
         <v>43554</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10722,7 +10722,7 @@
         <v>43556</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10779,7 +10779,7 @@
         <v>43557</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10841,7 +10841,7 @@
         <v>43557</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10898,7 +10898,7 @@
         <v>43557</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10955,7 +10955,7 @@
         <v>43557</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11012,7 +11012,7 @@
         <v>43557</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11074,7 +11074,7 @@
         <v>43564</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11131,7 +11131,7 @@
         <v>43564</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11188,7 +11188,7 @@
         <v>43567</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11245,7 +11245,7 @@
         <v>43570</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11302,7 +11302,7 @@
         <v>43570</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11359,7 +11359,7 @@
         <v>43570</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11416,7 +11416,7 @@
         <v>43584</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11473,7 +11473,7 @@
         <v>43605</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11530,7 +11530,7 @@
         <v>43608</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11587,7 +11587,7 @@
         <v>43614</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11649,7 +11649,7 @@
         <v>43616</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11711,7 +11711,7 @@
         <v>43616</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11773,7 +11773,7 @@
         <v>43629</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11830,7 +11830,7 @@
         <v>43629</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11892,7 +11892,7 @@
         <v>43633</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11949,7 +11949,7 @@
         <v>43633</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12006,7 +12006,7 @@
         <v>43640</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12063,7 +12063,7 @@
         <v>43640</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12120,7 +12120,7 @@
         <v>43647</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12177,7 +12177,7 @@
         <v>43647</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12234,7 +12234,7 @@
         <v>43650</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12291,7 +12291,7 @@
         <v>43652</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12353,7 +12353,7 @@
         <v>43677</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12410,7 +12410,7 @@
         <v>43678</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12467,7 +12467,7 @@
         <v>43682</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12524,7 +12524,7 @@
         <v>43691</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12586,7 +12586,7 @@
         <v>43691</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12648,7 +12648,7 @@
         <v>43696</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12710,7 +12710,7 @@
         <v>43697</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12767,7 +12767,7 @@
         <v>43698</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12829,7 +12829,7 @@
         <v>43698</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12891,7 +12891,7 @@
         <v>43706</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12948,7 +12948,7 @@
         <v>43707</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13010,7 +13010,7 @@
         <v>43711</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13067,7 +13067,7 @@
         <v>43713</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13124,7 +13124,7 @@
         <v>43718</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13181,7 +13181,7 @@
         <v>43718</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13238,7 +13238,7 @@
         <v>43718</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13300,7 +13300,7 @@
         <v>43720</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13357,7 +13357,7 @@
         <v>43721</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13414,7 +13414,7 @@
         <v>43732</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13471,7 +13471,7 @@
         <v>43741</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13533,7 +13533,7 @@
         <v>43741</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13590,7 +13590,7 @@
         <v>43752</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13652,7 +13652,7 @@
         <v>43755</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13709,7 +13709,7 @@
         <v>43755</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13766,7 +13766,7 @@
         <v>43755</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13823,7 +13823,7 @@
         <v>43755</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13880,7 +13880,7 @@
         <v>43760</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13942,7 +13942,7 @@
         <v>43760</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14004,7 +14004,7 @@
         <v>43760</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14061,7 +14061,7 @@
         <v>43762</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14123,7 +14123,7 @@
         <v>43766</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14180,7 +14180,7 @@
         <v>43766</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14237,7 +14237,7 @@
         <v>43768</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14294,7 +14294,7 @@
         <v>43770</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14356,7 +14356,7 @@
         <v>43775</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14418,7 +14418,7 @@
         <v>43775</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14480,7 +14480,7 @@
         <v>43777</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14537,7 +14537,7 @@
         <v>43780</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14594,7 +14594,7 @@
         <v>43780</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14651,7 +14651,7 @@
         <v>43780</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14708,7 +14708,7 @@
         <v>43782</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14770,7 +14770,7 @@
         <v>43789</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14832,7 +14832,7 @@
         <v>43798</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14889,7 +14889,7 @@
         <v>43801</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14951,7 +14951,7 @@
         <v>43802</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15008,7 +15008,7 @@
         <v>43802</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15065,7 +15065,7 @@
         <v>43802</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15122,7 +15122,7 @@
         <v>43802</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15179,7 +15179,7 @@
         <v>43802</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15236,7 +15236,7 @@
         <v>43802</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15293,7 +15293,7 @@
         <v>43807</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15350,7 +15350,7 @@
         <v>43809</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15407,7 +15407,7 @@
         <v>43817</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15464,7 +15464,7 @@
         <v>43817</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15526,7 +15526,7 @@
         <v>43822</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15583,7 +15583,7 @@
         <v>43822</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15640,7 +15640,7 @@
         <v>43833</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15697,7 +15697,7 @@
         <v>43846</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15754,7 +15754,7 @@
         <v>43852</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15811,7 +15811,7 @@
         <v>43853</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15868,7 +15868,7 @@
         <v>43854</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15925,7 +15925,7 @@
         <v>43859</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15987,7 +15987,7 @@
         <v>43859</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16044,7 +16044,7 @@
         <v>43859</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16101,7 +16101,7 @@
         <v>43859</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16158,7 +16158,7 @@
         <v>43859</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16215,7 +16215,7 @@
         <v>43860</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16272,7 +16272,7 @@
         <v>43868</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16329,7 +16329,7 @@
         <v>43868</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16386,7 +16386,7 @@
         <v>43874</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16448,7 +16448,7 @@
         <v>43878</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16505,7 +16505,7 @@
         <v>43880</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16562,7 +16562,7 @@
         <v>43880</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16619,7 +16619,7 @@
         <v>43889</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16676,7 +16676,7 @@
         <v>43895</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16738,7 +16738,7 @@
         <v>43896</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16795,7 +16795,7 @@
         <v>43902</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16852,7 +16852,7 @@
         <v>43902</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16914,7 +16914,7 @@
         <v>43907</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16971,7 +16971,7 @@
         <v>43913</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17028,7 +17028,7 @@
         <v>43914</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17090,7 +17090,7 @@
         <v>43927</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17152,7 +17152,7 @@
         <v>43929</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         <v>43929</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>43931</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17328,7 +17328,7 @@
         <v>43950</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17385,7 +17385,7 @@
         <v>43957</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17447,7 +17447,7 @@
         <v>43958</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17504,7 +17504,7 @@
         <v>43958</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17561,7 +17561,7 @@
         <v>43959</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17618,7 +17618,7 @@
         <v>43962</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17675,7 +17675,7 @@
         <v>43962</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17732,7 +17732,7 @@
         <v>43962</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17789,7 +17789,7 @@
         <v>43962</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17846,7 +17846,7 @@
         <v>43970</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17908,7 +17908,7 @@
         <v>43971</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17970,7 +17970,7 @@
         <v>43976</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18027,7 +18027,7 @@
         <v>43979</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18084,7 +18084,7 @@
         <v>43979</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18141,7 +18141,7 @@
         <v>43979</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18198,7 +18198,7 @@
         <v>43984</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18260,7 +18260,7 @@
         <v>43984</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18317,7 +18317,7 @@
         <v>43987</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18374,7 +18374,7 @@
         <v>43990</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18431,7 +18431,7 @@
         <v>43994</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18493,7 +18493,7 @@
         <v>43997</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18550,7 +18550,7 @@
         <v>43999</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18607,7 +18607,7 @@
         <v>44000</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18669,7 +18669,7 @@
         <v>44006</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18726,7 +18726,7 @@
         <v>44006</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18783,7 +18783,7 @@
         <v>44007</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18840,7 +18840,7 @@
         <v>44007</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18897,7 +18897,7 @@
         <v>44011</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18954,7 +18954,7 @@
         <v>44012</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19016,7 +19016,7 @@
         <v>44020</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19078,7 +19078,7 @@
         <v>44020</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19135,7 +19135,7 @@
         <v>44020</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19197,7 +19197,7 @@
         <v>44026</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19259,7 +19259,7 @@
         <v>44035</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19316,7 +19316,7 @@
         <v>44049</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19373,7 +19373,7 @@
         <v>44063</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19435,7 +19435,7 @@
         <v>44067</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19497,7 +19497,7 @@
         <v>44067</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19559,7 +19559,7 @@
         <v>44068</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19621,7 +19621,7 @@
         <v>44069</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19678,7 +19678,7 @@
         <v>44070</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19735,7 +19735,7 @@
         <v>44074</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19792,7 +19792,7 @@
         <v>44075</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19849,7 +19849,7 @@
         <v>44078</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19906,7 +19906,7 @@
         <v>44083</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19963,7 +19963,7 @@
         <v>44083</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20020,7 +20020,7 @@
         <v>44087</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20077,7 +20077,7 @@
         <v>44088</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20139,7 +20139,7 @@
         <v>44088</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20196,7 +20196,7 @@
         <v>44088</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20258,7 +20258,7 @@
         <v>44092</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20315,7 +20315,7 @@
         <v>44092</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20372,7 +20372,7 @@
         <v>44092</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20429,7 +20429,7 @@
         <v>44095</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20486,7 +20486,7 @@
         <v>44099</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20543,7 +20543,7 @@
         <v>44099</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20600,7 +20600,7 @@
         <v>44099</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20657,7 +20657,7 @@
         <v>44099</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20714,7 +20714,7 @@
         <v>44103</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20771,7 +20771,7 @@
         <v>44103</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20828,7 +20828,7 @@
         <v>44106</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20885,7 +20885,7 @@
         <v>44111</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20947,7 +20947,7 @@
         <v>44111</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21009,7 +21009,7 @@
         <v>44123</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21066,7 +21066,7 @@
         <v>44127</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21123,7 +21123,7 @@
         <v>44132</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21180,7 +21180,7 @@
         <v>44139</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21237,7 +21237,7 @@
         <v>44141</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21294,7 +21294,7 @@
         <v>44141</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21351,7 +21351,7 @@
         <v>44155</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21408,7 +21408,7 @@
         <v>44162</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21470,7 +21470,7 @@
         <v>44166</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21532,7 +21532,7 @@
         <v>44172</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21589,7 +21589,7 @@
         <v>44180</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21646,7 +21646,7 @@
         <v>44186</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21703,7 +21703,7 @@
         <v>44209</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21760,7 +21760,7 @@
         <v>44211</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21817,7 +21817,7 @@
         <v>44211</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21874,7 +21874,7 @@
         <v>44211</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21931,7 +21931,7 @@
         <v>44215</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21993,7 +21993,7 @@
         <v>44221</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22055,7 +22055,7 @@
         <v>44237</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22117,7 +22117,7 @@
         <v>44238</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22174,7 +22174,7 @@
         <v>44256</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22231,7 +22231,7 @@
         <v>44257</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22288,7 +22288,7 @@
         <v>44258</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22345,7 +22345,7 @@
         <v>44280</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22407,7 +22407,7 @@
         <v>44281</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22464,7 +22464,7 @@
         <v>44281</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22521,7 +22521,7 @@
         <v>44281</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22578,7 +22578,7 @@
         <v>44285</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22640,7 +22640,7 @@
         <v>44286</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22697,7 +22697,7 @@
         <v>44292</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22754,7 +22754,7 @@
         <v>44294</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22816,7 +22816,7 @@
         <v>44309</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22873,7 +22873,7 @@
         <v>44320</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22930,7 +22930,7 @@
         <v>44321</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22987,7 +22987,7 @@
         <v>44321</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23044,7 +23044,7 @@
         <v>44326</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23101,7 +23101,7 @@
         <v>44326</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23163,7 +23163,7 @@
         <v>44334</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23220,7 +23220,7 @@
         <v>44339</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23277,7 +23277,7 @@
         <v>44339</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23334,7 +23334,7 @@
         <v>44339</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23391,7 +23391,7 @@
         <v>44343</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23453,7 +23453,7 @@
         <v>44342</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23515,7 +23515,7 @@
         <v>44344</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23572,7 +23572,7 @@
         <v>44350</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23629,7 +23629,7 @@
         <v>44350</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23686,7 +23686,7 @@
         <v>44351</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23748,7 +23748,7 @@
         <v>44354</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23810,7 +23810,7 @@
         <v>44355</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23872,7 +23872,7 @@
         <v>44355</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23934,7 +23934,7 @@
         <v>44357</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23991,7 +23991,7 @@
         <v>44358</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24053,7 +24053,7 @@
         <v>44361</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24110,7 +24110,7 @@
         <v>44361</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24167,7 +24167,7 @@
         <v>44361</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24224,7 +24224,7 @@
         <v>44362</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24286,7 +24286,7 @@
         <v>44361</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24348,7 +24348,7 @@
         <v>44362</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24405,7 +24405,7 @@
         <v>44368</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24467,7 +24467,7 @@
         <v>44368</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24529,7 +24529,7 @@
         <v>44368</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24591,7 +24591,7 @@
         <v>44369</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24653,7 +24653,7 @@
         <v>44370</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24715,7 +24715,7 @@
         <v>44370</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24777,7 +24777,7 @@
         <v>44370</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24839,7 +24839,7 @@
         <v>44370</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24901,7 +24901,7 @@
         <v>44371</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24963,7 +24963,7 @@
         <v>44372</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25025,7 +25025,7 @@
         <v>44372</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25087,7 +25087,7 @@
         <v>44375</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25149,7 +25149,7 @@
         <v>44376</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25211,7 +25211,7 @@
         <v>44376</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25273,7 +25273,7 @@
         <v>44376</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25330,7 +25330,7 @@
         <v>44377</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25392,7 +25392,7 @@
         <v>44378</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25449,7 +25449,7 @@
         <v>44378</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25511,7 +25511,7 @@
         <v>44378</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25568,7 +25568,7 @@
         <v>44383</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25625,7 +25625,7 @@
         <v>44383</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25682,7 +25682,7 @@
         <v>44383</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25739,7 +25739,7 @@
         <v>44383</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25796,7 +25796,7 @@
         <v>44383</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25853,7 +25853,7 @@
         <v>44384</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25915,7 +25915,7 @@
         <v>44383</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25972,7 +25972,7 @@
         <v>44386</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26029,7 +26029,7 @@
         <v>44398</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26086,7 +26086,7 @@
         <v>44404</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26143,7 +26143,7 @@
         <v>44405</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26205,7 +26205,7 @@
         <v>44418</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26267,7 +26267,7 @@
         <v>44421</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26329,7 +26329,7 @@
         <v>44428</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26386,7 +26386,7 @@
         <v>44432</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26443,7 +26443,7 @@
         <v>44432</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26500,7 +26500,7 @@
         <v>44433</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26562,7 +26562,7 @@
         <v>44433</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26624,7 +26624,7 @@
         <v>44438</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26686,7 +26686,7 @@
         <v>44439</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26748,7 +26748,7 @@
         <v>44440</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26805,7 +26805,7 @@
         <v>44441</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26867,7 +26867,7 @@
         <v>44440</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26929,7 +26929,7 @@
         <v>44446</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26986,7 +26986,7 @@
         <v>44447</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27048,7 +27048,7 @@
         <v>44453</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27105,7 +27105,7 @@
         <v>44454</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27162,7 +27162,7 @@
         <v>44454</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27219,7 +27219,7 @@
         <v>44459</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27276,7 +27276,7 @@
         <v>44463</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27338,7 +27338,7 @@
         <v>44463</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27400,7 +27400,7 @@
         <v>44463</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27457,7 +27457,7 @@
         <v>44468</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27514,7 +27514,7 @@
         <v>44468</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27571,7 +27571,7 @@
         <v>44476</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27628,7 +27628,7 @@
         <v>44480</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27685,7 +27685,7 @@
         <v>44481</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27742,7 +27742,7 @@
         <v>44484</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27799,7 +27799,7 @@
         <v>44487</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27861,7 +27861,7 @@
         <v>44490</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27918,7 +27918,7 @@
         <v>44489</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27980,7 +27980,7 @@
         <v>44496</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28037,7 +28037,7 @@
         <v>44497</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28099,7 +28099,7 @@
         <v>44497</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28156,7 +28156,7 @@
         <v>44497</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28213,7 +28213,7 @@
         <v>44498</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28270,7 +28270,7 @@
         <v>44498</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28327,7 +28327,7 @@
         <v>44499</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28384,7 +28384,7 @@
         <v>44502</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28441,7 +28441,7 @@
         <v>44516</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28498,7 +28498,7 @@
         <v>44522</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28555,7 +28555,7 @@
         <v>44523</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28612,7 +28612,7 @@
         <v>44525</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28674,7 +28674,7 @@
         <v>44525</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28731,7 +28731,7 @@
         <v>44529</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28788,7 +28788,7 @@
         <v>44530</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28850,7 +28850,7 @@
         <v>44530</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28912,7 +28912,7 @@
         <v>44531</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28969,7 +28969,7 @@
         <v>44531</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29026,7 +29026,7 @@
         <v>44536</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29083,7 +29083,7 @@
         <v>44536</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29140,7 +29140,7 @@
         <v>44538</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29197,7 +29197,7 @@
         <v>44538</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29254,7 +29254,7 @@
         <v>44538</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29311,7 +29311,7 @@
         <v>44538</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29368,7 +29368,7 @@
         <v>44538</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29425,7 +29425,7 @@
         <v>44538</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29482,7 +29482,7 @@
         <v>44538</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29539,7 +29539,7 @@
         <v>44538</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29596,7 +29596,7 @@
         <v>44539</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29658,7 +29658,7 @@
         <v>44543</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29720,7 +29720,7 @@
         <v>44543</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29782,7 +29782,7 @@
         <v>44543</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29844,7 +29844,7 @@
         <v>44543</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29906,7 +29906,7 @@
         <v>44547</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29968,7 +29968,7 @@
         <v>44550</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30025,7 +30025,7 @@
         <v>44550</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30082,7 +30082,7 @@
         <v>44571</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30139,7 +30139,7 @@
         <v>44582</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30196,7 +30196,7 @@
         <v>44582</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30253,7 +30253,7 @@
         <v>44582</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30310,7 +30310,7 @@
         <v>44582</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30367,7 +30367,7 @@
         <v>44588</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30424,7 +30424,7 @@
         <v>44589</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30481,7 +30481,7 @@
         <v>44590</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30538,7 +30538,7 @@
         <v>44590</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30595,7 +30595,7 @@
         <v>44592</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30652,7 +30652,7 @@
         <v>44592</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30709,7 +30709,7 @@
         <v>44596</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30766,7 +30766,7 @@
         <v>44599</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30823,7 +30823,7 @@
         <v>44608</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30880,7 +30880,7 @@
         <v>44615</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30937,7 +30937,7 @@
         <v>44616</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30999,7 +30999,7 @@
         <v>44617</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31061,7 +31061,7 @@
         <v>44621</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31118,7 +31118,7 @@
         <v>44621</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31180,7 +31180,7 @@
         <v>44622</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31237,7 +31237,7 @@
         <v>44623</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31294,7 +31294,7 @@
         <v>44642</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31351,7 +31351,7 @@
         <v>44643</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31408,7 +31408,7 @@
         <v>44643</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31470,7 +31470,7 @@
         <v>44644</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31527,7 +31527,7 @@
         <v>44656</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31584,7 +31584,7 @@
         <v>44658</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31641,7 +31641,7 @@
         <v>44683</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31698,7 +31698,7 @@
         <v>44683</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31755,7 +31755,7 @@
         <v>44685</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31812,7 +31812,7 @@
         <v>44685</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31869,7 +31869,7 @@
         <v>44685</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31926,7 +31926,7 @@
         <v>44687</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31983,7 +31983,7 @@
         <v>44700</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32040,7 +32040,7 @@
         <v>44708</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32097,7 +32097,7 @@
         <v>44708</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32154,7 +32154,7 @@
         <v>44708</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32211,7 +32211,7 @@
         <v>44722</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32268,7 +32268,7 @@
         <v>44727</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32330,7 +32330,7 @@
         <v>44729</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32392,7 +32392,7 @@
         <v>44735</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32449,7 +32449,7 @@
         <v>44735</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32506,7 +32506,7 @@
         <v>44741</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32563,7 +32563,7 @@
         <v>44741</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32620,7 +32620,7 @@
         <v>44741</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32677,7 +32677,7 @@
         <v>44743</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32739,7 +32739,7 @@
         <v>44743</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32796,7 +32796,7 @@
         <v>44748</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32858,7 +32858,7 @@
         <v>44747</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32920,7 +32920,7 @@
         <v>44748</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32982,7 +32982,7 @@
         <v>44748</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33039,7 +33039,7 @@
         <v>44750</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33096,7 +33096,7 @@
         <v>44756</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33153,7 +33153,7 @@
         <v>44761</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33210,7 +33210,7 @@
         <v>44776</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33267,7 +33267,7 @@
         <v>44777</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33329,7 +33329,7 @@
         <v>44781</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33386,7 +33386,7 @@
         <v>44783</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33443,7 +33443,7 @@
         <v>44785</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33505,7 +33505,7 @@
         <v>44784</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33567,7 +33567,7 @@
         <v>44785</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33624,7 +33624,7 @@
         <v>44792</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33681,7 +33681,7 @@
         <v>44792</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33743,7 +33743,7 @@
         <v>44795</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33800,7 +33800,7 @@
         <v>44795</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33862,7 +33862,7 @@
         <v>44803</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33924,7 +33924,7 @@
         <v>44805</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33986,7 +33986,7 @@
         <v>44806</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34043,7 +34043,7 @@
         <v>44809</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34105,7 +34105,7 @@
         <v>44809</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34167,7 +34167,7 @@
         <v>44811</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34224,7 +34224,7 @@
         <v>44813</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34281,7 +34281,7 @@
         <v>44813</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34338,7 +34338,7 @@
         <v>44813</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34395,7 +34395,7 @@
         <v>44813</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34452,7 +34452,7 @@
         <v>44813</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34509,7 +34509,7 @@
         <v>44816</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34566,7 +34566,7 @@
         <v>44816</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34623,7 +34623,7 @@
         <v>44817</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34685,7 +34685,7 @@
         <v>44817</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34742,7 +34742,7 @@
         <v>44818</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34804,7 +34804,7 @@
         <v>44818</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34866,7 +34866,7 @@
         <v>44818</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34928,7 +34928,7 @@
         <v>44817</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34985,7 +34985,7 @@
         <v>44818</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35047,7 +35047,7 @@
         <v>44818</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35109,7 +35109,7 @@
         <v>44818</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35171,7 +35171,7 @@
         <v>44818</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35228,7 +35228,7 @@
         <v>44819</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35285,7 +35285,7 @@
         <v>44820</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35342,7 +35342,7 @@
         <v>44823</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35404,7 +35404,7 @@
         <v>44824</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35461,7 +35461,7 @@
         <v>44827</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35523,7 +35523,7 @@
         <v>44838</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35585,7 +35585,7 @@
         <v>44838</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35642,7 +35642,7 @@
         <v>44839</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35699,7 +35699,7 @@
         <v>44840</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35756,7 +35756,7 @@
         <v>44840</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35813,7 +35813,7 @@
         <v>44841</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35875,7 +35875,7 @@
         <v>44845</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35937,7 +35937,7 @@
         <v>44845</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35999,7 +35999,7 @@
         <v>44848</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36061,7 +36061,7 @@
         <v>44848</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36123,7 +36123,7 @@
         <v>44849</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36185,7 +36185,7 @@
         <v>44848</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36242,7 +36242,7 @@
         <v>44853</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36304,7 +36304,7 @@
         <v>44853</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36366,7 +36366,7 @@
         <v>44853</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36428,7 +36428,7 @@
         <v>44856</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36490,7 +36490,7 @@
         <v>44855</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36552,7 +36552,7 @@
         <v>44857</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36609,7 +36609,7 @@
         <v>44859</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36666,7 +36666,7 @@
         <v>44859</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36723,7 +36723,7 @@
         <v>44861</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36785,7 +36785,7 @@
         <v>44861</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36842,7 +36842,7 @@
         <v>44861</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36904,7 +36904,7 @@
         <v>44861</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36961,7 +36961,7 @@
         <v>44861</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37023,7 +37023,7 @@
         <v>44861</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37085,7 +37085,7 @@
         <v>44861</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37142,7 +37142,7 @@
         <v>44862</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37204,7 +37204,7 @@
         <v>44866</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37266,7 +37266,7 @@
         <v>44867</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37328,7 +37328,7 @@
         <v>44867</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37390,7 +37390,7 @@
         <v>44867</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37447,7 +37447,7 @@
         <v>44868</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37504,7 +37504,7 @@
         <v>44873</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37566,7 +37566,7 @@
         <v>44874</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37623,7 +37623,7 @@
         <v>44874</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37685,7 +37685,7 @@
         <v>44875</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37742,7 +37742,7 @@
         <v>44879</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37799,7 +37799,7 @@
         <v>44879</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37856,7 +37856,7 @@
         <v>44879</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37913,7 +37913,7 @@
         <v>44879</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37970,7 +37970,7 @@
         <v>44883</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38032,7 +38032,7 @@
         <v>44886</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38089,7 +38089,7 @@
         <v>44888</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38146,7 +38146,7 @@
         <v>44888</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38203,7 +38203,7 @@
         <v>44889</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38265,7 +38265,7 @@
         <v>44889</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38327,7 +38327,7 @@
         <v>44890</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38384,7 +38384,7 @@
         <v>44890</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38441,7 +38441,7 @@
         <v>44890</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38503,7 +38503,7 @@
         <v>44893</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38565,7 +38565,7 @@
         <v>44895</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38627,7 +38627,7 @@
         <v>44897</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38684,7 +38684,7 @@
         <v>44901</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38741,7 +38741,7 @@
         <v>44904</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38798,7 +38798,7 @@
         <v>44907</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38855,7 +38855,7 @@
         <v>44907</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38912,7 +38912,7 @@
         <v>44909</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38974,7 +38974,7 @@
         <v>44910</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39031,7 +39031,7 @@
         <v>44910</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39088,7 +39088,7 @@
         <v>44911</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39150,7 +39150,7 @@
         <v>44911</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39212,7 +39212,7 @@
         <v>44911</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39269,7 +39269,7 @@
         <v>44916</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39326,7 +39326,7 @@
         <v>44917</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39388,7 +39388,7 @@
         <v>44929</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39445,7 +39445,7 @@
         <v>44929</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39502,7 +39502,7 @@
         <v>44941</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39559,7 +39559,7 @@
         <v>44942</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39616,7 +39616,7 @@
         <v>44942</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39673,7 +39673,7 @@
         <v>44942</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39730,7 +39730,7 @@
         <v>44942</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39787,7 +39787,7 @@
         <v>44944</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39844,7 +39844,7 @@
         <v>44950</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39901,7 +39901,7 @@
         <v>44951</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39958,7 +39958,7 @@
         <v>44960</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40015,7 +40015,7 @@
         <v>44963</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40072,7 +40072,7 @@
         <v>44965</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40129,7 +40129,7 @@
         <v>44965</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40186,7 +40186,7 @@
         <v>44966</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40243,7 +40243,7 @@
         <v>44966</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40300,7 +40300,7 @@
         <v>44971</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40362,7 +40362,7 @@
         <v>44971</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40419,7 +40419,7 @@
         <v>44972</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40476,7 +40476,7 @@
         <v>44973</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40533,7 +40533,7 @@
         <v>44973</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40590,7 +40590,7 @@
         <v>44973</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40647,7 +40647,7 @@
         <v>44977</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40704,7 +40704,7 @@
         <v>44981</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40761,7 +40761,7 @@
         <v>44984</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40818,7 +40818,7 @@
         <v>44985</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40875,7 +40875,7 @@
         <v>44985</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40932,7 +40932,7 @@
         <v>44985</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40989,7 +40989,7 @@
         <v>44991</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41046,7 +41046,7 @@
         <v>44991</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41103,7 +41103,7 @@
         <v>45006</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41160,7 +41160,7 @@
         <v>45006</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41217,7 +41217,7 @@
         <v>45013</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41274,7 +41274,7 @@
         <v>45015</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41336,7 +41336,7 @@
         <v>45015</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41398,7 +41398,7 @@
         <v>45015</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41455,7 +41455,7 @@
         <v>45021</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41512,7 +41512,7 @@
         <v>45021</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41569,7 +41569,7 @@
         <v>45028</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41626,7 +41626,7 @@
         <v>45029</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41683,7 +41683,7 @@
         <v>45030</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41740,7 +41740,7 @@
         <v>45036</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41797,7 +41797,7 @@
         <v>45036</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41854,7 +41854,7 @@
         <v>45036</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41911,7 +41911,7 @@
         <v>45035</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41973,7 +41973,7 @@
         <v>45036</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42030,7 +42030,7 @@
         <v>45035</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42087,7 +42087,7 @@
         <v>45043</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42144,7 +42144,7 @@
         <v>45043</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42201,7 +42201,7 @@
         <v>45043</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42258,7 +42258,7 @@
         <v>45044</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42320,7 +42320,7 @@
         <v>45048</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42377,7 +42377,7 @@
         <v>45050</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42434,7 +42434,7 @@
         <v>45055</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42491,7 +42491,7 @@
         <v>45057</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42548,7 +42548,7 @@
         <v>45056</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42605,7 +42605,7 @@
         <v>45062</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42667,7 +42667,7 @@
         <v>45062</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42729,7 +42729,7 @@
         <v>45064</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42791,7 +42791,7 @@
         <v>45066</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42853,7 +42853,7 @@
         <v>45068</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42915,7 +42915,7 @@
         <v>45070</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42977,7 +42977,7 @@
         <v>45072</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -43039,7 +43039,7 @@
         <v>45072</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43101,7 +43101,7 @@
         <v>45076</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43158,7 +43158,7 @@
         <v>45076</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43215,7 +43215,7 @@
         <v>45077</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43272,7 +43272,7 @@
         <v>45079</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43334,7 +43334,7 @@
         <v>45079</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43396,7 +43396,7 @@
         <v>45086</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43458,7 +43458,7 @@
         <v>45085</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43520,7 +43520,7 @@
         <v>45086</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43577,7 +43577,7 @@
         <v>45086</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43634,7 +43634,7 @@
         <v>45086</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43691,7 +43691,7 @@
         <v>45086</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43748,7 +43748,7 @@
         <v>45086</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43805,7 +43805,7 @@
         <v>45086</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43862,7 +43862,7 @@
         <v>45090</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43924,7 +43924,7 @@
         <v>45089</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43981,7 +43981,7 @@
         <v>45090</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -44038,7 +44038,7 @@
         <v>45090</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44095,7 +44095,7 @@
         <v>45090</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44152,7 +44152,7 @@
         <v>45090</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44209,7 +44209,7 @@
         <v>45090</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44266,7 +44266,7 @@
         <v>45091</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44323,7 +44323,7 @@
         <v>45091</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44380,7 +44380,7 @@
         <v>45091</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44437,7 +44437,7 @@
         <v>45091</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44494,7 +44494,7 @@
         <v>45093</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44556,7 +44556,7 @@
         <v>45094</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44618,7 +44618,7 @@
         <v>45096</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44675,7 +44675,7 @@
         <v>45096</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44732,7 +44732,7 @@
         <v>45096</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44794,7 +44794,7 @@
         <v>45098</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44851,7 +44851,7 @@
         <v>45098</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44913,7 +44913,7 @@
         <v>45098</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44975,7 +44975,7 @@
         <v>45098</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -45037,7 +45037,7 @@
         <v>45098</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -45094,7 +45094,7 @@
         <v>45098</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45151,7 +45151,7 @@
         <v>45098</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45213,7 +45213,7 @@
         <v>45098</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45275,7 +45275,7 @@
         <v>45098</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45332,7 +45332,7 @@
         <v>45098</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45394,7 +45394,7 @@
         <v>45098</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45451,7 +45451,7 @@
         <v>45098</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45508,7 +45508,7 @@
         <v>45098</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45565,7 +45565,7 @@
         <v>45098</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45622,7 +45622,7 @@
         <v>45099</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45684,7 +45684,7 @@
         <v>45100</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45746,7 +45746,7 @@
         <v>45100</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45808,7 +45808,7 @@
         <v>45100</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45870,7 +45870,7 @@
         <v>45100</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45927,7 +45927,7 @@
         <v>45103</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45989,7 +45989,7 @@
         <v>45104</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -46046,7 +46046,7 @@
         <v>45104</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -46103,7 +46103,7 @@
         <v>45104</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46160,7 +46160,7 @@
         <v>45104</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46217,7 +46217,7 @@
         <v>45104</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46274,7 +46274,7 @@
         <v>45106</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46331,7 +46331,7 @@
         <v>45106</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46388,7 +46388,7 @@
         <v>45106</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46445,7 +46445,7 @@
         <v>45106</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46502,7 +46502,7 @@
         <v>45106</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46559,7 +46559,7 @@
         <v>45106</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46616,7 +46616,7 @@
         <v>45107</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46673,7 +46673,7 @@
         <v>45107</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46730,7 +46730,7 @@
         <v>45107</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46787,7 +46787,7 @@
         <v>45107</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46844,7 +46844,7 @@
         <v>45110</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46901,7 +46901,7 @@
         <v>45110</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46958,7 +46958,7 @@
         <v>45110</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -47015,7 +47015,7 @@
         <v>45110</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -47072,7 +47072,7 @@
         <v>45111</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47129,7 +47129,7 @@
         <v>45114</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47186,7 +47186,7 @@
         <v>45114</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47243,7 +47243,7 @@
         <v>45118</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47305,7 +47305,7 @@
         <v>45118</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47367,7 +47367,7 @@
         <v>45118</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47429,7 +47429,7 @@
         <v>45118</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47491,7 +47491,7 @@
         <v>45118</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47553,7 +47553,7 @@
         <v>45118</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47615,7 +47615,7 @@
         <v>45119</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47677,7 +47677,7 @@
         <v>45119</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47734,7 +47734,7 @@
         <v>45120</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47791,7 +47791,7 @@
         <v>45120</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47848,7 +47848,7 @@
         <v>45120</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47905,7 +47905,7 @@
         <v>45120</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47962,7 +47962,7 @@
         <v>45125</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -48019,7 +48019,7 @@
         <v>45125</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -48076,7 +48076,7 @@
         <v>45125</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -48133,7 +48133,7 @@
         <v>45129</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48190,7 +48190,7 @@
         <v>45129</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48247,7 +48247,7 @@
         <v>45135</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48304,7 +48304,7 @@
         <v>45135</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48361,7 +48361,7 @@
         <v>45138</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48418,7 +48418,7 @@
         <v>45138</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48475,7 +48475,7 @@
         <v>45139</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48532,7 +48532,7 @@
         <v>45139</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48589,7 +48589,7 @@
         <v>45139</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48646,7 +48646,7 @@
         <v>45140</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48708,7 +48708,7 @@
         <v>45140</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48765,7 +48765,7 @@
         <v>45140</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48827,7 +48827,7 @@
         <v>45141</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48884,7 +48884,7 @@
         <v>45145</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48941,7 +48941,7 @@
         <v>45152</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -49003,7 +49003,7 @@
         <v>45152</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -49065,7 +49065,7 @@
         <v>45156</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -49122,7 +49122,7 @@
         <v>45159</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49179,7 +49179,7 @@
         <v>45159</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49236,7 +49236,7 @@
         <v>45160</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49298,7 +49298,7 @@
         <v>45160</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49360,7 +49360,7 @@
         <v>45160</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49417,7 +49417,7 @@
         <v>45162</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49474,7 +49474,7 @@
         <v>45162</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49531,7 +49531,7 @@
         <v>45163</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49588,7 +49588,7 @@
         <v>45167</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49650,7 +49650,7 @@
         <v>45167</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49712,7 +49712,7 @@
         <v>45167</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49769,7 +49769,7 @@
         <v>45167</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49831,7 +49831,7 @@
         <v>45168</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49893,7 +49893,7 @@
         <v>45167</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49950,7 +49950,7 @@
         <v>45168</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -50012,7 +50012,7 @@
         <v>45168</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -50074,7 +50074,7 @@
         <v>45170</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -50131,7 +50131,7 @@
         <v>45170</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -50188,7 +50188,7 @@
         <v>45175</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -50245,7 +50245,7 @@
         <v>45176</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50307,7 +50307,7 @@
         <v>45176</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50369,7 +50369,7 @@
         <v>45176</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50426,7 +50426,7 @@
         <v>45177</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50483,7 +50483,7 @@
         <v>45177</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50540,7 +50540,7 @@
         <v>45177</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50597,7 +50597,7 @@
         <v>45180</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50654,7 +50654,7 @@
         <v>45181</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50716,7 +50716,7 @@
         <v>45181</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50778,7 +50778,7 @@
         <v>45181</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50835,7 +50835,7 @@
         <v>45181</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50892,7 +50892,7 @@
         <v>45182</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50949,7 +50949,7 @@
         <v>45183</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -51006,7 +51006,7 @@
         <v>45184</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -51068,7 +51068,7 @@
         <v>45187</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -51125,7 +51125,7 @@
         <v>45187</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -51182,7 +51182,7 @@
         <v>45187</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -51239,7 +51239,7 @@
         <v>45187</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -51296,7 +51296,7 @@
         <v>45187</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -51353,7 +51353,7 @@
         <v>45187</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -51410,7 +51410,7 @@
         <v>45187</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -51467,7 +51467,7 @@
         <v>45188</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51529,7 +51529,7 @@
         <v>45188</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51591,7 +51591,7 @@
         <v>45188</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51653,7 +51653,7 @@
         <v>45188</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51715,7 +51715,7 @@
         <v>45188</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51777,7 +51777,7 @@
         <v>45188</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51839,7 +51839,7 @@
         <v>45188</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51901,7 +51901,7 @@
         <v>45188</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51958,7 +51958,7 @@
         <v>45189</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -52020,7 +52020,7 @@
         <v>45190</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -52077,7 +52077,7 @@
         <v>45190</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -52134,7 +52134,7 @@
         <v>45190</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -52191,7 +52191,7 @@
         <v>45190</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -52248,7 +52248,7 @@
         <v>45196</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -52305,7 +52305,7 @@
         <v>45197</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -52362,7 +52362,7 @@
         <v>45197</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -52419,7 +52419,7 @@
         <v>45198</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -52481,7 +52481,7 @@
         <v>45201</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -52543,7 +52543,7 @@
         <v>45201</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52605,7 +52605,7 @@
         <v>45202</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52667,7 +52667,7 @@
         <v>45202</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52724,7 +52724,7 @@
         <v>45203</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52781,7 +52781,7 @@
         <v>45204</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52843,7 +52843,7 @@
         <v>45208</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52900,7 +52900,7 @@
         <v>45209</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52957,7 +52957,7 @@
         <v>45208</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -53019,7 +53019,7 @@
         <v>45211</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -53076,7 +53076,7 @@
         <v>45211</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -53133,7 +53133,7 @@
         <v>45211</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -53190,7 +53190,7 @@
         <v>45211</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -53252,7 +53252,7 @@
         <v>45211</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -53314,7 +53314,7 @@
         <v>45211</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -53371,7 +53371,7 @@
         <v>45212</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -53428,7 +53428,7 @@
         <v>45213</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -53485,7 +53485,7 @@
         <v>45215</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -53542,7 +53542,7 @@
         <v>45215</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53599,7 +53599,7 @@
         <v>45216</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53656,7 +53656,7 @@
         <v>45216</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53718,7 +53718,7 @@
         <v>45218</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -53775,7 +53775,7 @@
         <v>45218</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -53837,7 +53837,7 @@
         <v>45218</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -53894,7 +53894,7 @@
         <v>45218</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -53951,7 +53951,7 @@
         <v>45219</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -54008,7 +54008,7 @@
         <v>45219</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -54065,7 +54065,7 @@
         <v>45219</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -54127,7 +54127,7 @@
         <v>45219</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -54189,7 +54189,7 @@
         <v>45219</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -54246,7 +54246,7 @@
         <v>45219</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -54303,7 +54303,7 @@
         <v>45222</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -54360,7 +54360,7 @@
         <v>45222</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -54422,7 +54422,7 @@
         <v>45222</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -54479,7 +54479,7 @@
         <v>45225</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -54536,7 +54536,7 @@
         <v>45225</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -54593,7 +54593,7 @@
         <v>45230</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -54655,7 +54655,7 @@
         <v>45230</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -54712,7 +54712,7 @@
         <v>45230</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -54769,7 +54769,7 @@
         <v>45230</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -54826,7 +54826,7 @@
         <v>45232</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -54888,7 +54888,7 @@
         <v>45232</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -54950,7 +54950,7 @@
         <v>45232</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -55012,7 +55012,7 @@
         <v>45236</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -55074,7 +55074,7 @@
         <v>45236</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -55131,7 +55131,7 @@
         <v>45237</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -55188,7 +55188,7 @@
         <v>45237</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -55245,7 +55245,7 @@
         <v>45237</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -55302,7 +55302,7 @@
         <v>45237</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -55359,7 +55359,7 @@
         <v>45237</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -55421,7 +55421,7 @@
         <v>45237</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -55478,7 +55478,7 @@
         <v>45237</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -55535,7 +55535,7 @@
         <v>45238</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -55592,7 +55592,7 @@
         <v>45239</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -55649,7 +55649,7 @@
         <v>45239</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -55711,7 +55711,7 @@
         <v>45239</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -55768,7 +55768,7 @@
         <v>45239</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -55825,7 +55825,7 @@
         <v>45240</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -55882,7 +55882,7 @@
         <v>45240</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -55939,7 +55939,7 @@
         <v>45243</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -56001,7 +56001,7 @@
         <v>45243</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -56063,7 +56063,7 @@
         <v>45244</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -56120,7 +56120,7 @@
         <v>45244</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -56177,7 +56177,7 @@
         <v>45244</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -56234,7 +56234,7 @@
         <v>45244</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -56291,7 +56291,7 @@
         <v>45244</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -56348,7 +56348,7 @@
         <v>45244</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -56405,7 +56405,7 @@
         <v>45244</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -56462,7 +56462,7 @@
         <v>45244</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -56519,7 +56519,7 @@
         <v>45244</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -56576,7 +56576,7 @@
         <v>45245</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -56633,7 +56633,7 @@
         <v>45245</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -56690,7 +56690,7 @@
         <v>45245</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -56747,7 +56747,7 @@
         <v>45246</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -56804,7 +56804,7 @@
         <v>45246</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -56861,7 +56861,7 @@
         <v>45247</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -56918,7 +56918,7 @@
         <v>45251</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -56975,7 +56975,7 @@
         <v>45252</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -57032,7 +57032,7 @@
         <v>45252</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -57089,7 +57089,7 @@
         <v>45253</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -57146,7 +57146,7 @@
         <v>45254</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -57203,7 +57203,7 @@
         <v>45254</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -57260,7 +57260,7 @@
         <v>45257</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -57317,7 +57317,7 @@
         <v>45257</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -57374,7 +57374,7 @@
         <v>45258</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -57431,7 +57431,7 @@
         <v>45259</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -57488,7 +57488,7 @@
         <v>45259</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -57545,7 +57545,7 @@
         <v>45260</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -57602,7 +57602,7 @@
         <v>45260</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -57659,7 +57659,7 @@
         <v>45260</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -57716,7 +57716,7 @@
         <v>45260</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -57773,7 +57773,7 @@
         <v>45261</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -57830,7 +57830,7 @@
         <v>45261</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -57887,7 +57887,7 @@
         <v>45262</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -57944,7 +57944,7 @@
         <v>45264</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -58001,7 +58001,7 @@
         <v>45264</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -58058,7 +58058,7 @@
         <v>45264</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -58115,7 +58115,7 @@
         <v>45264</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -58177,7 +58177,7 @@
         <v>45264</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -58234,7 +58234,7 @@
         <v>45265</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -58291,7 +58291,7 @@
         <v>45265</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -58348,7 +58348,7 @@
         <v>45266</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -58405,7 +58405,7 @@
         <v>45266</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -58462,7 +58462,7 @@
         <v>45266</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -58519,7 +58519,7 @@
         <v>45267</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -58576,7 +58576,7 @@
         <v>45271</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -58633,7 +58633,7 @@
         <v>45271</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -58690,7 +58690,7 @@
         <v>45273</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -58747,7 +58747,7 @@
         <v>45273</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -58804,7 +58804,7 @@
         <v>45273</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -58861,7 +58861,7 @@
         <v>45273</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -58918,7 +58918,7 @@
         <v>45273</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -58975,7 +58975,7 @@
         <v>45273</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -59032,7 +59032,7 @@
         <v>45273</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -59089,7 +59089,7 @@
         <v>45278</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -59146,7 +59146,7 @@
         <v>45279</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -59203,7 +59203,7 @@
         <v>45279</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -59260,7 +59260,7 @@
         <v>45279</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -59317,7 +59317,7 @@
         <v>45281</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -59374,7 +59374,7 @@
         <v>45282</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -59436,7 +59436,7 @@
         <v>45285</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -59493,7 +59493,7 @@
         <v>45285</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -59550,7 +59550,7 @@
         <v>45285</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -59607,7 +59607,7 @@
         <v>45285</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -59664,7 +59664,7 @@
         <v>45287</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -59721,7 +59721,7 @@
         <v>45287</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -59778,7 +59778,7 @@
         <v>45289</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -59835,7 +59835,7 @@
         <v>45299</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -59892,7 +59892,7 @@
         <v>45308</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -59949,7 +59949,7 @@
         <v>45308</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -60006,7 +60006,7 @@
         <v>45309</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -60063,7 +60063,7 @@
         <v>45310</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -60120,7 +60120,7 @@
         <v>45310</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -60177,7 +60177,7 @@
         <v>45311</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -60234,7 +60234,7 @@
         <v>45311</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -60291,7 +60291,7 @@
         <v>45312</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -60348,7 +60348,7 @@
         <v>45312</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -60405,7 +60405,7 @@
         <v>45313</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -60462,7 +60462,7 @@
         <v>45315</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -60512,14 +60512,14 @@
     <row r="994" ht="15" customHeight="1">
       <c r="A994" t="inlineStr">
         <is>
-          <t>A 2889-2024</t>
+          <t>A 2847-2024</t>
         </is>
       </c>
       <c r="B994" s="1" t="n">
         <v>45315</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -60532,7 +60532,7 @@
         </is>
       </c>
       <c r="G994" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="H994" t="n">
         <v>0</v>
@@ -60569,14 +60569,14 @@
     <row r="995" ht="15" customHeight="1">
       <c r="A995" t="inlineStr">
         <is>
-          <t>A 2847-2024</t>
+          <t>A 2889-2024</t>
         </is>
       </c>
       <c r="B995" s="1" t="n">
         <v>45315</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -60589,7 +60589,7 @@
         </is>
       </c>
       <c r="G995" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="H995" t="n">
         <v>0</v>
@@ -60633,7 +60633,7 @@
         <v>45316</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -60690,7 +60690,7 @@
         <v>45316</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -60747,7 +60747,7 @@
         <v>45316</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -60804,7 +60804,7 @@
         <v>45320</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -60861,7 +60861,7 @@
         <v>45320</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -60918,7 +60918,7 @@
         <v>45323</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -60968,14 +60968,14 @@
     <row r="1002" ht="15" customHeight="1">
       <c r="A1002" t="inlineStr">
         <is>
-          <t>A 4049-2024</t>
+          <t>A 4122-2024</t>
         </is>
       </c>
       <c r="B1002" s="1" t="n">
         <v>45323</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -60985,6 +60985,11 @@
       <c r="E1002" t="inlineStr">
         <is>
           <t>PITEÅ</t>
+        </is>
+      </c>
+      <c r="F1002" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="G1002" t="n">
@@ -61025,14 +61030,14 @@
     <row r="1003" ht="15" customHeight="1">
       <c r="A1003" t="inlineStr">
         <is>
-          <t>A 4127-2024</t>
+          <t>A 4049-2024</t>
         </is>
       </c>
       <c r="B1003" s="1" t="n">
         <v>45323</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -61044,13 +61049,8 @@
           <t>PITEÅ</t>
         </is>
       </c>
-      <c r="F1003" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="G1003" t="n">
-        <v>4.5</v>
+        <v>2.8</v>
       </c>
       <c r="H1003" t="n">
         <v>0</v>
@@ -61087,14 +61087,14 @@
     <row r="1004" ht="15" customHeight="1">
       <c r="A1004" t="inlineStr">
         <is>
-          <t>A 4122-2024</t>
+          <t>A 4127-2024</t>
         </is>
       </c>
       <c r="B1004" s="1" t="n">
         <v>45323</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -61112,7 +61112,7 @@
         </is>
       </c>
       <c r="G1004" t="n">
-        <v>2.8</v>
+        <v>4.5</v>
       </c>
       <c r="H1004" t="n">
         <v>0</v>
@@ -61156,7 +61156,7 @@
         <v>45323</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -61218,7 +61218,7 @@
         <v>45324</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -61268,14 +61268,14 @@
     <row r="1007" ht="15" customHeight="1">
       <c r="A1007" t="inlineStr">
         <is>
-          <t>A 4232-2024</t>
+          <t>A 4242-2024</t>
         </is>
       </c>
       <c r="B1007" s="1" t="n">
         <v>45324</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -61293,7 +61293,7 @@
         </is>
       </c>
       <c r="G1007" t="n">
-        <v>11.1</v>
+        <v>3.9</v>
       </c>
       <c r="H1007" t="n">
         <v>0</v>
@@ -61330,14 +61330,14 @@
     <row r="1008" ht="15" customHeight="1">
       <c r="A1008" t="inlineStr">
         <is>
-          <t>A 4242-2024</t>
+          <t>A 4232-2024</t>
         </is>
       </c>
       <c r="B1008" s="1" t="n">
         <v>45324</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -61355,7 +61355,7 @@
         </is>
       </c>
       <c r="G1008" t="n">
-        <v>3.9</v>
+        <v>11.1</v>
       </c>
       <c r="H1008" t="n">
         <v>0</v>
@@ -61399,7 +61399,7 @@
         <v>45329</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -61456,7 +61456,7 @@
         <v>45330</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -61513,7 +61513,7 @@
         <v>45334</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -61570,7 +61570,7 @@
         <v>45335</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -61627,7 +61627,7 @@
         <v>45342</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -61684,7 +61684,7 @@
         <v>45343</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -61741,7 +61741,7 @@
         <v>45343</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>

--- a/Översikt PITEÅ.xlsx
+++ b/Översikt PITEÅ.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z1015"/>
+  <dimension ref="A1:Z1019"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>44617</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -665,7 +665,7 @@
         <v>44839</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
         <v>44839</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>44459</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
         <v>44617</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>43896</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>45191</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>45203</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>44740</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>44280</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>44539</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>44550</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>45119</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>44014</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>44522</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>44526</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         <v>44553</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>44810</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>44917</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>45103</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>45106</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         <v>43802</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>43902</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2727,7 +2727,7 @@
         <v>43908</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         <v>44053</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2908,7 +2908,7 @@
         <v>44193</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>44298</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>44840</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
         <v>44852</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3262,7 +3262,7 @@
         <v>44859</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>44944</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3434,7 +3434,7 @@
         <v>45120</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
         <v>45187</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         <v>45209</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3701,7 +3701,7 @@
         <v>45219</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>45243</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         <v>45293</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
         <v>45296</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>43714</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         <v>44014</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4225,7 +4225,7 @@
         <v>44106</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4310,7 +4310,7 @@
         <v>44309</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>44342</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4485,7 +4485,7 @@
         <v>44495</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
         <v>44525</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4665,7 +4665,7 @@
         <v>44525</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4755,7 +4755,7 @@
         <v>44538</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4840,7 +4840,7 @@
         <v>44727</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4929,7 +4929,7 @@
         <v>44804</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5014,7 +5014,7 @@
         <v>44917</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5104,7 +5104,7 @@
         <v>45049</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5193,7 +5193,7 @@
         <v>45098</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>45103</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5373,7 +5373,7 @@
         <v>45148</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
         <v>45175</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         <v>45181</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5642,7 +5642,7 @@
         <v>45188</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5732,7 +5732,7 @@
         <v>45224</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5817,7 +5817,7 @@
         <v>45243</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5907,7 +5907,7 @@
         <v>45265</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5992,7 +5992,7 @@
         <v>45323</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
         <v>43325</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6139,7 +6139,7 @@
         <v>43332</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6196,7 +6196,7 @@
         <v>43336</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6253,7 +6253,7 @@
         <v>43339</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         <v>43339</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
         <v>43341</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6424,7 +6424,7 @@
         <v>43355</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>43355</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         <v>43374</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6600,7 +6600,7 @@
         <v>43374</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6662,7 +6662,7 @@
         <v>43375</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6719,7 +6719,7 @@
         <v>43376</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
         <v>43376</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6833,7 +6833,7 @@
         <v>43381</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6890,7 +6890,7 @@
         <v>43383</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6947,7 +6947,7 @@
         <v>43391</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>43391</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7061,7 +7061,7 @@
         <v>43392</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7118,7 +7118,7 @@
         <v>43392</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7175,7 +7175,7 @@
         <v>43398</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7232,7 +7232,7 @@
         <v>43402</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7289,7 +7289,7 @@
         <v>43404</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7346,7 +7346,7 @@
         <v>43406</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7403,7 +7403,7 @@
         <v>43406</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
         <v>43406</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>43406</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>43406</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>43416</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>43418</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7745,7 +7745,7 @@
         <v>43418</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7802,7 +7802,7 @@
         <v>43418</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         <v>43419</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7916,7 +7916,7 @@
         <v>43420</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         <v>43424</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8035,7 +8035,7 @@
         <v>43427</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8097,7 +8097,7 @@
         <v>43427</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8154,7 +8154,7 @@
         <v>43427</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8216,7 +8216,7 @@
         <v>43427</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8278,7 +8278,7 @@
         <v>43436</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
         <v>43438</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8392,7 +8392,7 @@
         <v>43438</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8449,7 +8449,7 @@
         <v>43438</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8506,7 +8506,7 @@
         <v>43438</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8563,7 +8563,7 @@
         <v>43451</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8625,7 +8625,7 @@
         <v>43472</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8682,7 +8682,7 @@
         <v>43475</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8739,7 +8739,7 @@
         <v>43479</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8796,7 +8796,7 @@
         <v>43479</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8853,7 +8853,7 @@
         <v>43486</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
         <v>43489</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8967,7 +8967,7 @@
         <v>43489</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9024,7 +9024,7 @@
         <v>43489</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9081,7 +9081,7 @@
         <v>43489</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9138,7 +9138,7 @@
         <v>43489</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9195,7 +9195,7 @@
         <v>43490</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9252,7 +9252,7 @@
         <v>43490</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9309,7 +9309,7 @@
         <v>43493</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9371,7 +9371,7 @@
         <v>43509</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9428,7 +9428,7 @@
         <v>43510</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9485,7 +9485,7 @@
         <v>43510</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9542,7 +9542,7 @@
         <v>43514</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9599,7 +9599,7 @@
         <v>43514</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9656,7 +9656,7 @@
         <v>43514</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9713,7 +9713,7 @@
         <v>43516</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9775,7 +9775,7 @@
         <v>43518</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9832,7 +9832,7 @@
         <v>43521</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9894,7 +9894,7 @@
         <v>43521</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9956,7 +9956,7 @@
         <v>43521</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10018,7 +10018,7 @@
         <v>43521</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10080,7 +10080,7 @@
         <v>43521</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10142,7 +10142,7 @@
         <v>43522</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10199,7 +10199,7 @@
         <v>43523</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10256,7 +10256,7 @@
         <v>43523</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10313,7 +10313,7 @@
         <v>43523</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10370,7 +10370,7 @@
         <v>43532</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10427,7 +10427,7 @@
         <v>43532</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10484,7 +10484,7 @@
         <v>43542</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10541,7 +10541,7 @@
         <v>43544</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10603,7 +10603,7 @@
         <v>43544</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10665,7 +10665,7 @@
         <v>43554</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10722,7 +10722,7 @@
         <v>43556</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10779,7 +10779,7 @@
         <v>43557</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10841,7 +10841,7 @@
         <v>43557</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10898,7 +10898,7 @@
         <v>43557</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10955,7 +10955,7 @@
         <v>43557</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11012,7 +11012,7 @@
         <v>43557</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11074,7 +11074,7 @@
         <v>43564</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11131,7 +11131,7 @@
         <v>43564</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11188,7 +11188,7 @@
         <v>43567</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11245,7 +11245,7 @@
         <v>43570</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11302,7 +11302,7 @@
         <v>43570</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11359,7 +11359,7 @@
         <v>43570</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11416,7 +11416,7 @@
         <v>43584</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11473,7 +11473,7 @@
         <v>43605</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11530,7 +11530,7 @@
         <v>43608</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11587,7 +11587,7 @@
         <v>43614</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11649,7 +11649,7 @@
         <v>43616</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11711,7 +11711,7 @@
         <v>43616</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11773,7 +11773,7 @@
         <v>43629</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11830,7 +11830,7 @@
         <v>43629</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11892,7 +11892,7 @@
         <v>43633</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11949,7 +11949,7 @@
         <v>43633</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12006,7 +12006,7 @@
         <v>43640</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12063,7 +12063,7 @@
         <v>43640</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12120,7 +12120,7 @@
         <v>43647</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12177,7 +12177,7 @@
         <v>43647</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12234,7 +12234,7 @@
         <v>43650</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12291,7 +12291,7 @@
         <v>43652</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12353,7 +12353,7 @@
         <v>43677</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12410,7 +12410,7 @@
         <v>43678</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12467,7 +12467,7 @@
         <v>43682</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12524,7 +12524,7 @@
         <v>43691</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12586,7 +12586,7 @@
         <v>43691</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12648,7 +12648,7 @@
         <v>43696</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12710,7 +12710,7 @@
         <v>43697</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12767,7 +12767,7 @@
         <v>43698</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12829,7 +12829,7 @@
         <v>43698</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12891,7 +12891,7 @@
         <v>43706</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12948,7 +12948,7 @@
         <v>43707</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13010,7 +13010,7 @@
         <v>43711</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13067,7 +13067,7 @@
         <v>43713</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13124,7 +13124,7 @@
         <v>43718</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13181,7 +13181,7 @@
         <v>43718</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13238,7 +13238,7 @@
         <v>43718</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13300,7 +13300,7 @@
         <v>43720</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13357,7 +13357,7 @@
         <v>43721</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13414,7 +13414,7 @@
         <v>43732</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13471,7 +13471,7 @@
         <v>43741</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13533,7 +13533,7 @@
         <v>43741</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13590,7 +13590,7 @@
         <v>43752</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13652,7 +13652,7 @@
         <v>43755</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13709,7 +13709,7 @@
         <v>43755</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13766,7 +13766,7 @@
         <v>43755</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13823,7 +13823,7 @@
         <v>43755</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13880,7 +13880,7 @@
         <v>43760</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13942,7 +13942,7 @@
         <v>43760</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14004,7 +14004,7 @@
         <v>43760</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14061,7 +14061,7 @@
         <v>43762</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14123,7 +14123,7 @@
         <v>43766</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14180,7 +14180,7 @@
         <v>43766</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14237,7 +14237,7 @@
         <v>43768</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14294,7 +14294,7 @@
         <v>43770</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14356,7 +14356,7 @@
         <v>43775</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14418,7 +14418,7 @@
         <v>43775</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14480,7 +14480,7 @@
         <v>43777</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14537,7 +14537,7 @@
         <v>43780</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14594,7 +14594,7 @@
         <v>43780</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14651,7 +14651,7 @@
         <v>43780</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14708,7 +14708,7 @@
         <v>43782</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14770,7 +14770,7 @@
         <v>43789</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14832,7 +14832,7 @@
         <v>43798</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14889,7 +14889,7 @@
         <v>43801</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14951,7 +14951,7 @@
         <v>43802</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15008,7 +15008,7 @@
         <v>43802</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15065,7 +15065,7 @@
         <v>43802</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15122,7 +15122,7 @@
         <v>43802</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15179,7 +15179,7 @@
         <v>43802</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15236,7 +15236,7 @@
         <v>43802</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15293,7 +15293,7 @@
         <v>43807</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15350,7 +15350,7 @@
         <v>43809</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15407,7 +15407,7 @@
         <v>43817</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15464,7 +15464,7 @@
         <v>43817</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15526,7 +15526,7 @@
         <v>43822</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15583,7 +15583,7 @@
         <v>43822</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15640,7 +15640,7 @@
         <v>43833</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15697,7 +15697,7 @@
         <v>43846</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15754,7 +15754,7 @@
         <v>43852</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15811,7 +15811,7 @@
         <v>43853</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15868,7 +15868,7 @@
         <v>43854</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15925,7 +15925,7 @@
         <v>43859</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15987,7 +15987,7 @@
         <v>43859</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16044,7 +16044,7 @@
         <v>43859</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16101,7 +16101,7 @@
         <v>43859</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16158,7 +16158,7 @@
         <v>43859</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16215,7 +16215,7 @@
         <v>43860</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16272,7 +16272,7 @@
         <v>43868</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16329,7 +16329,7 @@
         <v>43868</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16386,7 +16386,7 @@
         <v>43874</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16448,7 +16448,7 @@
         <v>43878</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16505,7 +16505,7 @@
         <v>43880</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16562,7 +16562,7 @@
         <v>43880</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16619,7 +16619,7 @@
         <v>43889</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16676,7 +16676,7 @@
         <v>43895</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16738,7 +16738,7 @@
         <v>43896</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16795,7 +16795,7 @@
         <v>43902</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16852,7 +16852,7 @@
         <v>43902</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16914,7 +16914,7 @@
         <v>43907</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16971,7 +16971,7 @@
         <v>43913</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17028,7 +17028,7 @@
         <v>43914</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17090,7 +17090,7 @@
         <v>43927</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17152,7 +17152,7 @@
         <v>43929</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         <v>43929</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>43931</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17328,7 +17328,7 @@
         <v>43950</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17385,7 +17385,7 @@
         <v>43957</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17447,7 +17447,7 @@
         <v>43958</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17504,7 +17504,7 @@
         <v>43958</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17561,7 +17561,7 @@
         <v>43959</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17618,7 +17618,7 @@
         <v>43962</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17675,7 +17675,7 @@
         <v>43962</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17732,7 +17732,7 @@
         <v>43962</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17789,7 +17789,7 @@
         <v>43962</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17846,7 +17846,7 @@
         <v>43970</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17908,7 +17908,7 @@
         <v>43971</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17970,7 +17970,7 @@
         <v>43976</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18027,7 +18027,7 @@
         <v>43979</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18084,7 +18084,7 @@
         <v>43979</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18141,7 +18141,7 @@
         <v>43979</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18198,7 +18198,7 @@
         <v>43984</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18260,7 +18260,7 @@
         <v>43984</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18317,7 +18317,7 @@
         <v>43987</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18374,7 +18374,7 @@
         <v>43990</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18431,7 +18431,7 @@
         <v>43994</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18493,7 +18493,7 @@
         <v>43997</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18550,7 +18550,7 @@
         <v>43999</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18607,7 +18607,7 @@
         <v>44000</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18669,7 +18669,7 @@
         <v>44006</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18726,7 +18726,7 @@
         <v>44006</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18783,7 +18783,7 @@
         <v>44007</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18840,7 +18840,7 @@
         <v>44007</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18897,7 +18897,7 @@
         <v>44011</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18954,7 +18954,7 @@
         <v>44012</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19016,7 +19016,7 @@
         <v>44020</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19078,7 +19078,7 @@
         <v>44020</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19135,7 +19135,7 @@
         <v>44020</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19197,7 +19197,7 @@
         <v>44026</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19259,7 +19259,7 @@
         <v>44035</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19316,7 +19316,7 @@
         <v>44049</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19373,7 +19373,7 @@
         <v>44063</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19435,7 +19435,7 @@
         <v>44067</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19497,7 +19497,7 @@
         <v>44067</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19559,7 +19559,7 @@
         <v>44068</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19621,7 +19621,7 @@
         <v>44069</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19678,7 +19678,7 @@
         <v>44070</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19735,7 +19735,7 @@
         <v>44074</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19792,7 +19792,7 @@
         <v>44075</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19849,7 +19849,7 @@
         <v>44078</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19906,7 +19906,7 @@
         <v>44083</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19963,7 +19963,7 @@
         <v>44083</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20020,7 +20020,7 @@
         <v>44087</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20077,7 +20077,7 @@
         <v>44088</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20139,7 +20139,7 @@
         <v>44088</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20196,7 +20196,7 @@
         <v>44088</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20258,7 +20258,7 @@
         <v>44092</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20315,7 +20315,7 @@
         <v>44092</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20372,7 +20372,7 @@
         <v>44092</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20429,7 +20429,7 @@
         <v>44095</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20486,7 +20486,7 @@
         <v>44099</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20543,7 +20543,7 @@
         <v>44099</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20600,7 +20600,7 @@
         <v>44099</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20657,7 +20657,7 @@
         <v>44099</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20714,7 +20714,7 @@
         <v>44103</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20771,7 +20771,7 @@
         <v>44103</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20828,7 +20828,7 @@
         <v>44106</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20885,7 +20885,7 @@
         <v>44111</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20947,7 +20947,7 @@
         <v>44111</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21009,7 +21009,7 @@
         <v>44123</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21066,7 +21066,7 @@
         <v>44127</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21123,7 +21123,7 @@
         <v>44132</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21180,7 +21180,7 @@
         <v>44139</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21237,7 +21237,7 @@
         <v>44141</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21294,7 +21294,7 @@
         <v>44141</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21351,7 +21351,7 @@
         <v>44155</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21408,7 +21408,7 @@
         <v>44162</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21470,7 +21470,7 @@
         <v>44166</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21532,7 +21532,7 @@
         <v>44172</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21589,7 +21589,7 @@
         <v>44180</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21646,7 +21646,7 @@
         <v>44186</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21703,7 +21703,7 @@
         <v>44209</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21760,7 +21760,7 @@
         <v>44211</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21817,7 +21817,7 @@
         <v>44211</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21874,7 +21874,7 @@
         <v>44211</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21931,7 +21931,7 @@
         <v>44215</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21993,7 +21993,7 @@
         <v>44221</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22055,7 +22055,7 @@
         <v>44237</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22117,7 +22117,7 @@
         <v>44238</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22174,7 +22174,7 @@
         <v>44256</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22231,7 +22231,7 @@
         <v>44257</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22288,7 +22288,7 @@
         <v>44258</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22345,7 +22345,7 @@
         <v>44280</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22407,7 +22407,7 @@
         <v>44281</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22464,7 +22464,7 @@
         <v>44281</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22521,7 +22521,7 @@
         <v>44281</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22578,7 +22578,7 @@
         <v>44285</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22640,7 +22640,7 @@
         <v>44286</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22697,7 +22697,7 @@
         <v>44292</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22754,7 +22754,7 @@
         <v>44294</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22816,7 +22816,7 @@
         <v>44309</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22873,7 +22873,7 @@
         <v>44320</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22930,7 +22930,7 @@
         <v>44321</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22987,7 +22987,7 @@
         <v>44321</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23044,7 +23044,7 @@
         <v>44326</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23101,7 +23101,7 @@
         <v>44326</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23163,7 +23163,7 @@
         <v>44334</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23220,7 +23220,7 @@
         <v>44339</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23277,7 +23277,7 @@
         <v>44339</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23334,7 +23334,7 @@
         <v>44339</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23391,7 +23391,7 @@
         <v>44343</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23453,7 +23453,7 @@
         <v>44342</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23515,7 +23515,7 @@
         <v>44344</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23572,7 +23572,7 @@
         <v>44350</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23629,7 +23629,7 @@
         <v>44350</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23686,7 +23686,7 @@
         <v>44351</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23748,7 +23748,7 @@
         <v>44354</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23810,7 +23810,7 @@
         <v>44355</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23872,7 +23872,7 @@
         <v>44355</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23934,7 +23934,7 @@
         <v>44357</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23991,7 +23991,7 @@
         <v>44358</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24053,7 +24053,7 @@
         <v>44361</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24110,7 +24110,7 @@
         <v>44361</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24167,7 +24167,7 @@
         <v>44361</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24224,7 +24224,7 @@
         <v>44362</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24286,7 +24286,7 @@
         <v>44361</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24348,7 +24348,7 @@
         <v>44362</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24405,7 +24405,7 @@
         <v>44368</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24467,7 +24467,7 @@
         <v>44368</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24529,7 +24529,7 @@
         <v>44368</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24591,7 +24591,7 @@
         <v>44369</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24653,7 +24653,7 @@
         <v>44370</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24715,7 +24715,7 @@
         <v>44370</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24777,7 +24777,7 @@
         <v>44370</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24839,7 +24839,7 @@
         <v>44370</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24901,7 +24901,7 @@
         <v>44371</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24963,7 +24963,7 @@
         <v>44372</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25025,7 +25025,7 @@
         <v>44372</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25087,7 +25087,7 @@
         <v>44375</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25149,7 +25149,7 @@
         <v>44376</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25211,7 +25211,7 @@
         <v>44376</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25273,7 +25273,7 @@
         <v>44376</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25330,7 +25330,7 @@
         <v>44377</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25392,7 +25392,7 @@
         <v>44378</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25449,7 +25449,7 @@
         <v>44378</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25511,7 +25511,7 @@
         <v>44378</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25568,7 +25568,7 @@
         <v>44383</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25625,7 +25625,7 @@
         <v>44383</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25682,7 +25682,7 @@
         <v>44383</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25739,7 +25739,7 @@
         <v>44383</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25796,7 +25796,7 @@
         <v>44383</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25853,7 +25853,7 @@
         <v>44384</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25915,7 +25915,7 @@
         <v>44383</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25972,7 +25972,7 @@
         <v>44386</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26029,7 +26029,7 @@
         <v>44398</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26086,7 +26086,7 @@
         <v>44404</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26143,7 +26143,7 @@
         <v>44405</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26205,7 +26205,7 @@
         <v>44418</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26267,7 +26267,7 @@
         <v>44421</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26329,7 +26329,7 @@
         <v>44428</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26386,7 +26386,7 @@
         <v>44432</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26443,7 +26443,7 @@
         <v>44432</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26500,7 +26500,7 @@
         <v>44433</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26562,7 +26562,7 @@
         <v>44433</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26624,7 +26624,7 @@
         <v>44438</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26686,7 +26686,7 @@
         <v>44439</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26748,7 +26748,7 @@
         <v>44440</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26805,7 +26805,7 @@
         <v>44441</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26867,7 +26867,7 @@
         <v>44440</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26929,7 +26929,7 @@
         <v>44446</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26986,7 +26986,7 @@
         <v>44447</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27048,7 +27048,7 @@
         <v>44453</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27105,7 +27105,7 @@
         <v>44454</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27162,7 +27162,7 @@
         <v>44454</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27219,7 +27219,7 @@
         <v>44459</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27276,7 +27276,7 @@
         <v>44463</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27338,7 +27338,7 @@
         <v>44463</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27400,7 +27400,7 @@
         <v>44463</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27457,7 +27457,7 @@
         <v>44468</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27514,7 +27514,7 @@
         <v>44468</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27571,7 +27571,7 @@
         <v>44476</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27628,7 +27628,7 @@
         <v>44480</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27685,7 +27685,7 @@
         <v>44481</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27742,7 +27742,7 @@
         <v>44484</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27799,7 +27799,7 @@
         <v>44487</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27861,7 +27861,7 @@
         <v>44490</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27918,7 +27918,7 @@
         <v>44489</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27980,7 +27980,7 @@
         <v>44496</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28037,7 +28037,7 @@
         <v>44497</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28099,7 +28099,7 @@
         <v>44497</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28156,7 +28156,7 @@
         <v>44497</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28213,7 +28213,7 @@
         <v>44498</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28270,7 +28270,7 @@
         <v>44498</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28327,7 +28327,7 @@
         <v>44499</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28384,7 +28384,7 @@
         <v>44502</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28441,7 +28441,7 @@
         <v>44516</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28498,7 +28498,7 @@
         <v>44522</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28555,7 +28555,7 @@
         <v>44523</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28612,7 +28612,7 @@
         <v>44525</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28674,7 +28674,7 @@
         <v>44525</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28731,7 +28731,7 @@
         <v>44529</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28788,7 +28788,7 @@
         <v>44530</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28850,7 +28850,7 @@
         <v>44530</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28912,7 +28912,7 @@
         <v>44531</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28969,7 +28969,7 @@
         <v>44531</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29026,7 +29026,7 @@
         <v>44536</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29083,7 +29083,7 @@
         <v>44536</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29140,7 +29140,7 @@
         <v>44538</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29197,7 +29197,7 @@
         <v>44538</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29254,7 +29254,7 @@
         <v>44538</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29311,7 +29311,7 @@
         <v>44538</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29368,7 +29368,7 @@
         <v>44538</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29425,7 +29425,7 @@
         <v>44538</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29482,7 +29482,7 @@
         <v>44538</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29539,7 +29539,7 @@
         <v>44538</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29596,7 +29596,7 @@
         <v>44539</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29658,7 +29658,7 @@
         <v>44543</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29720,7 +29720,7 @@
         <v>44543</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29782,7 +29782,7 @@
         <v>44543</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29844,7 +29844,7 @@
         <v>44543</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29906,7 +29906,7 @@
         <v>44547</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29968,7 +29968,7 @@
         <v>44550</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30025,7 +30025,7 @@
         <v>44550</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30082,7 +30082,7 @@
         <v>44571</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30139,7 +30139,7 @@
         <v>44582</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30196,7 +30196,7 @@
         <v>44582</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30253,7 +30253,7 @@
         <v>44582</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30310,7 +30310,7 @@
         <v>44582</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30367,7 +30367,7 @@
         <v>44588</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30424,7 +30424,7 @@
         <v>44589</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30481,7 +30481,7 @@
         <v>44590</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30538,7 +30538,7 @@
         <v>44590</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30595,7 +30595,7 @@
         <v>44592</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30652,7 +30652,7 @@
         <v>44592</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30709,7 +30709,7 @@
         <v>44596</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30766,7 +30766,7 @@
         <v>44599</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30823,7 +30823,7 @@
         <v>44608</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30880,7 +30880,7 @@
         <v>44615</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30937,7 +30937,7 @@
         <v>44616</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30999,7 +30999,7 @@
         <v>44617</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31061,7 +31061,7 @@
         <v>44621</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31118,7 +31118,7 @@
         <v>44621</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31180,7 +31180,7 @@
         <v>44622</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31237,7 +31237,7 @@
         <v>44623</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31294,7 +31294,7 @@
         <v>44642</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31351,7 +31351,7 @@
         <v>44643</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31408,7 +31408,7 @@
         <v>44643</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31470,7 +31470,7 @@
         <v>44644</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31527,7 +31527,7 @@
         <v>44656</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31584,7 +31584,7 @@
         <v>44658</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31641,7 +31641,7 @@
         <v>44683</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31698,7 +31698,7 @@
         <v>44683</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31755,7 +31755,7 @@
         <v>44685</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31812,7 +31812,7 @@
         <v>44685</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31869,7 +31869,7 @@
         <v>44685</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31926,7 +31926,7 @@
         <v>44687</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31983,7 +31983,7 @@
         <v>44700</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32040,7 +32040,7 @@
         <v>44708</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32097,7 +32097,7 @@
         <v>44708</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32154,7 +32154,7 @@
         <v>44708</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32211,7 +32211,7 @@
         <v>44722</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32268,7 +32268,7 @@
         <v>44727</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32330,7 +32330,7 @@
         <v>44729</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32392,7 +32392,7 @@
         <v>44735</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32449,7 +32449,7 @@
         <v>44735</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32506,7 +32506,7 @@
         <v>44741</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32563,7 +32563,7 @@
         <v>44741</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32620,7 +32620,7 @@
         <v>44741</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32677,7 +32677,7 @@
         <v>44743</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32739,7 +32739,7 @@
         <v>44743</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32796,7 +32796,7 @@
         <v>44748</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32858,7 +32858,7 @@
         <v>44747</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32920,7 +32920,7 @@
         <v>44748</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32982,7 +32982,7 @@
         <v>44748</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33039,7 +33039,7 @@
         <v>44750</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33096,7 +33096,7 @@
         <v>44756</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33153,7 +33153,7 @@
         <v>44761</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33210,7 +33210,7 @@
         <v>44776</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33267,7 +33267,7 @@
         <v>44777</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33329,7 +33329,7 @@
         <v>44781</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33386,7 +33386,7 @@
         <v>44783</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33443,7 +33443,7 @@
         <v>44785</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33505,7 +33505,7 @@
         <v>44784</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33567,7 +33567,7 @@
         <v>44785</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33624,7 +33624,7 @@
         <v>44792</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33681,7 +33681,7 @@
         <v>44792</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33743,7 +33743,7 @@
         <v>44795</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33800,7 +33800,7 @@
         <v>44795</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33862,7 +33862,7 @@
         <v>44803</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33924,7 +33924,7 @@
         <v>44805</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33986,7 +33986,7 @@
         <v>44806</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34043,7 +34043,7 @@
         <v>44809</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34105,7 +34105,7 @@
         <v>44809</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34167,7 +34167,7 @@
         <v>44811</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34224,7 +34224,7 @@
         <v>44813</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34281,7 +34281,7 @@
         <v>44813</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34338,7 +34338,7 @@
         <v>44813</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34395,7 +34395,7 @@
         <v>44813</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34452,7 +34452,7 @@
         <v>44813</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34509,7 +34509,7 @@
         <v>44816</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34566,7 +34566,7 @@
         <v>44816</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34623,7 +34623,7 @@
         <v>44817</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34685,7 +34685,7 @@
         <v>44817</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34742,7 +34742,7 @@
         <v>44818</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34804,7 +34804,7 @@
         <v>44818</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34866,7 +34866,7 @@
         <v>44818</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34928,7 +34928,7 @@
         <v>44817</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34985,7 +34985,7 @@
         <v>44818</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35047,7 +35047,7 @@
         <v>44818</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35109,7 +35109,7 @@
         <v>44818</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35171,7 +35171,7 @@
         <v>44818</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35228,7 +35228,7 @@
         <v>44819</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35285,7 +35285,7 @@
         <v>44820</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35342,7 +35342,7 @@
         <v>44823</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35404,7 +35404,7 @@
         <v>44824</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35461,7 +35461,7 @@
         <v>44827</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35523,7 +35523,7 @@
         <v>44838</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35585,7 +35585,7 @@
         <v>44838</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35642,7 +35642,7 @@
         <v>44839</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35699,7 +35699,7 @@
         <v>44840</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35756,7 +35756,7 @@
         <v>44840</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35813,7 +35813,7 @@
         <v>44841</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35875,7 +35875,7 @@
         <v>44845</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35937,7 +35937,7 @@
         <v>44845</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35999,7 +35999,7 @@
         <v>44848</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36061,7 +36061,7 @@
         <v>44848</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36123,7 +36123,7 @@
         <v>44849</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36185,7 +36185,7 @@
         <v>44848</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36242,7 +36242,7 @@
         <v>44853</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36304,7 +36304,7 @@
         <v>44853</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36366,7 +36366,7 @@
         <v>44853</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36428,7 +36428,7 @@
         <v>44856</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36490,7 +36490,7 @@
         <v>44855</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36552,7 +36552,7 @@
         <v>44857</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36609,7 +36609,7 @@
         <v>44859</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36666,7 +36666,7 @@
         <v>44859</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36723,7 +36723,7 @@
         <v>44861</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36785,7 +36785,7 @@
         <v>44861</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36842,7 +36842,7 @@
         <v>44861</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36904,7 +36904,7 @@
         <v>44861</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36961,7 +36961,7 @@
         <v>44861</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37023,7 +37023,7 @@
         <v>44861</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37085,7 +37085,7 @@
         <v>44861</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37142,7 +37142,7 @@
         <v>44862</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37204,7 +37204,7 @@
         <v>44866</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37266,7 +37266,7 @@
         <v>44867</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37328,7 +37328,7 @@
         <v>44867</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37390,7 +37390,7 @@
         <v>44867</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37447,7 +37447,7 @@
         <v>44868</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37504,7 +37504,7 @@
         <v>44873</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37566,7 +37566,7 @@
         <v>44874</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37623,7 +37623,7 @@
         <v>44874</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37685,7 +37685,7 @@
         <v>44875</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37742,7 +37742,7 @@
         <v>44879</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37799,7 +37799,7 @@
         <v>44879</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37856,7 +37856,7 @@
         <v>44879</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37913,7 +37913,7 @@
         <v>44879</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37970,7 +37970,7 @@
         <v>44883</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38032,7 +38032,7 @@
         <v>44886</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38089,7 +38089,7 @@
         <v>44888</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38146,7 +38146,7 @@
         <v>44888</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38203,7 +38203,7 @@
         <v>44889</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38265,7 +38265,7 @@
         <v>44889</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38327,7 +38327,7 @@
         <v>44890</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38384,7 +38384,7 @@
         <v>44890</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38441,7 +38441,7 @@
         <v>44890</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38503,7 +38503,7 @@
         <v>44893</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38565,7 +38565,7 @@
         <v>44895</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38627,7 +38627,7 @@
         <v>44897</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38684,7 +38684,7 @@
         <v>44901</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38741,7 +38741,7 @@
         <v>44904</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38798,7 +38798,7 @@
         <v>44907</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38855,7 +38855,7 @@
         <v>44907</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38912,7 +38912,7 @@
         <v>44909</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38974,7 +38974,7 @@
         <v>44910</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39031,7 +39031,7 @@
         <v>44910</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39088,7 +39088,7 @@
         <v>44911</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39150,7 +39150,7 @@
         <v>44911</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39212,7 +39212,7 @@
         <v>44911</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39269,7 +39269,7 @@
         <v>44916</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39326,7 +39326,7 @@
         <v>44917</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39388,7 +39388,7 @@
         <v>44929</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39445,7 +39445,7 @@
         <v>44929</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39502,7 +39502,7 @@
         <v>44941</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39559,7 +39559,7 @@
         <v>44942</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39616,7 +39616,7 @@
         <v>44942</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39673,7 +39673,7 @@
         <v>44942</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39730,7 +39730,7 @@
         <v>44942</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39787,7 +39787,7 @@
         <v>44944</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39844,7 +39844,7 @@
         <v>44950</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39901,7 +39901,7 @@
         <v>44951</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39958,7 +39958,7 @@
         <v>44960</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40015,7 +40015,7 @@
         <v>44963</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40072,7 +40072,7 @@
         <v>44965</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40129,7 +40129,7 @@
         <v>44965</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40186,7 +40186,7 @@
         <v>44966</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40243,7 +40243,7 @@
         <v>44966</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40300,7 +40300,7 @@
         <v>44971</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40362,7 +40362,7 @@
         <v>44971</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40419,7 +40419,7 @@
         <v>44972</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40476,7 +40476,7 @@
         <v>44973</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40533,7 +40533,7 @@
         <v>44973</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40590,7 +40590,7 @@
         <v>44973</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40647,7 +40647,7 @@
         <v>44977</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40704,7 +40704,7 @@
         <v>44981</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40761,7 +40761,7 @@
         <v>44984</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40818,7 +40818,7 @@
         <v>44985</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40875,7 +40875,7 @@
         <v>44985</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40932,7 +40932,7 @@
         <v>44985</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40989,7 +40989,7 @@
         <v>44991</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41046,7 +41046,7 @@
         <v>44991</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41103,7 +41103,7 @@
         <v>45006</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41160,7 +41160,7 @@
         <v>45006</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41217,7 +41217,7 @@
         <v>45013</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41274,7 +41274,7 @@
         <v>45015</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41336,7 +41336,7 @@
         <v>45015</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41398,7 +41398,7 @@
         <v>45015</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41455,7 +41455,7 @@
         <v>45021</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41512,7 +41512,7 @@
         <v>45021</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41569,7 +41569,7 @@
         <v>45028</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41626,7 +41626,7 @@
         <v>45029</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41683,7 +41683,7 @@
         <v>45030</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41740,7 +41740,7 @@
         <v>45036</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41797,7 +41797,7 @@
         <v>45036</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41854,7 +41854,7 @@
         <v>45036</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41911,7 +41911,7 @@
         <v>45035</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41973,7 +41973,7 @@
         <v>45036</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42030,7 +42030,7 @@
         <v>45035</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42087,7 +42087,7 @@
         <v>45043</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42144,7 +42144,7 @@
         <v>45043</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42201,7 +42201,7 @@
         <v>45043</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42258,7 +42258,7 @@
         <v>45044</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42320,7 +42320,7 @@
         <v>45048</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42377,7 +42377,7 @@
         <v>45050</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42434,7 +42434,7 @@
         <v>45055</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42491,7 +42491,7 @@
         <v>45057</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42548,7 +42548,7 @@
         <v>45056</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42605,7 +42605,7 @@
         <v>45062</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42667,7 +42667,7 @@
         <v>45062</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42729,7 +42729,7 @@
         <v>45064</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42791,7 +42791,7 @@
         <v>45066</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42853,7 +42853,7 @@
         <v>45068</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42915,7 +42915,7 @@
         <v>45070</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42977,7 +42977,7 @@
         <v>45072</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -43039,7 +43039,7 @@
         <v>45072</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43101,7 +43101,7 @@
         <v>45076</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43158,7 +43158,7 @@
         <v>45076</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43215,7 +43215,7 @@
         <v>45077</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43272,7 +43272,7 @@
         <v>45079</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43334,7 +43334,7 @@
         <v>45079</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43396,7 +43396,7 @@
         <v>45086</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43458,7 +43458,7 @@
         <v>45085</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43520,7 +43520,7 @@
         <v>45086</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43577,7 +43577,7 @@
         <v>45086</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43634,7 +43634,7 @@
         <v>45086</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43691,7 +43691,7 @@
         <v>45086</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43748,7 +43748,7 @@
         <v>45086</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43805,7 +43805,7 @@
         <v>45086</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43862,7 +43862,7 @@
         <v>45090</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43924,7 +43924,7 @@
         <v>45089</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43981,7 +43981,7 @@
         <v>45090</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -44038,7 +44038,7 @@
         <v>45090</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44095,7 +44095,7 @@
         <v>45090</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44152,7 +44152,7 @@
         <v>45090</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44209,7 +44209,7 @@
         <v>45090</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44266,7 +44266,7 @@
         <v>45091</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44323,7 +44323,7 @@
         <v>45091</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44380,7 +44380,7 @@
         <v>45091</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44437,7 +44437,7 @@
         <v>45091</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44494,7 +44494,7 @@
         <v>45093</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44556,7 +44556,7 @@
         <v>45094</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44618,7 +44618,7 @@
         <v>45096</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44675,7 +44675,7 @@
         <v>45096</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44732,7 +44732,7 @@
         <v>45096</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44794,7 +44794,7 @@
         <v>45098</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44851,7 +44851,7 @@
         <v>45098</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44913,7 +44913,7 @@
         <v>45098</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44975,7 +44975,7 @@
         <v>45098</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -45037,7 +45037,7 @@
         <v>45098</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -45094,7 +45094,7 @@
         <v>45098</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45151,7 +45151,7 @@
         <v>45098</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45213,7 +45213,7 @@
         <v>45098</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45275,7 +45275,7 @@
         <v>45098</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45332,7 +45332,7 @@
         <v>45098</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45394,7 +45394,7 @@
         <v>45098</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45451,7 +45451,7 @@
         <v>45098</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45508,7 +45508,7 @@
         <v>45098</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45565,7 +45565,7 @@
         <v>45098</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45622,7 +45622,7 @@
         <v>45099</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45684,7 +45684,7 @@
         <v>45100</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45746,7 +45746,7 @@
         <v>45100</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45808,7 +45808,7 @@
         <v>45100</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45870,7 +45870,7 @@
         <v>45100</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45927,7 +45927,7 @@
         <v>45103</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45989,7 +45989,7 @@
         <v>45104</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -46046,7 +46046,7 @@
         <v>45104</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -46103,7 +46103,7 @@
         <v>45104</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46160,7 +46160,7 @@
         <v>45104</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46217,7 +46217,7 @@
         <v>45104</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46274,7 +46274,7 @@
         <v>45106</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46331,7 +46331,7 @@
         <v>45106</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46388,7 +46388,7 @@
         <v>45106</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46445,7 +46445,7 @@
         <v>45106</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46502,7 +46502,7 @@
         <v>45106</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46559,7 +46559,7 @@
         <v>45106</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46616,7 +46616,7 @@
         <v>45107</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46673,7 +46673,7 @@
         <v>45107</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46730,7 +46730,7 @@
         <v>45107</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46787,7 +46787,7 @@
         <v>45107</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46844,7 +46844,7 @@
         <v>45110</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46901,7 +46901,7 @@
         <v>45110</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46958,7 +46958,7 @@
         <v>45110</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -47015,7 +47015,7 @@
         <v>45110</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -47072,7 +47072,7 @@
         <v>45111</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47129,7 +47129,7 @@
         <v>45114</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47186,7 +47186,7 @@
         <v>45114</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47243,7 +47243,7 @@
         <v>45118</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47305,7 +47305,7 @@
         <v>45118</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47367,7 +47367,7 @@
         <v>45118</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47429,7 +47429,7 @@
         <v>45118</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47491,7 +47491,7 @@
         <v>45118</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47553,7 +47553,7 @@
         <v>45118</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47615,7 +47615,7 @@
         <v>45119</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47677,7 +47677,7 @@
         <v>45119</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47734,7 +47734,7 @@
         <v>45120</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47791,7 +47791,7 @@
         <v>45120</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47848,7 +47848,7 @@
         <v>45120</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47905,7 +47905,7 @@
         <v>45120</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47962,7 +47962,7 @@
         <v>45125</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -48019,7 +48019,7 @@
         <v>45125</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -48076,7 +48076,7 @@
         <v>45125</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -48133,7 +48133,7 @@
         <v>45129</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48190,7 +48190,7 @@
         <v>45129</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48247,7 +48247,7 @@
         <v>45135</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48304,7 +48304,7 @@
         <v>45135</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48361,7 +48361,7 @@
         <v>45138</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48418,7 +48418,7 @@
         <v>45138</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48475,7 +48475,7 @@
         <v>45139</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48532,7 +48532,7 @@
         <v>45139</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48589,7 +48589,7 @@
         <v>45139</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48646,7 +48646,7 @@
         <v>45140</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48708,7 +48708,7 @@
         <v>45140</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48765,7 +48765,7 @@
         <v>45140</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48827,7 +48827,7 @@
         <v>45141</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48884,7 +48884,7 @@
         <v>45145</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48941,7 +48941,7 @@
         <v>45152</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -49003,7 +49003,7 @@
         <v>45152</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -49065,7 +49065,7 @@
         <v>45156</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -49122,7 +49122,7 @@
         <v>45159</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49179,7 +49179,7 @@
         <v>45159</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49236,7 +49236,7 @@
         <v>45160</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49298,7 +49298,7 @@
         <v>45160</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49360,7 +49360,7 @@
         <v>45160</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49417,7 +49417,7 @@
         <v>45162</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49474,7 +49474,7 @@
         <v>45162</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49531,7 +49531,7 @@
         <v>45163</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49588,7 +49588,7 @@
         <v>45167</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49650,7 +49650,7 @@
         <v>45167</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49712,7 +49712,7 @@
         <v>45167</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49769,7 +49769,7 @@
         <v>45167</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49831,7 +49831,7 @@
         <v>45168</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49893,7 +49893,7 @@
         <v>45167</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49950,7 +49950,7 @@
         <v>45168</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -50012,7 +50012,7 @@
         <v>45168</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -50074,7 +50074,7 @@
         <v>45170</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -50131,7 +50131,7 @@
         <v>45170</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -50188,7 +50188,7 @@
         <v>45175</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -50245,7 +50245,7 @@
         <v>45176</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50307,7 +50307,7 @@
         <v>45176</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50369,7 +50369,7 @@
         <v>45176</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50426,7 +50426,7 @@
         <v>45177</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50483,7 +50483,7 @@
         <v>45177</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50540,7 +50540,7 @@
         <v>45177</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50597,7 +50597,7 @@
         <v>45180</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50654,7 +50654,7 @@
         <v>45181</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50716,7 +50716,7 @@
         <v>45181</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50778,7 +50778,7 @@
         <v>45181</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50835,7 +50835,7 @@
         <v>45181</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50892,7 +50892,7 @@
         <v>45182</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50949,7 +50949,7 @@
         <v>45183</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -51006,7 +51006,7 @@
         <v>45184</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -51068,7 +51068,7 @@
         <v>45187</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -51125,7 +51125,7 @@
         <v>45187</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -51182,7 +51182,7 @@
         <v>45187</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -51239,7 +51239,7 @@
         <v>45187</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -51296,7 +51296,7 @@
         <v>45187</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -51353,7 +51353,7 @@
         <v>45187</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -51410,7 +51410,7 @@
         <v>45187</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -51467,7 +51467,7 @@
         <v>45188</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51529,7 +51529,7 @@
         <v>45188</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51591,7 +51591,7 @@
         <v>45188</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51653,7 +51653,7 @@
         <v>45188</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51715,7 +51715,7 @@
         <v>45188</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51777,7 +51777,7 @@
         <v>45188</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51839,7 +51839,7 @@
         <v>45188</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51901,7 +51901,7 @@
         <v>45188</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51958,7 +51958,7 @@
         <v>45189</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -52020,7 +52020,7 @@
         <v>45190</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -52077,7 +52077,7 @@
         <v>45190</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -52134,7 +52134,7 @@
         <v>45190</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -52191,7 +52191,7 @@
         <v>45190</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -52248,7 +52248,7 @@
         <v>45196</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -52305,7 +52305,7 @@
         <v>45197</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -52362,7 +52362,7 @@
         <v>45197</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -52419,7 +52419,7 @@
         <v>45198</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -52481,7 +52481,7 @@
         <v>45201</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -52543,7 +52543,7 @@
         <v>45201</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52605,7 +52605,7 @@
         <v>45202</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52667,7 +52667,7 @@
         <v>45202</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52724,7 +52724,7 @@
         <v>45203</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52781,7 +52781,7 @@
         <v>45204</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52843,7 +52843,7 @@
         <v>45208</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52900,7 +52900,7 @@
         <v>45209</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52957,7 +52957,7 @@
         <v>45208</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -53019,7 +53019,7 @@
         <v>45211</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -53076,7 +53076,7 @@
         <v>45211</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -53133,7 +53133,7 @@
         <v>45211</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -53190,7 +53190,7 @@
         <v>45211</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -53252,7 +53252,7 @@
         <v>45211</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -53314,7 +53314,7 @@
         <v>45211</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -53371,7 +53371,7 @@
         <v>45212</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -53428,7 +53428,7 @@
         <v>45213</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -53485,7 +53485,7 @@
         <v>45215</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -53542,7 +53542,7 @@
         <v>45215</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53599,7 +53599,7 @@
         <v>45216</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53656,7 +53656,7 @@
         <v>45216</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53718,7 +53718,7 @@
         <v>45218</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -53775,7 +53775,7 @@
         <v>45218</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -53837,7 +53837,7 @@
         <v>45218</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -53894,7 +53894,7 @@
         <v>45218</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -53951,7 +53951,7 @@
         <v>45219</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -54008,7 +54008,7 @@
         <v>45219</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -54065,7 +54065,7 @@
         <v>45219</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -54127,7 +54127,7 @@
         <v>45219</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -54189,7 +54189,7 @@
         <v>45219</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -54246,7 +54246,7 @@
         <v>45219</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -54303,7 +54303,7 @@
         <v>45222</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -54360,7 +54360,7 @@
         <v>45222</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -54422,7 +54422,7 @@
         <v>45222</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -54479,7 +54479,7 @@
         <v>45225</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -54536,7 +54536,7 @@
         <v>45225</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -54593,7 +54593,7 @@
         <v>45230</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -54655,7 +54655,7 @@
         <v>45230</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -54712,7 +54712,7 @@
         <v>45230</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -54769,7 +54769,7 @@
         <v>45230</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -54826,7 +54826,7 @@
         <v>45232</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -54888,7 +54888,7 @@
         <v>45232</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -54950,7 +54950,7 @@
         <v>45232</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -55012,7 +55012,7 @@
         <v>45236</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -55074,7 +55074,7 @@
         <v>45236</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -55131,7 +55131,7 @@
         <v>45237</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -55188,7 +55188,7 @@
         <v>45237</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -55245,7 +55245,7 @@
         <v>45237</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -55302,7 +55302,7 @@
         <v>45237</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -55359,7 +55359,7 @@
         <v>45237</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -55421,7 +55421,7 @@
         <v>45237</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -55478,7 +55478,7 @@
         <v>45237</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -55535,7 +55535,7 @@
         <v>45238</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -55592,7 +55592,7 @@
         <v>45239</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -55649,7 +55649,7 @@
         <v>45239</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -55711,7 +55711,7 @@
         <v>45239</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -55768,7 +55768,7 @@
         <v>45239</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -55825,7 +55825,7 @@
         <v>45240</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -55882,7 +55882,7 @@
         <v>45240</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -55939,7 +55939,7 @@
         <v>45243</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -56001,7 +56001,7 @@
         <v>45243</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -56063,7 +56063,7 @@
         <v>45244</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -56120,7 +56120,7 @@
         <v>45244</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -56177,7 +56177,7 @@
         <v>45244</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -56234,7 +56234,7 @@
         <v>45244</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -56291,7 +56291,7 @@
         <v>45244</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -56348,7 +56348,7 @@
         <v>45244</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -56405,7 +56405,7 @@
         <v>45244</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -56462,7 +56462,7 @@
         <v>45244</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -56519,7 +56519,7 @@
         <v>45244</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -56576,7 +56576,7 @@
         <v>45245</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -56633,7 +56633,7 @@
         <v>45245</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -56690,7 +56690,7 @@
         <v>45245</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -56747,7 +56747,7 @@
         <v>45246</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -56804,7 +56804,7 @@
         <v>45246</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -56861,7 +56861,7 @@
         <v>45247</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -56918,7 +56918,7 @@
         <v>45251</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -56975,7 +56975,7 @@
         <v>45252</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -57032,7 +57032,7 @@
         <v>45252</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -57089,7 +57089,7 @@
         <v>45253</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -57146,7 +57146,7 @@
         <v>45254</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -57203,7 +57203,7 @@
         <v>45254</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -57260,7 +57260,7 @@
         <v>45257</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -57317,7 +57317,7 @@
         <v>45257</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -57374,7 +57374,7 @@
         <v>45258</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -57431,7 +57431,7 @@
         <v>45259</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -57488,7 +57488,7 @@
         <v>45259</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -57545,7 +57545,7 @@
         <v>45260</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -57602,7 +57602,7 @@
         <v>45260</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -57659,7 +57659,7 @@
         <v>45260</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -57716,7 +57716,7 @@
         <v>45260</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -57773,7 +57773,7 @@
         <v>45261</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -57830,7 +57830,7 @@
         <v>45261</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -57887,7 +57887,7 @@
         <v>45262</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -57944,7 +57944,7 @@
         <v>45264</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -58001,7 +58001,7 @@
         <v>45264</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -58058,7 +58058,7 @@
         <v>45264</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -58115,7 +58115,7 @@
         <v>45264</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -58177,7 +58177,7 @@
         <v>45264</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -58234,7 +58234,7 @@
         <v>45265</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -58291,7 +58291,7 @@
         <v>45265</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -58348,7 +58348,7 @@
         <v>45266</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -58405,7 +58405,7 @@
         <v>45266</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -58462,7 +58462,7 @@
         <v>45266</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -58519,7 +58519,7 @@
         <v>45267</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -58576,7 +58576,7 @@
         <v>45271</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -58633,7 +58633,7 @@
         <v>45271</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -58690,7 +58690,7 @@
         <v>45273</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -58747,7 +58747,7 @@
         <v>45273</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -58804,7 +58804,7 @@
         <v>45273</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -58861,7 +58861,7 @@
         <v>45273</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -58918,7 +58918,7 @@
         <v>45273</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -58975,7 +58975,7 @@
         <v>45273</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -59032,7 +59032,7 @@
         <v>45273</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -59089,7 +59089,7 @@
         <v>45278</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -59146,7 +59146,7 @@
         <v>45279</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -59203,7 +59203,7 @@
         <v>45279</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -59260,7 +59260,7 @@
         <v>45279</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -59317,7 +59317,7 @@
         <v>45281</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -59374,7 +59374,7 @@
         <v>45282</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -59436,7 +59436,7 @@
         <v>45285</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -59493,7 +59493,7 @@
         <v>45285</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -59550,7 +59550,7 @@
         <v>45285</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -59607,7 +59607,7 @@
         <v>45285</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -59664,7 +59664,7 @@
         <v>45287</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -59721,7 +59721,7 @@
         <v>45287</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -59778,7 +59778,7 @@
         <v>45289</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -59835,7 +59835,7 @@
         <v>45299</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -59892,7 +59892,7 @@
         <v>45308</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -59949,7 +59949,7 @@
         <v>45308</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -60006,7 +60006,7 @@
         <v>45309</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -60063,7 +60063,7 @@
         <v>45310</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -60120,7 +60120,7 @@
         <v>45310</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -60177,7 +60177,7 @@
         <v>45311</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -60234,7 +60234,7 @@
         <v>45311</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -60291,7 +60291,7 @@
         <v>45312</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -60348,7 +60348,7 @@
         <v>45312</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -60405,7 +60405,7 @@
         <v>45313</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -60455,14 +60455,14 @@
     <row r="993" ht="15" customHeight="1">
       <c r="A993" t="inlineStr">
         <is>
-          <t>A 2842-2024</t>
+          <t>A 2847-2024</t>
         </is>
       </c>
       <c r="B993" s="1" t="n">
         <v>45315</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -60475,7 +60475,7 @@
         </is>
       </c>
       <c r="G993" t="n">
-        <v>1.2</v>
+        <v>3.5</v>
       </c>
       <c r="H993" t="n">
         <v>0</v>
@@ -60512,14 +60512,14 @@
     <row r="994" ht="15" customHeight="1">
       <c r="A994" t="inlineStr">
         <is>
-          <t>A 2847-2024</t>
+          <t>A 2842-2024</t>
         </is>
       </c>
       <c r="B994" s="1" t="n">
         <v>45315</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -60532,7 +60532,7 @@
         </is>
       </c>
       <c r="G994" t="n">
-        <v>3.5</v>
+        <v>1.2</v>
       </c>
       <c r="H994" t="n">
         <v>0</v>
@@ -60576,7 +60576,7 @@
         <v>45315</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -60626,14 +60626,14 @@
     <row r="996" ht="15" customHeight="1">
       <c r="A996" t="inlineStr">
         <is>
-          <t>A 3215-2024</t>
+          <t>A 3218-2024</t>
         </is>
       </c>
       <c r="B996" s="1" t="n">
         <v>45316</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -60646,7 +60646,7 @@
         </is>
       </c>
       <c r="G996" t="n">
-        <v>4.1</v>
+        <v>2.1</v>
       </c>
       <c r="H996" t="n">
         <v>0</v>
@@ -60690,7 +60690,7 @@
         <v>45316</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -60740,14 +60740,14 @@
     <row r="998" ht="15" customHeight="1">
       <c r="A998" t="inlineStr">
         <is>
-          <t>A 3218-2024</t>
+          <t>A 3215-2024</t>
         </is>
       </c>
       <c r="B998" s="1" t="n">
         <v>45316</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -60760,7 +60760,7 @@
         </is>
       </c>
       <c r="G998" t="n">
-        <v>2.1</v>
+        <v>4.1</v>
       </c>
       <c r="H998" t="n">
         <v>0</v>
@@ -60804,7 +60804,7 @@
         <v>45320</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -60861,7 +60861,7 @@
         <v>45320</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -60918,7 +60918,7 @@
         <v>45323</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -60975,7 +60975,7 @@
         <v>45323</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -61037,7 +61037,7 @@
         <v>45323</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -61094,7 +61094,7 @@
         <v>45323</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -61156,7 +61156,7 @@
         <v>45323</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -61211,14 +61211,14 @@
     <row r="1006" ht="15" customHeight="1">
       <c r="A1006" t="inlineStr">
         <is>
-          <t>A 4245-2024</t>
+          <t>A 4232-2024</t>
         </is>
       </c>
       <c r="B1006" s="1" t="n">
         <v>45324</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -61230,8 +61230,13 @@
           <t>PITEÅ</t>
         </is>
       </c>
+      <c r="F1006" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="G1006" t="n">
-        <v>7.2</v>
+        <v>11.1</v>
       </c>
       <c r="H1006" t="n">
         <v>0</v>
@@ -61275,7 +61280,7 @@
         <v>45324</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -61330,14 +61335,14 @@
     <row r="1008" ht="15" customHeight="1">
       <c r="A1008" t="inlineStr">
         <is>
-          <t>A 4232-2024</t>
+          <t>A 4245-2024</t>
         </is>
       </c>
       <c r="B1008" s="1" t="n">
         <v>45324</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -61349,13 +61354,8 @@
           <t>PITEÅ</t>
         </is>
       </c>
-      <c r="F1008" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="G1008" t="n">
-        <v>11.1</v>
+        <v>7.2</v>
       </c>
       <c r="H1008" t="n">
         <v>0</v>
@@ -61399,7 +61399,7 @@
         <v>45329</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -61456,7 +61456,7 @@
         <v>45330</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -61513,7 +61513,7 @@
         <v>45334</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -61570,7 +61570,7 @@
         <v>45335</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -61627,7 +61627,7 @@
         <v>45342</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -61677,14 +61677,14 @@
     <row r="1014" ht="15" customHeight="1">
       <c r="A1014" t="inlineStr">
         <is>
-          <t>A 6920-2024</t>
+          <t>A 6988-2024</t>
         </is>
       </c>
       <c r="B1014" s="1" t="n">
         <v>45343</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -61697,7 +61697,7 @@
         </is>
       </c>
       <c r="G1014" t="n">
-        <v>7.6</v>
+        <v>1.6</v>
       </c>
       <c r="H1014" t="n">
         <v>0</v>
@@ -61731,62 +61731,290 @@
       </c>
       <c r="R1014" s="2" t="inlineStr"/>
     </row>
-    <row r="1015">
+    <row r="1015" ht="15" customHeight="1">
       <c r="A1015" t="inlineStr">
         <is>
-          <t>A 6988-2024</t>
+          <t>A 6920-2024</t>
         </is>
       </c>
       <c r="B1015" s="1" t="n">
         <v>45343</v>
       </c>
       <c r="C1015" s="1" t="n">
+        <v>45346</v>
+      </c>
+      <c r="D1015" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="E1015" t="inlineStr">
+        <is>
+          <t>PITEÅ</t>
+        </is>
+      </c>
+      <c r="G1015" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="H1015" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1015" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1015" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1015" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1015" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1015" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1015" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1015" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1015" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1015" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1015" s="2" t="inlineStr"/>
+    </row>
+    <row r="1016" ht="15" customHeight="1">
+      <c r="A1016" t="inlineStr">
+        <is>
+          <t>A 7458-2024</t>
+        </is>
+      </c>
+      <c r="B1016" s="1" t="n">
         <v>45345</v>
       </c>
-      <c r="D1015" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="E1015" t="inlineStr">
-        <is>
-          <t>PITEÅ</t>
-        </is>
-      </c>
-      <c r="G1015" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="H1015" t="n">
-        <v>0</v>
-      </c>
-      <c r="I1015" t="n">
-        <v>0</v>
-      </c>
-      <c r="J1015" t="n">
-        <v>0</v>
-      </c>
-      <c r="K1015" t="n">
-        <v>0</v>
-      </c>
-      <c r="L1015" t="n">
-        <v>0</v>
-      </c>
-      <c r="M1015" t="n">
-        <v>0</v>
-      </c>
-      <c r="N1015" t="n">
-        <v>0</v>
-      </c>
-      <c r="O1015" t="n">
-        <v>0</v>
-      </c>
-      <c r="P1015" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q1015" t="n">
-        <v>0</v>
-      </c>
-      <c r="R1015" s="2" t="inlineStr"/>
+      <c r="C1016" s="1" t="n">
+        <v>45346</v>
+      </c>
+      <c r="D1016" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="E1016" t="inlineStr">
+        <is>
+          <t>PITEÅ</t>
+        </is>
+      </c>
+      <c r="G1016" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H1016" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1016" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1016" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1016" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1016" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1016" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1016" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1016" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1016" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1016" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1016" s="2" t="inlineStr"/>
+    </row>
+    <row r="1017" ht="15" customHeight="1">
+      <c r="A1017" t="inlineStr">
+        <is>
+          <t>A 7459-2024</t>
+        </is>
+      </c>
+      <c r="B1017" s="1" t="n">
+        <v>45345</v>
+      </c>
+      <c r="C1017" s="1" t="n">
+        <v>45346</v>
+      </c>
+      <c r="D1017" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="E1017" t="inlineStr">
+        <is>
+          <t>PITEÅ</t>
+        </is>
+      </c>
+      <c r="G1017" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H1017" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1017" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1017" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1017" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1017" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1017" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1017" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1017" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1017" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1017" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1017" s="2" t="inlineStr"/>
+    </row>
+    <row r="1018" ht="15" customHeight="1">
+      <c r="A1018" t="inlineStr">
+        <is>
+          <t>A 7457-2024</t>
+        </is>
+      </c>
+      <c r="B1018" s="1" t="n">
+        <v>45345</v>
+      </c>
+      <c r="C1018" s="1" t="n">
+        <v>45346</v>
+      </c>
+      <c r="D1018" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="E1018" t="inlineStr">
+        <is>
+          <t>PITEÅ</t>
+        </is>
+      </c>
+      <c r="G1018" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="H1018" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1018" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1018" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1018" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1018" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1018" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1018" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1018" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1018" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1018" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1018" s="2" t="inlineStr"/>
+    </row>
+    <row r="1019">
+      <c r="A1019" t="inlineStr">
+        <is>
+          <t>A 7461-2024</t>
+        </is>
+      </c>
+      <c r="B1019" s="1" t="n">
+        <v>45345</v>
+      </c>
+      <c r="C1019" s="1" t="n">
+        <v>45346</v>
+      </c>
+      <c r="D1019" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="E1019" t="inlineStr">
+        <is>
+          <t>PITEÅ</t>
+        </is>
+      </c>
+      <c r="G1019" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="H1019" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1019" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1019" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1019" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1019" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1019" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1019" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1019" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1019" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1019" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1019" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt PITEÅ.xlsx
+++ b/Översikt PITEÅ.xlsx
@@ -569,7 +569,7 @@
         <v>44617</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -665,7 +665,7 @@
         <v>44839</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
         <v>44839</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>44459</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
         <v>44617</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>43896</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>45191</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>45203</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>44740</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>44280</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>44539</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>44550</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>45119</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>44014</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>44522</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>44526</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         <v>44553</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>44810</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>44917</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>45103</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>45106</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         <v>43802</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>43902</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2727,7 +2727,7 @@
         <v>43908</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         <v>44053</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2908,7 +2908,7 @@
         <v>44193</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>44298</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>44840</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
         <v>44852</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3262,7 +3262,7 @@
         <v>44859</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>44944</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3434,7 +3434,7 @@
         <v>45120</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
         <v>45187</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         <v>45209</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3701,7 +3701,7 @@
         <v>45219</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>45243</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         <v>45293</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
         <v>45296</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>43714</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         <v>44014</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4225,7 +4225,7 @@
         <v>44106</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4310,7 +4310,7 @@
         <v>44309</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>44342</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4485,7 +4485,7 @@
         <v>44495</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
         <v>44525</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4665,7 +4665,7 @@
         <v>44525</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4755,7 +4755,7 @@
         <v>44538</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4840,7 +4840,7 @@
         <v>44727</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4929,7 +4929,7 @@
         <v>44804</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5014,7 +5014,7 @@
         <v>44917</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5104,7 +5104,7 @@
         <v>45049</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5193,7 +5193,7 @@
         <v>45098</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>45103</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5373,7 +5373,7 @@
         <v>45148</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
         <v>45175</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         <v>45181</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5642,7 +5642,7 @@
         <v>45188</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5732,7 +5732,7 @@
         <v>45224</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5817,7 +5817,7 @@
         <v>45243</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5907,7 +5907,7 @@
         <v>45265</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5992,7 +5992,7 @@
         <v>45323</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
         <v>43325</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6139,7 +6139,7 @@
         <v>43332</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6196,7 +6196,7 @@
         <v>43336</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6253,7 +6253,7 @@
         <v>43339</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         <v>43339</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
         <v>43341</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6424,7 +6424,7 @@
         <v>43355</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>43355</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         <v>43374</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6600,7 +6600,7 @@
         <v>43374</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6662,7 +6662,7 @@
         <v>43375</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6719,7 +6719,7 @@
         <v>43376</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
         <v>43376</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6833,7 +6833,7 @@
         <v>43381</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6890,7 +6890,7 @@
         <v>43383</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6947,7 +6947,7 @@
         <v>43391</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>43391</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7061,7 +7061,7 @@
         <v>43392</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7118,7 +7118,7 @@
         <v>43392</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7175,7 +7175,7 @@
         <v>43398</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7232,7 +7232,7 @@
         <v>43402</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7289,7 +7289,7 @@
         <v>43404</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7346,7 +7346,7 @@
         <v>43406</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7403,7 +7403,7 @@
         <v>43406</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
         <v>43406</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>43406</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>43406</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>43416</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>43418</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7745,7 +7745,7 @@
         <v>43418</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7802,7 +7802,7 @@
         <v>43418</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         <v>43419</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7916,7 +7916,7 @@
         <v>43420</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         <v>43424</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8035,7 +8035,7 @@
         <v>43427</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8097,7 +8097,7 @@
         <v>43427</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8154,7 +8154,7 @@
         <v>43427</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8216,7 +8216,7 @@
         <v>43427</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8278,7 +8278,7 @@
         <v>43436</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
         <v>43438</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8392,7 +8392,7 @@
         <v>43438</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8449,7 +8449,7 @@
         <v>43438</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8506,7 +8506,7 @@
         <v>43438</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8563,7 +8563,7 @@
         <v>43451</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8625,7 +8625,7 @@
         <v>43472</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8682,7 +8682,7 @@
         <v>43475</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8739,7 +8739,7 @@
         <v>43479</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8796,7 +8796,7 @@
         <v>43479</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8853,7 +8853,7 @@
         <v>43486</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
         <v>43489</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8967,7 +8967,7 @@
         <v>43489</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9024,7 +9024,7 @@
         <v>43489</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9081,7 +9081,7 @@
         <v>43489</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9138,7 +9138,7 @@
         <v>43489</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9195,7 +9195,7 @@
         <v>43490</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9252,7 +9252,7 @@
         <v>43490</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9309,7 +9309,7 @@
         <v>43493</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9371,7 +9371,7 @@
         <v>43509</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9428,7 +9428,7 @@
         <v>43510</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9485,7 +9485,7 @@
         <v>43510</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9542,7 +9542,7 @@
         <v>43514</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9599,7 +9599,7 @@
         <v>43514</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9656,7 +9656,7 @@
         <v>43514</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9713,7 +9713,7 @@
         <v>43516</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9775,7 +9775,7 @@
         <v>43518</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9832,7 +9832,7 @@
         <v>43521</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9894,7 +9894,7 @@
         <v>43521</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9956,7 +9956,7 @@
         <v>43521</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10018,7 +10018,7 @@
         <v>43521</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10080,7 +10080,7 @@
         <v>43521</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10142,7 +10142,7 @@
         <v>43522</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10199,7 +10199,7 @@
         <v>43523</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10256,7 +10256,7 @@
         <v>43523</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10313,7 +10313,7 @@
         <v>43523</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10370,7 +10370,7 @@
         <v>43532</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10427,7 +10427,7 @@
         <v>43532</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10484,7 +10484,7 @@
         <v>43542</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10541,7 +10541,7 @@
         <v>43544</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10603,7 +10603,7 @@
         <v>43544</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10665,7 +10665,7 @@
         <v>43554</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10722,7 +10722,7 @@
         <v>43556</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10779,7 +10779,7 @@
         <v>43557</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10841,7 +10841,7 @@
         <v>43557</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10898,7 +10898,7 @@
         <v>43557</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10955,7 +10955,7 @@
         <v>43557</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11012,7 +11012,7 @@
         <v>43557</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11074,7 +11074,7 @@
         <v>43564</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11131,7 +11131,7 @@
         <v>43564</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11188,7 +11188,7 @@
         <v>43567</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11245,7 +11245,7 @@
         <v>43570</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11302,7 +11302,7 @@
         <v>43570</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11359,7 +11359,7 @@
         <v>43570</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11416,7 +11416,7 @@
         <v>43584</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11473,7 +11473,7 @@
         <v>43605</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11530,7 +11530,7 @@
         <v>43608</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11587,7 +11587,7 @@
         <v>43614</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11649,7 +11649,7 @@
         <v>43616</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11711,7 +11711,7 @@
         <v>43616</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11773,7 +11773,7 @@
         <v>43629</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11830,7 +11830,7 @@
         <v>43629</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11892,7 +11892,7 @@
         <v>43633</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11949,7 +11949,7 @@
         <v>43633</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12006,7 +12006,7 @@
         <v>43640</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12063,7 +12063,7 @@
         <v>43640</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12120,7 +12120,7 @@
         <v>43647</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12177,7 +12177,7 @@
         <v>43647</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12234,7 +12234,7 @@
         <v>43650</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12291,7 +12291,7 @@
         <v>43652</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12353,7 +12353,7 @@
         <v>43677</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12410,7 +12410,7 @@
         <v>43678</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12467,7 +12467,7 @@
         <v>43682</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12524,7 +12524,7 @@
         <v>43691</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12586,7 +12586,7 @@
         <v>43691</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12648,7 +12648,7 @@
         <v>43696</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12710,7 +12710,7 @@
         <v>43697</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12767,7 +12767,7 @@
         <v>43698</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12829,7 +12829,7 @@
         <v>43698</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12891,7 +12891,7 @@
         <v>43706</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12948,7 +12948,7 @@
         <v>43707</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13010,7 +13010,7 @@
         <v>43711</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13067,7 +13067,7 @@
         <v>43713</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13124,7 +13124,7 @@
         <v>43718</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13181,7 +13181,7 @@
         <v>43718</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13238,7 +13238,7 @@
         <v>43718</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13300,7 +13300,7 @@
         <v>43720</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13357,7 +13357,7 @@
         <v>43721</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13414,7 +13414,7 @@
         <v>43732</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13471,7 +13471,7 @@
         <v>43741</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13533,7 +13533,7 @@
         <v>43741</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13590,7 +13590,7 @@
         <v>43752</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13652,7 +13652,7 @@
         <v>43755</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13709,7 +13709,7 @@
         <v>43755</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13766,7 +13766,7 @@
         <v>43755</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13823,7 +13823,7 @@
         <v>43755</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13880,7 +13880,7 @@
         <v>43760</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13942,7 +13942,7 @@
         <v>43760</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14004,7 +14004,7 @@
         <v>43760</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14061,7 +14061,7 @@
         <v>43762</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14123,7 +14123,7 @@
         <v>43766</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14180,7 +14180,7 @@
         <v>43766</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14237,7 +14237,7 @@
         <v>43768</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14294,7 +14294,7 @@
         <v>43770</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14356,7 +14356,7 @@
         <v>43775</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14418,7 +14418,7 @@
         <v>43775</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14480,7 +14480,7 @@
         <v>43777</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14537,7 +14537,7 @@
         <v>43780</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14594,7 +14594,7 @@
         <v>43780</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14651,7 +14651,7 @@
         <v>43780</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14708,7 +14708,7 @@
         <v>43782</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14770,7 +14770,7 @@
         <v>43789</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14832,7 +14832,7 @@
         <v>43798</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14889,7 +14889,7 @@
         <v>43801</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14951,7 +14951,7 @@
         <v>43802</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15008,7 +15008,7 @@
         <v>43802</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15065,7 +15065,7 @@
         <v>43802</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15122,7 +15122,7 @@
         <v>43802</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15179,7 +15179,7 @@
         <v>43802</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15236,7 +15236,7 @@
         <v>43802</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15293,7 +15293,7 @@
         <v>43807</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15350,7 +15350,7 @@
         <v>43809</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15407,7 +15407,7 @@
         <v>43817</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15464,7 +15464,7 @@
         <v>43817</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15526,7 +15526,7 @@
         <v>43822</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15583,7 +15583,7 @@
         <v>43822</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15640,7 +15640,7 @@
         <v>43833</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15697,7 +15697,7 @@
         <v>43846</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15754,7 +15754,7 @@
         <v>43852</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15811,7 +15811,7 @@
         <v>43853</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15868,7 +15868,7 @@
         <v>43854</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15925,7 +15925,7 @@
         <v>43859</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15987,7 +15987,7 @@
         <v>43859</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16044,7 +16044,7 @@
         <v>43859</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16101,7 +16101,7 @@
         <v>43859</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16158,7 +16158,7 @@
         <v>43859</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16215,7 +16215,7 @@
         <v>43860</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16272,7 +16272,7 @@
         <v>43868</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16329,7 +16329,7 @@
         <v>43868</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16386,7 +16386,7 @@
         <v>43874</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16448,7 +16448,7 @@
         <v>43878</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16505,7 +16505,7 @@
         <v>43880</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16562,7 +16562,7 @@
         <v>43880</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16619,7 +16619,7 @@
         <v>43889</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16676,7 +16676,7 @@
         <v>43895</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16738,7 +16738,7 @@
         <v>43896</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16795,7 +16795,7 @@
         <v>43902</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16852,7 +16852,7 @@
         <v>43902</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16914,7 +16914,7 @@
         <v>43907</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16971,7 +16971,7 @@
         <v>43913</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17028,7 +17028,7 @@
         <v>43914</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17090,7 +17090,7 @@
         <v>43927</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17152,7 +17152,7 @@
         <v>43929</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         <v>43929</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>43931</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17328,7 +17328,7 @@
         <v>43950</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17385,7 +17385,7 @@
         <v>43957</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17447,7 +17447,7 @@
         <v>43958</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17504,7 +17504,7 @@
         <v>43958</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17561,7 +17561,7 @@
         <v>43959</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17618,7 +17618,7 @@
         <v>43962</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17675,7 +17675,7 @@
         <v>43962</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17732,7 +17732,7 @@
         <v>43962</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17789,7 +17789,7 @@
         <v>43962</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17846,7 +17846,7 @@
         <v>43970</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17908,7 +17908,7 @@
         <v>43971</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17970,7 +17970,7 @@
         <v>43976</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18027,7 +18027,7 @@
         <v>43979</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18084,7 +18084,7 @@
         <v>43979</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18141,7 +18141,7 @@
         <v>43979</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18198,7 +18198,7 @@
         <v>43984</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18260,7 +18260,7 @@
         <v>43984</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18317,7 +18317,7 @@
         <v>43987</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18374,7 +18374,7 @@
         <v>43990</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18431,7 +18431,7 @@
         <v>43994</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18493,7 +18493,7 @@
         <v>43997</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18550,7 +18550,7 @@
         <v>43999</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18607,7 +18607,7 @@
         <v>44000</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18669,7 +18669,7 @@
         <v>44006</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18726,7 +18726,7 @@
         <v>44006</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18783,7 +18783,7 @@
         <v>44007</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18840,7 +18840,7 @@
         <v>44007</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18897,7 +18897,7 @@
         <v>44011</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18954,7 +18954,7 @@
         <v>44012</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19016,7 +19016,7 @@
         <v>44020</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19078,7 +19078,7 @@
         <v>44020</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19135,7 +19135,7 @@
         <v>44020</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19197,7 +19197,7 @@
         <v>44026</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19259,7 +19259,7 @@
         <v>44035</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19316,7 +19316,7 @@
         <v>44049</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19373,7 +19373,7 @@
         <v>44063</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19435,7 +19435,7 @@
         <v>44067</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19497,7 +19497,7 @@
         <v>44067</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19559,7 +19559,7 @@
         <v>44068</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19621,7 +19621,7 @@
         <v>44069</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19678,7 +19678,7 @@
         <v>44070</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19735,7 +19735,7 @@
         <v>44074</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19792,7 +19792,7 @@
         <v>44075</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19849,7 +19849,7 @@
         <v>44078</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19906,7 +19906,7 @@
         <v>44083</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19963,7 +19963,7 @@
         <v>44083</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20020,7 +20020,7 @@
         <v>44087</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20077,7 +20077,7 @@
         <v>44088</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20139,7 +20139,7 @@
         <v>44088</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20196,7 +20196,7 @@
         <v>44088</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20258,7 +20258,7 @@
         <v>44092</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20315,7 +20315,7 @@
         <v>44092</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20372,7 +20372,7 @@
         <v>44092</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20429,7 +20429,7 @@
         <v>44095</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20486,7 +20486,7 @@
         <v>44099</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20543,7 +20543,7 @@
         <v>44099</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20600,7 +20600,7 @@
         <v>44099</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20657,7 +20657,7 @@
         <v>44099</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20714,7 +20714,7 @@
         <v>44103</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20771,7 +20771,7 @@
         <v>44103</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20828,7 +20828,7 @@
         <v>44106</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20885,7 +20885,7 @@
         <v>44111</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20947,7 +20947,7 @@
         <v>44111</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21009,7 +21009,7 @@
         <v>44123</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21066,7 +21066,7 @@
         <v>44127</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21123,7 +21123,7 @@
         <v>44132</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21180,7 +21180,7 @@
         <v>44139</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21237,7 +21237,7 @@
         <v>44141</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21294,7 +21294,7 @@
         <v>44141</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21351,7 +21351,7 @@
         <v>44155</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21408,7 +21408,7 @@
         <v>44162</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21470,7 +21470,7 @@
         <v>44166</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21532,7 +21532,7 @@
         <v>44172</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21589,7 +21589,7 @@
         <v>44180</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21646,7 +21646,7 @@
         <v>44186</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21703,7 +21703,7 @@
         <v>44209</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21760,7 +21760,7 @@
         <v>44211</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21817,7 +21817,7 @@
         <v>44211</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21874,7 +21874,7 @@
         <v>44211</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21931,7 +21931,7 @@
         <v>44215</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21993,7 +21993,7 @@
         <v>44221</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22055,7 +22055,7 @@
         <v>44237</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22117,7 +22117,7 @@
         <v>44238</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22174,7 +22174,7 @@
         <v>44256</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22231,7 +22231,7 @@
         <v>44257</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22288,7 +22288,7 @@
         <v>44258</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22345,7 +22345,7 @@
         <v>44280</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22407,7 +22407,7 @@
         <v>44281</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22464,7 +22464,7 @@
         <v>44281</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22521,7 +22521,7 @@
         <v>44281</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22578,7 +22578,7 @@
         <v>44285</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22640,7 +22640,7 @@
         <v>44286</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22697,7 +22697,7 @@
         <v>44292</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22754,7 +22754,7 @@
         <v>44294</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22816,7 +22816,7 @@
         <v>44309</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22873,7 +22873,7 @@
         <v>44320</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22930,7 +22930,7 @@
         <v>44321</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22987,7 +22987,7 @@
         <v>44321</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23044,7 +23044,7 @@
         <v>44326</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23101,7 +23101,7 @@
         <v>44326</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23163,7 +23163,7 @@
         <v>44334</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23220,7 +23220,7 @@
         <v>44339</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23277,7 +23277,7 @@
         <v>44339</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23334,7 +23334,7 @@
         <v>44339</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23391,7 +23391,7 @@
         <v>44343</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23453,7 +23453,7 @@
         <v>44342</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23515,7 +23515,7 @@
         <v>44344</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23572,7 +23572,7 @@
         <v>44350</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23629,7 +23629,7 @@
         <v>44350</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23686,7 +23686,7 @@
         <v>44351</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23748,7 +23748,7 @@
         <v>44354</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23810,7 +23810,7 @@
         <v>44355</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23872,7 +23872,7 @@
         <v>44355</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23934,7 +23934,7 @@
         <v>44357</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23991,7 +23991,7 @@
         <v>44358</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24053,7 +24053,7 @@
         <v>44361</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24110,7 +24110,7 @@
         <v>44361</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24167,7 +24167,7 @@
         <v>44361</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24224,7 +24224,7 @@
         <v>44362</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24286,7 +24286,7 @@
         <v>44361</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24348,7 +24348,7 @@
         <v>44362</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24405,7 +24405,7 @@
         <v>44368</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24467,7 +24467,7 @@
         <v>44368</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24529,7 +24529,7 @@
         <v>44368</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24591,7 +24591,7 @@
         <v>44369</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24653,7 +24653,7 @@
         <v>44370</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24715,7 +24715,7 @@
         <v>44370</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24777,7 +24777,7 @@
         <v>44370</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24839,7 +24839,7 @@
         <v>44370</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24901,7 +24901,7 @@
         <v>44371</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24963,7 +24963,7 @@
         <v>44372</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25025,7 +25025,7 @@
         <v>44372</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25087,7 +25087,7 @@
         <v>44375</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25149,7 +25149,7 @@
         <v>44376</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25211,7 +25211,7 @@
         <v>44376</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25273,7 +25273,7 @@
         <v>44376</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25330,7 +25330,7 @@
         <v>44377</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25392,7 +25392,7 @@
         <v>44378</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25449,7 +25449,7 @@
         <v>44378</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25511,7 +25511,7 @@
         <v>44378</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25568,7 +25568,7 @@
         <v>44383</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25625,7 +25625,7 @@
         <v>44383</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25682,7 +25682,7 @@
         <v>44383</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25739,7 +25739,7 @@
         <v>44383</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25796,7 +25796,7 @@
         <v>44383</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25853,7 +25853,7 @@
         <v>44384</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25915,7 +25915,7 @@
         <v>44383</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25972,7 +25972,7 @@
         <v>44386</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26029,7 +26029,7 @@
         <v>44398</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26086,7 +26086,7 @@
         <v>44404</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26143,7 +26143,7 @@
         <v>44405</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26205,7 +26205,7 @@
         <v>44418</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26267,7 +26267,7 @@
         <v>44421</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26329,7 +26329,7 @@
         <v>44428</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26386,7 +26386,7 @@
         <v>44432</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26443,7 +26443,7 @@
         <v>44432</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26500,7 +26500,7 @@
         <v>44433</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26562,7 +26562,7 @@
         <v>44433</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26624,7 +26624,7 @@
         <v>44438</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26686,7 +26686,7 @@
         <v>44439</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26748,7 +26748,7 @@
         <v>44440</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26805,7 +26805,7 @@
         <v>44441</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26867,7 +26867,7 @@
         <v>44440</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26929,7 +26929,7 @@
         <v>44446</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26986,7 +26986,7 @@
         <v>44447</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27048,7 +27048,7 @@
         <v>44453</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27105,7 +27105,7 @@
         <v>44454</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27162,7 +27162,7 @@
         <v>44454</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27219,7 +27219,7 @@
         <v>44459</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27276,7 +27276,7 @@
         <v>44463</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27338,7 +27338,7 @@
         <v>44463</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27400,7 +27400,7 @@
         <v>44463</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27457,7 +27457,7 @@
         <v>44468</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27514,7 +27514,7 @@
         <v>44468</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27571,7 +27571,7 @@
         <v>44476</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27628,7 +27628,7 @@
         <v>44480</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27685,7 +27685,7 @@
         <v>44481</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27742,7 +27742,7 @@
         <v>44484</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27799,7 +27799,7 @@
         <v>44487</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27861,7 +27861,7 @@
         <v>44490</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27918,7 +27918,7 @@
         <v>44489</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27980,7 +27980,7 @@
         <v>44496</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28037,7 +28037,7 @@
         <v>44497</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28099,7 +28099,7 @@
         <v>44497</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28156,7 +28156,7 @@
         <v>44497</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28213,7 +28213,7 @@
         <v>44498</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28270,7 +28270,7 @@
         <v>44498</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28327,7 +28327,7 @@
         <v>44499</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28384,7 +28384,7 @@
         <v>44502</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28441,7 +28441,7 @@
         <v>44516</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28498,7 +28498,7 @@
         <v>44522</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28555,7 +28555,7 @@
         <v>44523</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28612,7 +28612,7 @@
         <v>44525</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28674,7 +28674,7 @@
         <v>44525</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28731,7 +28731,7 @@
         <v>44529</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28788,7 +28788,7 @@
         <v>44530</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28850,7 +28850,7 @@
         <v>44530</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28912,7 +28912,7 @@
         <v>44531</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28969,7 +28969,7 @@
         <v>44531</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29026,7 +29026,7 @@
         <v>44536</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29083,7 +29083,7 @@
         <v>44536</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29140,7 +29140,7 @@
         <v>44538</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29197,7 +29197,7 @@
         <v>44538</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29254,7 +29254,7 @@
         <v>44538</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29311,7 +29311,7 @@
         <v>44538</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29368,7 +29368,7 @@
         <v>44538</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29425,7 +29425,7 @@
         <v>44538</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29482,7 +29482,7 @@
         <v>44538</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29539,7 +29539,7 @@
         <v>44538</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29596,7 +29596,7 @@
         <v>44539</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29658,7 +29658,7 @@
         <v>44543</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29720,7 +29720,7 @@
         <v>44543</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29782,7 +29782,7 @@
         <v>44543</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29844,7 +29844,7 @@
         <v>44543</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29906,7 +29906,7 @@
         <v>44547</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29968,7 +29968,7 @@
         <v>44550</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30025,7 +30025,7 @@
         <v>44550</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30082,7 +30082,7 @@
         <v>44571</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30139,7 +30139,7 @@
         <v>44582</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30196,7 +30196,7 @@
         <v>44582</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30253,7 +30253,7 @@
         <v>44582</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30310,7 +30310,7 @@
         <v>44582</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30367,7 +30367,7 @@
         <v>44588</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30424,7 +30424,7 @@
         <v>44589</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30481,7 +30481,7 @@
         <v>44590</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30538,7 +30538,7 @@
         <v>44590</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30595,7 +30595,7 @@
         <v>44592</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30652,7 +30652,7 @@
         <v>44592</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30709,7 +30709,7 @@
         <v>44596</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30766,7 +30766,7 @@
         <v>44599</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30823,7 +30823,7 @@
         <v>44608</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30880,7 +30880,7 @@
         <v>44615</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30937,7 +30937,7 @@
         <v>44616</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30999,7 +30999,7 @@
         <v>44617</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31061,7 +31061,7 @@
         <v>44621</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31118,7 +31118,7 @@
         <v>44621</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31180,7 +31180,7 @@
         <v>44622</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31237,7 +31237,7 @@
         <v>44623</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31294,7 +31294,7 @@
         <v>44642</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31351,7 +31351,7 @@
         <v>44643</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31408,7 +31408,7 @@
         <v>44643</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31470,7 +31470,7 @@
         <v>44644</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31527,7 +31527,7 @@
         <v>44656</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31584,7 +31584,7 @@
         <v>44658</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31641,7 +31641,7 @@
         <v>44683</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31698,7 +31698,7 @@
         <v>44683</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31755,7 +31755,7 @@
         <v>44685</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31812,7 +31812,7 @@
         <v>44685</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31869,7 +31869,7 @@
         <v>44685</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31926,7 +31926,7 @@
         <v>44687</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31983,7 +31983,7 @@
         <v>44700</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32040,7 +32040,7 @@
         <v>44708</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32097,7 +32097,7 @@
         <v>44708</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32154,7 +32154,7 @@
         <v>44708</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32211,7 +32211,7 @@
         <v>44722</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32268,7 +32268,7 @@
         <v>44727</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32330,7 +32330,7 @@
         <v>44729</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32392,7 +32392,7 @@
         <v>44735</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32449,7 +32449,7 @@
         <v>44735</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32506,7 +32506,7 @@
         <v>44741</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32563,7 +32563,7 @@
         <v>44741</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32620,7 +32620,7 @@
         <v>44741</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32677,7 +32677,7 @@
         <v>44743</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32739,7 +32739,7 @@
         <v>44743</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32796,7 +32796,7 @@
         <v>44748</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32858,7 +32858,7 @@
         <v>44747</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32920,7 +32920,7 @@
         <v>44748</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32982,7 +32982,7 @@
         <v>44748</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33039,7 +33039,7 @@
         <v>44750</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33096,7 +33096,7 @@
         <v>44756</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33153,7 +33153,7 @@
         <v>44761</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33210,7 +33210,7 @@
         <v>44776</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33267,7 +33267,7 @@
         <v>44777</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33329,7 +33329,7 @@
         <v>44781</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33386,7 +33386,7 @@
         <v>44783</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33443,7 +33443,7 @@
         <v>44785</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33505,7 +33505,7 @@
         <v>44784</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33567,7 +33567,7 @@
         <v>44785</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33624,7 +33624,7 @@
         <v>44792</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33681,7 +33681,7 @@
         <v>44792</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33743,7 +33743,7 @@
         <v>44795</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33800,7 +33800,7 @@
         <v>44795</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33862,7 +33862,7 @@
         <v>44803</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33924,7 +33924,7 @@
         <v>44805</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33986,7 +33986,7 @@
         <v>44806</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34043,7 +34043,7 @@
         <v>44809</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34105,7 +34105,7 @@
         <v>44809</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34167,7 +34167,7 @@
         <v>44811</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34224,7 +34224,7 @@
         <v>44813</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34281,7 +34281,7 @@
         <v>44813</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34338,7 +34338,7 @@
         <v>44813</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34395,7 +34395,7 @@
         <v>44813</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34452,7 +34452,7 @@
         <v>44813</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34509,7 +34509,7 @@
         <v>44816</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34566,7 +34566,7 @@
         <v>44816</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34623,7 +34623,7 @@
         <v>44817</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34685,7 +34685,7 @@
         <v>44817</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34742,7 +34742,7 @@
         <v>44818</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34804,7 +34804,7 @@
         <v>44818</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34866,7 +34866,7 @@
         <v>44818</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34928,7 +34928,7 @@
         <v>44817</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34985,7 +34985,7 @@
         <v>44818</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35047,7 +35047,7 @@
         <v>44818</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35109,7 +35109,7 @@
         <v>44818</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35171,7 +35171,7 @@
         <v>44818</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35228,7 +35228,7 @@
         <v>44819</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35285,7 +35285,7 @@
         <v>44820</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35342,7 +35342,7 @@
         <v>44823</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35404,7 +35404,7 @@
         <v>44824</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35461,7 +35461,7 @@
         <v>44827</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35523,7 +35523,7 @@
         <v>44838</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35585,7 +35585,7 @@
         <v>44838</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35642,7 +35642,7 @@
         <v>44839</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35699,7 +35699,7 @@
         <v>44840</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35756,7 +35756,7 @@
         <v>44840</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35813,7 +35813,7 @@
         <v>44841</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35875,7 +35875,7 @@
         <v>44845</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35937,7 +35937,7 @@
         <v>44845</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35999,7 +35999,7 @@
         <v>44848</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36061,7 +36061,7 @@
         <v>44848</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36123,7 +36123,7 @@
         <v>44849</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36185,7 +36185,7 @@
         <v>44848</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36242,7 +36242,7 @@
         <v>44853</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36304,7 +36304,7 @@
         <v>44853</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36366,7 +36366,7 @@
         <v>44853</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36428,7 +36428,7 @@
         <v>44856</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36490,7 +36490,7 @@
         <v>44855</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36552,7 +36552,7 @@
         <v>44857</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36609,7 +36609,7 @@
         <v>44859</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36666,7 +36666,7 @@
         <v>44859</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36723,7 +36723,7 @@
         <v>44861</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36785,7 +36785,7 @@
         <v>44861</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36842,7 +36842,7 @@
         <v>44861</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36904,7 +36904,7 @@
         <v>44861</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36961,7 +36961,7 @@
         <v>44861</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37023,7 +37023,7 @@
         <v>44861</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37085,7 +37085,7 @@
         <v>44861</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37142,7 +37142,7 @@
         <v>44862</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37204,7 +37204,7 @@
         <v>44866</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37266,7 +37266,7 @@
         <v>44867</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37328,7 +37328,7 @@
         <v>44867</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37390,7 +37390,7 @@
         <v>44867</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37447,7 +37447,7 @@
         <v>44868</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37504,7 +37504,7 @@
         <v>44873</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37566,7 +37566,7 @@
         <v>44874</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37623,7 +37623,7 @@
         <v>44874</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37685,7 +37685,7 @@
         <v>44875</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37742,7 +37742,7 @@
         <v>44879</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37799,7 +37799,7 @@
         <v>44879</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37856,7 +37856,7 @@
         <v>44879</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37913,7 +37913,7 @@
         <v>44879</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37970,7 +37970,7 @@
         <v>44883</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38032,7 +38032,7 @@
         <v>44886</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38089,7 +38089,7 @@
         <v>44888</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38146,7 +38146,7 @@
         <v>44888</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38203,7 +38203,7 @@
         <v>44889</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38265,7 +38265,7 @@
         <v>44889</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38327,7 +38327,7 @@
         <v>44890</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38384,7 +38384,7 @@
         <v>44890</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38441,7 +38441,7 @@
         <v>44890</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38503,7 +38503,7 @@
         <v>44893</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38565,7 +38565,7 @@
         <v>44895</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38627,7 +38627,7 @@
         <v>44897</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38684,7 +38684,7 @@
         <v>44901</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38741,7 +38741,7 @@
         <v>44904</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38798,7 +38798,7 @@
         <v>44907</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38855,7 +38855,7 @@
         <v>44907</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38912,7 +38912,7 @@
         <v>44909</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38974,7 +38974,7 @@
         <v>44910</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39031,7 +39031,7 @@
         <v>44910</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39088,7 +39088,7 @@
         <v>44911</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39150,7 +39150,7 @@
         <v>44911</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39212,7 +39212,7 @@
         <v>44911</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39269,7 +39269,7 @@
         <v>44916</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39326,7 +39326,7 @@
         <v>44917</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39388,7 +39388,7 @@
         <v>44929</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39445,7 +39445,7 @@
         <v>44929</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39502,7 +39502,7 @@
         <v>44941</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39559,7 +39559,7 @@
         <v>44942</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39616,7 +39616,7 @@
         <v>44942</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39673,7 +39673,7 @@
         <v>44942</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39730,7 +39730,7 @@
         <v>44942</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39787,7 +39787,7 @@
         <v>44944</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39844,7 +39844,7 @@
         <v>44950</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39901,7 +39901,7 @@
         <v>44951</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39958,7 +39958,7 @@
         <v>44960</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40015,7 +40015,7 @@
         <v>44963</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40072,7 +40072,7 @@
         <v>44965</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40129,7 +40129,7 @@
         <v>44965</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40186,7 +40186,7 @@
         <v>44966</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40243,7 +40243,7 @@
         <v>44966</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40300,7 +40300,7 @@
         <v>44971</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40362,7 +40362,7 @@
         <v>44971</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40419,7 +40419,7 @@
         <v>44972</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40476,7 +40476,7 @@
         <v>44973</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40533,7 +40533,7 @@
         <v>44973</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40590,7 +40590,7 @@
         <v>44973</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40647,7 +40647,7 @@
         <v>44977</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40704,7 +40704,7 @@
         <v>44981</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40761,7 +40761,7 @@
         <v>44984</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40818,7 +40818,7 @@
         <v>44985</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40875,7 +40875,7 @@
         <v>44985</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40932,7 +40932,7 @@
         <v>44985</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40989,7 +40989,7 @@
         <v>44991</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41046,7 +41046,7 @@
         <v>44991</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41103,7 +41103,7 @@
         <v>45006</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41160,7 +41160,7 @@
         <v>45006</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41217,7 +41217,7 @@
         <v>45013</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41274,7 +41274,7 @@
         <v>45015</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41336,7 +41336,7 @@
         <v>45015</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41398,7 +41398,7 @@
         <v>45015</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41455,7 +41455,7 @@
         <v>45021</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41512,7 +41512,7 @@
         <v>45021</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41569,7 +41569,7 @@
         <v>45028</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41626,7 +41626,7 @@
         <v>45029</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41683,7 +41683,7 @@
         <v>45030</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41740,7 +41740,7 @@
         <v>45036</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41797,7 +41797,7 @@
         <v>45036</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41854,7 +41854,7 @@
         <v>45036</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41911,7 +41911,7 @@
         <v>45035</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41973,7 +41973,7 @@
         <v>45036</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42030,7 +42030,7 @@
         <v>45035</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42087,7 +42087,7 @@
         <v>45043</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42144,7 +42144,7 @@
         <v>45043</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42201,7 +42201,7 @@
         <v>45043</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42258,7 +42258,7 @@
         <v>45044</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42320,7 +42320,7 @@
         <v>45048</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42377,7 +42377,7 @@
         <v>45050</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42434,7 +42434,7 @@
         <v>45055</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42491,7 +42491,7 @@
         <v>45057</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42548,7 +42548,7 @@
         <v>45056</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42605,7 +42605,7 @@
         <v>45062</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42667,7 +42667,7 @@
         <v>45062</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42729,7 +42729,7 @@
         <v>45064</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42791,7 +42791,7 @@
         <v>45066</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42853,7 +42853,7 @@
         <v>45068</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42915,7 +42915,7 @@
         <v>45070</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42977,7 +42977,7 @@
         <v>45072</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -43039,7 +43039,7 @@
         <v>45072</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43101,7 +43101,7 @@
         <v>45076</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43158,7 +43158,7 @@
         <v>45076</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43215,7 +43215,7 @@
         <v>45077</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43272,7 +43272,7 @@
         <v>45079</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43334,7 +43334,7 @@
         <v>45079</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43396,7 +43396,7 @@
         <v>45086</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43458,7 +43458,7 @@
         <v>45085</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43520,7 +43520,7 @@
         <v>45086</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43577,7 +43577,7 @@
         <v>45086</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43634,7 +43634,7 @@
         <v>45086</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43691,7 +43691,7 @@
         <v>45086</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43748,7 +43748,7 @@
         <v>45086</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43805,7 +43805,7 @@
         <v>45086</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43862,7 +43862,7 @@
         <v>45090</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43924,7 +43924,7 @@
         <v>45089</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43981,7 +43981,7 @@
         <v>45090</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -44038,7 +44038,7 @@
         <v>45090</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44095,7 +44095,7 @@
         <v>45090</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44152,7 +44152,7 @@
         <v>45090</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44209,7 +44209,7 @@
         <v>45090</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44266,7 +44266,7 @@
         <v>45091</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44323,7 +44323,7 @@
         <v>45091</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44380,7 +44380,7 @@
         <v>45091</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44437,7 +44437,7 @@
         <v>45091</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44494,7 +44494,7 @@
         <v>45093</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44556,7 +44556,7 @@
         <v>45094</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44618,7 +44618,7 @@
         <v>45096</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44675,7 +44675,7 @@
         <v>45096</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44732,7 +44732,7 @@
         <v>45096</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44794,7 +44794,7 @@
         <v>45098</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44851,7 +44851,7 @@
         <v>45098</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44913,7 +44913,7 @@
         <v>45098</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44975,7 +44975,7 @@
         <v>45098</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -45037,7 +45037,7 @@
         <v>45098</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -45094,7 +45094,7 @@
         <v>45098</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45151,7 +45151,7 @@
         <v>45098</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45213,7 +45213,7 @@
         <v>45098</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45275,7 +45275,7 @@
         <v>45098</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45332,7 +45332,7 @@
         <v>45098</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45394,7 +45394,7 @@
         <v>45098</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45451,7 +45451,7 @@
         <v>45098</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45508,7 +45508,7 @@
         <v>45098</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45565,7 +45565,7 @@
         <v>45098</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45622,7 +45622,7 @@
         <v>45099</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45684,7 +45684,7 @@
         <v>45100</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45746,7 +45746,7 @@
         <v>45100</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45808,7 +45808,7 @@
         <v>45100</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45870,7 +45870,7 @@
         <v>45100</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45927,7 +45927,7 @@
         <v>45103</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45989,7 +45989,7 @@
         <v>45104</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -46046,7 +46046,7 @@
         <v>45104</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -46103,7 +46103,7 @@
         <v>45104</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46160,7 +46160,7 @@
         <v>45104</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46217,7 +46217,7 @@
         <v>45104</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46274,7 +46274,7 @@
         <v>45106</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46331,7 +46331,7 @@
         <v>45106</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46388,7 +46388,7 @@
         <v>45106</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46445,7 +46445,7 @@
         <v>45106</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46502,7 +46502,7 @@
         <v>45106</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46559,7 +46559,7 @@
         <v>45106</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46616,7 +46616,7 @@
         <v>45107</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46673,7 +46673,7 @@
         <v>45107</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46730,7 +46730,7 @@
         <v>45107</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46787,7 +46787,7 @@
         <v>45107</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46844,7 +46844,7 @@
         <v>45110</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46901,7 +46901,7 @@
         <v>45110</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46958,7 +46958,7 @@
         <v>45110</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -47015,7 +47015,7 @@
         <v>45110</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -47072,7 +47072,7 @@
         <v>45111</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47129,7 +47129,7 @@
         <v>45114</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47186,7 +47186,7 @@
         <v>45114</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47243,7 +47243,7 @@
         <v>45118</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47305,7 +47305,7 @@
         <v>45118</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47367,7 +47367,7 @@
         <v>45118</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47429,7 +47429,7 @@
         <v>45118</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47491,7 +47491,7 @@
         <v>45118</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47553,7 +47553,7 @@
         <v>45118</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47615,7 +47615,7 @@
         <v>45119</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47677,7 +47677,7 @@
         <v>45119</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47734,7 +47734,7 @@
         <v>45120</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47791,7 +47791,7 @@
         <v>45120</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47848,7 +47848,7 @@
         <v>45120</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47905,7 +47905,7 @@
         <v>45120</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47962,7 +47962,7 @@
         <v>45125</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -48019,7 +48019,7 @@
         <v>45125</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -48076,7 +48076,7 @@
         <v>45125</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -48133,7 +48133,7 @@
         <v>45129</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48190,7 +48190,7 @@
         <v>45129</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48247,7 +48247,7 @@
         <v>45135</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48304,7 +48304,7 @@
         <v>45135</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48361,7 +48361,7 @@
         <v>45138</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48418,7 +48418,7 @@
         <v>45138</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48475,7 +48475,7 @@
         <v>45139</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48532,7 +48532,7 @@
         <v>45139</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48589,7 +48589,7 @@
         <v>45139</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48646,7 +48646,7 @@
         <v>45140</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48708,7 +48708,7 @@
         <v>45140</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48765,7 +48765,7 @@
         <v>45140</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48827,7 +48827,7 @@
         <v>45141</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48884,7 +48884,7 @@
         <v>45145</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48941,7 +48941,7 @@
         <v>45152</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -49003,7 +49003,7 @@
         <v>45152</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -49065,7 +49065,7 @@
         <v>45156</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -49122,7 +49122,7 @@
         <v>45159</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49179,7 +49179,7 @@
         <v>45159</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49236,7 +49236,7 @@
         <v>45160</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49298,7 +49298,7 @@
         <v>45160</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49360,7 +49360,7 @@
         <v>45160</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49417,7 +49417,7 @@
         <v>45162</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49474,7 +49474,7 @@
         <v>45162</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49531,7 +49531,7 @@
         <v>45163</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49588,7 +49588,7 @@
         <v>45167</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49650,7 +49650,7 @@
         <v>45167</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49712,7 +49712,7 @@
         <v>45167</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49769,7 +49769,7 @@
         <v>45167</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49831,7 +49831,7 @@
         <v>45168</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49893,7 +49893,7 @@
         <v>45167</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49950,7 +49950,7 @@
         <v>45168</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -50012,7 +50012,7 @@
         <v>45168</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -50074,7 +50074,7 @@
         <v>45170</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -50131,7 +50131,7 @@
         <v>45170</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -50188,7 +50188,7 @@
         <v>45175</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -50245,7 +50245,7 @@
         <v>45176</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50307,7 +50307,7 @@
         <v>45176</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50369,7 +50369,7 @@
         <v>45176</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50426,7 +50426,7 @@
         <v>45177</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50483,7 +50483,7 @@
         <v>45177</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50540,7 +50540,7 @@
         <v>45177</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50597,7 +50597,7 @@
         <v>45180</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50654,7 +50654,7 @@
         <v>45181</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50716,7 +50716,7 @@
         <v>45181</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50778,7 +50778,7 @@
         <v>45181</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50835,7 +50835,7 @@
         <v>45181</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50892,7 +50892,7 @@
         <v>45182</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50949,7 +50949,7 @@
         <v>45183</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -51006,7 +51006,7 @@
         <v>45184</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -51068,7 +51068,7 @@
         <v>45187</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -51125,7 +51125,7 @@
         <v>45187</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -51182,7 +51182,7 @@
         <v>45187</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -51239,7 +51239,7 @@
         <v>45187</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -51296,7 +51296,7 @@
         <v>45187</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -51353,7 +51353,7 @@
         <v>45187</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -51410,7 +51410,7 @@
         <v>45187</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -51467,7 +51467,7 @@
         <v>45188</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51529,7 +51529,7 @@
         <v>45188</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51591,7 +51591,7 @@
         <v>45188</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51653,7 +51653,7 @@
         <v>45188</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51715,7 +51715,7 @@
         <v>45188</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51777,7 +51777,7 @@
         <v>45188</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51839,7 +51839,7 @@
         <v>45188</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51901,7 +51901,7 @@
         <v>45188</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51958,7 +51958,7 @@
         <v>45189</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -52020,7 +52020,7 @@
         <v>45190</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -52077,7 +52077,7 @@
         <v>45190</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -52134,7 +52134,7 @@
         <v>45190</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -52191,7 +52191,7 @@
         <v>45190</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -52248,7 +52248,7 @@
         <v>45196</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -52305,7 +52305,7 @@
         <v>45197</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -52362,7 +52362,7 @@
         <v>45197</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -52419,7 +52419,7 @@
         <v>45198</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -52481,7 +52481,7 @@
         <v>45201</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -52543,7 +52543,7 @@
         <v>45201</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52605,7 +52605,7 @@
         <v>45202</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52667,7 +52667,7 @@
         <v>45202</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52724,7 +52724,7 @@
         <v>45203</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52781,7 +52781,7 @@
         <v>45204</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52843,7 +52843,7 @@
         <v>45208</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52900,7 +52900,7 @@
         <v>45209</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52957,7 +52957,7 @@
         <v>45208</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -53019,7 +53019,7 @@
         <v>45211</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -53076,7 +53076,7 @@
         <v>45211</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -53133,7 +53133,7 @@
         <v>45211</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -53190,7 +53190,7 @@
         <v>45211</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -53252,7 +53252,7 @@
         <v>45211</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -53314,7 +53314,7 @@
         <v>45211</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -53371,7 +53371,7 @@
         <v>45212</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -53428,7 +53428,7 @@
         <v>45213</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -53485,7 +53485,7 @@
         <v>45215</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -53542,7 +53542,7 @@
         <v>45215</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53599,7 +53599,7 @@
         <v>45216</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53656,7 +53656,7 @@
         <v>45216</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53718,7 +53718,7 @@
         <v>45218</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -53775,7 +53775,7 @@
         <v>45218</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -53837,7 +53837,7 @@
         <v>45218</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -53894,7 +53894,7 @@
         <v>45218</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -53951,7 +53951,7 @@
         <v>45219</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -54008,7 +54008,7 @@
         <v>45219</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -54065,7 +54065,7 @@
         <v>45219</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -54127,7 +54127,7 @@
         <v>45219</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -54189,7 +54189,7 @@
         <v>45219</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -54246,7 +54246,7 @@
         <v>45219</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -54303,7 +54303,7 @@
         <v>45222</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -54360,7 +54360,7 @@
         <v>45222</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -54422,7 +54422,7 @@
         <v>45222</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -54479,7 +54479,7 @@
         <v>45225</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -54536,7 +54536,7 @@
         <v>45225</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -54593,7 +54593,7 @@
         <v>45230</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -54655,7 +54655,7 @@
         <v>45230</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -54712,7 +54712,7 @@
         <v>45230</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -54769,7 +54769,7 @@
         <v>45230</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -54826,7 +54826,7 @@
         <v>45232</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -54888,7 +54888,7 @@
         <v>45232</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -54950,7 +54950,7 @@
         <v>45232</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -55012,7 +55012,7 @@
         <v>45236</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -55074,7 +55074,7 @@
         <v>45236</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -55131,7 +55131,7 @@
         <v>45237</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -55188,7 +55188,7 @@
         <v>45237</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -55245,7 +55245,7 @@
         <v>45237</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -55302,7 +55302,7 @@
         <v>45237</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -55359,7 +55359,7 @@
         <v>45237</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -55421,7 +55421,7 @@
         <v>45237</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -55478,7 +55478,7 @@
         <v>45237</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -55535,7 +55535,7 @@
         <v>45238</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -55592,7 +55592,7 @@
         <v>45239</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -55649,7 +55649,7 @@
         <v>45239</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -55711,7 +55711,7 @@
         <v>45239</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -55768,7 +55768,7 @@
         <v>45239</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -55825,7 +55825,7 @@
         <v>45240</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -55882,7 +55882,7 @@
         <v>45240</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -55939,7 +55939,7 @@
         <v>45243</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -56001,7 +56001,7 @@
         <v>45243</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -56063,7 +56063,7 @@
         <v>45244</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -56120,7 +56120,7 @@
         <v>45244</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -56177,7 +56177,7 @@
         <v>45244</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -56234,7 +56234,7 @@
         <v>45244</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -56291,7 +56291,7 @@
         <v>45244</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -56348,7 +56348,7 @@
         <v>45244</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -56405,7 +56405,7 @@
         <v>45244</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -56462,7 +56462,7 @@
         <v>45244</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -56519,7 +56519,7 @@
         <v>45244</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -56576,7 +56576,7 @@
         <v>45245</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -56633,7 +56633,7 @@
         <v>45245</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -56690,7 +56690,7 @@
         <v>45245</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -56747,7 +56747,7 @@
         <v>45246</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -56804,7 +56804,7 @@
         <v>45246</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -56861,7 +56861,7 @@
         <v>45247</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -56918,7 +56918,7 @@
         <v>45251</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -56975,7 +56975,7 @@
         <v>45252</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -57032,7 +57032,7 @@
         <v>45252</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -57089,7 +57089,7 @@
         <v>45253</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -57146,7 +57146,7 @@
         <v>45254</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -57203,7 +57203,7 @@
         <v>45254</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -57260,7 +57260,7 @@
         <v>45257</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -57317,7 +57317,7 @@
         <v>45257</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -57374,7 +57374,7 @@
         <v>45258</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -57431,7 +57431,7 @@
         <v>45259</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -57488,7 +57488,7 @@
         <v>45259</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -57545,7 +57545,7 @@
         <v>45260</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -57602,7 +57602,7 @@
         <v>45260</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -57659,7 +57659,7 @@
         <v>45260</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -57716,7 +57716,7 @@
         <v>45260</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -57773,7 +57773,7 @@
         <v>45261</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -57830,7 +57830,7 @@
         <v>45261</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -57887,7 +57887,7 @@
         <v>45262</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -57944,7 +57944,7 @@
         <v>45264</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -58001,7 +58001,7 @@
         <v>45264</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -58058,7 +58058,7 @@
         <v>45264</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -58115,7 +58115,7 @@
         <v>45264</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -58177,7 +58177,7 @@
         <v>45264</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -58234,7 +58234,7 @@
         <v>45265</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -58291,7 +58291,7 @@
         <v>45265</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -58348,7 +58348,7 @@
         <v>45266</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -58405,7 +58405,7 @@
         <v>45266</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -58462,7 +58462,7 @@
         <v>45266</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -58519,7 +58519,7 @@
         <v>45267</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -58576,7 +58576,7 @@
         <v>45271</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -58633,7 +58633,7 @@
         <v>45271</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -58690,7 +58690,7 @@
         <v>45273</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -58747,7 +58747,7 @@
         <v>45273</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -58804,7 +58804,7 @@
         <v>45273</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -58861,7 +58861,7 @@
         <v>45273</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -58918,7 +58918,7 @@
         <v>45273</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -58975,7 +58975,7 @@
         <v>45273</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -59032,7 +59032,7 @@
         <v>45273</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -59089,7 +59089,7 @@
         <v>45278</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -59146,7 +59146,7 @@
         <v>45279</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -59203,7 +59203,7 @@
         <v>45279</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -59260,7 +59260,7 @@
         <v>45279</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -59317,7 +59317,7 @@
         <v>45281</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -59374,7 +59374,7 @@
         <v>45282</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -59436,7 +59436,7 @@
         <v>45285</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -59493,7 +59493,7 @@
         <v>45285</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -59550,7 +59550,7 @@
         <v>45285</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -59607,7 +59607,7 @@
         <v>45285</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -59664,7 +59664,7 @@
         <v>45287</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -59721,7 +59721,7 @@
         <v>45287</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -59778,7 +59778,7 @@
         <v>45289</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -59835,7 +59835,7 @@
         <v>45299</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -59892,7 +59892,7 @@
         <v>45308</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -59949,7 +59949,7 @@
         <v>45308</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -60006,7 +60006,7 @@
         <v>45309</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -60063,7 +60063,7 @@
         <v>45310</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -60120,7 +60120,7 @@
         <v>45310</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -60177,7 +60177,7 @@
         <v>45311</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -60234,7 +60234,7 @@
         <v>45311</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -60291,7 +60291,7 @@
         <v>45312</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -60348,7 +60348,7 @@
         <v>45312</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -60405,7 +60405,7 @@
         <v>45313</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -60462,7 +60462,7 @@
         <v>45315</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -60519,7 +60519,7 @@
         <v>45315</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -60576,7 +60576,7 @@
         <v>45315</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -60633,7 +60633,7 @@
         <v>45316</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -60690,7 +60690,7 @@
         <v>45316</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -60747,7 +60747,7 @@
         <v>45316</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -60797,14 +60797,14 @@
     <row r="999" ht="15" customHeight="1">
       <c r="A999" t="inlineStr">
         <is>
-          <t>A 3504-2024</t>
+          <t>A 3521-2024</t>
         </is>
       </c>
       <c r="B999" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -60817,7 +60817,7 @@
         </is>
       </c>
       <c r="G999" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="H999" t="n">
         <v>0</v>
@@ -60854,14 +60854,14 @@
     <row r="1000" ht="15" customHeight="1">
       <c r="A1000" t="inlineStr">
         <is>
-          <t>A 3521-2024</t>
+          <t>A 3504-2024</t>
         </is>
       </c>
       <c r="B1000" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -60874,7 +60874,7 @@
         </is>
       </c>
       <c r="G1000" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="H1000" t="n">
         <v>0</v>
@@ -60918,7 +60918,7 @@
         <v>45323</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -60968,14 +60968,14 @@
     <row r="1002" ht="15" customHeight="1">
       <c r="A1002" t="inlineStr">
         <is>
-          <t>A 4122-2024</t>
+          <t>A 4049-2024</t>
         </is>
       </c>
       <c r="B1002" s="1" t="n">
         <v>45323</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -60985,11 +60985,6 @@
       <c r="E1002" t="inlineStr">
         <is>
           <t>PITEÅ</t>
-        </is>
-      </c>
-      <c r="F1002" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
         </is>
       </c>
       <c r="G1002" t="n">
@@ -61030,14 +61025,14 @@
     <row r="1003" ht="15" customHeight="1">
       <c r="A1003" t="inlineStr">
         <is>
-          <t>A 4049-2024</t>
+          <t>A 4127-2024</t>
         </is>
       </c>
       <c r="B1003" s="1" t="n">
         <v>45323</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -61049,8 +61044,13 @@
           <t>PITEÅ</t>
         </is>
       </c>
+      <c r="F1003" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="G1003" t="n">
-        <v>2.8</v>
+        <v>4.5</v>
       </c>
       <c r="H1003" t="n">
         <v>0</v>
@@ -61087,14 +61087,14 @@
     <row r="1004" ht="15" customHeight="1">
       <c r="A1004" t="inlineStr">
         <is>
-          <t>A 4127-2024</t>
+          <t>A 4122-2024</t>
         </is>
       </c>
       <c r="B1004" s="1" t="n">
         <v>45323</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -61112,7 +61112,7 @@
         </is>
       </c>
       <c r="G1004" t="n">
-        <v>4.5</v>
+        <v>2.8</v>
       </c>
       <c r="H1004" t="n">
         <v>0</v>
@@ -61156,7 +61156,7 @@
         <v>45323</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -61218,7 +61218,7 @@
         <v>45324</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -61280,7 +61280,7 @@
         <v>45324</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -61342,7 +61342,7 @@
         <v>45324</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -61399,7 +61399,7 @@
         <v>45329</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -61456,7 +61456,7 @@
         <v>45330</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -61513,7 +61513,7 @@
         <v>45334</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -61570,7 +61570,7 @@
         <v>45335</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -61627,7 +61627,7 @@
         <v>45342</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -61677,14 +61677,14 @@
     <row r="1014" ht="15" customHeight="1">
       <c r="A1014" t="inlineStr">
         <is>
-          <t>A 6988-2024</t>
+          <t>A 6920-2024</t>
         </is>
       </c>
       <c r="B1014" s="1" t="n">
         <v>45343</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -61697,7 +61697,7 @@
         </is>
       </c>
       <c r="G1014" t="n">
-        <v>1.6</v>
+        <v>7.6</v>
       </c>
       <c r="H1014" t="n">
         <v>0</v>
@@ -61734,14 +61734,14 @@
     <row r="1015" ht="15" customHeight="1">
       <c r="A1015" t="inlineStr">
         <is>
-          <t>A 6920-2024</t>
+          <t>A 6988-2024</t>
         </is>
       </c>
       <c r="B1015" s="1" t="n">
         <v>45343</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -61754,7 +61754,7 @@
         </is>
       </c>
       <c r="G1015" t="n">
-        <v>7.6</v>
+        <v>1.6</v>
       </c>
       <c r="H1015" t="n">
         <v>0</v>
@@ -61791,14 +61791,14 @@
     <row r="1016" ht="15" customHeight="1">
       <c r="A1016" t="inlineStr">
         <is>
-          <t>A 7458-2024</t>
+          <t>A 7457-2024</t>
         </is>
       </c>
       <c r="B1016" s="1" t="n">
         <v>45345</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -61811,7 +61811,7 @@
         </is>
       </c>
       <c r="G1016" t="n">
-        <v>9.5</v>
+        <v>7.3</v>
       </c>
       <c r="H1016" t="n">
         <v>0</v>
@@ -61848,14 +61848,14 @@
     <row r="1017" ht="15" customHeight="1">
       <c r="A1017" t="inlineStr">
         <is>
-          <t>A 7459-2024</t>
+          <t>A 7461-2024</t>
         </is>
       </c>
       <c r="B1017" s="1" t="n">
         <v>45345</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -61868,7 +61868,7 @@
         </is>
       </c>
       <c r="G1017" t="n">
-        <v>3.5</v>
+        <v>14.7</v>
       </c>
       <c r="H1017" t="n">
         <v>0</v>
@@ -61905,14 +61905,14 @@
     <row r="1018" ht="15" customHeight="1">
       <c r="A1018" t="inlineStr">
         <is>
-          <t>A 7457-2024</t>
+          <t>A 7459-2024</t>
         </is>
       </c>
       <c r="B1018" s="1" t="n">
         <v>45345</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -61925,7 +61925,7 @@
         </is>
       </c>
       <c r="G1018" t="n">
-        <v>7.3</v>
+        <v>3.5</v>
       </c>
       <c r="H1018" t="n">
         <v>0</v>
@@ -61962,14 +61962,14 @@
     <row r="1019">
       <c r="A1019" t="inlineStr">
         <is>
-          <t>A 7461-2024</t>
+          <t>A 7458-2024</t>
         </is>
       </c>
       <c r="B1019" s="1" t="n">
         <v>45345</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -61982,7 +61982,7 @@
         </is>
       </c>
       <c r="G1019" t="n">
-        <v>14.7</v>
+        <v>9.5</v>
       </c>
       <c r="H1019" t="n">
         <v>0</v>

--- a/Översikt PITEÅ.xlsx
+++ b/Översikt PITEÅ.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z1019"/>
+  <dimension ref="A1:Z1022"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>44617</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -665,7 +665,7 @@
         <v>44839</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
         <v>44839</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>44459</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
         <v>44617</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>43896</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>45191</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>45203</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>44740</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>44280</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>44539</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>44550</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>45119</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>44014</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>44522</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>44526</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         <v>44553</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>44810</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>44917</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>45103</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>45106</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         <v>43802</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>43902</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2727,7 +2727,7 @@
         <v>43908</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         <v>44053</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2908,7 +2908,7 @@
         <v>44193</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>44298</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>44840</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
         <v>44852</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3262,7 +3262,7 @@
         <v>44859</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>44944</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3434,7 +3434,7 @@
         <v>45120</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
         <v>45187</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         <v>45209</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3701,7 +3701,7 @@
         <v>45219</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>45243</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         <v>45293</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
         <v>45296</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>43714</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         <v>44014</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4225,7 +4225,7 @@
         <v>44106</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4310,7 +4310,7 @@
         <v>44309</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>44342</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4485,7 +4485,7 @@
         <v>44495</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
         <v>44525</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4665,7 +4665,7 @@
         <v>44525</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4755,7 +4755,7 @@
         <v>44538</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4840,7 +4840,7 @@
         <v>44727</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4929,7 +4929,7 @@
         <v>44804</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5014,7 +5014,7 @@
         <v>44917</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5104,7 +5104,7 @@
         <v>45049</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5193,7 +5193,7 @@
         <v>45098</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>45103</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5373,7 +5373,7 @@
         <v>45148</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
         <v>45175</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         <v>45181</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5642,7 +5642,7 @@
         <v>45188</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5732,7 +5732,7 @@
         <v>45224</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5817,7 +5817,7 @@
         <v>45243</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5907,7 +5907,7 @@
         <v>45265</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5992,7 +5992,7 @@
         <v>45323</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
         <v>43325</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6139,7 +6139,7 @@
         <v>43332</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6196,7 +6196,7 @@
         <v>43336</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6253,7 +6253,7 @@
         <v>43339</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         <v>43339</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
         <v>43341</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6424,7 +6424,7 @@
         <v>43355</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>43355</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         <v>43374</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6600,7 +6600,7 @@
         <v>43374</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6662,7 +6662,7 @@
         <v>43375</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6719,7 +6719,7 @@
         <v>43376</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
         <v>43376</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6833,7 +6833,7 @@
         <v>43381</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6890,7 +6890,7 @@
         <v>43383</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6947,7 +6947,7 @@
         <v>43391</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>43391</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7061,7 +7061,7 @@
         <v>43392</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7118,7 +7118,7 @@
         <v>43392</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7175,7 +7175,7 @@
         <v>43398</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7232,7 +7232,7 @@
         <v>43402</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7289,7 +7289,7 @@
         <v>43404</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7346,7 +7346,7 @@
         <v>43406</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7403,7 +7403,7 @@
         <v>43406</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
         <v>43406</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>43406</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>43406</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>43416</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>43418</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7745,7 +7745,7 @@
         <v>43418</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7802,7 +7802,7 @@
         <v>43418</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         <v>43419</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7916,7 +7916,7 @@
         <v>43420</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         <v>43424</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8035,7 +8035,7 @@
         <v>43427</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8097,7 +8097,7 @@
         <v>43427</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8154,7 +8154,7 @@
         <v>43427</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8216,7 +8216,7 @@
         <v>43427</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8278,7 +8278,7 @@
         <v>43436</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
         <v>43438</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8392,7 +8392,7 @@
         <v>43438</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8449,7 +8449,7 @@
         <v>43438</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8506,7 +8506,7 @@
         <v>43438</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8563,7 +8563,7 @@
         <v>43451</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8625,7 +8625,7 @@
         <v>43472</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8682,7 +8682,7 @@
         <v>43475</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8739,7 +8739,7 @@
         <v>43479</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8796,7 +8796,7 @@
         <v>43479</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8853,7 +8853,7 @@
         <v>43486</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
         <v>43489</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8967,7 +8967,7 @@
         <v>43489</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9024,7 +9024,7 @@
         <v>43489</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9081,7 +9081,7 @@
         <v>43489</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9138,7 +9138,7 @@
         <v>43489</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9195,7 +9195,7 @@
         <v>43490</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9252,7 +9252,7 @@
         <v>43490</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9309,7 +9309,7 @@
         <v>43493</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9371,7 +9371,7 @@
         <v>43509</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9428,7 +9428,7 @@
         <v>43510</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9485,7 +9485,7 @@
         <v>43510</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9542,7 +9542,7 @@
         <v>43514</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9599,7 +9599,7 @@
         <v>43514</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9656,7 +9656,7 @@
         <v>43514</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9713,7 +9713,7 @@
         <v>43516</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9775,7 +9775,7 @@
         <v>43518</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9832,7 +9832,7 @@
         <v>43521</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9894,7 +9894,7 @@
         <v>43521</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9956,7 +9956,7 @@
         <v>43521</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10018,7 +10018,7 @@
         <v>43521</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10080,7 +10080,7 @@
         <v>43521</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10142,7 +10142,7 @@
         <v>43522</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10199,7 +10199,7 @@
         <v>43523</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10256,7 +10256,7 @@
         <v>43523</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10313,7 +10313,7 @@
         <v>43523</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10370,7 +10370,7 @@
         <v>43532</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10427,7 +10427,7 @@
         <v>43532</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10484,7 +10484,7 @@
         <v>43542</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10541,7 +10541,7 @@
         <v>43544</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10603,7 +10603,7 @@
         <v>43544</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10665,7 +10665,7 @@
         <v>43554</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10722,7 +10722,7 @@
         <v>43556</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10779,7 +10779,7 @@
         <v>43557</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10841,7 +10841,7 @@
         <v>43557</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10898,7 +10898,7 @@
         <v>43557</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10955,7 +10955,7 @@
         <v>43557</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11012,7 +11012,7 @@
         <v>43557</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11074,7 +11074,7 @@
         <v>43564</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11131,7 +11131,7 @@
         <v>43564</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11188,7 +11188,7 @@
         <v>43567</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11245,7 +11245,7 @@
         <v>43570</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11302,7 +11302,7 @@
         <v>43570</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11359,7 +11359,7 @@
         <v>43570</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11416,7 +11416,7 @@
         <v>43584</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11473,7 +11473,7 @@
         <v>43605</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11530,7 +11530,7 @@
         <v>43608</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11587,7 +11587,7 @@
         <v>43614</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11649,7 +11649,7 @@
         <v>43616</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11711,7 +11711,7 @@
         <v>43616</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11773,7 +11773,7 @@
         <v>43629</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11830,7 +11830,7 @@
         <v>43629</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11892,7 +11892,7 @@
         <v>43633</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11949,7 +11949,7 @@
         <v>43633</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12006,7 +12006,7 @@
         <v>43640</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12063,7 +12063,7 @@
         <v>43640</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12120,7 +12120,7 @@
         <v>43647</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12177,7 +12177,7 @@
         <v>43647</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12234,7 +12234,7 @@
         <v>43650</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12291,7 +12291,7 @@
         <v>43652</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12353,7 +12353,7 @@
         <v>43677</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12410,7 +12410,7 @@
         <v>43678</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12467,7 +12467,7 @@
         <v>43682</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12524,7 +12524,7 @@
         <v>43691</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12586,7 +12586,7 @@
         <v>43691</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12648,7 +12648,7 @@
         <v>43696</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12710,7 +12710,7 @@
         <v>43697</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12767,7 +12767,7 @@
         <v>43698</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12829,7 +12829,7 @@
         <v>43698</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12891,7 +12891,7 @@
         <v>43706</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12948,7 +12948,7 @@
         <v>43707</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13010,7 +13010,7 @@
         <v>43711</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13067,7 +13067,7 @@
         <v>43713</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13124,7 +13124,7 @@
         <v>43718</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13181,7 +13181,7 @@
         <v>43718</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13238,7 +13238,7 @@
         <v>43718</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13300,7 +13300,7 @@
         <v>43720</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13357,7 +13357,7 @@
         <v>43721</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13414,7 +13414,7 @@
         <v>43732</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13471,7 +13471,7 @@
         <v>43741</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13533,7 +13533,7 @@
         <v>43741</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13590,7 +13590,7 @@
         <v>43752</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13652,7 +13652,7 @@
         <v>43755</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13709,7 +13709,7 @@
         <v>43755</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13766,7 +13766,7 @@
         <v>43755</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13823,7 +13823,7 @@
         <v>43755</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13880,7 +13880,7 @@
         <v>43760</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13942,7 +13942,7 @@
         <v>43760</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14004,7 +14004,7 @@
         <v>43760</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14061,7 +14061,7 @@
         <v>43762</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14123,7 +14123,7 @@
         <v>43766</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14180,7 +14180,7 @@
         <v>43766</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14237,7 +14237,7 @@
         <v>43768</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14294,7 +14294,7 @@
         <v>43770</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14356,7 +14356,7 @@
         <v>43775</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14418,7 +14418,7 @@
         <v>43775</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14480,7 +14480,7 @@
         <v>43777</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14537,7 +14537,7 @@
         <v>43780</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14594,7 +14594,7 @@
         <v>43780</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14651,7 +14651,7 @@
         <v>43780</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14708,7 +14708,7 @@
         <v>43782</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14770,7 +14770,7 @@
         <v>43789</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14832,7 +14832,7 @@
         <v>43798</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14889,7 +14889,7 @@
         <v>43801</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14951,7 +14951,7 @@
         <v>43802</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15008,7 +15008,7 @@
         <v>43802</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15065,7 +15065,7 @@
         <v>43802</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15122,7 +15122,7 @@
         <v>43802</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15179,7 +15179,7 @@
         <v>43802</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15236,7 +15236,7 @@
         <v>43802</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15293,7 +15293,7 @@
         <v>43807</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15350,7 +15350,7 @@
         <v>43809</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15407,7 +15407,7 @@
         <v>43817</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15464,7 +15464,7 @@
         <v>43817</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15526,7 +15526,7 @@
         <v>43822</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15583,7 +15583,7 @@
         <v>43822</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15640,7 +15640,7 @@
         <v>43833</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15697,7 +15697,7 @@
         <v>43846</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15754,7 +15754,7 @@
         <v>43852</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15811,7 +15811,7 @@
         <v>43853</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15868,7 +15868,7 @@
         <v>43854</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15925,7 +15925,7 @@
         <v>43859</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15987,7 +15987,7 @@
         <v>43859</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16044,7 +16044,7 @@
         <v>43859</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16101,7 +16101,7 @@
         <v>43859</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16158,7 +16158,7 @@
         <v>43859</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16215,7 +16215,7 @@
         <v>43860</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16272,7 +16272,7 @@
         <v>43868</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16329,7 +16329,7 @@
         <v>43868</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16386,7 +16386,7 @@
         <v>43874</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16448,7 +16448,7 @@
         <v>43878</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16505,7 +16505,7 @@
         <v>43880</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16562,7 +16562,7 @@
         <v>43880</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16619,7 +16619,7 @@
         <v>43889</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16676,7 +16676,7 @@
         <v>43895</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16738,7 +16738,7 @@
         <v>43896</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16795,7 +16795,7 @@
         <v>43902</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16852,7 +16852,7 @@
         <v>43902</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16914,7 +16914,7 @@
         <v>43907</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16971,7 +16971,7 @@
         <v>43913</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17028,7 +17028,7 @@
         <v>43914</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17090,7 +17090,7 @@
         <v>43927</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17152,7 +17152,7 @@
         <v>43929</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         <v>43929</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>43931</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17328,7 +17328,7 @@
         <v>43950</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17385,7 +17385,7 @@
         <v>43957</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17447,7 +17447,7 @@
         <v>43958</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17504,7 +17504,7 @@
         <v>43958</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17561,7 +17561,7 @@
         <v>43959</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17618,7 +17618,7 @@
         <v>43962</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17675,7 +17675,7 @@
         <v>43962</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17732,7 +17732,7 @@
         <v>43962</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17789,7 +17789,7 @@
         <v>43962</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17846,7 +17846,7 @@
         <v>43970</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17908,7 +17908,7 @@
         <v>43971</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17970,7 +17970,7 @@
         <v>43976</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18027,7 +18027,7 @@
         <v>43979</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18084,7 +18084,7 @@
         <v>43979</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18141,7 +18141,7 @@
         <v>43979</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18198,7 +18198,7 @@
         <v>43984</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18260,7 +18260,7 @@
         <v>43984</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18317,7 +18317,7 @@
         <v>43987</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18374,7 +18374,7 @@
         <v>43990</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18431,7 +18431,7 @@
         <v>43994</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18493,7 +18493,7 @@
         <v>43997</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18550,7 +18550,7 @@
         <v>43999</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18607,7 +18607,7 @@
         <v>44000</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18669,7 +18669,7 @@
         <v>44006</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18726,7 +18726,7 @@
         <v>44006</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18783,7 +18783,7 @@
         <v>44007</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18840,7 +18840,7 @@
         <v>44007</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18897,7 +18897,7 @@
         <v>44011</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18954,7 +18954,7 @@
         <v>44012</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19016,7 +19016,7 @@
         <v>44020</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19078,7 +19078,7 @@
         <v>44020</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19135,7 +19135,7 @@
         <v>44020</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19197,7 +19197,7 @@
         <v>44026</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19259,7 +19259,7 @@
         <v>44035</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19316,7 +19316,7 @@
         <v>44049</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19373,7 +19373,7 @@
         <v>44063</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19435,7 +19435,7 @@
         <v>44067</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19497,7 +19497,7 @@
         <v>44067</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19559,7 +19559,7 @@
         <v>44068</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19621,7 +19621,7 @@
         <v>44069</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19678,7 +19678,7 @@
         <v>44070</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19735,7 +19735,7 @@
         <v>44074</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19792,7 +19792,7 @@
         <v>44075</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19849,7 +19849,7 @@
         <v>44078</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19906,7 +19906,7 @@
         <v>44083</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19963,7 +19963,7 @@
         <v>44083</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20020,7 +20020,7 @@
         <v>44087</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20077,7 +20077,7 @@
         <v>44088</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20139,7 +20139,7 @@
         <v>44088</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20196,7 +20196,7 @@
         <v>44088</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20258,7 +20258,7 @@
         <v>44092</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20315,7 +20315,7 @@
         <v>44092</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20372,7 +20372,7 @@
         <v>44092</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20429,7 +20429,7 @@
         <v>44095</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20486,7 +20486,7 @@
         <v>44099</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20543,7 +20543,7 @@
         <v>44099</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20600,7 +20600,7 @@
         <v>44099</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20657,7 +20657,7 @@
         <v>44099</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20714,7 +20714,7 @@
         <v>44103</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20771,7 +20771,7 @@
         <v>44103</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20828,7 +20828,7 @@
         <v>44106</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20885,7 +20885,7 @@
         <v>44111</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20947,7 +20947,7 @@
         <v>44111</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21009,7 +21009,7 @@
         <v>44123</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21066,7 +21066,7 @@
         <v>44127</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21123,7 +21123,7 @@
         <v>44132</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21180,7 +21180,7 @@
         <v>44139</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21237,7 +21237,7 @@
         <v>44141</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21294,7 +21294,7 @@
         <v>44141</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21351,7 +21351,7 @@
         <v>44155</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21408,7 +21408,7 @@
         <v>44162</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21470,7 +21470,7 @@
         <v>44166</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21532,7 +21532,7 @@
         <v>44172</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21589,7 +21589,7 @@
         <v>44180</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21646,7 +21646,7 @@
         <v>44186</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21703,7 +21703,7 @@
         <v>44209</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21760,7 +21760,7 @@
         <v>44211</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21817,7 +21817,7 @@
         <v>44211</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21874,7 +21874,7 @@
         <v>44211</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21931,7 +21931,7 @@
         <v>44215</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21993,7 +21993,7 @@
         <v>44221</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22055,7 +22055,7 @@
         <v>44237</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22117,7 +22117,7 @@
         <v>44238</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22174,7 +22174,7 @@
         <v>44256</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22231,7 +22231,7 @@
         <v>44257</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22288,7 +22288,7 @@
         <v>44258</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22345,7 +22345,7 @@
         <v>44280</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22407,7 +22407,7 @@
         <v>44281</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22464,7 +22464,7 @@
         <v>44281</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22521,7 +22521,7 @@
         <v>44281</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22578,7 +22578,7 @@
         <v>44285</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22640,7 +22640,7 @@
         <v>44286</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22697,7 +22697,7 @@
         <v>44292</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22754,7 +22754,7 @@
         <v>44294</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22816,7 +22816,7 @@
         <v>44309</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22873,7 +22873,7 @@
         <v>44320</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22930,7 +22930,7 @@
         <v>44321</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22987,7 +22987,7 @@
         <v>44321</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23044,7 +23044,7 @@
         <v>44326</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23101,7 +23101,7 @@
         <v>44326</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23163,7 +23163,7 @@
         <v>44334</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23220,7 +23220,7 @@
         <v>44339</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23277,7 +23277,7 @@
         <v>44339</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23334,7 +23334,7 @@
         <v>44339</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23391,7 +23391,7 @@
         <v>44343</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23453,7 +23453,7 @@
         <v>44342</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23515,7 +23515,7 @@
         <v>44344</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23572,7 +23572,7 @@
         <v>44350</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23629,7 +23629,7 @@
         <v>44350</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23686,7 +23686,7 @@
         <v>44351</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23748,7 +23748,7 @@
         <v>44354</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23810,7 +23810,7 @@
         <v>44355</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23872,7 +23872,7 @@
         <v>44355</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23934,7 +23934,7 @@
         <v>44357</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23991,7 +23991,7 @@
         <v>44358</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24053,7 +24053,7 @@
         <v>44361</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24110,7 +24110,7 @@
         <v>44361</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24167,7 +24167,7 @@
         <v>44361</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24224,7 +24224,7 @@
         <v>44362</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24286,7 +24286,7 @@
         <v>44361</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24348,7 +24348,7 @@
         <v>44362</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24405,7 +24405,7 @@
         <v>44368</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24467,7 +24467,7 @@
         <v>44368</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24529,7 +24529,7 @@
         <v>44368</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24591,7 +24591,7 @@
         <v>44369</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24653,7 +24653,7 @@
         <v>44370</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24715,7 +24715,7 @@
         <v>44370</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24777,7 +24777,7 @@
         <v>44370</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24839,7 +24839,7 @@
         <v>44370</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24901,7 +24901,7 @@
         <v>44371</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24963,7 +24963,7 @@
         <v>44372</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25025,7 +25025,7 @@
         <v>44372</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25087,7 +25087,7 @@
         <v>44375</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25149,7 +25149,7 @@
         <v>44376</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25211,7 +25211,7 @@
         <v>44376</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25273,7 +25273,7 @@
         <v>44376</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25330,7 +25330,7 @@
         <v>44377</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25392,7 +25392,7 @@
         <v>44378</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25449,7 +25449,7 @@
         <v>44378</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25511,7 +25511,7 @@
         <v>44378</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25568,7 +25568,7 @@
         <v>44383</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25625,7 +25625,7 @@
         <v>44383</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25682,7 +25682,7 @@
         <v>44383</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25739,7 +25739,7 @@
         <v>44383</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25796,7 +25796,7 @@
         <v>44383</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25853,7 +25853,7 @@
         <v>44384</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25915,7 +25915,7 @@
         <v>44383</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25972,7 +25972,7 @@
         <v>44386</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26029,7 +26029,7 @@
         <v>44398</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26086,7 +26086,7 @@
         <v>44404</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26143,7 +26143,7 @@
         <v>44405</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26205,7 +26205,7 @@
         <v>44418</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26267,7 +26267,7 @@
         <v>44421</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26329,7 +26329,7 @@
         <v>44428</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26386,7 +26386,7 @@
         <v>44432</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26443,7 +26443,7 @@
         <v>44432</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26500,7 +26500,7 @@
         <v>44433</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26562,7 +26562,7 @@
         <v>44433</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26624,7 +26624,7 @@
         <v>44438</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26686,7 +26686,7 @@
         <v>44439</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26748,7 +26748,7 @@
         <v>44440</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26805,7 +26805,7 @@
         <v>44441</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26867,7 +26867,7 @@
         <v>44440</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26929,7 +26929,7 @@
         <v>44446</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26986,7 +26986,7 @@
         <v>44447</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27048,7 +27048,7 @@
         <v>44453</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27105,7 +27105,7 @@
         <v>44454</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27162,7 +27162,7 @@
         <v>44454</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27219,7 +27219,7 @@
         <v>44459</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27276,7 +27276,7 @@
         <v>44463</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27338,7 +27338,7 @@
         <v>44463</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27400,7 +27400,7 @@
         <v>44463</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27457,7 +27457,7 @@
         <v>44468</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27514,7 +27514,7 @@
         <v>44468</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27571,7 +27571,7 @@
         <v>44476</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27628,7 +27628,7 @@
         <v>44480</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27685,7 +27685,7 @@
         <v>44481</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27742,7 +27742,7 @@
         <v>44484</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27799,7 +27799,7 @@
         <v>44487</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27861,7 +27861,7 @@
         <v>44490</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27918,7 +27918,7 @@
         <v>44489</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27980,7 +27980,7 @@
         <v>44496</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28037,7 +28037,7 @@
         <v>44497</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28099,7 +28099,7 @@
         <v>44497</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28156,7 +28156,7 @@
         <v>44497</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28213,7 +28213,7 @@
         <v>44498</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28270,7 +28270,7 @@
         <v>44498</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28327,7 +28327,7 @@
         <v>44499</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28384,7 +28384,7 @@
         <v>44502</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28441,7 +28441,7 @@
         <v>44516</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28498,7 +28498,7 @@
         <v>44522</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28555,7 +28555,7 @@
         <v>44523</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28612,7 +28612,7 @@
         <v>44525</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28674,7 +28674,7 @@
         <v>44525</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28731,7 +28731,7 @@
         <v>44529</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28788,7 +28788,7 @@
         <v>44530</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28850,7 +28850,7 @@
         <v>44530</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28912,7 +28912,7 @@
         <v>44531</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28969,7 +28969,7 @@
         <v>44531</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29026,7 +29026,7 @@
         <v>44536</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29083,7 +29083,7 @@
         <v>44536</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29140,7 +29140,7 @@
         <v>44538</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29197,7 +29197,7 @@
         <v>44538</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29254,7 +29254,7 @@
         <v>44538</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29311,7 +29311,7 @@
         <v>44538</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29368,7 +29368,7 @@
         <v>44538</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29425,7 +29425,7 @@
         <v>44538</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29482,7 +29482,7 @@
         <v>44538</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29539,7 +29539,7 @@
         <v>44538</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29596,7 +29596,7 @@
         <v>44539</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29658,7 +29658,7 @@
         <v>44543</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29720,7 +29720,7 @@
         <v>44543</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29782,7 +29782,7 @@
         <v>44543</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29844,7 +29844,7 @@
         <v>44543</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29906,7 +29906,7 @@
         <v>44547</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29968,7 +29968,7 @@
         <v>44550</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30025,7 +30025,7 @@
         <v>44550</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30082,7 +30082,7 @@
         <v>44571</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30139,7 +30139,7 @@
         <v>44582</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30196,7 +30196,7 @@
         <v>44582</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30253,7 +30253,7 @@
         <v>44582</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30310,7 +30310,7 @@
         <v>44582</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30367,7 +30367,7 @@
         <v>44588</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30424,7 +30424,7 @@
         <v>44589</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30481,7 +30481,7 @@
         <v>44590</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30538,7 +30538,7 @@
         <v>44590</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30595,7 +30595,7 @@
         <v>44592</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30652,7 +30652,7 @@
         <v>44592</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30709,7 +30709,7 @@
         <v>44596</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30766,7 +30766,7 @@
         <v>44599</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30823,7 +30823,7 @@
         <v>44608</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30880,7 +30880,7 @@
         <v>44615</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30937,7 +30937,7 @@
         <v>44616</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30999,7 +30999,7 @@
         <v>44617</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31061,7 +31061,7 @@
         <v>44621</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31118,7 +31118,7 @@
         <v>44621</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31180,7 +31180,7 @@
         <v>44622</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31237,7 +31237,7 @@
         <v>44623</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31294,7 +31294,7 @@
         <v>44642</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31351,7 +31351,7 @@
         <v>44643</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31408,7 +31408,7 @@
         <v>44643</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31470,7 +31470,7 @@
         <v>44644</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31527,7 +31527,7 @@
         <v>44656</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31584,7 +31584,7 @@
         <v>44658</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31641,7 +31641,7 @@
         <v>44683</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31698,7 +31698,7 @@
         <v>44683</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31755,7 +31755,7 @@
         <v>44685</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31812,7 +31812,7 @@
         <v>44685</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31869,7 +31869,7 @@
         <v>44685</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31926,7 +31926,7 @@
         <v>44687</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31983,7 +31983,7 @@
         <v>44700</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32040,7 +32040,7 @@
         <v>44708</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32097,7 +32097,7 @@
         <v>44708</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32154,7 +32154,7 @@
         <v>44708</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32211,7 +32211,7 @@
         <v>44722</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32268,7 +32268,7 @@
         <v>44727</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32330,7 +32330,7 @@
         <v>44729</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32392,7 +32392,7 @@
         <v>44735</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32449,7 +32449,7 @@
         <v>44735</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32506,7 +32506,7 @@
         <v>44741</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32563,7 +32563,7 @@
         <v>44741</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32620,7 +32620,7 @@
         <v>44741</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32677,7 +32677,7 @@
         <v>44743</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32739,7 +32739,7 @@
         <v>44743</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32796,7 +32796,7 @@
         <v>44748</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32858,7 +32858,7 @@
         <v>44747</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32920,7 +32920,7 @@
         <v>44748</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32982,7 +32982,7 @@
         <v>44748</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33039,7 +33039,7 @@
         <v>44750</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33096,7 +33096,7 @@
         <v>44756</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33153,7 +33153,7 @@
         <v>44761</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33210,7 +33210,7 @@
         <v>44776</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33267,7 +33267,7 @@
         <v>44777</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33329,7 +33329,7 @@
         <v>44781</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33386,7 +33386,7 @@
         <v>44783</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33443,7 +33443,7 @@
         <v>44785</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33505,7 +33505,7 @@
         <v>44784</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33567,7 +33567,7 @@
         <v>44785</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33624,7 +33624,7 @@
         <v>44792</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33681,7 +33681,7 @@
         <v>44792</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33743,7 +33743,7 @@
         <v>44795</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33800,7 +33800,7 @@
         <v>44795</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33862,7 +33862,7 @@
         <v>44803</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33924,7 +33924,7 @@
         <v>44805</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33986,7 +33986,7 @@
         <v>44806</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34043,7 +34043,7 @@
         <v>44809</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34105,7 +34105,7 @@
         <v>44809</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34167,7 +34167,7 @@
         <v>44811</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34224,7 +34224,7 @@
         <v>44813</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34281,7 +34281,7 @@
         <v>44813</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34338,7 +34338,7 @@
         <v>44813</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34395,7 +34395,7 @@
         <v>44813</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34452,7 +34452,7 @@
         <v>44813</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34509,7 +34509,7 @@
         <v>44816</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34566,7 +34566,7 @@
         <v>44816</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34623,7 +34623,7 @@
         <v>44817</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34685,7 +34685,7 @@
         <v>44817</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34742,7 +34742,7 @@
         <v>44818</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34804,7 +34804,7 @@
         <v>44818</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34866,7 +34866,7 @@
         <v>44818</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34928,7 +34928,7 @@
         <v>44817</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34985,7 +34985,7 @@
         <v>44818</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35047,7 +35047,7 @@
         <v>44818</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35109,7 +35109,7 @@
         <v>44818</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35171,7 +35171,7 @@
         <v>44818</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35228,7 +35228,7 @@
         <v>44819</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35285,7 +35285,7 @@
         <v>44820</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35342,7 +35342,7 @@
         <v>44823</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35404,7 +35404,7 @@
         <v>44824</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35461,7 +35461,7 @@
         <v>44827</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35523,7 +35523,7 @@
         <v>44838</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35585,7 +35585,7 @@
         <v>44838</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35642,7 +35642,7 @@
         <v>44839</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35699,7 +35699,7 @@
         <v>44840</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35756,7 +35756,7 @@
         <v>44840</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35813,7 +35813,7 @@
         <v>44841</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35875,7 +35875,7 @@
         <v>44845</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35937,7 +35937,7 @@
         <v>44845</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35999,7 +35999,7 @@
         <v>44848</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36061,7 +36061,7 @@
         <v>44848</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36123,7 +36123,7 @@
         <v>44849</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36185,7 +36185,7 @@
         <v>44848</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36242,7 +36242,7 @@
         <v>44853</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36304,7 +36304,7 @@
         <v>44853</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36366,7 +36366,7 @@
         <v>44853</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36428,7 +36428,7 @@
         <v>44856</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36490,7 +36490,7 @@
         <v>44855</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36552,7 +36552,7 @@
         <v>44857</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36609,7 +36609,7 @@
         <v>44859</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36666,7 +36666,7 @@
         <v>44859</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36723,7 +36723,7 @@
         <v>44861</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36785,7 +36785,7 @@
         <v>44861</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36842,7 +36842,7 @@
         <v>44861</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36904,7 +36904,7 @@
         <v>44861</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36961,7 +36961,7 @@
         <v>44861</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37023,7 +37023,7 @@
         <v>44861</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37085,7 +37085,7 @@
         <v>44861</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37142,7 +37142,7 @@
         <v>44862</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37204,7 +37204,7 @@
         <v>44866</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37266,7 +37266,7 @@
         <v>44867</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37328,7 +37328,7 @@
         <v>44867</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37390,7 +37390,7 @@
         <v>44867</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37447,7 +37447,7 @@
         <v>44868</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37504,7 +37504,7 @@
         <v>44873</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37566,7 +37566,7 @@
         <v>44874</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37623,7 +37623,7 @@
         <v>44874</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37685,7 +37685,7 @@
         <v>44875</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37742,7 +37742,7 @@
         <v>44879</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37799,7 +37799,7 @@
         <v>44879</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37856,7 +37856,7 @@
         <v>44879</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37913,7 +37913,7 @@
         <v>44879</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37970,7 +37970,7 @@
         <v>44883</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38032,7 +38032,7 @@
         <v>44886</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38089,7 +38089,7 @@
         <v>44888</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38146,7 +38146,7 @@
         <v>44888</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38203,7 +38203,7 @@
         <v>44889</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38265,7 +38265,7 @@
         <v>44889</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38327,7 +38327,7 @@
         <v>44890</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38384,7 +38384,7 @@
         <v>44890</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38441,7 +38441,7 @@
         <v>44890</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38503,7 +38503,7 @@
         <v>44893</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38565,7 +38565,7 @@
         <v>44895</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38627,7 +38627,7 @@
         <v>44897</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38684,7 +38684,7 @@
         <v>44901</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38741,7 +38741,7 @@
         <v>44904</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38798,7 +38798,7 @@
         <v>44907</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38855,7 +38855,7 @@
         <v>44907</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38912,7 +38912,7 @@
         <v>44909</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38974,7 +38974,7 @@
         <v>44910</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39031,7 +39031,7 @@
         <v>44910</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39088,7 +39088,7 @@
         <v>44911</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39150,7 +39150,7 @@
         <v>44911</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39212,7 +39212,7 @@
         <v>44911</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39269,7 +39269,7 @@
         <v>44916</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39326,7 +39326,7 @@
         <v>44917</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39388,7 +39388,7 @@
         <v>44929</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39445,7 +39445,7 @@
         <v>44929</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39502,7 +39502,7 @@
         <v>44941</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39559,7 +39559,7 @@
         <v>44942</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39616,7 +39616,7 @@
         <v>44942</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39673,7 +39673,7 @@
         <v>44942</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39730,7 +39730,7 @@
         <v>44942</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39787,7 +39787,7 @@
         <v>44944</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39844,7 +39844,7 @@
         <v>44950</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39901,7 +39901,7 @@
         <v>44951</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39958,7 +39958,7 @@
         <v>44960</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40015,7 +40015,7 @@
         <v>44963</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40072,7 +40072,7 @@
         <v>44965</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40129,7 +40129,7 @@
         <v>44965</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40186,7 +40186,7 @@
         <v>44966</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40243,7 +40243,7 @@
         <v>44966</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40300,7 +40300,7 @@
         <v>44971</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40362,7 +40362,7 @@
         <v>44971</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40419,7 +40419,7 @@
         <v>44972</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40476,7 +40476,7 @@
         <v>44973</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40533,7 +40533,7 @@
         <v>44973</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40590,7 +40590,7 @@
         <v>44973</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40647,7 +40647,7 @@
         <v>44977</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40704,7 +40704,7 @@
         <v>44981</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40761,7 +40761,7 @@
         <v>44984</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40818,7 +40818,7 @@
         <v>44985</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40875,7 +40875,7 @@
         <v>44985</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40932,7 +40932,7 @@
         <v>44985</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40989,7 +40989,7 @@
         <v>44991</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41046,7 +41046,7 @@
         <v>44991</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41103,7 +41103,7 @@
         <v>45006</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41160,7 +41160,7 @@
         <v>45006</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41217,7 +41217,7 @@
         <v>45013</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41274,7 +41274,7 @@
         <v>45015</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41336,7 +41336,7 @@
         <v>45015</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41398,7 +41398,7 @@
         <v>45015</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41455,7 +41455,7 @@
         <v>45021</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41512,7 +41512,7 @@
         <v>45021</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41569,7 +41569,7 @@
         <v>45028</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41626,7 +41626,7 @@
         <v>45029</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41683,7 +41683,7 @@
         <v>45030</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41740,7 +41740,7 @@
         <v>45036</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41797,7 +41797,7 @@
         <v>45036</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41854,7 +41854,7 @@
         <v>45036</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41911,7 +41911,7 @@
         <v>45035</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41973,7 +41973,7 @@
         <v>45036</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42030,7 +42030,7 @@
         <v>45035</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42087,7 +42087,7 @@
         <v>45043</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42144,7 +42144,7 @@
         <v>45043</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42201,7 +42201,7 @@
         <v>45043</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42258,7 +42258,7 @@
         <v>45044</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42320,7 +42320,7 @@
         <v>45048</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42377,7 +42377,7 @@
         <v>45050</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42434,7 +42434,7 @@
         <v>45055</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42491,7 +42491,7 @@
         <v>45057</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42548,7 +42548,7 @@
         <v>45056</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42605,7 +42605,7 @@
         <v>45062</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42667,7 +42667,7 @@
         <v>45062</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42729,7 +42729,7 @@
         <v>45064</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42791,7 +42791,7 @@
         <v>45066</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42853,7 +42853,7 @@
         <v>45068</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42915,7 +42915,7 @@
         <v>45070</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42977,7 +42977,7 @@
         <v>45072</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -43039,7 +43039,7 @@
         <v>45072</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43101,7 +43101,7 @@
         <v>45076</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43158,7 +43158,7 @@
         <v>45076</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43215,7 +43215,7 @@
         <v>45077</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43272,7 +43272,7 @@
         <v>45079</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43334,7 +43334,7 @@
         <v>45079</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43396,7 +43396,7 @@
         <v>45086</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43458,7 +43458,7 @@
         <v>45085</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43520,7 +43520,7 @@
         <v>45086</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43577,7 +43577,7 @@
         <v>45086</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43634,7 +43634,7 @@
         <v>45086</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43691,7 +43691,7 @@
         <v>45086</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43748,7 +43748,7 @@
         <v>45086</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43805,7 +43805,7 @@
         <v>45086</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43862,7 +43862,7 @@
         <v>45090</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43924,7 +43924,7 @@
         <v>45089</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43981,7 +43981,7 @@
         <v>45090</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -44038,7 +44038,7 @@
         <v>45090</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44095,7 +44095,7 @@
         <v>45090</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44152,7 +44152,7 @@
         <v>45090</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44209,7 +44209,7 @@
         <v>45090</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44266,7 +44266,7 @@
         <v>45091</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44323,7 +44323,7 @@
         <v>45091</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44380,7 +44380,7 @@
         <v>45091</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44437,7 +44437,7 @@
         <v>45091</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44494,7 +44494,7 @@
         <v>45093</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44556,7 +44556,7 @@
         <v>45094</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44618,7 +44618,7 @@
         <v>45096</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44675,7 +44675,7 @@
         <v>45096</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44732,7 +44732,7 @@
         <v>45096</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44794,7 +44794,7 @@
         <v>45098</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44851,7 +44851,7 @@
         <v>45098</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44913,7 +44913,7 @@
         <v>45098</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44975,7 +44975,7 @@
         <v>45098</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -45037,7 +45037,7 @@
         <v>45098</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -45094,7 +45094,7 @@
         <v>45098</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45151,7 +45151,7 @@
         <v>45098</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45213,7 +45213,7 @@
         <v>45098</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45275,7 +45275,7 @@
         <v>45098</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45332,7 +45332,7 @@
         <v>45098</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45394,7 +45394,7 @@
         <v>45098</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45451,7 +45451,7 @@
         <v>45098</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45508,7 +45508,7 @@
         <v>45098</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45565,7 +45565,7 @@
         <v>45098</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45622,7 +45622,7 @@
         <v>45099</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45684,7 +45684,7 @@
         <v>45100</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45746,7 +45746,7 @@
         <v>45100</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45808,7 +45808,7 @@
         <v>45100</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45870,7 +45870,7 @@
         <v>45100</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45927,7 +45927,7 @@
         <v>45103</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45989,7 +45989,7 @@
         <v>45104</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -46046,7 +46046,7 @@
         <v>45104</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -46103,7 +46103,7 @@
         <v>45104</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46160,7 +46160,7 @@
         <v>45104</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46217,7 +46217,7 @@
         <v>45104</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46274,7 +46274,7 @@
         <v>45106</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46331,7 +46331,7 @@
         <v>45106</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46388,7 +46388,7 @@
         <v>45106</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46445,7 +46445,7 @@
         <v>45106</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46502,7 +46502,7 @@
         <v>45106</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46559,7 +46559,7 @@
         <v>45106</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46616,7 +46616,7 @@
         <v>45107</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46673,7 +46673,7 @@
         <v>45107</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46730,7 +46730,7 @@
         <v>45107</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46787,7 +46787,7 @@
         <v>45107</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46844,7 +46844,7 @@
         <v>45110</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46901,7 +46901,7 @@
         <v>45110</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46958,7 +46958,7 @@
         <v>45110</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -47015,7 +47015,7 @@
         <v>45110</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -47072,7 +47072,7 @@
         <v>45111</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47129,7 +47129,7 @@
         <v>45114</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47186,7 +47186,7 @@
         <v>45114</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47243,7 +47243,7 @@
         <v>45118</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47305,7 +47305,7 @@
         <v>45118</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47367,7 +47367,7 @@
         <v>45118</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47429,7 +47429,7 @@
         <v>45118</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47491,7 +47491,7 @@
         <v>45118</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47553,7 +47553,7 @@
         <v>45118</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47615,7 +47615,7 @@
         <v>45119</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47677,7 +47677,7 @@
         <v>45119</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47734,7 +47734,7 @@
         <v>45120</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47791,7 +47791,7 @@
         <v>45120</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47848,7 +47848,7 @@
         <v>45120</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47905,7 +47905,7 @@
         <v>45120</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47962,7 +47962,7 @@
         <v>45125</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -48019,7 +48019,7 @@
         <v>45125</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -48076,7 +48076,7 @@
         <v>45125</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -48133,7 +48133,7 @@
         <v>45129</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48190,7 +48190,7 @@
         <v>45129</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48247,7 +48247,7 @@
         <v>45135</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48304,7 +48304,7 @@
         <v>45135</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48361,7 +48361,7 @@
         <v>45138</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48418,7 +48418,7 @@
         <v>45138</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48475,7 +48475,7 @@
         <v>45139</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48532,7 +48532,7 @@
         <v>45139</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48589,7 +48589,7 @@
         <v>45139</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48646,7 +48646,7 @@
         <v>45140</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48708,7 +48708,7 @@
         <v>45140</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48765,7 +48765,7 @@
         <v>45140</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48827,7 +48827,7 @@
         <v>45141</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48884,7 +48884,7 @@
         <v>45145</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48941,7 +48941,7 @@
         <v>45152</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -49003,7 +49003,7 @@
         <v>45152</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -49065,7 +49065,7 @@
         <v>45156</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -49122,7 +49122,7 @@
         <v>45159</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49179,7 +49179,7 @@
         <v>45159</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49236,7 +49236,7 @@
         <v>45160</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49298,7 +49298,7 @@
         <v>45160</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49360,7 +49360,7 @@
         <v>45160</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49417,7 +49417,7 @@
         <v>45162</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49474,7 +49474,7 @@
         <v>45162</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49531,7 +49531,7 @@
         <v>45163</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49588,7 +49588,7 @@
         <v>45167</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49650,7 +49650,7 @@
         <v>45167</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49712,7 +49712,7 @@
         <v>45167</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49769,7 +49769,7 @@
         <v>45167</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49831,7 +49831,7 @@
         <v>45168</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49893,7 +49893,7 @@
         <v>45167</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49950,7 +49950,7 @@
         <v>45168</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -50012,7 +50012,7 @@
         <v>45168</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -50074,7 +50074,7 @@
         <v>45170</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -50131,7 +50131,7 @@
         <v>45170</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -50188,7 +50188,7 @@
         <v>45175</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -50245,7 +50245,7 @@
         <v>45176</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50307,7 +50307,7 @@
         <v>45176</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50369,7 +50369,7 @@
         <v>45176</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50426,7 +50426,7 @@
         <v>45177</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50483,7 +50483,7 @@
         <v>45177</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50540,7 +50540,7 @@
         <v>45177</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50597,7 +50597,7 @@
         <v>45180</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50654,7 +50654,7 @@
         <v>45181</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50716,7 +50716,7 @@
         <v>45181</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50778,7 +50778,7 @@
         <v>45181</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50835,7 +50835,7 @@
         <v>45181</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50892,7 +50892,7 @@
         <v>45182</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50949,7 +50949,7 @@
         <v>45183</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -51006,7 +51006,7 @@
         <v>45184</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -51068,7 +51068,7 @@
         <v>45187</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -51125,7 +51125,7 @@
         <v>45187</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -51182,7 +51182,7 @@
         <v>45187</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -51239,7 +51239,7 @@
         <v>45187</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -51296,7 +51296,7 @@
         <v>45187</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -51353,7 +51353,7 @@
         <v>45187</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -51410,7 +51410,7 @@
         <v>45187</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -51467,7 +51467,7 @@
         <v>45188</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51529,7 +51529,7 @@
         <v>45188</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51591,7 +51591,7 @@
         <v>45188</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51653,7 +51653,7 @@
         <v>45188</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51715,7 +51715,7 @@
         <v>45188</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51777,7 +51777,7 @@
         <v>45188</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51839,7 +51839,7 @@
         <v>45188</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51901,7 +51901,7 @@
         <v>45188</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51958,7 +51958,7 @@
         <v>45189</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -52020,7 +52020,7 @@
         <v>45190</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -52077,7 +52077,7 @@
         <v>45190</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -52134,7 +52134,7 @@
         <v>45190</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -52191,7 +52191,7 @@
         <v>45190</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -52248,7 +52248,7 @@
         <v>45196</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -52305,7 +52305,7 @@
         <v>45197</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -52362,7 +52362,7 @@
         <v>45197</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -52419,7 +52419,7 @@
         <v>45198</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -52481,7 +52481,7 @@
         <v>45201</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -52543,7 +52543,7 @@
         <v>45201</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52605,7 +52605,7 @@
         <v>45202</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52667,7 +52667,7 @@
         <v>45202</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52724,7 +52724,7 @@
         <v>45203</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52781,7 +52781,7 @@
         <v>45204</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52843,7 +52843,7 @@
         <v>45208</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52900,7 +52900,7 @@
         <v>45209</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52957,7 +52957,7 @@
         <v>45208</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -53019,7 +53019,7 @@
         <v>45211</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -53076,7 +53076,7 @@
         <v>45211</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -53133,7 +53133,7 @@
         <v>45211</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -53190,7 +53190,7 @@
         <v>45211</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -53252,7 +53252,7 @@
         <v>45211</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -53314,7 +53314,7 @@
         <v>45211</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -53371,7 +53371,7 @@
         <v>45212</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -53428,7 +53428,7 @@
         <v>45213</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -53485,7 +53485,7 @@
         <v>45215</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -53542,7 +53542,7 @@
         <v>45215</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53599,7 +53599,7 @@
         <v>45216</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53656,7 +53656,7 @@
         <v>45216</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53718,7 +53718,7 @@
         <v>45218</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -53775,7 +53775,7 @@
         <v>45218</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -53837,7 +53837,7 @@
         <v>45218</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -53894,7 +53894,7 @@
         <v>45218</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -53951,7 +53951,7 @@
         <v>45219</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -54008,7 +54008,7 @@
         <v>45219</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -54065,7 +54065,7 @@
         <v>45219</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -54127,7 +54127,7 @@
         <v>45219</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -54189,7 +54189,7 @@
         <v>45219</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -54246,7 +54246,7 @@
         <v>45219</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -54303,7 +54303,7 @@
         <v>45222</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -54360,7 +54360,7 @@
         <v>45222</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -54422,7 +54422,7 @@
         <v>45222</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -54479,7 +54479,7 @@
         <v>45225</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -54536,7 +54536,7 @@
         <v>45225</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -54593,7 +54593,7 @@
         <v>45230</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -54655,7 +54655,7 @@
         <v>45230</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -54712,7 +54712,7 @@
         <v>45230</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -54769,7 +54769,7 @@
         <v>45230</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -54826,7 +54826,7 @@
         <v>45232</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -54888,7 +54888,7 @@
         <v>45232</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -54950,7 +54950,7 @@
         <v>45232</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -55012,7 +55012,7 @@
         <v>45236</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -55074,7 +55074,7 @@
         <v>45236</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -55131,7 +55131,7 @@
         <v>45237</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -55188,7 +55188,7 @@
         <v>45237</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -55245,7 +55245,7 @@
         <v>45237</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -55302,7 +55302,7 @@
         <v>45237</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -55359,7 +55359,7 @@
         <v>45237</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -55421,7 +55421,7 @@
         <v>45237</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -55478,7 +55478,7 @@
         <v>45237</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -55535,7 +55535,7 @@
         <v>45238</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -55592,7 +55592,7 @@
         <v>45239</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -55649,7 +55649,7 @@
         <v>45239</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -55711,7 +55711,7 @@
         <v>45239</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -55768,7 +55768,7 @@
         <v>45239</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -55825,7 +55825,7 @@
         <v>45240</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -55882,7 +55882,7 @@
         <v>45240</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -55939,7 +55939,7 @@
         <v>45243</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -56001,7 +56001,7 @@
         <v>45243</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -56063,7 +56063,7 @@
         <v>45244</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -56120,7 +56120,7 @@
         <v>45244</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -56177,7 +56177,7 @@
         <v>45244</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -56234,7 +56234,7 @@
         <v>45244</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -56291,7 +56291,7 @@
         <v>45244</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -56348,7 +56348,7 @@
         <v>45244</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -56405,7 +56405,7 @@
         <v>45244</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -56462,7 +56462,7 @@
         <v>45244</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -56519,7 +56519,7 @@
         <v>45244</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -56576,7 +56576,7 @@
         <v>45245</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -56633,7 +56633,7 @@
         <v>45245</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -56690,7 +56690,7 @@
         <v>45245</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -56747,7 +56747,7 @@
         <v>45246</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -56804,7 +56804,7 @@
         <v>45246</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -56861,7 +56861,7 @@
         <v>45247</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -56918,7 +56918,7 @@
         <v>45251</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -56975,7 +56975,7 @@
         <v>45252</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -57032,7 +57032,7 @@
         <v>45252</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -57089,7 +57089,7 @@
         <v>45253</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -57146,7 +57146,7 @@
         <v>45254</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -57203,7 +57203,7 @@
         <v>45254</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -57260,7 +57260,7 @@
         <v>45257</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -57317,7 +57317,7 @@
         <v>45257</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -57374,7 +57374,7 @@
         <v>45258</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -57431,7 +57431,7 @@
         <v>45259</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -57488,7 +57488,7 @@
         <v>45259</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -57545,7 +57545,7 @@
         <v>45260</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -57602,7 +57602,7 @@
         <v>45260</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -57659,7 +57659,7 @@
         <v>45260</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -57716,7 +57716,7 @@
         <v>45260</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -57773,7 +57773,7 @@
         <v>45261</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -57830,7 +57830,7 @@
         <v>45261</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -57887,7 +57887,7 @@
         <v>45262</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -57944,7 +57944,7 @@
         <v>45264</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -58001,7 +58001,7 @@
         <v>45264</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -58058,7 +58058,7 @@
         <v>45264</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -58115,7 +58115,7 @@
         <v>45264</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -58177,7 +58177,7 @@
         <v>45264</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -58234,7 +58234,7 @@
         <v>45265</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -58291,7 +58291,7 @@
         <v>45265</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -58348,7 +58348,7 @@
         <v>45266</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -58405,7 +58405,7 @@
         <v>45266</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -58462,7 +58462,7 @@
         <v>45266</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -58519,7 +58519,7 @@
         <v>45267</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -58576,7 +58576,7 @@
         <v>45271</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -58633,7 +58633,7 @@
         <v>45271</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -58690,7 +58690,7 @@
         <v>45273</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -58747,7 +58747,7 @@
         <v>45273</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -58804,7 +58804,7 @@
         <v>45273</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -58861,7 +58861,7 @@
         <v>45273</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -58918,7 +58918,7 @@
         <v>45273</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -58975,7 +58975,7 @@
         <v>45273</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -59032,7 +59032,7 @@
         <v>45273</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -59089,7 +59089,7 @@
         <v>45278</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -59146,7 +59146,7 @@
         <v>45279</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -59203,7 +59203,7 @@
         <v>45279</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -59260,7 +59260,7 @@
         <v>45279</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -59317,7 +59317,7 @@
         <v>45281</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -59374,7 +59374,7 @@
         <v>45282</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -59436,7 +59436,7 @@
         <v>45285</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -59493,7 +59493,7 @@
         <v>45285</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -59550,7 +59550,7 @@
         <v>45285</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -59607,7 +59607,7 @@
         <v>45285</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -59664,7 +59664,7 @@
         <v>45287</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -59721,7 +59721,7 @@
         <v>45287</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -59778,7 +59778,7 @@
         <v>45289</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -59835,7 +59835,7 @@
         <v>45299</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -59892,7 +59892,7 @@
         <v>45308</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -59949,7 +59949,7 @@
         <v>45308</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -60006,7 +60006,7 @@
         <v>45309</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -60063,7 +60063,7 @@
         <v>45310</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -60120,7 +60120,7 @@
         <v>45310</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -60177,7 +60177,7 @@
         <v>45311</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -60234,7 +60234,7 @@
         <v>45311</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -60291,7 +60291,7 @@
         <v>45312</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -60348,7 +60348,7 @@
         <v>45312</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -60405,7 +60405,7 @@
         <v>45313</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -60462,7 +60462,7 @@
         <v>45315</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -60519,7 +60519,7 @@
         <v>45315</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -60576,7 +60576,7 @@
         <v>45315</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -60633,7 +60633,7 @@
         <v>45316</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -60690,7 +60690,7 @@
         <v>45316</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -60747,7 +60747,7 @@
         <v>45316</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -60804,7 +60804,7 @@
         <v>45320</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -60861,7 +60861,7 @@
         <v>45320</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -60918,7 +60918,7 @@
         <v>45323</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -60975,7 +60975,7 @@
         <v>45323</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -61025,14 +61025,14 @@
     <row r="1003" ht="15" customHeight="1">
       <c r="A1003" t="inlineStr">
         <is>
-          <t>A 4127-2024</t>
+          <t>A 4122-2024</t>
         </is>
       </c>
       <c r="B1003" s="1" t="n">
         <v>45323</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -61050,7 +61050,7 @@
         </is>
       </c>
       <c r="G1003" t="n">
-        <v>4.5</v>
+        <v>2.8</v>
       </c>
       <c r="H1003" t="n">
         <v>0</v>
@@ -61087,14 +61087,14 @@
     <row r="1004" ht="15" customHeight="1">
       <c r="A1004" t="inlineStr">
         <is>
-          <t>A 4122-2024</t>
+          <t>A 4127-2024</t>
         </is>
       </c>
       <c r="B1004" s="1" t="n">
         <v>45323</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -61112,7 +61112,7 @@
         </is>
       </c>
       <c r="G1004" t="n">
-        <v>2.8</v>
+        <v>4.5</v>
       </c>
       <c r="H1004" t="n">
         <v>0</v>
@@ -61156,7 +61156,7 @@
         <v>45323</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -61211,14 +61211,14 @@
     <row r="1006" ht="15" customHeight="1">
       <c r="A1006" t="inlineStr">
         <is>
-          <t>A 4232-2024</t>
+          <t>A 4242-2024</t>
         </is>
       </c>
       <c r="B1006" s="1" t="n">
         <v>45324</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -61236,7 +61236,7 @@
         </is>
       </c>
       <c r="G1006" t="n">
-        <v>11.1</v>
+        <v>3.9</v>
       </c>
       <c r="H1006" t="n">
         <v>0</v>
@@ -61273,14 +61273,14 @@
     <row r="1007" ht="15" customHeight="1">
       <c r="A1007" t="inlineStr">
         <is>
-          <t>A 4242-2024</t>
+          <t>A 4245-2024</t>
         </is>
       </c>
       <c r="B1007" s="1" t="n">
         <v>45324</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -61292,13 +61292,8 @@
           <t>PITEÅ</t>
         </is>
       </c>
-      <c r="F1007" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="G1007" t="n">
-        <v>3.9</v>
+        <v>7.2</v>
       </c>
       <c r="H1007" t="n">
         <v>0</v>
@@ -61335,14 +61330,14 @@
     <row r="1008" ht="15" customHeight="1">
       <c r="A1008" t="inlineStr">
         <is>
-          <t>A 4245-2024</t>
+          <t>A 4232-2024</t>
         </is>
       </c>
       <c r="B1008" s="1" t="n">
         <v>45324</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -61354,8 +61349,13 @@
           <t>PITEÅ</t>
         </is>
       </c>
+      <c r="F1008" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="G1008" t="n">
-        <v>7.2</v>
+        <v>11.1</v>
       </c>
       <c r="H1008" t="n">
         <v>0</v>
@@ -61399,7 +61399,7 @@
         <v>45329</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -61456,7 +61456,7 @@
         <v>45330</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -61513,7 +61513,7 @@
         <v>45334</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -61570,7 +61570,7 @@
         <v>45335</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -61627,7 +61627,7 @@
         <v>45342</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -61677,14 +61677,14 @@
     <row r="1014" ht="15" customHeight="1">
       <c r="A1014" t="inlineStr">
         <is>
-          <t>A 6920-2024</t>
+          <t>A 6988-2024</t>
         </is>
       </c>
       <c r="B1014" s="1" t="n">
         <v>45343</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -61697,7 +61697,7 @@
         </is>
       </c>
       <c r="G1014" t="n">
-        <v>7.6</v>
+        <v>1.6</v>
       </c>
       <c r="H1014" t="n">
         <v>0</v>
@@ -61734,14 +61734,14 @@
     <row r="1015" ht="15" customHeight="1">
       <c r="A1015" t="inlineStr">
         <is>
-          <t>A 6988-2024</t>
+          <t>A 6920-2024</t>
         </is>
       </c>
       <c r="B1015" s="1" t="n">
         <v>45343</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -61754,7 +61754,7 @@
         </is>
       </c>
       <c r="G1015" t="n">
-        <v>1.6</v>
+        <v>7.6</v>
       </c>
       <c r="H1015" t="n">
         <v>0</v>
@@ -61791,14 +61791,14 @@
     <row r="1016" ht="15" customHeight="1">
       <c r="A1016" t="inlineStr">
         <is>
-          <t>A 7457-2024</t>
+          <t>A 7458-2024</t>
         </is>
       </c>
       <c r="B1016" s="1" t="n">
         <v>45345</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -61811,7 +61811,7 @@
         </is>
       </c>
       <c r="G1016" t="n">
-        <v>7.3</v>
+        <v>9.5</v>
       </c>
       <c r="H1016" t="n">
         <v>0</v>
@@ -61848,14 +61848,14 @@
     <row r="1017" ht="15" customHeight="1">
       <c r="A1017" t="inlineStr">
         <is>
-          <t>A 7461-2024</t>
+          <t>A 7457-2024</t>
         </is>
       </c>
       <c r="B1017" s="1" t="n">
         <v>45345</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -61868,7 +61868,7 @@
         </is>
       </c>
       <c r="G1017" t="n">
-        <v>14.7</v>
+        <v>7.3</v>
       </c>
       <c r="H1017" t="n">
         <v>0</v>
@@ -61905,14 +61905,14 @@
     <row r="1018" ht="15" customHeight="1">
       <c r="A1018" t="inlineStr">
         <is>
-          <t>A 7459-2024</t>
+          <t>A 7461-2024</t>
         </is>
       </c>
       <c r="B1018" s="1" t="n">
         <v>45345</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -61925,7 +61925,7 @@
         </is>
       </c>
       <c r="G1018" t="n">
-        <v>3.5</v>
+        <v>14.7</v>
       </c>
       <c r="H1018" t="n">
         <v>0</v>
@@ -61959,62 +61959,233 @@
       </c>
       <c r="R1018" s="2" t="inlineStr"/>
     </row>
-    <row r="1019">
+    <row r="1019" ht="15" customHeight="1">
       <c r="A1019" t="inlineStr">
         <is>
-          <t>A 7458-2024</t>
+          <t>A 7459-2024</t>
         </is>
       </c>
       <c r="B1019" s="1" t="n">
         <v>45345</v>
       </c>
       <c r="C1019" s="1" t="n">
+        <v>45348</v>
+      </c>
+      <c r="D1019" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="E1019" t="inlineStr">
+        <is>
+          <t>PITEÅ</t>
+        </is>
+      </c>
+      <c r="G1019" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H1019" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1019" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1019" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1019" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1019" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1019" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1019" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1019" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1019" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1019" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1019" s="2" t="inlineStr"/>
+    </row>
+    <row r="1020" ht="15" customHeight="1">
+      <c r="A1020" t="inlineStr">
+        <is>
+          <t>A 7502-2024</t>
+        </is>
+      </c>
+      <c r="B1020" s="1" t="n">
         <v>45347</v>
       </c>
-      <c r="D1019" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="E1019" t="inlineStr">
-        <is>
-          <t>PITEÅ</t>
-        </is>
-      </c>
-      <c r="G1019" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="H1019" t="n">
-        <v>0</v>
-      </c>
-      <c r="I1019" t="n">
-        <v>0</v>
-      </c>
-      <c r="J1019" t="n">
-        <v>0</v>
-      </c>
-      <c r="K1019" t="n">
-        <v>0</v>
-      </c>
-      <c r="L1019" t="n">
-        <v>0</v>
-      </c>
-      <c r="M1019" t="n">
-        <v>0</v>
-      </c>
-      <c r="N1019" t="n">
-        <v>0</v>
-      </c>
-      <c r="O1019" t="n">
-        <v>0</v>
-      </c>
-      <c r="P1019" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q1019" t="n">
-        <v>0</v>
-      </c>
-      <c r="R1019" s="2" t="inlineStr"/>
+      <c r="C1020" s="1" t="n">
+        <v>45348</v>
+      </c>
+      <c r="D1020" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="E1020" t="inlineStr">
+        <is>
+          <t>PITEÅ</t>
+        </is>
+      </c>
+      <c r="G1020" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H1020" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1020" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1020" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1020" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1020" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1020" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1020" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1020" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1020" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1020" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1020" s="2" t="inlineStr"/>
+    </row>
+    <row r="1021" ht="15" customHeight="1">
+      <c r="A1021" t="inlineStr">
+        <is>
+          <t>A 7503-2024</t>
+        </is>
+      </c>
+      <c r="B1021" s="1" t="n">
+        <v>45347</v>
+      </c>
+      <c r="C1021" s="1" t="n">
+        <v>45348</v>
+      </c>
+      <c r="D1021" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="E1021" t="inlineStr">
+        <is>
+          <t>PITEÅ</t>
+        </is>
+      </c>
+      <c r="G1021" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="H1021" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1021" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1021" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1021" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1021" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1021" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1021" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1021" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1021" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1021" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1021" s="2" t="inlineStr"/>
+    </row>
+    <row r="1022">
+      <c r="A1022" t="inlineStr">
+        <is>
+          <t>A 7504-2024</t>
+        </is>
+      </c>
+      <c r="B1022" s="1" t="n">
+        <v>45347</v>
+      </c>
+      <c r="C1022" s="1" t="n">
+        <v>45348</v>
+      </c>
+      <c r="D1022" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="E1022" t="inlineStr">
+        <is>
+          <t>PITEÅ</t>
+        </is>
+      </c>
+      <c r="G1022" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1022" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1022" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1022" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1022" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1022" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1022" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1022" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1022" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1022" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1022" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1022" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt PITEÅ.xlsx
+++ b/Översikt PITEÅ.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z1026"/>
+  <dimension ref="A1:Z1027"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>44617</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -665,7 +665,7 @@
         <v>44839</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
         <v>44839</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>44459</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
         <v>44617</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>43896</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>45191</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>45203</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>44740</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>44280</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>44539</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>44550</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>45119</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>44014</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>44522</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>44526</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         <v>44553</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>44810</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>44917</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>45103</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>45106</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         <v>43802</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>43902</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2727,7 +2727,7 @@
         <v>43908</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         <v>44053</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2908,7 +2908,7 @@
         <v>44193</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>44298</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>44840</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
         <v>44852</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3262,7 +3262,7 @@
         <v>44859</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>44944</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3434,7 +3434,7 @@
         <v>45120</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
         <v>45187</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         <v>45209</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3701,7 +3701,7 @@
         <v>45219</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>45243</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         <v>45293</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
         <v>45296</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>43714</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         <v>44014</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4225,7 +4225,7 @@
         <v>44106</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4310,7 +4310,7 @@
         <v>44309</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>44342</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4485,7 +4485,7 @@
         <v>44495</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
         <v>44525</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4665,7 +4665,7 @@
         <v>44525</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4755,7 +4755,7 @@
         <v>44538</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4840,7 +4840,7 @@
         <v>44727</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4929,7 +4929,7 @@
         <v>44804</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5014,7 +5014,7 @@
         <v>44917</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5104,7 +5104,7 @@
         <v>45049</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5193,7 +5193,7 @@
         <v>45098</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>45103</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5373,7 +5373,7 @@
         <v>45148</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
         <v>45175</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         <v>45181</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5642,7 +5642,7 @@
         <v>45188</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5732,7 +5732,7 @@
         <v>45224</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5817,7 +5817,7 @@
         <v>45243</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5907,7 +5907,7 @@
         <v>45265</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5992,7 +5992,7 @@
         <v>45323</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
         <v>45348</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6172,7 +6172,7 @@
         <v>43325</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6229,7 +6229,7 @@
         <v>43332</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6286,7 +6286,7 @@
         <v>43336</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6343,7 +6343,7 @@
         <v>43339</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6400,7 +6400,7 @@
         <v>43339</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6457,7 +6457,7 @@
         <v>43341</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6514,7 +6514,7 @@
         <v>43355</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6571,7 +6571,7 @@
         <v>43355</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6628,7 +6628,7 @@
         <v>43374</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6690,7 +6690,7 @@
         <v>43374</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6752,7 +6752,7 @@
         <v>43375</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6809,7 +6809,7 @@
         <v>43376</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6866,7 +6866,7 @@
         <v>43376</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6923,7 +6923,7 @@
         <v>43381</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6980,7 +6980,7 @@
         <v>43383</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7037,7 +7037,7 @@
         <v>43391</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7094,7 +7094,7 @@
         <v>43391</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7151,7 +7151,7 @@
         <v>43392</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7208,7 +7208,7 @@
         <v>43392</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7265,7 +7265,7 @@
         <v>43398</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7322,7 +7322,7 @@
         <v>43402</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7379,7 +7379,7 @@
         <v>43404</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7436,7 +7436,7 @@
         <v>43406</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7493,7 +7493,7 @@
         <v>43406</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
         <v>43406</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7607,7 +7607,7 @@
         <v>43406</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7664,7 +7664,7 @@
         <v>43406</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         <v>43416</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7778,7 +7778,7 @@
         <v>43418</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7835,7 +7835,7 @@
         <v>43418</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7892,7 +7892,7 @@
         <v>43418</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7949,7 +7949,7 @@
         <v>43419</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8006,7 +8006,7 @@
         <v>43420</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8063,7 +8063,7 @@
         <v>43424</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         <v>43427</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8187,7 +8187,7 @@
         <v>43427</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8244,7 +8244,7 @@
         <v>43427</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8306,7 +8306,7 @@
         <v>43427</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8368,7 +8368,7 @@
         <v>43436</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8425,7 +8425,7 @@
         <v>43438</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8482,7 +8482,7 @@
         <v>43438</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8539,7 +8539,7 @@
         <v>43438</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8596,7 +8596,7 @@
         <v>43438</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8653,7 +8653,7 @@
         <v>43451</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8715,7 +8715,7 @@
         <v>43472</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8772,7 +8772,7 @@
         <v>43475</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8829,7 +8829,7 @@
         <v>43479</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8886,7 +8886,7 @@
         <v>43479</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8943,7 +8943,7 @@
         <v>43486</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9000,7 +9000,7 @@
         <v>43489</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9057,7 +9057,7 @@
         <v>43489</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
         <v>43489</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9171,7 +9171,7 @@
         <v>43489</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9228,7 +9228,7 @@
         <v>43489</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         <v>43490</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9342,7 +9342,7 @@
         <v>43490</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9399,7 +9399,7 @@
         <v>43493</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9461,7 +9461,7 @@
         <v>43509</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9518,7 +9518,7 @@
         <v>43510</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9575,7 +9575,7 @@
         <v>43510</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9632,7 +9632,7 @@
         <v>43514</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9689,7 +9689,7 @@
         <v>43514</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9746,7 +9746,7 @@
         <v>43514</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9803,7 +9803,7 @@
         <v>43516</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9865,7 +9865,7 @@
         <v>43518</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9922,7 +9922,7 @@
         <v>43521</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9984,7 +9984,7 @@
         <v>43521</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10046,7 +10046,7 @@
         <v>43521</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10108,7 +10108,7 @@
         <v>43521</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10170,7 +10170,7 @@
         <v>43521</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10232,7 +10232,7 @@
         <v>43522</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10289,7 +10289,7 @@
         <v>43523</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10346,7 +10346,7 @@
         <v>43523</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10403,7 +10403,7 @@
         <v>43523</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10460,7 +10460,7 @@
         <v>43532</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10517,7 +10517,7 @@
         <v>43532</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10574,7 +10574,7 @@
         <v>43542</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10631,7 +10631,7 @@
         <v>43544</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10693,7 +10693,7 @@
         <v>43544</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10755,7 +10755,7 @@
         <v>43554</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10812,7 +10812,7 @@
         <v>43556</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10869,7 +10869,7 @@
         <v>43557</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10931,7 +10931,7 @@
         <v>43557</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10988,7 +10988,7 @@
         <v>43557</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11045,7 +11045,7 @@
         <v>43557</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11102,7 +11102,7 @@
         <v>43557</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11164,7 +11164,7 @@
         <v>43564</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11221,7 +11221,7 @@
         <v>43564</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11278,7 +11278,7 @@
         <v>43567</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11335,7 +11335,7 @@
         <v>43570</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11392,7 +11392,7 @@
         <v>43570</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11449,7 +11449,7 @@
         <v>43570</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11506,7 +11506,7 @@
         <v>43584</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11563,7 +11563,7 @@
         <v>43605</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11620,7 +11620,7 @@
         <v>43608</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11677,7 +11677,7 @@
         <v>43614</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11739,7 +11739,7 @@
         <v>43616</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11801,7 +11801,7 @@
         <v>43616</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11863,7 +11863,7 @@
         <v>43629</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11920,7 +11920,7 @@
         <v>43629</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11982,7 +11982,7 @@
         <v>43633</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12039,7 +12039,7 @@
         <v>43633</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12096,7 +12096,7 @@
         <v>43640</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12153,7 +12153,7 @@
         <v>43640</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12210,7 +12210,7 @@
         <v>43647</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12267,7 +12267,7 @@
         <v>43647</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12324,7 +12324,7 @@
         <v>43650</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12381,7 +12381,7 @@
         <v>43652</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12443,7 +12443,7 @@
         <v>43677</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12500,7 +12500,7 @@
         <v>43678</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12557,7 +12557,7 @@
         <v>43682</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12614,7 +12614,7 @@
         <v>43691</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12676,7 +12676,7 @@
         <v>43691</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12738,7 +12738,7 @@
         <v>43696</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12800,7 +12800,7 @@
         <v>43697</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12857,7 +12857,7 @@
         <v>43698</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12919,7 +12919,7 @@
         <v>43698</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12981,7 +12981,7 @@
         <v>43706</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13038,7 +13038,7 @@
         <v>43707</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13100,7 +13100,7 @@
         <v>43711</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13157,7 +13157,7 @@
         <v>43713</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13214,7 +13214,7 @@
         <v>43718</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13271,7 +13271,7 @@
         <v>43718</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13328,7 +13328,7 @@
         <v>43718</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13390,7 +13390,7 @@
         <v>43720</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13447,7 +13447,7 @@
         <v>43721</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13504,7 +13504,7 @@
         <v>43732</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13561,7 +13561,7 @@
         <v>43741</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13623,7 +13623,7 @@
         <v>43741</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13680,7 +13680,7 @@
         <v>43752</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13742,7 +13742,7 @@
         <v>43755</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13799,7 +13799,7 @@
         <v>43755</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13856,7 +13856,7 @@
         <v>43755</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13913,7 +13913,7 @@
         <v>43755</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13970,7 +13970,7 @@
         <v>43760</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14032,7 +14032,7 @@
         <v>43760</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14094,7 +14094,7 @@
         <v>43760</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14151,7 +14151,7 @@
         <v>43762</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14213,7 +14213,7 @@
         <v>43766</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14270,7 +14270,7 @@
         <v>43766</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14327,7 +14327,7 @@
         <v>43768</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14384,7 +14384,7 @@
         <v>43770</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14446,7 +14446,7 @@
         <v>43775</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14508,7 +14508,7 @@
         <v>43775</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14570,7 +14570,7 @@
         <v>43777</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14627,7 +14627,7 @@
         <v>43780</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14684,7 +14684,7 @@
         <v>43780</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14741,7 +14741,7 @@
         <v>43780</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14798,7 +14798,7 @@
         <v>43782</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14860,7 +14860,7 @@
         <v>43789</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14922,7 +14922,7 @@
         <v>43798</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14979,7 +14979,7 @@
         <v>43801</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15041,7 +15041,7 @@
         <v>43802</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15098,7 +15098,7 @@
         <v>43802</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15155,7 +15155,7 @@
         <v>43802</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15212,7 +15212,7 @@
         <v>43802</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15269,7 +15269,7 @@
         <v>43802</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15326,7 +15326,7 @@
         <v>43802</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15383,7 +15383,7 @@
         <v>43807</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15440,7 +15440,7 @@
         <v>43809</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15497,7 +15497,7 @@
         <v>43817</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15554,7 +15554,7 @@
         <v>43817</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15616,7 +15616,7 @@
         <v>43822</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15673,7 +15673,7 @@
         <v>43822</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15730,7 +15730,7 @@
         <v>43833</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15787,7 +15787,7 @@
         <v>43846</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15844,7 +15844,7 @@
         <v>43852</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15901,7 +15901,7 @@
         <v>43853</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15958,7 +15958,7 @@
         <v>43854</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16015,7 +16015,7 @@
         <v>43859</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16077,7 +16077,7 @@
         <v>43859</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16134,7 +16134,7 @@
         <v>43859</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16191,7 +16191,7 @@
         <v>43859</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16248,7 +16248,7 @@
         <v>43859</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16305,7 +16305,7 @@
         <v>43860</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16362,7 +16362,7 @@
         <v>43868</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16419,7 +16419,7 @@
         <v>43868</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16476,7 +16476,7 @@
         <v>43874</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16538,7 +16538,7 @@
         <v>43878</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16595,7 +16595,7 @@
         <v>43880</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16652,7 +16652,7 @@
         <v>43880</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16709,7 +16709,7 @@
         <v>43889</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16766,7 +16766,7 @@
         <v>43895</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16828,7 +16828,7 @@
         <v>43896</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16885,7 +16885,7 @@
         <v>43902</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16942,7 +16942,7 @@
         <v>43902</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17004,7 +17004,7 @@
         <v>43907</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17061,7 +17061,7 @@
         <v>43913</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17118,7 +17118,7 @@
         <v>43914</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17180,7 +17180,7 @@
         <v>43927</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17242,7 +17242,7 @@
         <v>43929</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17299,7 +17299,7 @@
         <v>43929</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17356,7 +17356,7 @@
         <v>43931</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17418,7 +17418,7 @@
         <v>43950</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17475,7 +17475,7 @@
         <v>43957</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17537,7 +17537,7 @@
         <v>43958</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17594,7 +17594,7 @@
         <v>43958</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17651,7 +17651,7 @@
         <v>43959</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17708,7 +17708,7 @@
         <v>43962</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17765,7 +17765,7 @@
         <v>43962</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17822,7 +17822,7 @@
         <v>43962</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17879,7 +17879,7 @@
         <v>43962</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17936,7 +17936,7 @@
         <v>43970</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17998,7 +17998,7 @@
         <v>43971</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18060,7 +18060,7 @@
         <v>43976</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18117,7 +18117,7 @@
         <v>43979</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18174,7 +18174,7 @@
         <v>43979</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18231,7 +18231,7 @@
         <v>43979</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18288,7 +18288,7 @@
         <v>43984</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18350,7 +18350,7 @@
         <v>43984</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18407,7 +18407,7 @@
         <v>43987</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18464,7 +18464,7 @@
         <v>43990</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18521,7 +18521,7 @@
         <v>43994</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18583,7 +18583,7 @@
         <v>43997</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18640,7 +18640,7 @@
         <v>43999</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18697,7 +18697,7 @@
         <v>44000</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18759,7 +18759,7 @@
         <v>44006</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18816,7 +18816,7 @@
         <v>44006</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18873,7 +18873,7 @@
         <v>44007</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18930,7 +18930,7 @@
         <v>44007</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18987,7 +18987,7 @@
         <v>44011</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19044,7 +19044,7 @@
         <v>44012</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19106,7 +19106,7 @@
         <v>44020</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19168,7 +19168,7 @@
         <v>44020</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19225,7 +19225,7 @@
         <v>44020</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19287,7 +19287,7 @@
         <v>44026</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19349,7 +19349,7 @@
         <v>44035</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19406,7 +19406,7 @@
         <v>44049</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19463,7 +19463,7 @@
         <v>44063</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19525,7 +19525,7 @@
         <v>44067</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19587,7 +19587,7 @@
         <v>44067</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19649,7 +19649,7 @@
         <v>44068</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19711,7 +19711,7 @@
         <v>44069</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19768,7 +19768,7 @@
         <v>44070</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19825,7 +19825,7 @@
         <v>44074</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19882,7 +19882,7 @@
         <v>44075</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19939,7 +19939,7 @@
         <v>44078</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19996,7 +19996,7 @@
         <v>44083</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20053,7 +20053,7 @@
         <v>44083</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20110,7 +20110,7 @@
         <v>44087</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20167,7 +20167,7 @@
         <v>44088</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20229,7 +20229,7 @@
         <v>44088</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20286,7 +20286,7 @@
         <v>44088</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20348,7 +20348,7 @@
         <v>44092</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20405,7 +20405,7 @@
         <v>44092</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20462,7 +20462,7 @@
         <v>44092</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20519,7 +20519,7 @@
         <v>44095</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20576,7 +20576,7 @@
         <v>44099</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20633,7 +20633,7 @@
         <v>44099</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20690,7 +20690,7 @@
         <v>44099</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20747,7 +20747,7 @@
         <v>44099</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20804,7 +20804,7 @@
         <v>44103</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20861,7 +20861,7 @@
         <v>44103</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20918,7 +20918,7 @@
         <v>44106</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20975,7 +20975,7 @@
         <v>44111</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21037,7 +21037,7 @@
         <v>44111</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21099,7 +21099,7 @@
         <v>44123</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21156,7 +21156,7 @@
         <v>44127</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21213,7 +21213,7 @@
         <v>44132</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21270,7 +21270,7 @@
         <v>44139</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21327,7 +21327,7 @@
         <v>44141</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21384,7 +21384,7 @@
         <v>44141</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21441,7 +21441,7 @@
         <v>44155</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21498,7 +21498,7 @@
         <v>44162</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21560,7 +21560,7 @@
         <v>44166</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21622,7 +21622,7 @@
         <v>44172</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21679,7 +21679,7 @@
         <v>44180</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21736,7 +21736,7 @@
         <v>44186</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21793,7 +21793,7 @@
         <v>44209</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21850,7 +21850,7 @@
         <v>44211</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21907,7 +21907,7 @@
         <v>44211</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21964,7 +21964,7 @@
         <v>44211</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22021,7 +22021,7 @@
         <v>44215</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22083,7 +22083,7 @@
         <v>44221</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22145,7 +22145,7 @@
         <v>44237</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22207,7 +22207,7 @@
         <v>44238</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22264,7 +22264,7 @@
         <v>44256</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22321,7 +22321,7 @@
         <v>44257</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22378,7 +22378,7 @@
         <v>44258</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22435,7 +22435,7 @@
         <v>44280</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22497,7 +22497,7 @@
         <v>44281</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22554,7 +22554,7 @@
         <v>44281</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22611,7 +22611,7 @@
         <v>44281</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22668,7 +22668,7 @@
         <v>44285</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22730,7 +22730,7 @@
         <v>44286</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22787,7 +22787,7 @@
         <v>44292</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22844,7 +22844,7 @@
         <v>44294</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22906,7 +22906,7 @@
         <v>44309</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22963,7 +22963,7 @@
         <v>44320</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23020,7 +23020,7 @@
         <v>44321</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23077,7 +23077,7 @@
         <v>44321</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23134,7 +23134,7 @@
         <v>44326</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23191,7 +23191,7 @@
         <v>44326</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23253,7 +23253,7 @@
         <v>44334</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23310,7 +23310,7 @@
         <v>44339</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23367,7 +23367,7 @@
         <v>44339</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23424,7 +23424,7 @@
         <v>44339</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23481,7 +23481,7 @@
         <v>44343</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23543,7 +23543,7 @@
         <v>44342</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23605,7 +23605,7 @@
         <v>44344</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23662,7 +23662,7 @@
         <v>44350</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23719,7 +23719,7 @@
         <v>44350</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23776,7 +23776,7 @@
         <v>44351</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23838,7 +23838,7 @@
         <v>44354</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23900,7 +23900,7 @@
         <v>44355</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23962,7 +23962,7 @@
         <v>44355</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24024,7 +24024,7 @@
         <v>44357</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24081,7 +24081,7 @@
         <v>44358</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24143,7 +24143,7 @@
         <v>44361</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24200,7 +24200,7 @@
         <v>44361</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24257,7 +24257,7 @@
         <v>44361</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24314,7 +24314,7 @@
         <v>44362</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24376,7 +24376,7 @@
         <v>44361</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24438,7 +24438,7 @@
         <v>44362</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24495,7 +24495,7 @@
         <v>44368</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24557,7 +24557,7 @@
         <v>44368</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24619,7 +24619,7 @@
         <v>44368</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24681,7 +24681,7 @@
         <v>44369</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24743,7 +24743,7 @@
         <v>44370</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24805,7 +24805,7 @@
         <v>44370</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24867,7 +24867,7 @@
         <v>44370</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24929,7 +24929,7 @@
         <v>44370</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24991,7 +24991,7 @@
         <v>44371</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25053,7 +25053,7 @@
         <v>44372</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25115,7 +25115,7 @@
         <v>44372</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25177,7 +25177,7 @@
         <v>44375</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25239,7 +25239,7 @@
         <v>44376</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25301,7 +25301,7 @@
         <v>44376</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25363,7 +25363,7 @@
         <v>44376</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25420,7 +25420,7 @@
         <v>44377</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25482,7 +25482,7 @@
         <v>44378</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25539,7 +25539,7 @@
         <v>44378</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25601,7 +25601,7 @@
         <v>44378</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25658,7 +25658,7 @@
         <v>44383</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25715,7 +25715,7 @@
         <v>44383</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25772,7 +25772,7 @@
         <v>44383</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25829,7 +25829,7 @@
         <v>44383</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25886,7 +25886,7 @@
         <v>44383</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25943,7 +25943,7 @@
         <v>44384</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26005,7 +26005,7 @@
         <v>44383</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26062,7 +26062,7 @@
         <v>44386</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26119,7 +26119,7 @@
         <v>44398</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26176,7 +26176,7 @@
         <v>44404</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26233,7 +26233,7 @@
         <v>44405</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26295,7 +26295,7 @@
         <v>44418</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26357,7 +26357,7 @@
         <v>44421</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26419,7 +26419,7 @@
         <v>44428</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26476,7 +26476,7 @@
         <v>44432</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26533,7 +26533,7 @@
         <v>44432</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26590,7 +26590,7 @@
         <v>44433</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26652,7 +26652,7 @@
         <v>44433</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26714,7 +26714,7 @@
         <v>44438</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26776,7 +26776,7 @@
         <v>44439</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26838,7 +26838,7 @@
         <v>44440</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26895,7 +26895,7 @@
         <v>44441</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26957,7 +26957,7 @@
         <v>44440</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27019,7 +27019,7 @@
         <v>44446</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27076,7 +27076,7 @@
         <v>44447</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27138,7 +27138,7 @@
         <v>44453</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27195,7 +27195,7 @@
         <v>44454</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27252,7 +27252,7 @@
         <v>44454</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27309,7 +27309,7 @@
         <v>44459</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27366,7 +27366,7 @@
         <v>44463</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27428,7 +27428,7 @@
         <v>44463</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27490,7 +27490,7 @@
         <v>44463</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27547,7 +27547,7 @@
         <v>44468</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27604,7 +27604,7 @@
         <v>44468</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27661,7 +27661,7 @@
         <v>44476</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27718,7 +27718,7 @@
         <v>44480</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27775,7 +27775,7 @@
         <v>44481</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27832,7 +27832,7 @@
         <v>44484</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27889,7 +27889,7 @@
         <v>44487</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27951,7 +27951,7 @@
         <v>44490</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28008,7 +28008,7 @@
         <v>44489</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28070,7 +28070,7 @@
         <v>44496</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28127,7 +28127,7 @@
         <v>44497</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28189,7 +28189,7 @@
         <v>44497</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28246,7 +28246,7 @@
         <v>44497</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28303,7 +28303,7 @@
         <v>44498</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28360,7 +28360,7 @@
         <v>44498</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28417,7 +28417,7 @@
         <v>44499</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28474,7 +28474,7 @@
         <v>44502</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28531,7 +28531,7 @@
         <v>44516</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28588,7 +28588,7 @@
         <v>44522</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28645,7 +28645,7 @@
         <v>44523</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28702,7 +28702,7 @@
         <v>44525</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28764,7 +28764,7 @@
         <v>44525</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28821,7 +28821,7 @@
         <v>44529</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28878,7 +28878,7 @@
         <v>44530</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28940,7 +28940,7 @@
         <v>44530</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29002,7 +29002,7 @@
         <v>44531</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29059,7 +29059,7 @@
         <v>44531</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29116,7 +29116,7 @@
         <v>44536</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29173,7 +29173,7 @@
         <v>44536</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29230,7 +29230,7 @@
         <v>44538</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29287,7 +29287,7 @@
         <v>44538</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29344,7 +29344,7 @@
         <v>44538</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29401,7 +29401,7 @@
         <v>44538</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29458,7 +29458,7 @@
         <v>44538</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29515,7 +29515,7 @@
         <v>44538</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29572,7 +29572,7 @@
         <v>44538</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29629,7 +29629,7 @@
         <v>44538</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29686,7 +29686,7 @@
         <v>44539</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29748,7 +29748,7 @@
         <v>44543</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29810,7 +29810,7 @@
         <v>44543</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29872,7 +29872,7 @@
         <v>44543</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29934,7 +29934,7 @@
         <v>44543</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29996,7 +29996,7 @@
         <v>44547</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30058,7 +30058,7 @@
         <v>44550</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30115,7 +30115,7 @@
         <v>44550</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30172,7 +30172,7 @@
         <v>44571</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30229,7 +30229,7 @@
         <v>44582</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30286,7 +30286,7 @@
         <v>44582</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30343,7 +30343,7 @@
         <v>44582</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30400,7 +30400,7 @@
         <v>44582</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30457,7 +30457,7 @@
         <v>44588</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30514,7 +30514,7 @@
         <v>44589</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30571,7 +30571,7 @@
         <v>44590</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30628,7 +30628,7 @@
         <v>44590</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30685,7 +30685,7 @@
         <v>44592</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30742,7 +30742,7 @@
         <v>44592</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30799,7 +30799,7 @@
         <v>44596</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30856,7 +30856,7 @@
         <v>44599</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30913,7 +30913,7 @@
         <v>44608</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30970,7 +30970,7 @@
         <v>44615</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31027,7 +31027,7 @@
         <v>44616</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31089,7 +31089,7 @@
         <v>44617</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31151,7 +31151,7 @@
         <v>44621</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31208,7 +31208,7 @@
         <v>44621</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31270,7 +31270,7 @@
         <v>44622</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31327,7 +31327,7 @@
         <v>44623</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31384,7 +31384,7 @@
         <v>44642</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31441,7 +31441,7 @@
         <v>44643</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31498,7 +31498,7 @@
         <v>44643</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31560,7 +31560,7 @@
         <v>44644</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31617,7 +31617,7 @@
         <v>44656</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31674,7 +31674,7 @@
         <v>44658</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31731,7 +31731,7 @@
         <v>44683</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31788,7 +31788,7 @@
         <v>44683</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31845,7 +31845,7 @@
         <v>44685</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31902,7 +31902,7 @@
         <v>44685</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31959,7 +31959,7 @@
         <v>44685</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32016,7 +32016,7 @@
         <v>44687</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32073,7 +32073,7 @@
         <v>44700</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32130,7 +32130,7 @@
         <v>44708</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32187,7 +32187,7 @@
         <v>44708</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32244,7 +32244,7 @@
         <v>44708</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32301,7 +32301,7 @@
         <v>44722</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32358,7 +32358,7 @@
         <v>44727</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32420,7 +32420,7 @@
         <v>44729</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32482,7 +32482,7 @@
         <v>44735</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32539,7 +32539,7 @@
         <v>44735</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32596,7 +32596,7 @@
         <v>44741</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32653,7 +32653,7 @@
         <v>44741</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32710,7 +32710,7 @@
         <v>44741</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32767,7 +32767,7 @@
         <v>44743</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32829,7 +32829,7 @@
         <v>44743</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32886,7 +32886,7 @@
         <v>44748</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32948,7 +32948,7 @@
         <v>44747</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33010,7 +33010,7 @@
         <v>44748</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33072,7 +33072,7 @@
         <v>44748</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33129,7 +33129,7 @@
         <v>44750</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33186,7 +33186,7 @@
         <v>44756</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33243,7 +33243,7 @@
         <v>44761</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33300,7 +33300,7 @@
         <v>44776</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33357,7 +33357,7 @@
         <v>44777</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33419,7 +33419,7 @@
         <v>44781</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33476,7 +33476,7 @@
         <v>44783</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33533,7 +33533,7 @@
         <v>44785</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33595,7 +33595,7 @@
         <v>44784</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33657,7 +33657,7 @@
         <v>44785</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33714,7 +33714,7 @@
         <v>44792</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33771,7 +33771,7 @@
         <v>44792</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33833,7 +33833,7 @@
         <v>44795</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33890,7 +33890,7 @@
         <v>44795</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33952,7 +33952,7 @@
         <v>44803</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34014,7 +34014,7 @@
         <v>44805</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34076,7 +34076,7 @@
         <v>44806</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34133,7 +34133,7 @@
         <v>44809</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34195,7 +34195,7 @@
         <v>44809</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34257,7 +34257,7 @@
         <v>44811</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34314,7 +34314,7 @@
         <v>44813</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34371,7 +34371,7 @@
         <v>44813</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34428,7 +34428,7 @@
         <v>44813</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34485,7 +34485,7 @@
         <v>44813</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34542,7 +34542,7 @@
         <v>44813</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34599,7 +34599,7 @@
         <v>44816</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34656,7 +34656,7 @@
         <v>44816</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34713,7 +34713,7 @@
         <v>44817</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34775,7 +34775,7 @@
         <v>44817</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34832,7 +34832,7 @@
         <v>44818</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34894,7 +34894,7 @@
         <v>44818</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34956,7 +34956,7 @@
         <v>44818</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35018,7 +35018,7 @@
         <v>44817</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35075,7 +35075,7 @@
         <v>44818</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35137,7 +35137,7 @@
         <v>44818</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35199,7 +35199,7 @@
         <v>44818</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35261,7 +35261,7 @@
         <v>44818</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35318,7 +35318,7 @@
         <v>44819</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35375,7 +35375,7 @@
         <v>44820</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35432,7 +35432,7 @@
         <v>44823</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35494,7 +35494,7 @@
         <v>44824</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35551,7 +35551,7 @@
         <v>44827</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35613,7 +35613,7 @@
         <v>44838</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35675,7 +35675,7 @@
         <v>44838</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35732,7 +35732,7 @@
         <v>44839</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35789,7 +35789,7 @@
         <v>44840</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35846,7 +35846,7 @@
         <v>44840</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35903,7 +35903,7 @@
         <v>44841</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35965,7 +35965,7 @@
         <v>44845</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36027,7 +36027,7 @@
         <v>44845</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36089,7 +36089,7 @@
         <v>44848</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36151,7 +36151,7 @@
         <v>44848</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36213,7 +36213,7 @@
         <v>44849</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36275,7 +36275,7 @@
         <v>44848</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36332,7 +36332,7 @@
         <v>44853</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36394,7 +36394,7 @@
         <v>44853</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36456,7 +36456,7 @@
         <v>44853</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36518,7 +36518,7 @@
         <v>44856</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36580,7 +36580,7 @@
         <v>44855</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36642,7 +36642,7 @@
         <v>44857</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36699,7 +36699,7 @@
         <v>44859</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36756,7 +36756,7 @@
         <v>44859</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36813,7 +36813,7 @@
         <v>44861</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36875,7 +36875,7 @@
         <v>44861</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36932,7 +36932,7 @@
         <v>44861</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36994,7 +36994,7 @@
         <v>44861</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37051,7 +37051,7 @@
         <v>44861</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37113,7 +37113,7 @@
         <v>44861</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37175,7 +37175,7 @@
         <v>44861</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37232,7 +37232,7 @@
         <v>44862</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37294,7 +37294,7 @@
         <v>44866</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37356,7 +37356,7 @@
         <v>44867</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37418,7 +37418,7 @@
         <v>44867</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37480,7 +37480,7 @@
         <v>44867</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37537,7 +37537,7 @@
         <v>44868</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37594,7 +37594,7 @@
         <v>44873</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37656,7 +37656,7 @@
         <v>44874</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37713,7 +37713,7 @@
         <v>44874</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37775,7 +37775,7 @@
         <v>44875</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37832,7 +37832,7 @@
         <v>44879</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37889,7 +37889,7 @@
         <v>44879</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37946,7 +37946,7 @@
         <v>44879</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38003,7 +38003,7 @@
         <v>44879</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38060,7 +38060,7 @@
         <v>44883</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38122,7 +38122,7 @@
         <v>44886</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38179,7 +38179,7 @@
         <v>44888</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38236,7 +38236,7 @@
         <v>44888</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38293,7 +38293,7 @@
         <v>44889</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38355,7 +38355,7 @@
         <v>44889</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38417,7 +38417,7 @@
         <v>44890</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38474,7 +38474,7 @@
         <v>44890</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38531,7 +38531,7 @@
         <v>44890</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38593,7 +38593,7 @@
         <v>44893</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38655,7 +38655,7 @@
         <v>44895</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38717,7 +38717,7 @@
         <v>44897</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38774,7 +38774,7 @@
         <v>44901</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38831,7 +38831,7 @@
         <v>44904</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38888,7 +38888,7 @@
         <v>44907</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38945,7 +38945,7 @@
         <v>44907</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39002,7 +39002,7 @@
         <v>44909</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39064,7 +39064,7 @@
         <v>44910</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39121,7 +39121,7 @@
         <v>44910</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39178,7 +39178,7 @@
         <v>44911</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39240,7 +39240,7 @@
         <v>44911</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39302,7 +39302,7 @@
         <v>44911</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39359,7 +39359,7 @@
         <v>44916</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39416,7 +39416,7 @@
         <v>44917</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39478,7 +39478,7 @@
         <v>44929</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39535,7 +39535,7 @@
         <v>44929</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39592,7 +39592,7 @@
         <v>44941</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39649,7 +39649,7 @@
         <v>44942</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39706,7 +39706,7 @@
         <v>44942</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39763,7 +39763,7 @@
         <v>44942</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39820,7 +39820,7 @@
         <v>44942</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39877,7 +39877,7 @@
         <v>44944</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39934,7 +39934,7 @@
         <v>44950</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39991,7 +39991,7 @@
         <v>44951</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40048,7 +40048,7 @@
         <v>44960</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40105,7 +40105,7 @@
         <v>44963</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40162,7 +40162,7 @@
         <v>44965</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40219,7 +40219,7 @@
         <v>44965</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40276,7 +40276,7 @@
         <v>44966</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40333,7 +40333,7 @@
         <v>44966</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40390,7 +40390,7 @@
         <v>44971</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40452,7 +40452,7 @@
         <v>44971</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40509,7 +40509,7 @@
         <v>44972</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40566,7 +40566,7 @@
         <v>44973</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40623,7 +40623,7 @@
         <v>44973</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40680,7 +40680,7 @@
         <v>44973</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40737,7 +40737,7 @@
         <v>44977</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40794,7 +40794,7 @@
         <v>44981</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40851,7 +40851,7 @@
         <v>44984</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40908,7 +40908,7 @@
         <v>44985</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40965,7 +40965,7 @@
         <v>44985</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41022,7 +41022,7 @@
         <v>44985</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41079,7 +41079,7 @@
         <v>44991</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41136,7 +41136,7 @@
         <v>44991</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41193,7 +41193,7 @@
         <v>45006</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41250,7 +41250,7 @@
         <v>45006</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41307,7 +41307,7 @@
         <v>45013</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41364,7 +41364,7 @@
         <v>45015</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41426,7 +41426,7 @@
         <v>45015</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41488,7 +41488,7 @@
         <v>45015</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41545,7 +41545,7 @@
         <v>45021</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41602,7 +41602,7 @@
         <v>45021</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41659,7 +41659,7 @@
         <v>45028</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41716,7 +41716,7 @@
         <v>45029</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41773,7 +41773,7 @@
         <v>45030</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41830,7 +41830,7 @@
         <v>45036</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41887,7 +41887,7 @@
         <v>45036</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41944,7 +41944,7 @@
         <v>45036</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42001,7 +42001,7 @@
         <v>45035</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42063,7 +42063,7 @@
         <v>45036</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42120,7 +42120,7 @@
         <v>45035</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42177,7 +42177,7 @@
         <v>45043</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42234,7 +42234,7 @@
         <v>45043</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42291,7 +42291,7 @@
         <v>45043</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42348,7 +42348,7 @@
         <v>45044</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42410,7 +42410,7 @@
         <v>45048</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42467,7 +42467,7 @@
         <v>45050</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42524,7 +42524,7 @@
         <v>45055</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42581,7 +42581,7 @@
         <v>45057</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42638,7 +42638,7 @@
         <v>45056</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42695,7 +42695,7 @@
         <v>45062</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42757,7 +42757,7 @@
         <v>45062</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42819,7 +42819,7 @@
         <v>45064</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42881,7 +42881,7 @@
         <v>45066</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42943,7 +42943,7 @@
         <v>45068</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43005,7 +43005,7 @@
         <v>45070</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -43067,7 +43067,7 @@
         <v>45072</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43129,7 +43129,7 @@
         <v>45072</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43191,7 +43191,7 @@
         <v>45076</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43248,7 +43248,7 @@
         <v>45076</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43305,7 +43305,7 @@
         <v>45077</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43362,7 +43362,7 @@
         <v>45079</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43424,7 +43424,7 @@
         <v>45079</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43486,7 +43486,7 @@
         <v>45086</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43548,7 +43548,7 @@
         <v>45085</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43610,7 +43610,7 @@
         <v>45086</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43667,7 +43667,7 @@
         <v>45086</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43724,7 +43724,7 @@
         <v>45086</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43781,7 +43781,7 @@
         <v>45086</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43838,7 +43838,7 @@
         <v>45086</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43895,7 +43895,7 @@
         <v>45086</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43952,7 +43952,7 @@
         <v>45090</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -44014,7 +44014,7 @@
         <v>45089</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -44071,7 +44071,7 @@
         <v>45090</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44128,7 +44128,7 @@
         <v>45090</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44185,7 +44185,7 @@
         <v>45090</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44242,7 +44242,7 @@
         <v>45090</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44299,7 +44299,7 @@
         <v>45090</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44356,7 +44356,7 @@
         <v>45091</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44413,7 +44413,7 @@
         <v>45091</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44470,7 +44470,7 @@
         <v>45091</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44527,7 +44527,7 @@
         <v>45091</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44584,7 +44584,7 @@
         <v>45093</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44646,7 +44646,7 @@
         <v>45094</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44708,7 +44708,7 @@
         <v>45096</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44765,7 +44765,7 @@
         <v>45096</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44822,7 +44822,7 @@
         <v>45096</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44884,7 +44884,7 @@
         <v>45098</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44941,7 +44941,7 @@
         <v>45098</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -45003,7 +45003,7 @@
         <v>45098</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -45065,7 +45065,7 @@
         <v>45098</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -45127,7 +45127,7 @@
         <v>45098</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45184,7 +45184,7 @@
         <v>45098</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45241,7 +45241,7 @@
         <v>45098</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45303,7 +45303,7 @@
         <v>45098</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45365,7 +45365,7 @@
         <v>45098</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45422,7 +45422,7 @@
         <v>45098</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45484,7 +45484,7 @@
         <v>45098</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45541,7 +45541,7 @@
         <v>45098</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45598,7 +45598,7 @@
         <v>45098</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45655,7 +45655,7 @@
         <v>45098</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45712,7 +45712,7 @@
         <v>45099</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45774,7 +45774,7 @@
         <v>45100</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45836,7 +45836,7 @@
         <v>45100</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45898,7 +45898,7 @@
         <v>45100</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45960,7 +45960,7 @@
         <v>45100</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -46017,7 +46017,7 @@
         <v>45103</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -46079,7 +46079,7 @@
         <v>45104</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -46136,7 +46136,7 @@
         <v>45104</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46193,7 +46193,7 @@
         <v>45104</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46250,7 +46250,7 @@
         <v>45104</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46307,7 +46307,7 @@
         <v>45104</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46364,7 +46364,7 @@
         <v>45106</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46421,7 +46421,7 @@
         <v>45106</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46478,7 +46478,7 @@
         <v>45106</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46535,7 +46535,7 @@
         <v>45106</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46592,7 +46592,7 @@
         <v>45106</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46649,7 +46649,7 @@
         <v>45106</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46706,7 +46706,7 @@
         <v>45107</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46763,7 +46763,7 @@
         <v>45107</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46820,7 +46820,7 @@
         <v>45107</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46877,7 +46877,7 @@
         <v>45107</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46934,7 +46934,7 @@
         <v>45110</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46991,7 +46991,7 @@
         <v>45110</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -47048,7 +47048,7 @@
         <v>45110</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -47105,7 +47105,7 @@
         <v>45110</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47162,7 +47162,7 @@
         <v>45111</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47219,7 +47219,7 @@
         <v>45114</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47276,7 +47276,7 @@
         <v>45114</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47333,7 +47333,7 @@
         <v>45118</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47395,7 +47395,7 @@
         <v>45118</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47457,7 +47457,7 @@
         <v>45118</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47519,7 +47519,7 @@
         <v>45118</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47581,7 +47581,7 @@
         <v>45118</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47643,7 +47643,7 @@
         <v>45118</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47705,7 +47705,7 @@
         <v>45119</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47767,7 +47767,7 @@
         <v>45119</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47824,7 +47824,7 @@
         <v>45120</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47881,7 +47881,7 @@
         <v>45120</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47938,7 +47938,7 @@
         <v>45120</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47995,7 +47995,7 @@
         <v>45120</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -48052,7 +48052,7 @@
         <v>45125</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -48109,7 +48109,7 @@
         <v>45125</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -48166,7 +48166,7 @@
         <v>45125</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48223,7 +48223,7 @@
         <v>45129</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48280,7 +48280,7 @@
         <v>45129</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48337,7 +48337,7 @@
         <v>45135</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48394,7 +48394,7 @@
         <v>45135</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48451,7 +48451,7 @@
         <v>45138</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48508,7 +48508,7 @@
         <v>45138</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48565,7 +48565,7 @@
         <v>45139</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48622,7 +48622,7 @@
         <v>45139</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48679,7 +48679,7 @@
         <v>45139</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48736,7 +48736,7 @@
         <v>45140</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48798,7 +48798,7 @@
         <v>45140</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48855,7 +48855,7 @@
         <v>45140</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48917,7 +48917,7 @@
         <v>45141</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48974,7 +48974,7 @@
         <v>45145</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -49031,7 +49031,7 @@
         <v>45152</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -49093,7 +49093,7 @@
         <v>45152</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -49155,7 +49155,7 @@
         <v>45156</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49212,7 +49212,7 @@
         <v>45159</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49269,7 +49269,7 @@
         <v>45159</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49326,7 +49326,7 @@
         <v>45160</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49388,7 +49388,7 @@
         <v>45160</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49450,7 +49450,7 @@
         <v>45160</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49507,7 +49507,7 @@
         <v>45162</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49564,7 +49564,7 @@
         <v>45162</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49621,7 +49621,7 @@
         <v>45163</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49678,7 +49678,7 @@
         <v>45167</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49740,7 +49740,7 @@
         <v>45167</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49802,7 +49802,7 @@
         <v>45167</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49859,7 +49859,7 @@
         <v>45167</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49921,7 +49921,7 @@
         <v>45168</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49983,7 +49983,7 @@
         <v>45167</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -50040,7 +50040,7 @@
         <v>45168</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -50102,7 +50102,7 @@
         <v>45168</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -50164,7 +50164,7 @@
         <v>45170</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -50221,7 +50221,7 @@
         <v>45170</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -50278,7 +50278,7 @@
         <v>45175</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50335,7 +50335,7 @@
         <v>45176</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50397,7 +50397,7 @@
         <v>45176</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50459,7 +50459,7 @@
         <v>45176</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50516,7 +50516,7 @@
         <v>45177</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50573,7 +50573,7 @@
         <v>45177</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50630,7 +50630,7 @@
         <v>45177</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50687,7 +50687,7 @@
         <v>45180</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50744,7 +50744,7 @@
         <v>45181</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50806,7 +50806,7 @@
         <v>45181</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50868,7 +50868,7 @@
         <v>45181</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50925,7 +50925,7 @@
         <v>45181</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50982,7 +50982,7 @@
         <v>45182</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -51039,7 +51039,7 @@
         <v>45183</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -51096,7 +51096,7 @@
         <v>45184</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -51158,7 +51158,7 @@
         <v>45187</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -51215,7 +51215,7 @@
         <v>45187</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -51272,7 +51272,7 @@
         <v>45187</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -51329,7 +51329,7 @@
         <v>45187</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -51386,7 +51386,7 @@
         <v>45187</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -51443,7 +51443,7 @@
         <v>45187</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -51500,7 +51500,7 @@
         <v>45187</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51557,7 +51557,7 @@
         <v>45188</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51619,7 +51619,7 @@
         <v>45188</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51681,7 +51681,7 @@
         <v>45188</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51743,7 +51743,7 @@
         <v>45188</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51805,7 +51805,7 @@
         <v>45188</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51867,7 +51867,7 @@
         <v>45188</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51929,7 +51929,7 @@
         <v>45188</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51991,7 +51991,7 @@
         <v>45188</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -52048,7 +52048,7 @@
         <v>45189</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -52110,7 +52110,7 @@
         <v>45190</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -52167,7 +52167,7 @@
         <v>45190</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -52224,7 +52224,7 @@
         <v>45190</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -52281,7 +52281,7 @@
         <v>45190</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -52338,7 +52338,7 @@
         <v>45196</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -52395,7 +52395,7 @@
         <v>45197</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -52452,7 +52452,7 @@
         <v>45197</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -52509,7 +52509,7 @@
         <v>45198</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -52571,7 +52571,7 @@
         <v>45201</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52633,7 +52633,7 @@
         <v>45201</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52695,7 +52695,7 @@
         <v>45202</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52757,7 +52757,7 @@
         <v>45202</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52814,7 +52814,7 @@
         <v>45203</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52871,7 +52871,7 @@
         <v>45204</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52933,7 +52933,7 @@
         <v>45208</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52990,7 +52990,7 @@
         <v>45209</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -53047,7 +53047,7 @@
         <v>45208</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -53109,7 +53109,7 @@
         <v>45211</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -53166,7 +53166,7 @@
         <v>45211</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -53223,7 +53223,7 @@
         <v>45211</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -53280,7 +53280,7 @@
         <v>45211</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -53342,7 +53342,7 @@
         <v>45211</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -53404,7 +53404,7 @@
         <v>45211</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -53461,7 +53461,7 @@
         <v>45212</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -53518,7 +53518,7 @@
         <v>45213</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -53575,7 +53575,7 @@
         <v>45215</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53632,7 +53632,7 @@
         <v>45215</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53689,7 +53689,7 @@
         <v>45216</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53746,7 +53746,7 @@
         <v>45216</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -53808,7 +53808,7 @@
         <v>45218</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -53865,7 +53865,7 @@
         <v>45218</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -53927,7 +53927,7 @@
         <v>45218</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -53984,7 +53984,7 @@
         <v>45218</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -54041,7 +54041,7 @@
         <v>45219</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -54098,7 +54098,7 @@
         <v>45219</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -54155,7 +54155,7 @@
         <v>45219</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -54217,7 +54217,7 @@
         <v>45219</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -54279,7 +54279,7 @@
         <v>45219</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -54336,7 +54336,7 @@
         <v>45219</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -54393,7 +54393,7 @@
         <v>45222</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -54450,7 +54450,7 @@
         <v>45222</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -54512,7 +54512,7 @@
         <v>45222</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -54569,7 +54569,7 @@
         <v>45225</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -54626,7 +54626,7 @@
         <v>45225</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -54683,7 +54683,7 @@
         <v>45230</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -54745,7 +54745,7 @@
         <v>45230</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -54802,7 +54802,7 @@
         <v>45230</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -54859,7 +54859,7 @@
         <v>45230</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -54916,7 +54916,7 @@
         <v>45232</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -54978,7 +54978,7 @@
         <v>45232</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -55040,7 +55040,7 @@
         <v>45232</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -55102,7 +55102,7 @@
         <v>45236</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -55164,7 +55164,7 @@
         <v>45236</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -55221,7 +55221,7 @@
         <v>45237</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -55278,7 +55278,7 @@
         <v>45237</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -55335,7 +55335,7 @@
         <v>45237</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -55392,7 +55392,7 @@
         <v>45237</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -55449,7 +55449,7 @@
         <v>45237</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -55511,7 +55511,7 @@
         <v>45237</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -55568,7 +55568,7 @@
         <v>45237</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -55625,7 +55625,7 @@
         <v>45238</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -55682,7 +55682,7 @@
         <v>45239</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -55739,7 +55739,7 @@
         <v>45239</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -55801,7 +55801,7 @@
         <v>45239</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -55858,7 +55858,7 @@
         <v>45239</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -55915,7 +55915,7 @@
         <v>45240</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -55972,7 +55972,7 @@
         <v>45240</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -56029,7 +56029,7 @@
         <v>45243</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -56091,7 +56091,7 @@
         <v>45243</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -56153,7 +56153,7 @@
         <v>45244</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -56210,7 +56210,7 @@
         <v>45244</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -56267,7 +56267,7 @@
         <v>45244</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -56324,7 +56324,7 @@
         <v>45244</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -56381,7 +56381,7 @@
         <v>45244</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -56438,7 +56438,7 @@
         <v>45244</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -56495,7 +56495,7 @@
         <v>45244</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -56552,7 +56552,7 @@
         <v>45244</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -56609,7 +56609,7 @@
         <v>45244</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -56666,7 +56666,7 @@
         <v>45245</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -56723,7 +56723,7 @@
         <v>45245</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -56780,7 +56780,7 @@
         <v>45245</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -56837,7 +56837,7 @@
         <v>45246</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -56894,7 +56894,7 @@
         <v>45246</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -56951,7 +56951,7 @@
         <v>45247</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -57008,7 +57008,7 @@
         <v>45251</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -57065,7 +57065,7 @@
         <v>45252</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -57122,7 +57122,7 @@
         <v>45252</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -57179,7 +57179,7 @@
         <v>45253</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -57236,7 +57236,7 @@
         <v>45254</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -57293,7 +57293,7 @@
         <v>45254</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -57350,7 +57350,7 @@
         <v>45257</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -57407,7 +57407,7 @@
         <v>45257</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -57464,7 +57464,7 @@
         <v>45258</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -57521,7 +57521,7 @@
         <v>45259</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -57578,7 +57578,7 @@
         <v>45259</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -57635,7 +57635,7 @@
         <v>45260</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -57692,7 +57692,7 @@
         <v>45260</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -57749,7 +57749,7 @@
         <v>45260</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -57806,7 +57806,7 @@
         <v>45260</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -57863,7 +57863,7 @@
         <v>45261</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -57920,7 +57920,7 @@
         <v>45261</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -57977,7 +57977,7 @@
         <v>45262</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -58034,7 +58034,7 @@
         <v>45264</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -58091,7 +58091,7 @@
         <v>45264</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -58148,7 +58148,7 @@
         <v>45264</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -58205,7 +58205,7 @@
         <v>45264</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -58267,7 +58267,7 @@
         <v>45264</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -58324,7 +58324,7 @@
         <v>45265</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -58381,7 +58381,7 @@
         <v>45265</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -58438,7 +58438,7 @@
         <v>45266</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -58495,7 +58495,7 @@
         <v>45266</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -58552,7 +58552,7 @@
         <v>45266</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -58609,7 +58609,7 @@
         <v>45267</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -58666,7 +58666,7 @@
         <v>45271</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -58723,7 +58723,7 @@
         <v>45271</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -58780,7 +58780,7 @@
         <v>45273</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -58837,7 +58837,7 @@
         <v>45273</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -58894,7 +58894,7 @@
         <v>45273</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -58951,7 +58951,7 @@
         <v>45273</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -59008,7 +59008,7 @@
         <v>45273</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -59065,7 +59065,7 @@
         <v>45273</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -59122,7 +59122,7 @@
         <v>45273</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -59179,7 +59179,7 @@
         <v>45278</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -59236,7 +59236,7 @@
         <v>45279</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -59293,7 +59293,7 @@
         <v>45279</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -59350,7 +59350,7 @@
         <v>45279</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -59407,7 +59407,7 @@
         <v>45281</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -59464,7 +59464,7 @@
         <v>45282</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -59526,7 +59526,7 @@
         <v>45285</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -59583,7 +59583,7 @@
         <v>45285</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -59640,7 +59640,7 @@
         <v>45285</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -59697,7 +59697,7 @@
         <v>45285</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -59754,7 +59754,7 @@
         <v>45287</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -59811,7 +59811,7 @@
         <v>45287</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -59868,7 +59868,7 @@
         <v>45289</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -59925,7 +59925,7 @@
         <v>45299</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -59982,7 +59982,7 @@
         <v>45308</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -60039,7 +60039,7 @@
         <v>45308</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -60096,7 +60096,7 @@
         <v>45309</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -60153,7 +60153,7 @@
         <v>45310</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -60210,7 +60210,7 @@
         <v>45310</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -60267,7 +60267,7 @@
         <v>45311</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -60324,7 +60324,7 @@
         <v>45311</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -60381,7 +60381,7 @@
         <v>45312</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -60438,7 +60438,7 @@
         <v>45312</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -60495,7 +60495,7 @@
         <v>45313</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -60552,7 +60552,7 @@
         <v>45315</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -60609,7 +60609,7 @@
         <v>45315</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -60666,7 +60666,7 @@
         <v>45315</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -60723,7 +60723,7 @@
         <v>45316</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -60780,7 +60780,7 @@
         <v>45316</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -60837,7 +60837,7 @@
         <v>45316</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -60894,7 +60894,7 @@
         <v>45320</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -60951,7 +60951,7 @@
         <v>45320</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -61001,14 +61001,14 @@
     <row r="1002" ht="15" customHeight="1">
       <c r="A1002" t="inlineStr">
         <is>
-          <t>A 4122-2024</t>
+          <t>A 4129-2024</t>
         </is>
       </c>
       <c r="B1002" s="1" t="n">
         <v>45323</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -61026,7 +61026,7 @@
         </is>
       </c>
       <c r="G1002" t="n">
-        <v>2.8</v>
+        <v>37.1</v>
       </c>
       <c r="H1002" t="n">
         <v>0</v>
@@ -61063,14 +61063,14 @@
     <row r="1003" ht="15" customHeight="1">
       <c r="A1003" t="inlineStr">
         <is>
-          <t>A 4129-2024</t>
+          <t>A 4049-2024</t>
         </is>
       </c>
       <c r="B1003" s="1" t="n">
         <v>45323</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -61082,13 +61082,8 @@
           <t>PITEÅ</t>
         </is>
       </c>
-      <c r="F1003" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="G1003" t="n">
-        <v>37.1</v>
+        <v>2.8</v>
       </c>
       <c r="H1003" t="n">
         <v>0</v>
@@ -61125,14 +61120,14 @@
     <row r="1004" ht="15" customHeight="1">
       <c r="A1004" t="inlineStr">
         <is>
-          <t>A 4049-2024</t>
+          <t>A 4122-2024</t>
         </is>
       </c>
       <c r="B1004" s="1" t="n">
         <v>45323</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -61142,6 +61137,11 @@
       <c r="E1004" t="inlineStr">
         <is>
           <t>PITEÅ</t>
+        </is>
+      </c>
+      <c r="F1004" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="G1004" t="n">
@@ -61189,7 +61189,7 @@
         <v>45323</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -61251,7 +61251,7 @@
         <v>45323</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -61301,14 +61301,14 @@
     <row r="1007" ht="15" customHeight="1">
       <c r="A1007" t="inlineStr">
         <is>
-          <t>A 4245-2024</t>
+          <t>A 4242-2024</t>
         </is>
       </c>
       <c r="B1007" s="1" t="n">
         <v>45324</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -61320,8 +61320,13 @@
           <t>PITEÅ</t>
         </is>
       </c>
+      <c r="F1007" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="G1007" t="n">
-        <v>7.2</v>
+        <v>3.9</v>
       </c>
       <c r="H1007" t="n">
         <v>0</v>
@@ -61365,7 +61370,7 @@
         <v>45324</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -61420,14 +61425,14 @@
     <row r="1009" ht="15" customHeight="1">
       <c r="A1009" t="inlineStr">
         <is>
-          <t>A 4242-2024</t>
+          <t>A 4245-2024</t>
         </is>
       </c>
       <c r="B1009" s="1" t="n">
         <v>45324</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -61439,13 +61444,8 @@
           <t>PITEÅ</t>
         </is>
       </c>
-      <c r="F1009" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="G1009" t="n">
-        <v>3.9</v>
+        <v>7.2</v>
       </c>
       <c r="H1009" t="n">
         <v>0</v>
@@ -61489,7 +61489,7 @@
         <v>45329</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -61546,7 +61546,7 @@
         <v>45330</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -61603,7 +61603,7 @@
         <v>45334</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -61660,7 +61660,7 @@
         <v>45335</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -61717,7 +61717,7 @@
         <v>45342</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -61774,7 +61774,7 @@
         <v>45343</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -61831,7 +61831,7 @@
         <v>45343</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -61888,7 +61888,7 @@
         <v>45345</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -61945,7 +61945,7 @@
         <v>45345</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -61995,14 +61995,14 @@
     <row r="1019" ht="15" customHeight="1">
       <c r="A1019" t="inlineStr">
         <is>
-          <t>A 7458-2024</t>
+          <t>A 7459-2024</t>
         </is>
       </c>
       <c r="B1019" s="1" t="n">
         <v>45345</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -62015,7 +62015,7 @@
         </is>
       </c>
       <c r="G1019" t="n">
-        <v>9.5</v>
+        <v>3.5</v>
       </c>
       <c r="H1019" t="n">
         <v>0</v>
@@ -62052,14 +62052,14 @@
     <row r="1020" ht="15" customHeight="1">
       <c r="A1020" t="inlineStr">
         <is>
-          <t>A 7459-2024</t>
+          <t>A 7458-2024</t>
         </is>
       </c>
       <c r="B1020" s="1" t="n">
         <v>45345</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -62072,7 +62072,7 @@
         </is>
       </c>
       <c r="G1020" t="n">
-        <v>3.5</v>
+        <v>9.5</v>
       </c>
       <c r="H1020" t="n">
         <v>0</v>
@@ -62109,14 +62109,14 @@
     <row r="1021" ht="15" customHeight="1">
       <c r="A1021" t="inlineStr">
         <is>
-          <t>A 7503-2024</t>
+          <t>A 7504-2024</t>
         </is>
       </c>
       <c r="B1021" s="1" t="n">
         <v>45347</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -62129,7 +62129,7 @@
         </is>
       </c>
       <c r="G1021" t="n">
-        <v>5.4</v>
+        <v>2</v>
       </c>
       <c r="H1021" t="n">
         <v>0</v>
@@ -62173,7 +62173,7 @@
         <v>45347</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -62223,14 +62223,14 @@
     <row r="1023" ht="15" customHeight="1">
       <c r="A1023" t="inlineStr">
         <is>
-          <t>A 7504-2024</t>
+          <t>A 7503-2024</t>
         </is>
       </c>
       <c r="B1023" s="1" t="n">
         <v>45347</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -62243,7 +62243,7 @@
         </is>
       </c>
       <c r="G1023" t="n">
-        <v>2</v>
+        <v>5.4</v>
       </c>
       <c r="H1023" t="n">
         <v>0</v>
@@ -62280,14 +62280,14 @@
     <row r="1024" ht="15" customHeight="1">
       <c r="A1024" t="inlineStr">
         <is>
-          <t>A 7552-2024</t>
+          <t>A 7553-2024</t>
         </is>
       </c>
       <c r="B1024" s="1" t="n">
         <v>45348</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -62305,7 +62305,7 @@
         </is>
       </c>
       <c r="G1024" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="H1024" t="n">
         <v>0</v>
@@ -62342,14 +62342,14 @@
     <row r="1025" ht="15" customHeight="1">
       <c r="A1025" t="inlineStr">
         <is>
-          <t>A 7553-2024</t>
+          <t>A 7555-2024</t>
         </is>
       </c>
       <c r="B1025" s="1" t="n">
         <v>45348</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -62367,7 +62367,7 @@
         </is>
       </c>
       <c r="G1025" t="n">
-        <v>3</v>
+        <v>6.1</v>
       </c>
       <c r="H1025" t="n">
         <v>0</v>
@@ -62401,17 +62401,17 @@
       </c>
       <c r="R1025" s="2" t="inlineStr"/>
     </row>
-    <row r="1026">
+    <row r="1026" ht="15" customHeight="1">
       <c r="A1026" t="inlineStr">
         <is>
-          <t>A 7555-2024</t>
+          <t>A 7552-2024</t>
         </is>
       </c>
       <c r="B1026" s="1" t="n">
         <v>45348</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -62429,7 +62429,7 @@
         </is>
       </c>
       <c r="G1026" t="n">
-        <v>6.1</v>
+        <v>2.5</v>
       </c>
       <c r="H1026" t="n">
         <v>0</v>
@@ -62462,6 +62462,63 @@
         <v>0</v>
       </c>
       <c r="R1026" s="2" t="inlineStr"/>
+    </row>
+    <row r="1027">
+      <c r="A1027" t="inlineStr">
+        <is>
+          <t>A 7799-2024</t>
+        </is>
+      </c>
+      <c r="B1027" s="1" t="n">
+        <v>45348</v>
+      </c>
+      <c r="C1027" s="1" t="n">
+        <v>45350</v>
+      </c>
+      <c r="D1027" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="E1027" t="inlineStr">
+        <is>
+          <t>PITEÅ</t>
+        </is>
+      </c>
+      <c r="G1027" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="H1027" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1027" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1027" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1027" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1027" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1027" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1027" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1027" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1027" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1027" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1027" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt PITEÅ.xlsx
+++ b/Översikt PITEÅ.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z1027"/>
+  <dimension ref="A1:Z1035"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>44617</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -665,7 +665,7 @@
         <v>44839</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
         <v>44839</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>44459</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
         <v>44617</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>43896</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>45191</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>45203</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>44740</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>44280</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>44539</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>44550</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>45119</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>44014</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>44522</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>44526</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         <v>44553</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>44810</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>44917</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>45103</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>45106</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         <v>43802</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>43902</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2727,7 +2727,7 @@
         <v>43908</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         <v>44053</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2908,7 +2908,7 @@
         <v>44193</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>44298</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>44840</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
         <v>44852</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3262,7 +3262,7 @@
         <v>44859</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>44944</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3434,7 +3434,7 @@
         <v>45120</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
         <v>45187</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         <v>45209</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3701,7 +3701,7 @@
         <v>45219</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>45243</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         <v>45293</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
         <v>45296</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>43714</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         <v>44014</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4225,7 +4225,7 @@
         <v>44106</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4310,7 +4310,7 @@
         <v>44309</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>44342</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4485,7 +4485,7 @@
         <v>44495</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
         <v>44525</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4665,7 +4665,7 @@
         <v>44525</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4755,7 +4755,7 @@
         <v>44538</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4840,7 +4840,7 @@
         <v>44727</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4929,7 +4929,7 @@
         <v>44804</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5014,7 +5014,7 @@
         <v>44917</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5104,7 +5104,7 @@
         <v>45049</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5193,7 +5193,7 @@
         <v>45098</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>45103</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5373,7 +5373,7 @@
         <v>45148</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
         <v>45175</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         <v>45181</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5642,7 +5642,7 @@
         <v>45188</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5732,7 +5732,7 @@
         <v>45224</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5817,7 +5817,7 @@
         <v>45243</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5907,7 +5907,7 @@
         <v>45265</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5992,7 +5992,7 @@
         <v>45323</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
         <v>45348</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6172,7 +6172,7 @@
         <v>43325</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6229,7 +6229,7 @@
         <v>43332</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6286,7 +6286,7 @@
         <v>43336</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6343,7 +6343,7 @@
         <v>43339</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6400,7 +6400,7 @@
         <v>43339</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6457,7 +6457,7 @@
         <v>43341</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6514,7 +6514,7 @@
         <v>43355</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6571,7 +6571,7 @@
         <v>43355</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6628,7 +6628,7 @@
         <v>43374</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6690,7 +6690,7 @@
         <v>43374</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6752,7 +6752,7 @@
         <v>43375</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6809,7 +6809,7 @@
         <v>43376</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6866,7 +6866,7 @@
         <v>43376</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6923,7 +6923,7 @@
         <v>43381</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6980,7 +6980,7 @@
         <v>43383</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7037,7 +7037,7 @@
         <v>43391</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7094,7 +7094,7 @@
         <v>43391</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7151,7 +7151,7 @@
         <v>43392</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7208,7 +7208,7 @@
         <v>43392</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7265,7 +7265,7 @@
         <v>43398</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7322,7 +7322,7 @@
         <v>43402</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7379,7 +7379,7 @@
         <v>43404</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7436,7 +7436,7 @@
         <v>43406</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7493,7 +7493,7 @@
         <v>43406</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
         <v>43406</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7607,7 +7607,7 @@
         <v>43406</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7664,7 +7664,7 @@
         <v>43406</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         <v>43416</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7778,7 +7778,7 @@
         <v>43418</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7835,7 +7835,7 @@
         <v>43418</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7892,7 +7892,7 @@
         <v>43418</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7949,7 +7949,7 @@
         <v>43419</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8006,7 +8006,7 @@
         <v>43420</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8063,7 +8063,7 @@
         <v>43424</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         <v>43427</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8187,7 +8187,7 @@
         <v>43427</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8244,7 +8244,7 @@
         <v>43427</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8306,7 +8306,7 @@
         <v>43427</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8368,7 +8368,7 @@
         <v>43436</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8425,7 +8425,7 @@
         <v>43438</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8482,7 +8482,7 @@
         <v>43438</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8539,7 +8539,7 @@
         <v>43438</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8596,7 +8596,7 @@
         <v>43438</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8653,7 +8653,7 @@
         <v>43451</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8715,7 +8715,7 @@
         <v>43472</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8772,7 +8772,7 @@
         <v>43475</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8829,7 +8829,7 @@
         <v>43479</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8886,7 +8886,7 @@
         <v>43479</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8943,7 +8943,7 @@
         <v>43486</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9000,7 +9000,7 @@
         <v>43489</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9057,7 +9057,7 @@
         <v>43489</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
         <v>43489</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9171,7 +9171,7 @@
         <v>43489</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9228,7 +9228,7 @@
         <v>43489</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         <v>43490</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9342,7 +9342,7 @@
         <v>43490</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9399,7 +9399,7 @@
         <v>43493</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9461,7 +9461,7 @@
         <v>43509</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9518,7 +9518,7 @@
         <v>43510</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9575,7 +9575,7 @@
         <v>43510</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9632,7 +9632,7 @@
         <v>43514</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9689,7 +9689,7 @@
         <v>43514</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9746,7 +9746,7 @@
         <v>43514</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9803,7 +9803,7 @@
         <v>43516</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9865,7 +9865,7 @@
         <v>43518</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9922,7 +9922,7 @@
         <v>43521</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9984,7 +9984,7 @@
         <v>43521</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10046,7 +10046,7 @@
         <v>43521</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10108,7 +10108,7 @@
         <v>43521</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10170,7 +10170,7 @@
         <v>43521</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10232,7 +10232,7 @@
         <v>43522</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10289,7 +10289,7 @@
         <v>43523</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10346,7 +10346,7 @@
         <v>43523</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10403,7 +10403,7 @@
         <v>43523</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10460,7 +10460,7 @@
         <v>43532</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10517,7 +10517,7 @@
         <v>43532</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10574,7 +10574,7 @@
         <v>43542</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10631,7 +10631,7 @@
         <v>43544</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10693,7 +10693,7 @@
         <v>43544</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10755,7 +10755,7 @@
         <v>43554</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10812,7 +10812,7 @@
         <v>43556</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10869,7 +10869,7 @@
         <v>43557</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10931,7 +10931,7 @@
         <v>43557</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10988,7 +10988,7 @@
         <v>43557</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11045,7 +11045,7 @@
         <v>43557</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11102,7 +11102,7 @@
         <v>43557</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11164,7 +11164,7 @@
         <v>43564</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11221,7 +11221,7 @@
         <v>43564</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11278,7 +11278,7 @@
         <v>43567</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11335,7 +11335,7 @@
         <v>43570</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11392,7 +11392,7 @@
         <v>43570</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11449,7 +11449,7 @@
         <v>43570</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11506,7 +11506,7 @@
         <v>43584</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11563,7 +11563,7 @@
         <v>43605</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11620,7 +11620,7 @@
         <v>43608</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11677,7 +11677,7 @@
         <v>43614</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11739,7 +11739,7 @@
         <v>43616</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11801,7 +11801,7 @@
         <v>43616</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11863,7 +11863,7 @@
         <v>43629</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11920,7 +11920,7 @@
         <v>43629</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11982,7 +11982,7 @@
         <v>43633</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12039,7 +12039,7 @@
         <v>43633</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12096,7 +12096,7 @@
         <v>43640</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12153,7 +12153,7 @@
         <v>43640</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12210,7 +12210,7 @@
         <v>43647</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12267,7 +12267,7 @@
         <v>43647</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12324,7 +12324,7 @@
         <v>43650</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12381,7 +12381,7 @@
         <v>43652</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12443,7 +12443,7 @@
         <v>43677</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12500,7 +12500,7 @@
         <v>43678</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12557,7 +12557,7 @@
         <v>43682</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12614,7 +12614,7 @@
         <v>43691</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12676,7 +12676,7 @@
         <v>43691</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12738,7 +12738,7 @@
         <v>43696</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12800,7 +12800,7 @@
         <v>43697</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12857,7 +12857,7 @@
         <v>43698</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12919,7 +12919,7 @@
         <v>43698</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12981,7 +12981,7 @@
         <v>43706</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13038,7 +13038,7 @@
         <v>43707</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13100,7 +13100,7 @@
         <v>43711</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13157,7 +13157,7 @@
         <v>43713</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13214,7 +13214,7 @@
         <v>43718</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13271,7 +13271,7 @@
         <v>43718</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13328,7 +13328,7 @@
         <v>43718</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13390,7 +13390,7 @@
         <v>43720</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13447,7 +13447,7 @@
         <v>43721</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13504,7 +13504,7 @@
         <v>43732</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13561,7 +13561,7 @@
         <v>43741</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13623,7 +13623,7 @@
         <v>43741</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13680,7 +13680,7 @@
         <v>43752</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13742,7 +13742,7 @@
         <v>43755</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13799,7 +13799,7 @@
         <v>43755</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13856,7 +13856,7 @@
         <v>43755</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13913,7 +13913,7 @@
         <v>43755</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13970,7 +13970,7 @@
         <v>43760</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14032,7 +14032,7 @@
         <v>43760</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14094,7 +14094,7 @@
         <v>43760</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14151,7 +14151,7 @@
         <v>43762</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14213,7 +14213,7 @@
         <v>43766</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14270,7 +14270,7 @@
         <v>43766</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14327,7 +14327,7 @@
         <v>43768</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14384,7 +14384,7 @@
         <v>43770</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14446,7 +14446,7 @@
         <v>43775</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14508,7 +14508,7 @@
         <v>43775</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14570,7 +14570,7 @@
         <v>43777</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14627,7 +14627,7 @@
         <v>43780</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14684,7 +14684,7 @@
         <v>43780</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14741,7 +14741,7 @@
         <v>43780</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14798,7 +14798,7 @@
         <v>43782</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14860,7 +14860,7 @@
         <v>43789</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14922,7 +14922,7 @@
         <v>43798</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14979,7 +14979,7 @@
         <v>43801</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15041,7 +15041,7 @@
         <v>43802</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15098,7 +15098,7 @@
         <v>43802</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15155,7 +15155,7 @@
         <v>43802</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15212,7 +15212,7 @@
         <v>43802</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15269,7 +15269,7 @@
         <v>43802</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15326,7 +15326,7 @@
         <v>43802</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15383,7 +15383,7 @@
         <v>43807</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15440,7 +15440,7 @@
         <v>43809</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15497,7 +15497,7 @@
         <v>43817</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15554,7 +15554,7 @@
         <v>43817</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15616,7 +15616,7 @@
         <v>43822</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15673,7 +15673,7 @@
         <v>43822</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15730,7 +15730,7 @@
         <v>43833</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15787,7 +15787,7 @@
         <v>43846</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15844,7 +15844,7 @@
         <v>43852</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15901,7 +15901,7 @@
         <v>43853</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15958,7 +15958,7 @@
         <v>43854</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16015,7 +16015,7 @@
         <v>43859</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16077,7 +16077,7 @@
         <v>43859</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16134,7 +16134,7 @@
         <v>43859</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16191,7 +16191,7 @@
         <v>43859</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16248,7 +16248,7 @@
         <v>43859</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16305,7 +16305,7 @@
         <v>43860</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16362,7 +16362,7 @@
         <v>43868</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16419,7 +16419,7 @@
         <v>43868</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16476,7 +16476,7 @@
         <v>43874</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16538,7 +16538,7 @@
         <v>43878</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16595,7 +16595,7 @@
         <v>43880</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16652,7 +16652,7 @@
         <v>43880</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16709,7 +16709,7 @@
         <v>43889</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16766,7 +16766,7 @@
         <v>43895</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16828,7 +16828,7 @@
         <v>43896</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16885,7 +16885,7 @@
         <v>43902</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16942,7 +16942,7 @@
         <v>43902</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17004,7 +17004,7 @@
         <v>43907</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17061,7 +17061,7 @@
         <v>43913</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17118,7 +17118,7 @@
         <v>43914</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17180,7 +17180,7 @@
         <v>43927</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17242,7 +17242,7 @@
         <v>43929</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17299,7 +17299,7 @@
         <v>43929</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17356,7 +17356,7 @@
         <v>43931</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17418,7 +17418,7 @@
         <v>43950</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17475,7 +17475,7 @@
         <v>43957</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17537,7 +17537,7 @@
         <v>43958</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17594,7 +17594,7 @@
         <v>43958</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17651,7 +17651,7 @@
         <v>43959</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17708,7 +17708,7 @@
         <v>43962</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17765,7 +17765,7 @@
         <v>43962</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17822,7 +17822,7 @@
         <v>43962</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17879,7 +17879,7 @@
         <v>43962</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17936,7 +17936,7 @@
         <v>43970</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17998,7 +17998,7 @@
         <v>43971</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18060,7 +18060,7 @@
         <v>43976</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18117,7 +18117,7 @@
         <v>43979</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18174,7 +18174,7 @@
         <v>43979</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18231,7 +18231,7 @@
         <v>43979</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18288,7 +18288,7 @@
         <v>43984</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18350,7 +18350,7 @@
         <v>43984</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18407,7 +18407,7 @@
         <v>43987</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18464,7 +18464,7 @@
         <v>43990</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18521,7 +18521,7 @@
         <v>43994</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18583,7 +18583,7 @@
         <v>43997</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18640,7 +18640,7 @@
         <v>43999</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18697,7 +18697,7 @@
         <v>44000</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18759,7 +18759,7 @@
         <v>44006</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18816,7 +18816,7 @@
         <v>44006</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18873,7 +18873,7 @@
         <v>44007</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18930,7 +18930,7 @@
         <v>44007</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18987,7 +18987,7 @@
         <v>44011</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19044,7 +19044,7 @@
         <v>44012</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19106,7 +19106,7 @@
         <v>44020</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19168,7 +19168,7 @@
         <v>44020</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19225,7 +19225,7 @@
         <v>44020</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19287,7 +19287,7 @@
         <v>44026</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19349,7 +19349,7 @@
         <v>44035</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19406,7 +19406,7 @@
         <v>44049</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19463,7 +19463,7 @@
         <v>44063</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19525,7 +19525,7 @@
         <v>44067</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19587,7 +19587,7 @@
         <v>44067</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19649,7 +19649,7 @@
         <v>44068</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19711,7 +19711,7 @@
         <v>44069</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19768,7 +19768,7 @@
         <v>44070</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19825,7 +19825,7 @@
         <v>44074</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19882,7 +19882,7 @@
         <v>44075</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19939,7 +19939,7 @@
         <v>44078</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19996,7 +19996,7 @@
         <v>44083</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20053,7 +20053,7 @@
         <v>44083</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20110,7 +20110,7 @@
         <v>44087</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20167,7 +20167,7 @@
         <v>44088</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20229,7 +20229,7 @@
         <v>44088</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20286,7 +20286,7 @@
         <v>44088</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20348,7 +20348,7 @@
         <v>44092</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20405,7 +20405,7 @@
         <v>44092</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20462,7 +20462,7 @@
         <v>44092</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20519,7 +20519,7 @@
         <v>44095</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20576,7 +20576,7 @@
         <v>44099</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20633,7 +20633,7 @@
         <v>44099</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20690,7 +20690,7 @@
         <v>44099</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20747,7 +20747,7 @@
         <v>44099</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20804,7 +20804,7 @@
         <v>44103</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20861,7 +20861,7 @@
         <v>44103</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20918,7 +20918,7 @@
         <v>44106</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20975,7 +20975,7 @@
         <v>44111</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21037,7 +21037,7 @@
         <v>44111</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21099,7 +21099,7 @@
         <v>44123</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21156,7 +21156,7 @@
         <v>44127</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21213,7 +21213,7 @@
         <v>44132</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21270,7 +21270,7 @@
         <v>44139</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21327,7 +21327,7 @@
         <v>44141</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21384,7 +21384,7 @@
         <v>44141</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21441,7 +21441,7 @@
         <v>44155</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21498,7 +21498,7 @@
         <v>44162</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21560,7 +21560,7 @@
         <v>44166</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21622,7 +21622,7 @@
         <v>44172</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21679,7 +21679,7 @@
         <v>44180</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21736,7 +21736,7 @@
         <v>44186</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21793,7 +21793,7 @@
         <v>44209</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21850,7 +21850,7 @@
         <v>44211</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21907,7 +21907,7 @@
         <v>44211</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21964,7 +21964,7 @@
         <v>44211</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22021,7 +22021,7 @@
         <v>44215</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22083,7 +22083,7 @@
         <v>44221</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22145,7 +22145,7 @@
         <v>44237</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22207,7 +22207,7 @@
         <v>44238</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22264,7 +22264,7 @@
         <v>44256</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22321,7 +22321,7 @@
         <v>44257</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22378,7 +22378,7 @@
         <v>44258</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22435,7 +22435,7 @@
         <v>44280</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22497,7 +22497,7 @@
         <v>44281</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22554,7 +22554,7 @@
         <v>44281</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22611,7 +22611,7 @@
         <v>44281</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22668,7 +22668,7 @@
         <v>44285</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22730,7 +22730,7 @@
         <v>44286</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22787,7 +22787,7 @@
         <v>44292</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22844,7 +22844,7 @@
         <v>44294</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22906,7 +22906,7 @@
         <v>44309</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22963,7 +22963,7 @@
         <v>44320</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23020,7 +23020,7 @@
         <v>44321</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23077,7 +23077,7 @@
         <v>44321</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23134,7 +23134,7 @@
         <v>44326</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23191,7 +23191,7 @@
         <v>44326</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23253,7 +23253,7 @@
         <v>44334</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23310,7 +23310,7 @@
         <v>44339</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23367,7 +23367,7 @@
         <v>44339</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23424,7 +23424,7 @@
         <v>44339</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23481,7 +23481,7 @@
         <v>44343</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23543,7 +23543,7 @@
         <v>44342</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23605,7 +23605,7 @@
         <v>44344</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23662,7 +23662,7 @@
         <v>44350</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23719,7 +23719,7 @@
         <v>44350</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23776,7 +23776,7 @@
         <v>44351</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23838,7 +23838,7 @@
         <v>44354</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23900,7 +23900,7 @@
         <v>44355</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23962,7 +23962,7 @@
         <v>44355</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24024,7 +24024,7 @@
         <v>44357</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24081,7 +24081,7 @@
         <v>44358</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24143,7 +24143,7 @@
         <v>44361</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24200,7 +24200,7 @@
         <v>44361</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24257,7 +24257,7 @@
         <v>44361</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24314,7 +24314,7 @@
         <v>44362</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24376,7 +24376,7 @@
         <v>44361</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24438,7 +24438,7 @@
         <v>44362</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24495,7 +24495,7 @@
         <v>44368</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24557,7 +24557,7 @@
         <v>44368</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24619,7 +24619,7 @@
         <v>44368</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24681,7 +24681,7 @@
         <v>44369</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24743,7 +24743,7 @@
         <v>44370</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24805,7 +24805,7 @@
         <v>44370</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24867,7 +24867,7 @@
         <v>44370</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24929,7 +24929,7 @@
         <v>44370</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24991,7 +24991,7 @@
         <v>44371</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25053,7 +25053,7 @@
         <v>44372</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25115,7 +25115,7 @@
         <v>44372</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25177,7 +25177,7 @@
         <v>44375</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25239,7 +25239,7 @@
         <v>44376</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25301,7 +25301,7 @@
         <v>44376</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25363,7 +25363,7 @@
         <v>44376</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25420,7 +25420,7 @@
         <v>44377</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25482,7 +25482,7 @@
         <v>44378</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25539,7 +25539,7 @@
         <v>44378</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25601,7 +25601,7 @@
         <v>44378</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25658,7 +25658,7 @@
         <v>44383</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25715,7 +25715,7 @@
         <v>44383</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25772,7 +25772,7 @@
         <v>44383</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25829,7 +25829,7 @@
         <v>44383</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25886,7 +25886,7 @@
         <v>44383</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25943,7 +25943,7 @@
         <v>44384</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26005,7 +26005,7 @@
         <v>44383</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26062,7 +26062,7 @@
         <v>44386</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26119,7 +26119,7 @@
         <v>44398</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26176,7 +26176,7 @@
         <v>44404</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26233,7 +26233,7 @@
         <v>44405</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26295,7 +26295,7 @@
         <v>44418</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26357,7 +26357,7 @@
         <v>44421</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26419,7 +26419,7 @@
         <v>44428</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26476,7 +26476,7 @@
         <v>44432</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26533,7 +26533,7 @@
         <v>44432</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26590,7 +26590,7 @@
         <v>44433</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26652,7 +26652,7 @@
         <v>44433</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26714,7 +26714,7 @@
         <v>44438</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26776,7 +26776,7 @@
         <v>44439</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26838,7 +26838,7 @@
         <v>44440</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26895,7 +26895,7 @@
         <v>44441</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26957,7 +26957,7 @@
         <v>44440</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27019,7 +27019,7 @@
         <v>44446</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27076,7 +27076,7 @@
         <v>44447</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27138,7 +27138,7 @@
         <v>44453</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27195,7 +27195,7 @@
         <v>44454</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27252,7 +27252,7 @@
         <v>44454</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27309,7 +27309,7 @@
         <v>44459</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27366,7 +27366,7 @@
         <v>44463</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27428,7 +27428,7 @@
         <v>44463</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27490,7 +27490,7 @@
         <v>44463</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27547,7 +27547,7 @@
         <v>44468</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27604,7 +27604,7 @@
         <v>44468</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27661,7 +27661,7 @@
         <v>44476</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27718,7 +27718,7 @@
         <v>44480</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27775,7 +27775,7 @@
         <v>44481</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27832,7 +27832,7 @@
         <v>44484</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27889,7 +27889,7 @@
         <v>44487</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27951,7 +27951,7 @@
         <v>44490</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28008,7 +28008,7 @@
         <v>44489</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28070,7 +28070,7 @@
         <v>44496</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28127,7 +28127,7 @@
         <v>44497</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28189,7 +28189,7 @@
         <v>44497</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28246,7 +28246,7 @@
         <v>44497</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28303,7 +28303,7 @@
         <v>44498</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28360,7 +28360,7 @@
         <v>44498</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28417,7 +28417,7 @@
         <v>44499</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28474,7 +28474,7 @@
         <v>44502</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28531,7 +28531,7 @@
         <v>44516</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28588,7 +28588,7 @@
         <v>44522</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28645,7 +28645,7 @@
         <v>44523</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28702,7 +28702,7 @@
         <v>44525</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28764,7 +28764,7 @@
         <v>44525</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28821,7 +28821,7 @@
         <v>44529</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28878,7 +28878,7 @@
         <v>44530</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28940,7 +28940,7 @@
         <v>44530</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29002,7 +29002,7 @@
         <v>44531</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29059,7 +29059,7 @@
         <v>44531</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29116,7 +29116,7 @@
         <v>44536</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29173,7 +29173,7 @@
         <v>44536</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29230,7 +29230,7 @@
         <v>44538</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29287,7 +29287,7 @@
         <v>44538</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29344,7 +29344,7 @@
         <v>44538</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29401,7 +29401,7 @@
         <v>44538</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29458,7 +29458,7 @@
         <v>44538</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29515,7 +29515,7 @@
         <v>44538</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29572,7 +29572,7 @@
         <v>44538</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29629,7 +29629,7 @@
         <v>44538</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29686,7 +29686,7 @@
         <v>44539</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29748,7 +29748,7 @@
         <v>44543</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29810,7 +29810,7 @@
         <v>44543</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29872,7 +29872,7 @@
         <v>44543</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29934,7 +29934,7 @@
         <v>44543</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29996,7 +29996,7 @@
         <v>44547</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30058,7 +30058,7 @@
         <v>44550</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30115,7 +30115,7 @@
         <v>44550</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30172,7 +30172,7 @@
         <v>44571</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30229,7 +30229,7 @@
         <v>44582</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30286,7 +30286,7 @@
         <v>44582</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30343,7 +30343,7 @@
         <v>44582</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30400,7 +30400,7 @@
         <v>44582</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30457,7 +30457,7 @@
         <v>44588</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30514,7 +30514,7 @@
         <v>44589</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30571,7 +30571,7 @@
         <v>44590</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30628,7 +30628,7 @@
         <v>44590</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30685,7 +30685,7 @@
         <v>44592</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30742,7 +30742,7 @@
         <v>44592</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30799,7 +30799,7 @@
         <v>44596</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30856,7 +30856,7 @@
         <v>44599</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30913,7 +30913,7 @@
         <v>44608</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30970,7 +30970,7 @@
         <v>44615</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31027,7 +31027,7 @@
         <v>44616</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31089,7 +31089,7 @@
         <v>44617</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31151,7 +31151,7 @@
         <v>44621</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31208,7 +31208,7 @@
         <v>44621</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31270,7 +31270,7 @@
         <v>44622</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31327,7 +31327,7 @@
         <v>44623</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31384,7 +31384,7 @@
         <v>44642</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31441,7 +31441,7 @@
         <v>44643</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31498,7 +31498,7 @@
         <v>44643</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31560,7 +31560,7 @@
         <v>44644</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31617,7 +31617,7 @@
         <v>44656</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31674,7 +31674,7 @@
         <v>44658</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31731,7 +31731,7 @@
         <v>44683</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31788,7 +31788,7 @@
         <v>44683</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31845,7 +31845,7 @@
         <v>44685</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31902,7 +31902,7 @@
         <v>44685</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31959,7 +31959,7 @@
         <v>44685</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32016,7 +32016,7 @@
         <v>44687</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32073,7 +32073,7 @@
         <v>44700</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32130,7 +32130,7 @@
         <v>44708</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32187,7 +32187,7 @@
         <v>44708</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32244,7 +32244,7 @@
         <v>44708</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32301,7 +32301,7 @@
         <v>44722</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32358,7 +32358,7 @@
         <v>44727</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32420,7 +32420,7 @@
         <v>44729</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32482,7 +32482,7 @@
         <v>44735</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32539,7 +32539,7 @@
         <v>44735</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32596,7 +32596,7 @@
         <v>44741</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32653,7 +32653,7 @@
         <v>44741</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32710,7 +32710,7 @@
         <v>44741</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32767,7 +32767,7 @@
         <v>44743</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32829,7 +32829,7 @@
         <v>44743</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32886,7 +32886,7 @@
         <v>44748</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32948,7 +32948,7 @@
         <v>44747</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33010,7 +33010,7 @@
         <v>44748</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33072,7 +33072,7 @@
         <v>44748</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33129,7 +33129,7 @@
         <v>44750</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33186,7 +33186,7 @@
         <v>44756</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33243,7 +33243,7 @@
         <v>44761</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33300,7 +33300,7 @@
         <v>44776</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33357,7 +33357,7 @@
         <v>44777</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33419,7 +33419,7 @@
         <v>44781</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33476,7 +33476,7 @@
         <v>44783</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33533,7 +33533,7 @@
         <v>44785</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33595,7 +33595,7 @@
         <v>44784</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33657,7 +33657,7 @@
         <v>44785</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33714,7 +33714,7 @@
         <v>44792</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33771,7 +33771,7 @@
         <v>44792</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33833,7 +33833,7 @@
         <v>44795</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33890,7 +33890,7 @@
         <v>44795</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33952,7 +33952,7 @@
         <v>44803</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34014,7 +34014,7 @@
         <v>44805</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34076,7 +34076,7 @@
         <v>44806</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34133,7 +34133,7 @@
         <v>44809</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34195,7 +34195,7 @@
         <v>44809</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34257,7 +34257,7 @@
         <v>44811</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34314,7 +34314,7 @@
         <v>44813</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34371,7 +34371,7 @@
         <v>44813</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34428,7 +34428,7 @@
         <v>44813</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34485,7 +34485,7 @@
         <v>44813</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34542,7 +34542,7 @@
         <v>44813</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34599,7 +34599,7 @@
         <v>44816</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34656,7 +34656,7 @@
         <v>44816</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34713,7 +34713,7 @@
         <v>44817</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34775,7 +34775,7 @@
         <v>44817</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34832,7 +34832,7 @@
         <v>44818</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34894,7 +34894,7 @@
         <v>44818</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34956,7 +34956,7 @@
         <v>44818</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35018,7 +35018,7 @@
         <v>44817</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35075,7 +35075,7 @@
         <v>44818</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35137,7 +35137,7 @@
         <v>44818</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35199,7 +35199,7 @@
         <v>44818</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35261,7 +35261,7 @@
         <v>44818</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35318,7 +35318,7 @@
         <v>44819</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35375,7 +35375,7 @@
         <v>44820</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35432,7 +35432,7 @@
         <v>44823</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35494,7 +35494,7 @@
         <v>44824</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35551,7 +35551,7 @@
         <v>44827</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35613,7 +35613,7 @@
         <v>44838</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35675,7 +35675,7 @@
         <v>44838</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35732,7 +35732,7 @@
         <v>44839</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35789,7 +35789,7 @@
         <v>44840</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35846,7 +35846,7 @@
         <v>44840</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35903,7 +35903,7 @@
         <v>44841</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35965,7 +35965,7 @@
         <v>44845</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36027,7 +36027,7 @@
         <v>44845</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36089,7 +36089,7 @@
         <v>44848</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36151,7 +36151,7 @@
         <v>44848</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36213,7 +36213,7 @@
         <v>44849</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36275,7 +36275,7 @@
         <v>44848</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36332,7 +36332,7 @@
         <v>44853</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36394,7 +36394,7 @@
         <v>44853</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36456,7 +36456,7 @@
         <v>44853</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36518,7 +36518,7 @@
         <v>44856</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36580,7 +36580,7 @@
         <v>44855</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36642,7 +36642,7 @@
         <v>44857</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36699,7 +36699,7 @@
         <v>44859</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36756,7 +36756,7 @@
         <v>44859</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36813,7 +36813,7 @@
         <v>44861</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36875,7 +36875,7 @@
         <v>44861</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36932,7 +36932,7 @@
         <v>44861</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36994,7 +36994,7 @@
         <v>44861</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37051,7 +37051,7 @@
         <v>44861</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37113,7 +37113,7 @@
         <v>44861</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37175,7 +37175,7 @@
         <v>44861</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37232,7 +37232,7 @@
         <v>44862</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37294,7 +37294,7 @@
         <v>44866</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37356,7 +37356,7 @@
         <v>44867</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37418,7 +37418,7 @@
         <v>44867</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37480,7 +37480,7 @@
         <v>44867</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37537,7 +37537,7 @@
         <v>44868</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37594,7 +37594,7 @@
         <v>44873</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37656,7 +37656,7 @@
         <v>44874</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37713,7 +37713,7 @@
         <v>44874</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37775,7 +37775,7 @@
         <v>44875</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37832,7 +37832,7 @@
         <v>44879</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37889,7 +37889,7 @@
         <v>44879</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37946,7 +37946,7 @@
         <v>44879</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38003,7 +38003,7 @@
         <v>44879</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38060,7 +38060,7 @@
         <v>44883</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38122,7 +38122,7 @@
         <v>44886</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38179,7 +38179,7 @@
         <v>44888</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38236,7 +38236,7 @@
         <v>44888</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38293,7 +38293,7 @@
         <v>44889</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38355,7 +38355,7 @@
         <v>44889</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38417,7 +38417,7 @@
         <v>44890</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38474,7 +38474,7 @@
         <v>44890</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38531,7 +38531,7 @@
         <v>44890</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38593,7 +38593,7 @@
         <v>44893</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38655,7 +38655,7 @@
         <v>44895</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38717,7 +38717,7 @@
         <v>44897</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38774,7 +38774,7 @@
         <v>44901</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38831,7 +38831,7 @@
         <v>44904</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38888,7 +38888,7 @@
         <v>44907</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38945,7 +38945,7 @@
         <v>44907</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39002,7 +39002,7 @@
         <v>44909</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39064,7 +39064,7 @@
         <v>44910</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39121,7 +39121,7 @@
         <v>44910</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39178,7 +39178,7 @@
         <v>44911</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39240,7 +39240,7 @@
         <v>44911</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39302,7 +39302,7 @@
         <v>44911</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39359,7 +39359,7 @@
         <v>44916</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39416,7 +39416,7 @@
         <v>44917</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39478,7 +39478,7 @@
         <v>44929</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39535,7 +39535,7 @@
         <v>44929</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39592,7 +39592,7 @@
         <v>44941</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39649,7 +39649,7 @@
         <v>44942</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39706,7 +39706,7 @@
         <v>44942</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39763,7 +39763,7 @@
         <v>44942</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39820,7 +39820,7 @@
         <v>44942</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39877,7 +39877,7 @@
         <v>44944</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39934,7 +39934,7 @@
         <v>44950</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39991,7 +39991,7 @@
         <v>44951</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40048,7 +40048,7 @@
         <v>44960</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40105,7 +40105,7 @@
         <v>44963</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40162,7 +40162,7 @@
         <v>44965</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40219,7 +40219,7 @@
         <v>44965</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40276,7 +40276,7 @@
         <v>44966</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40333,7 +40333,7 @@
         <v>44966</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40390,7 +40390,7 @@
         <v>44971</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40452,7 +40452,7 @@
         <v>44971</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40509,7 +40509,7 @@
         <v>44972</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40566,7 +40566,7 @@
         <v>44973</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40623,7 +40623,7 @@
         <v>44973</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40680,7 +40680,7 @@
         <v>44973</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40737,7 +40737,7 @@
         <v>44977</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40794,7 +40794,7 @@
         <v>44981</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40851,7 +40851,7 @@
         <v>44984</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40908,7 +40908,7 @@
         <v>44985</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40965,7 +40965,7 @@
         <v>44985</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41022,7 +41022,7 @@
         <v>44985</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41079,7 +41079,7 @@
         <v>44991</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41136,7 +41136,7 @@
         <v>44991</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41193,7 +41193,7 @@
         <v>45006</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41250,7 +41250,7 @@
         <v>45006</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41307,7 +41307,7 @@
         <v>45013</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41364,7 +41364,7 @@
         <v>45015</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41426,7 +41426,7 @@
         <v>45015</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41488,7 +41488,7 @@
         <v>45015</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41545,7 +41545,7 @@
         <v>45021</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41602,7 +41602,7 @@
         <v>45021</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41659,7 +41659,7 @@
         <v>45028</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41716,7 +41716,7 @@
         <v>45029</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41773,7 +41773,7 @@
         <v>45030</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41830,7 +41830,7 @@
         <v>45036</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41887,7 +41887,7 @@
         <v>45036</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41944,7 +41944,7 @@
         <v>45036</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42001,7 +42001,7 @@
         <v>45035</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42063,7 +42063,7 @@
         <v>45036</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42120,7 +42120,7 @@
         <v>45035</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42177,7 +42177,7 @@
         <v>45043</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42234,7 +42234,7 @@
         <v>45043</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42291,7 +42291,7 @@
         <v>45043</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42348,7 +42348,7 @@
         <v>45044</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42410,7 +42410,7 @@
         <v>45048</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42467,7 +42467,7 @@
         <v>45050</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42524,7 +42524,7 @@
         <v>45055</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42581,7 +42581,7 @@
         <v>45057</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42638,7 +42638,7 @@
         <v>45056</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42695,7 +42695,7 @@
         <v>45062</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42757,7 +42757,7 @@
         <v>45062</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42819,7 +42819,7 @@
         <v>45064</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42881,7 +42881,7 @@
         <v>45066</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42943,7 +42943,7 @@
         <v>45068</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43005,7 +43005,7 @@
         <v>45070</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -43067,7 +43067,7 @@
         <v>45072</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43129,7 +43129,7 @@
         <v>45072</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43191,7 +43191,7 @@
         <v>45076</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43248,7 +43248,7 @@
         <v>45076</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43305,7 +43305,7 @@
         <v>45077</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43362,7 +43362,7 @@
         <v>45079</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43424,7 +43424,7 @@
         <v>45079</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43486,7 +43486,7 @@
         <v>45086</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43548,7 +43548,7 @@
         <v>45085</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43610,7 +43610,7 @@
         <v>45086</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43667,7 +43667,7 @@
         <v>45086</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43724,7 +43724,7 @@
         <v>45086</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43781,7 +43781,7 @@
         <v>45086</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43838,7 +43838,7 @@
         <v>45086</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43895,7 +43895,7 @@
         <v>45086</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43952,7 +43952,7 @@
         <v>45090</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -44014,7 +44014,7 @@
         <v>45089</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -44071,7 +44071,7 @@
         <v>45090</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44128,7 +44128,7 @@
         <v>45090</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44185,7 +44185,7 @@
         <v>45090</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44242,7 +44242,7 @@
         <v>45090</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44299,7 +44299,7 @@
         <v>45090</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44356,7 +44356,7 @@
         <v>45091</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44413,7 +44413,7 @@
         <v>45091</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44470,7 +44470,7 @@
         <v>45091</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44527,7 +44527,7 @@
         <v>45091</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44584,7 +44584,7 @@
         <v>45093</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44646,7 +44646,7 @@
         <v>45094</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44708,7 +44708,7 @@
         <v>45096</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44765,7 +44765,7 @@
         <v>45096</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44822,7 +44822,7 @@
         <v>45096</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44884,7 +44884,7 @@
         <v>45098</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44941,7 +44941,7 @@
         <v>45098</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -45003,7 +45003,7 @@
         <v>45098</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -45065,7 +45065,7 @@
         <v>45098</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -45127,7 +45127,7 @@
         <v>45098</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45184,7 +45184,7 @@
         <v>45098</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45241,7 +45241,7 @@
         <v>45098</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45303,7 +45303,7 @@
         <v>45098</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45365,7 +45365,7 @@
         <v>45098</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45422,7 +45422,7 @@
         <v>45098</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45484,7 +45484,7 @@
         <v>45098</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45541,7 +45541,7 @@
         <v>45098</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45598,7 +45598,7 @@
         <v>45098</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45655,7 +45655,7 @@
         <v>45098</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45712,7 +45712,7 @@
         <v>45099</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45774,7 +45774,7 @@
         <v>45100</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45836,7 +45836,7 @@
         <v>45100</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45898,7 +45898,7 @@
         <v>45100</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45960,7 +45960,7 @@
         <v>45100</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -46017,7 +46017,7 @@
         <v>45103</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -46079,7 +46079,7 @@
         <v>45104</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -46136,7 +46136,7 @@
         <v>45104</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46193,7 +46193,7 @@
         <v>45104</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46250,7 +46250,7 @@
         <v>45104</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46307,7 +46307,7 @@
         <v>45104</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46364,7 +46364,7 @@
         <v>45106</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46421,7 +46421,7 @@
         <v>45106</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46478,7 +46478,7 @@
         <v>45106</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46535,7 +46535,7 @@
         <v>45106</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46592,7 +46592,7 @@
         <v>45106</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46649,7 +46649,7 @@
         <v>45106</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46706,7 +46706,7 @@
         <v>45107</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46763,7 +46763,7 @@
         <v>45107</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46820,7 +46820,7 @@
         <v>45107</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46877,7 +46877,7 @@
         <v>45107</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46934,7 +46934,7 @@
         <v>45110</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46991,7 +46991,7 @@
         <v>45110</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -47048,7 +47048,7 @@
         <v>45110</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -47105,7 +47105,7 @@
         <v>45110</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47162,7 +47162,7 @@
         <v>45111</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47219,7 +47219,7 @@
         <v>45114</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47276,7 +47276,7 @@
         <v>45114</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47333,7 +47333,7 @@
         <v>45118</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47395,7 +47395,7 @@
         <v>45118</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47457,7 +47457,7 @@
         <v>45118</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47519,7 +47519,7 @@
         <v>45118</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47581,7 +47581,7 @@
         <v>45118</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47643,7 +47643,7 @@
         <v>45118</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47705,7 +47705,7 @@
         <v>45119</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47767,7 +47767,7 @@
         <v>45119</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47824,7 +47824,7 @@
         <v>45120</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47881,7 +47881,7 @@
         <v>45120</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47938,7 +47938,7 @@
         <v>45120</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47995,7 +47995,7 @@
         <v>45120</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -48052,7 +48052,7 @@
         <v>45125</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -48109,7 +48109,7 @@
         <v>45125</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -48166,7 +48166,7 @@
         <v>45125</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48223,7 +48223,7 @@
         <v>45129</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48280,7 +48280,7 @@
         <v>45129</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48337,7 +48337,7 @@
         <v>45135</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48394,7 +48394,7 @@
         <v>45135</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48451,7 +48451,7 @@
         <v>45138</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48508,7 +48508,7 @@
         <v>45138</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48565,7 +48565,7 @@
         <v>45139</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48622,7 +48622,7 @@
         <v>45139</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48679,7 +48679,7 @@
         <v>45139</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48736,7 +48736,7 @@
         <v>45140</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48798,7 +48798,7 @@
         <v>45140</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48855,7 +48855,7 @@
         <v>45140</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48917,7 +48917,7 @@
         <v>45141</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48974,7 +48974,7 @@
         <v>45145</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -49031,7 +49031,7 @@
         <v>45152</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -49093,7 +49093,7 @@
         <v>45152</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -49155,7 +49155,7 @@
         <v>45156</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49212,7 +49212,7 @@
         <v>45159</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49269,7 +49269,7 @@
         <v>45159</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49326,7 +49326,7 @@
         <v>45160</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49388,7 +49388,7 @@
         <v>45160</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49450,7 +49450,7 @@
         <v>45160</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49507,7 +49507,7 @@
         <v>45162</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49564,7 +49564,7 @@
         <v>45162</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49621,7 +49621,7 @@
         <v>45163</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49678,7 +49678,7 @@
         <v>45167</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49740,7 +49740,7 @@
         <v>45167</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49802,7 +49802,7 @@
         <v>45167</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49859,7 +49859,7 @@
         <v>45167</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49921,7 +49921,7 @@
         <v>45168</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49983,7 +49983,7 @@
         <v>45167</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -50040,7 +50040,7 @@
         <v>45168</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -50102,7 +50102,7 @@
         <v>45168</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -50164,7 +50164,7 @@
         <v>45170</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -50221,7 +50221,7 @@
         <v>45170</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -50278,7 +50278,7 @@
         <v>45175</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50335,7 +50335,7 @@
         <v>45176</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50397,7 +50397,7 @@
         <v>45176</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50459,7 +50459,7 @@
         <v>45176</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50516,7 +50516,7 @@
         <v>45177</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50573,7 +50573,7 @@
         <v>45177</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50630,7 +50630,7 @@
         <v>45177</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50687,7 +50687,7 @@
         <v>45180</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50744,7 +50744,7 @@
         <v>45181</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50806,7 +50806,7 @@
         <v>45181</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50868,7 +50868,7 @@
         <v>45181</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50925,7 +50925,7 @@
         <v>45181</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50982,7 +50982,7 @@
         <v>45182</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -51039,7 +51039,7 @@
         <v>45183</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -51096,7 +51096,7 @@
         <v>45184</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -51158,7 +51158,7 @@
         <v>45187</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -51215,7 +51215,7 @@
         <v>45187</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -51272,7 +51272,7 @@
         <v>45187</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -51329,7 +51329,7 @@
         <v>45187</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -51386,7 +51386,7 @@
         <v>45187</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -51443,7 +51443,7 @@
         <v>45187</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -51500,7 +51500,7 @@
         <v>45187</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51557,7 +51557,7 @@
         <v>45188</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51619,7 +51619,7 @@
         <v>45188</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51681,7 +51681,7 @@
         <v>45188</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51743,7 +51743,7 @@
         <v>45188</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51805,7 +51805,7 @@
         <v>45188</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51867,7 +51867,7 @@
         <v>45188</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51929,7 +51929,7 @@
         <v>45188</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51991,7 +51991,7 @@
         <v>45188</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -52048,7 +52048,7 @@
         <v>45189</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -52110,7 +52110,7 @@
         <v>45190</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -52167,7 +52167,7 @@
         <v>45190</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -52224,7 +52224,7 @@
         <v>45190</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -52281,7 +52281,7 @@
         <v>45190</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -52338,7 +52338,7 @@
         <v>45196</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -52395,7 +52395,7 @@
         <v>45197</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -52452,7 +52452,7 @@
         <v>45197</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -52509,7 +52509,7 @@
         <v>45198</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -52571,7 +52571,7 @@
         <v>45201</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52633,7 +52633,7 @@
         <v>45201</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52695,7 +52695,7 @@
         <v>45202</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52757,7 +52757,7 @@
         <v>45202</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52814,7 +52814,7 @@
         <v>45203</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52871,7 +52871,7 @@
         <v>45204</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52933,7 +52933,7 @@
         <v>45208</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52990,7 +52990,7 @@
         <v>45209</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -53047,7 +53047,7 @@
         <v>45208</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -53109,7 +53109,7 @@
         <v>45211</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -53166,7 +53166,7 @@
         <v>45211</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -53223,7 +53223,7 @@
         <v>45211</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -53280,7 +53280,7 @@
         <v>45211</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -53342,7 +53342,7 @@
         <v>45211</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -53404,7 +53404,7 @@
         <v>45211</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -53461,7 +53461,7 @@
         <v>45212</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -53518,7 +53518,7 @@
         <v>45213</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -53575,7 +53575,7 @@
         <v>45215</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53632,7 +53632,7 @@
         <v>45215</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53689,7 +53689,7 @@
         <v>45216</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53746,7 +53746,7 @@
         <v>45216</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -53808,7 +53808,7 @@
         <v>45218</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -53865,7 +53865,7 @@
         <v>45218</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -53927,7 +53927,7 @@
         <v>45218</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -53984,7 +53984,7 @@
         <v>45218</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -54041,7 +54041,7 @@
         <v>45219</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -54098,7 +54098,7 @@
         <v>45219</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -54155,7 +54155,7 @@
         <v>45219</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -54217,7 +54217,7 @@
         <v>45219</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -54279,7 +54279,7 @@
         <v>45219</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -54336,7 +54336,7 @@
         <v>45219</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -54393,7 +54393,7 @@
         <v>45222</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -54450,7 +54450,7 @@
         <v>45222</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -54512,7 +54512,7 @@
         <v>45222</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -54569,7 +54569,7 @@
         <v>45225</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -54626,7 +54626,7 @@
         <v>45225</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -54683,7 +54683,7 @@
         <v>45230</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -54745,7 +54745,7 @@
         <v>45230</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -54802,7 +54802,7 @@
         <v>45230</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -54859,7 +54859,7 @@
         <v>45230</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -54916,7 +54916,7 @@
         <v>45232</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -54978,7 +54978,7 @@
         <v>45232</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -55040,7 +55040,7 @@
         <v>45232</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -55102,7 +55102,7 @@
         <v>45236</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -55164,7 +55164,7 @@
         <v>45236</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -55221,7 +55221,7 @@
         <v>45237</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -55278,7 +55278,7 @@
         <v>45237</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -55335,7 +55335,7 @@
         <v>45237</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -55392,7 +55392,7 @@
         <v>45237</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -55449,7 +55449,7 @@
         <v>45237</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -55511,7 +55511,7 @@
         <v>45237</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -55568,7 +55568,7 @@
         <v>45237</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -55625,7 +55625,7 @@
         <v>45238</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -55682,7 +55682,7 @@
         <v>45239</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -55739,7 +55739,7 @@
         <v>45239</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -55801,7 +55801,7 @@
         <v>45239</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -55858,7 +55858,7 @@
         <v>45239</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -55915,7 +55915,7 @@
         <v>45240</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -55972,7 +55972,7 @@
         <v>45240</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -56029,7 +56029,7 @@
         <v>45243</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -56091,7 +56091,7 @@
         <v>45243</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -56153,7 +56153,7 @@
         <v>45244</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -56210,7 +56210,7 @@
         <v>45244</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -56267,7 +56267,7 @@
         <v>45244</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -56324,7 +56324,7 @@
         <v>45244</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -56381,7 +56381,7 @@
         <v>45244</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -56438,7 +56438,7 @@
         <v>45244</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -56495,7 +56495,7 @@
         <v>45244</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -56552,7 +56552,7 @@
         <v>45244</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -56609,7 +56609,7 @@
         <v>45244</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -56666,7 +56666,7 @@
         <v>45245</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -56723,7 +56723,7 @@
         <v>45245</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -56780,7 +56780,7 @@
         <v>45245</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -56837,7 +56837,7 @@
         <v>45246</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -56894,7 +56894,7 @@
         <v>45246</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -56951,7 +56951,7 @@
         <v>45247</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -57008,7 +57008,7 @@
         <v>45251</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -57065,7 +57065,7 @@
         <v>45252</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -57122,7 +57122,7 @@
         <v>45252</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -57179,7 +57179,7 @@
         <v>45253</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -57236,7 +57236,7 @@
         <v>45254</v>
   